--- a/appium-tests/reports/appium-mobile-test-report-400.xlsx
+++ b/appium-tests/reports/appium-mobile-test-report-400.xlsx
@@ -449,7 +449,7 @@
         <v>Suite Duration (seconds)</v>
       </c>
       <c r="B6">
-        <v>6.2</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="7">
@@ -473,7 +473,7 @@
         <v>Generated At</v>
       </c>
       <c r="B9" t="str">
-        <v>31/7/2026, 4:48:42 pm</v>
+        <v>1/8/2026, 4:19:44 pm</v>
       </c>
     </row>
   </sheetData>
@@ -554,13 +554,13 @@
         <v>PASS</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" t="str">
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>2026-07-31T11:18:36.458Z</v>
+        <v>2026-08-01T10:49:38.258Z</v>
       </c>
     </row>
     <row r="3">
@@ -586,13 +586,13 @@
         <v>PASS</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I3" t="str">
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>2026-07-31T11:18:36.463Z</v>
+        <v>2026-08-01T10:49:38.275Z</v>
       </c>
     </row>
     <row r="4">
@@ -618,13 +618,13 @@
         <v>PASS</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>2026-07-31T11:18:36.473Z</v>
+        <v>2026-08-01T10:49:38.290Z</v>
       </c>
     </row>
     <row r="5">
@@ -656,7 +656,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>2026-07-31T11:18:36.489Z</v>
+        <v>2026-08-01T10:49:38.306Z</v>
       </c>
     </row>
     <row r="6">
@@ -682,13 +682,13 @@
         <v>PASS</v>
       </c>
       <c r="H6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" t="str">
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>2026-07-31T11:18:36.504Z</v>
+        <v>2026-08-01T10:49:38.322Z</v>
       </c>
     </row>
     <row r="7">
@@ -720,7 +720,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>2026-07-31T11:18:36.520Z</v>
+        <v>2026-08-01T10:49:38.338Z</v>
       </c>
     </row>
     <row r="8">
@@ -752,7 +752,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>2026-07-31T11:18:36.535Z</v>
+        <v>2026-08-01T10:49:38.353Z</v>
       </c>
     </row>
     <row r="9">
@@ -784,7 +784,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>2026-07-31T11:18:36.551Z</v>
+        <v>2026-08-01T10:49:38.369Z</v>
       </c>
     </row>
     <row r="10">
@@ -810,13 +810,13 @@
         <v>PASS</v>
       </c>
       <c r="H10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" t="str">
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>2026-07-31T11:18:36.566Z</v>
+        <v>2026-08-01T10:49:38.385Z</v>
       </c>
     </row>
     <row r="11">
@@ -842,13 +842,13 @@
         <v>PASS</v>
       </c>
       <c r="H11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I11" t="str">
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>2026-07-31T11:18:36.582Z</v>
+        <v>2026-08-01T10:49:38.400Z</v>
       </c>
     </row>
     <row r="12">
@@ -874,13 +874,13 @@
         <v>PASS</v>
       </c>
       <c r="H12">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I12" t="str">
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>2026-07-31T11:18:36.598Z</v>
+        <v>2026-08-01T10:49:38.415Z</v>
       </c>
     </row>
     <row r="13">
@@ -906,13 +906,13 @@
         <v>PASS</v>
       </c>
       <c r="H13">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I13" t="str">
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>2026-07-31T11:18:36.613Z</v>
+        <v>2026-08-01T10:49:38.432Z</v>
       </c>
     </row>
     <row r="14">
@@ -944,7 +944,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>2026-07-31T11:18:36.629Z</v>
+        <v>2026-08-01T10:49:38.448Z</v>
       </c>
     </row>
     <row r="15">
@@ -970,13 +970,13 @@
         <v>PASS</v>
       </c>
       <c r="H15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I15" t="str">
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>2026-07-31T11:18:36.644Z</v>
+        <v>2026-08-01T10:49:38.463Z</v>
       </c>
     </row>
     <row r="16">
@@ -1002,13 +1002,13 @@
         <v>PASS</v>
       </c>
       <c r="H16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I16" t="str">
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>2026-07-31T11:18:36.659Z</v>
+        <v>2026-08-01T10:49:38.477Z</v>
       </c>
     </row>
     <row r="17">
@@ -1040,7 +1040,7 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>2026-07-31T11:18:36.675Z</v>
+        <v>2026-08-01T10:49:38.493Z</v>
       </c>
     </row>
     <row r="18">
@@ -1066,13 +1066,13 @@
         <v>PASS</v>
       </c>
       <c r="H18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I18" t="str">
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>2026-07-31T11:18:36.690Z</v>
+        <v>2026-08-01T10:49:38.509Z</v>
       </c>
     </row>
     <row r="19">
@@ -1098,13 +1098,13 @@
         <v>PASS</v>
       </c>
       <c r="H19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I19" t="str">
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>2026-07-31T11:18:36.706Z</v>
+        <v>2026-08-01T10:49:38.524Z</v>
       </c>
     </row>
     <row r="20">
@@ -1130,13 +1130,13 @@
         <v>PASS</v>
       </c>
       <c r="H20">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I20" t="str">
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>2026-07-31T11:18:36.722Z</v>
+        <v>2026-08-01T10:49:38.539Z</v>
       </c>
     </row>
     <row r="21">
@@ -1162,13 +1162,13 @@
         <v>PASS</v>
       </c>
       <c r="H21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I21" t="str">
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>2026-07-31T11:18:36.737Z</v>
+        <v>2026-08-01T10:49:38.555Z</v>
       </c>
     </row>
     <row r="22">
@@ -1194,13 +1194,13 @@
         <v>PASS</v>
       </c>
       <c r="H22">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I22" t="str">
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>2026-07-31T11:18:36.753Z</v>
+        <v>2026-08-01T10:49:38.570Z</v>
       </c>
     </row>
     <row r="23">
@@ -1226,13 +1226,13 @@
         <v>PASS</v>
       </c>
       <c r="H23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I23" t="str">
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>2026-07-31T11:18:36.768Z</v>
+        <v>2026-08-01T10:49:38.586Z</v>
       </c>
     </row>
     <row r="24">
@@ -1264,7 +1264,7 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>2026-07-31T11:18:36.784Z</v>
+        <v>2026-08-01T10:49:38.602Z</v>
       </c>
     </row>
     <row r="25">
@@ -1296,7 +1296,7 @@
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>2026-07-31T11:18:36.800Z</v>
+        <v>2026-08-01T10:49:38.618Z</v>
       </c>
     </row>
     <row r="26">
@@ -1322,13 +1322,13 @@
         <v>PASS</v>
       </c>
       <c r="H26">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>2026-07-31T11:18:36.816Z</v>
+        <v>2026-08-01T10:49:38.633Z</v>
       </c>
     </row>
     <row r="27">
@@ -1360,7 +1360,7 @@
         <v/>
       </c>
       <c r="J27" t="str">
-        <v>2026-07-31T11:18:36.832Z</v>
+        <v>2026-08-01T10:49:38.649Z</v>
       </c>
     </row>
     <row r="28">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="J28" t="str">
-        <v>2026-07-31T11:18:36.847Z</v>
+        <v>2026-08-01T10:49:38.664Z</v>
       </c>
     </row>
     <row r="29">
@@ -1418,13 +1418,13 @@
         <v>PASS</v>
       </c>
       <c r="H29">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I29" t="str">
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>2026-07-31T11:18:36.863Z</v>
+        <v>2026-08-01T10:49:38.679Z</v>
       </c>
     </row>
     <row r="30">
@@ -1456,7 +1456,7 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>2026-07-31T11:18:36.879Z</v>
+        <v>2026-08-01T10:49:38.695Z</v>
       </c>
     </row>
     <row r="31">
@@ -1488,7 +1488,7 @@
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>2026-07-31T11:18:36.894Z</v>
+        <v>2026-08-01T10:49:38.710Z</v>
       </c>
     </row>
     <row r="32">
@@ -1520,7 +1520,7 @@
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>2026-07-31T11:18:36.910Z</v>
+        <v>2026-08-01T10:49:38.726Z</v>
       </c>
     </row>
     <row r="33">
@@ -1552,7 +1552,7 @@
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>2026-07-31T11:18:36.925Z</v>
+        <v>2026-08-01T10:49:38.741Z</v>
       </c>
     </row>
     <row r="34">
@@ -1578,13 +1578,13 @@
         <v>PASS</v>
       </c>
       <c r="H34">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I34" t="str">
         <v/>
       </c>
       <c r="J34" t="str">
-        <v>2026-07-31T11:18:36.940Z</v>
+        <v>2026-08-01T10:49:38.758Z</v>
       </c>
     </row>
     <row r="35">
@@ -1610,13 +1610,13 @@
         <v>PASS</v>
       </c>
       <c r="H35">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I35" t="str">
         <v/>
       </c>
       <c r="J35" t="str">
-        <v>2026-07-31T11:18:36.957Z</v>
+        <v>2026-08-01T10:49:38.773Z</v>
       </c>
     </row>
     <row r="36">
@@ -1642,13 +1642,13 @@
         <v>PASS</v>
       </c>
       <c r="H36">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I36" t="str">
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>2026-07-31T11:18:36.971Z</v>
+        <v>2026-08-01T10:49:38.788Z</v>
       </c>
     </row>
     <row r="37">
@@ -1680,7 +1680,7 @@
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>2026-07-31T11:18:36.987Z</v>
+        <v>2026-08-01T10:49:38.804Z</v>
       </c>
     </row>
     <row r="38">
@@ -1712,7 +1712,7 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>2026-07-31T11:18:37.003Z</v>
+        <v>2026-08-01T10:49:38.820Z</v>
       </c>
     </row>
     <row r="39">
@@ -1744,7 +1744,7 @@
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>2026-07-31T11:18:37.018Z</v>
+        <v>2026-08-01T10:49:38.835Z</v>
       </c>
     </row>
     <row r="40">
@@ -1770,13 +1770,13 @@
         <v>PASS</v>
       </c>
       <c r="H40">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I40" t="str">
         <v/>
       </c>
       <c r="J40" t="str">
-        <v>2026-07-31T11:18:37.034Z</v>
+        <v>2026-08-01T10:49:38.850Z</v>
       </c>
     </row>
     <row r="41">
@@ -1808,7 +1808,7 @@
         <v/>
       </c>
       <c r="J41" t="str">
-        <v>2026-07-31T11:18:37.050Z</v>
+        <v>2026-08-01T10:49:38.867Z</v>
       </c>
     </row>
     <row r="42">
@@ -1840,7 +1840,7 @@
         <v/>
       </c>
       <c r="J42" t="str">
-        <v>2026-07-31T11:18:37.066Z</v>
+        <v>2026-08-01T10:49:38.883Z</v>
       </c>
     </row>
     <row r="43">
@@ -1866,13 +1866,13 @@
         <v>PASS</v>
       </c>
       <c r="H43">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I43" t="str">
         <v/>
       </c>
       <c r="J43" t="str">
-        <v>2026-07-31T11:18:37.080Z</v>
+        <v>2026-08-01T10:49:38.899Z</v>
       </c>
     </row>
     <row r="44">
@@ -1898,13 +1898,13 @@
         <v>PASS</v>
       </c>
       <c r="H44">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I44" t="str">
         <v/>
       </c>
       <c r="J44" t="str">
-        <v>2026-07-31T11:18:37.095Z</v>
+        <v>2026-08-01T10:49:38.913Z</v>
       </c>
     </row>
     <row r="45">
@@ -1936,7 +1936,7 @@
         <v/>
       </c>
       <c r="J45" t="str">
-        <v>2026-07-31T11:18:37.111Z</v>
+        <v>2026-08-01T10:49:38.929Z</v>
       </c>
     </row>
     <row r="46">
@@ -1968,7 +1968,7 @@
         <v/>
       </c>
       <c r="J46" t="str">
-        <v>2026-07-31T11:18:37.127Z</v>
+        <v>2026-08-01T10:49:38.945Z</v>
       </c>
     </row>
     <row r="47">
@@ -2000,7 +2000,7 @@
         <v/>
       </c>
       <c r="J47" t="str">
-        <v>2026-07-31T11:18:37.142Z</v>
+        <v>2026-08-01T10:49:38.960Z</v>
       </c>
     </row>
     <row r="48">
@@ -2032,7 +2032,7 @@
         <v/>
       </c>
       <c r="J48" t="str">
-        <v>2026-07-31T11:18:37.158Z</v>
+        <v>2026-08-01T10:49:38.976Z</v>
       </c>
     </row>
     <row r="49">
@@ -2064,7 +2064,7 @@
         <v/>
       </c>
       <c r="J49" t="str">
-        <v>2026-07-31T11:18:37.173Z</v>
+        <v>2026-08-01T10:49:38.991Z</v>
       </c>
     </row>
     <row r="50">
@@ -2096,7 +2096,7 @@
         <v/>
       </c>
       <c r="J50" t="str">
-        <v>2026-07-31T11:18:37.189Z</v>
+        <v>2026-08-01T10:49:39.007Z</v>
       </c>
     </row>
     <row r="51">
@@ -2122,13 +2122,13 @@
         <v>PASS</v>
       </c>
       <c r="H51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I51" t="str">
         <v/>
       </c>
       <c r="J51" t="str">
-        <v>2026-07-31T11:18:37.204Z</v>
+        <v>2026-08-01T10:49:39.023Z</v>
       </c>
     </row>
     <row r="52">
@@ -2154,13 +2154,13 @@
         <v>PASS</v>
       </c>
       <c r="H52">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I52" t="str">
         <v/>
       </c>
       <c r="J52" t="str">
-        <v>2026-07-31T11:18:37.220Z</v>
+        <v>2026-08-01T10:49:39.038Z</v>
       </c>
     </row>
     <row r="53">
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="J53" t="str">
-        <v>2026-07-31T11:18:37.236Z</v>
+        <v>2026-08-01T10:49:39.054Z</v>
       </c>
     </row>
     <row r="54">
@@ -2224,7 +2224,7 @@
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>2026-07-31T11:18:37.252Z</v>
+        <v>2026-08-01T10:49:39.070Z</v>
       </c>
     </row>
     <row r="55">
@@ -2250,13 +2250,13 @@
         <v>PASS</v>
       </c>
       <c r="H55">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I55" t="str">
         <v/>
       </c>
       <c r="J55" t="str">
-        <v>2026-07-31T11:18:37.267Z</v>
+        <v>2026-08-01T10:49:39.086Z</v>
       </c>
     </row>
     <row r="56">
@@ -2288,7 +2288,7 @@
         <v/>
       </c>
       <c r="J56" t="str">
-        <v>2026-07-31T11:18:37.282Z</v>
+        <v>2026-08-01T10:49:39.101Z</v>
       </c>
     </row>
     <row r="57">
@@ -2314,13 +2314,13 @@
         <v>PASS</v>
       </c>
       <c r="H57">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I57" t="str">
         <v/>
       </c>
       <c r="J57" t="str">
-        <v>2026-07-31T11:18:37.297Z</v>
+        <v>2026-08-01T10:49:39.117Z</v>
       </c>
     </row>
     <row r="58">
@@ -2346,13 +2346,13 @@
         <v>PASS</v>
       </c>
       <c r="H58">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I58" t="str">
         <v/>
       </c>
       <c r="J58" t="str">
-        <v>2026-07-31T11:18:37.313Z</v>
+        <v>2026-08-01T10:49:39.132Z</v>
       </c>
     </row>
     <row r="59">
@@ -2378,13 +2378,13 @@
         <v>PASS</v>
       </c>
       <c r="H59">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I59" t="str">
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>2026-07-31T11:18:37.329Z</v>
+        <v>2026-08-01T10:49:39.147Z</v>
       </c>
     </row>
     <row r="60">
@@ -2410,13 +2410,13 @@
         <v>PASS</v>
       </c>
       <c r="H60">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I60" t="str">
         <v/>
       </c>
       <c r="J60" t="str">
-        <v>2026-07-31T11:18:37.344Z</v>
+        <v>2026-08-01T10:49:39.162Z</v>
       </c>
     </row>
     <row r="61">
@@ -2448,7 +2448,7 @@
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>2026-07-31T11:18:37.360Z</v>
+        <v>2026-08-01T10:49:39.177Z</v>
       </c>
     </row>
     <row r="62">
@@ -2474,13 +2474,13 @@
         <v>PASS</v>
       </c>
       <c r="H62">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I62" t="str">
         <v/>
       </c>
       <c r="J62" t="str">
-        <v>2026-07-31T11:18:37.376Z</v>
+        <v>2026-08-01T10:49:39.193Z</v>
       </c>
     </row>
     <row r="63">
@@ -2506,13 +2506,13 @@
         <v>PASS</v>
       </c>
       <c r="H63">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I63" t="str">
         <v/>
       </c>
       <c r="J63" t="str">
-        <v>2026-07-31T11:18:37.392Z</v>
+        <v>2026-08-01T10:49:39.209Z</v>
       </c>
     </row>
     <row r="64">
@@ -2538,13 +2538,13 @@
         <v>PASS</v>
       </c>
       <c r="H64">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I64" t="str">
         <v/>
       </c>
       <c r="J64" t="str">
-        <v>2026-07-31T11:18:37.407Z</v>
+        <v>2026-08-01T10:49:39.225Z</v>
       </c>
     </row>
     <row r="65">
@@ -2570,13 +2570,13 @@
         <v>PASS</v>
       </c>
       <c r="H65">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I65" t="str">
         <v/>
       </c>
       <c r="J65" t="str">
-        <v>2026-07-31T11:18:37.423Z</v>
+        <v>2026-08-01T10:49:39.240Z</v>
       </c>
     </row>
     <row r="66">
@@ -2608,7 +2608,7 @@
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>2026-07-31T11:18:37.438Z</v>
+        <v>2026-08-01T10:49:39.255Z</v>
       </c>
     </row>
     <row r="67">
@@ -2634,13 +2634,13 @@
         <v>PASS</v>
       </c>
       <c r="H67">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I67" t="str">
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>2026-07-31T11:18:37.454Z</v>
+        <v>2026-08-01T10:49:39.271Z</v>
       </c>
     </row>
     <row r="68">
@@ -2672,7 +2672,7 @@
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>2026-07-31T11:18:37.470Z</v>
+        <v>2026-08-01T10:49:39.287Z</v>
       </c>
     </row>
     <row r="69">
@@ -2698,13 +2698,13 @@
         <v>PASS</v>
       </c>
       <c r="H69">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I69" t="str">
         <v/>
       </c>
       <c r="J69" t="str">
-        <v>2026-07-31T11:18:37.485Z</v>
+        <v>2026-08-01T10:49:39.303Z</v>
       </c>
     </row>
     <row r="70">
@@ -2730,13 +2730,13 @@
         <v>PASS</v>
       </c>
       <c r="H70">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I70" t="str">
         <v/>
       </c>
       <c r="J70" t="str">
-        <v>2026-07-31T11:18:37.502Z</v>
+        <v>2026-08-01T10:49:39.318Z</v>
       </c>
     </row>
     <row r="71">
@@ -2762,13 +2762,13 @@
         <v>PASS</v>
       </c>
       <c r="H71">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I71" t="str">
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>2026-07-31T11:18:37.517Z</v>
+        <v>2026-08-01T10:49:39.334Z</v>
       </c>
     </row>
     <row r="72">
@@ -2800,7 +2800,7 @@
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>2026-07-31T11:18:37.531Z</v>
+        <v>2026-08-01T10:49:39.348Z</v>
       </c>
     </row>
     <row r="73">
@@ -2826,13 +2826,13 @@
         <v>PASS</v>
       </c>
       <c r="H73">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I73" t="str">
         <v/>
       </c>
       <c r="J73" t="str">
-        <v>2026-07-31T11:18:37.548Z</v>
+        <v>2026-08-01T10:49:39.364Z</v>
       </c>
     </row>
     <row r="74">
@@ -2864,7 +2864,7 @@
         <v/>
       </c>
       <c r="J74" t="str">
-        <v>2026-07-31T11:18:37.564Z</v>
+        <v>2026-08-01T10:49:39.380Z</v>
       </c>
     </row>
     <row r="75">
@@ -2890,13 +2890,13 @@
         <v>PASS</v>
       </c>
       <c r="H75">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I75" t="str">
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>2026-07-31T11:18:37.579Z</v>
+        <v>2026-08-01T10:49:39.396Z</v>
       </c>
     </row>
     <row r="76">
@@ -2928,7 +2928,7 @@
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>2026-07-31T11:18:37.594Z</v>
+        <v>2026-08-01T10:49:39.411Z</v>
       </c>
     </row>
     <row r="77">
@@ -2960,7 +2960,7 @@
         <v/>
       </c>
       <c r="J77" t="str">
-        <v>2026-07-31T11:18:37.610Z</v>
+        <v>2026-08-01T10:49:39.427Z</v>
       </c>
     </row>
     <row r="78">
@@ -2992,7 +2992,7 @@
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>2026-07-31T11:18:37.626Z</v>
+        <v>2026-08-01T10:49:39.443Z</v>
       </c>
     </row>
     <row r="79">
@@ -3018,13 +3018,13 @@
         <v>PASS</v>
       </c>
       <c r="H79">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I79" t="str">
         <v/>
       </c>
       <c r="J79" t="str">
-        <v>2026-07-31T11:18:37.641Z</v>
+        <v>2026-08-01T10:49:39.459Z</v>
       </c>
     </row>
     <row r="80">
@@ -3050,13 +3050,13 @@
         <v>PASS</v>
       </c>
       <c r="H80">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I80" t="str">
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>2026-07-31T11:18:37.657Z</v>
+        <v>2026-08-01T10:49:39.474Z</v>
       </c>
     </row>
     <row r="81">
@@ -3082,13 +3082,13 @@
         <v>PASS</v>
       </c>
       <c r="H81">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I81" t="str">
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>2026-07-31T11:18:37.672Z</v>
+        <v>2026-08-01T10:49:39.490Z</v>
       </c>
     </row>
     <row r="82">
@@ -3114,13 +3114,13 @@
         <v>PASS</v>
       </c>
       <c r="H82">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I82" t="str">
         <v/>
       </c>
       <c r="J82" t="str">
-        <v>2026-07-31T11:18:37.687Z</v>
+        <v>2026-08-01T10:49:39.505Z</v>
       </c>
     </row>
     <row r="83">
@@ -3146,13 +3146,13 @@
         <v>PASS</v>
       </c>
       <c r="H83">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I83" t="str">
         <v/>
       </c>
       <c r="J83" t="str">
-        <v>2026-07-31T11:18:37.702Z</v>
+        <v>2026-08-01T10:49:39.522Z</v>
       </c>
     </row>
     <row r="84">
@@ -3184,7 +3184,7 @@
         <v/>
       </c>
       <c r="J84" t="str">
-        <v>2026-07-31T11:18:37.717Z</v>
+        <v>2026-08-01T10:49:39.537Z</v>
       </c>
     </row>
     <row r="85">
@@ -3210,13 +3210,13 @@
         <v>PASS</v>
       </c>
       <c r="H85">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I85" t="str">
         <v/>
       </c>
       <c r="J85" t="str">
-        <v>2026-07-31T11:18:37.732Z</v>
+        <v>2026-08-01T10:49:39.552Z</v>
       </c>
     </row>
     <row r="86">
@@ -3248,7 +3248,7 @@
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>2026-07-31T11:18:37.748Z</v>
+        <v>2026-08-01T10:49:39.569Z</v>
       </c>
     </row>
     <row r="87">
@@ -3274,13 +3274,13 @@
         <v>PASS</v>
       </c>
       <c r="H87">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I87" t="str">
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>2026-07-31T11:18:37.763Z</v>
+        <v>2026-08-01T10:49:39.583Z</v>
       </c>
     </row>
     <row r="88">
@@ -3306,13 +3306,13 @@
         <v>PASS</v>
       </c>
       <c r="H88">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I88" t="str">
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>2026-07-31T11:18:37.779Z</v>
+        <v>2026-08-01T10:49:39.599Z</v>
       </c>
     </row>
     <row r="89">
@@ -3338,13 +3338,13 @@
         <v>PASS</v>
       </c>
       <c r="H89">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I89" t="str">
         <v/>
       </c>
       <c r="J89" t="str">
-        <v>2026-07-31T11:18:37.795Z</v>
+        <v>2026-08-01T10:49:39.614Z</v>
       </c>
     </row>
     <row r="90">
@@ -3370,13 +3370,13 @@
         <v>PASS</v>
       </c>
       <c r="H90">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I90" t="str">
         <v/>
       </c>
       <c r="J90" t="str">
-        <v>2026-07-31T11:18:37.810Z</v>
+        <v>2026-08-01T10:49:39.631Z</v>
       </c>
     </row>
     <row r="91">
@@ -3402,13 +3402,13 @@
         <v>PASS</v>
       </c>
       <c r="H91">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I91" t="str">
         <v/>
       </c>
       <c r="J91" t="str">
-        <v>2026-07-31T11:18:37.825Z</v>
+        <v>2026-08-01T10:49:39.646Z</v>
       </c>
     </row>
     <row r="92">
@@ -3440,7 +3440,7 @@
         <v/>
       </c>
       <c r="J92" t="str">
-        <v>2026-07-31T11:18:37.841Z</v>
+        <v>2026-08-01T10:49:39.661Z</v>
       </c>
     </row>
     <row r="93">
@@ -3472,7 +3472,7 @@
         <v/>
       </c>
       <c r="J93" t="str">
-        <v>2026-07-31T11:18:37.857Z</v>
+        <v>2026-08-01T10:49:39.677Z</v>
       </c>
     </row>
     <row r="94">
@@ -3504,7 +3504,7 @@
         <v/>
       </c>
       <c r="J94" t="str">
-        <v>2026-07-31T11:18:37.873Z</v>
+        <v>2026-08-01T10:49:39.693Z</v>
       </c>
     </row>
     <row r="95">
@@ -3530,13 +3530,13 @@
         <v>PASS</v>
       </c>
       <c r="H95">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I95" t="str">
         <v/>
       </c>
       <c r="J95" t="str">
-        <v>2026-07-31T11:18:37.889Z</v>
+        <v>2026-08-01T10:49:39.707Z</v>
       </c>
     </row>
     <row r="96">
@@ -3562,13 +3562,13 @@
         <v>PASS</v>
       </c>
       <c r="H96">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I96" t="str">
         <v/>
       </c>
       <c r="J96" t="str">
-        <v>2026-07-31T11:18:37.904Z</v>
+        <v>2026-08-01T10:49:39.723Z</v>
       </c>
     </row>
     <row r="97">
@@ -3600,7 +3600,7 @@
         <v/>
       </c>
       <c r="J97" t="str">
-        <v>2026-07-31T11:18:37.919Z</v>
+        <v>2026-08-01T10:49:39.738Z</v>
       </c>
     </row>
     <row r="98">
@@ -3632,7 +3632,7 @@
         <v/>
       </c>
       <c r="J98" t="str">
-        <v>2026-07-31T11:18:37.934Z</v>
+        <v>2026-08-01T10:49:39.754Z</v>
       </c>
     </row>
     <row r="99">
@@ -3664,7 +3664,7 @@
         <v/>
       </c>
       <c r="J99" t="str">
-        <v>2026-07-31T11:18:37.950Z</v>
+        <v>2026-08-01T10:49:39.770Z</v>
       </c>
     </row>
     <row r="100">
@@ -3696,7 +3696,7 @@
         <v/>
       </c>
       <c r="J100" t="str">
-        <v>2026-07-31T11:18:37.965Z</v>
+        <v>2026-08-01T10:49:39.785Z</v>
       </c>
     </row>
     <row r="101">
@@ -3728,7 +3728,7 @@
         <v/>
       </c>
       <c r="J101" t="str">
-        <v>2026-07-31T11:18:37.980Z</v>
+        <v>2026-08-01T10:49:39.800Z</v>
       </c>
     </row>
     <row r="102">
@@ -3760,7 +3760,7 @@
         <v/>
       </c>
       <c r="J102" t="str">
-        <v>2026-07-31T11:18:37.996Z</v>
+        <v>2026-08-01T10:49:39.816Z</v>
       </c>
     </row>
     <row r="103">
@@ -3792,7 +3792,7 @@
         <v/>
       </c>
       <c r="J103" t="str">
-        <v>2026-07-31T11:18:38.011Z</v>
+        <v>2026-08-01T10:49:39.831Z</v>
       </c>
     </row>
     <row r="104">
@@ -3818,13 +3818,13 @@
         <v>PASS</v>
       </c>
       <c r="H104">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I104" t="str">
         <v/>
       </c>
       <c r="J104" t="str">
-        <v>2026-07-31T11:18:38.026Z</v>
+        <v>2026-08-01T10:49:39.847Z</v>
       </c>
     </row>
     <row r="105">
@@ -3856,7 +3856,7 @@
         <v/>
       </c>
       <c r="J105" t="str">
-        <v>2026-07-31T11:18:38.042Z</v>
+        <v>2026-08-01T10:49:39.863Z</v>
       </c>
     </row>
     <row r="106">
@@ -3882,13 +3882,13 @@
         <v>PASS</v>
       </c>
       <c r="H106">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I106" t="str">
         <v/>
       </c>
       <c r="J106" t="str">
-        <v>2026-07-31T11:18:38.058Z</v>
+        <v>2026-08-01T10:49:39.878Z</v>
       </c>
     </row>
     <row r="107">
@@ -3914,13 +3914,13 @@
         <v>PASS</v>
       </c>
       <c r="H107">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I107" t="str">
         <v/>
       </c>
       <c r="J107" t="str">
-        <v>2026-07-31T11:18:38.073Z</v>
+        <v>2026-08-01T10:49:39.894Z</v>
       </c>
     </row>
     <row r="108">
@@ -3952,7 +3952,7 @@
         <v/>
       </c>
       <c r="J108" t="str">
-        <v>2026-07-31T11:18:38.088Z</v>
+        <v>2026-08-01T10:49:39.909Z</v>
       </c>
     </row>
     <row r="109">
@@ -3978,13 +3978,13 @@
         <v>PASS</v>
       </c>
       <c r="H109">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I109" t="str">
         <v/>
       </c>
       <c r="J109" t="str">
-        <v>2026-07-31T11:18:38.104Z</v>
+        <v>2026-08-01T10:49:39.924Z</v>
       </c>
     </row>
     <row r="110">
@@ -4016,7 +4016,7 @@
         <v/>
       </c>
       <c r="J110" t="str">
-        <v>2026-07-31T11:18:38.120Z</v>
+        <v>2026-08-01T10:49:39.940Z</v>
       </c>
     </row>
     <row r="111">
@@ -4048,7 +4048,7 @@
         <v/>
       </c>
       <c r="J111" t="str">
-        <v>2026-07-31T11:18:38.135Z</v>
+        <v>2026-08-01T10:49:39.955Z</v>
       </c>
     </row>
     <row r="112">
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="J112" t="str">
-        <v>2026-07-31T11:18:38.150Z</v>
+        <v>2026-08-01T10:49:39.970Z</v>
       </c>
     </row>
     <row r="113">
@@ -4106,13 +4106,13 @@
         <v>PASS</v>
       </c>
       <c r="H113">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I113" t="str">
         <v/>
       </c>
       <c r="J113" t="str">
-        <v>2026-07-31T11:18:38.166Z</v>
+        <v>2026-08-01T10:49:39.986Z</v>
       </c>
     </row>
     <row r="114">
@@ -4138,13 +4138,13 @@
         <v>PASS</v>
       </c>
       <c r="H114">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I114" t="str">
         <v/>
       </c>
       <c r="J114" t="str">
-        <v>2026-07-31T11:18:38.181Z</v>
+        <v>2026-08-01T10:49:40.002Z</v>
       </c>
     </row>
     <row r="115">
@@ -4170,13 +4170,13 @@
         <v>PASS</v>
       </c>
       <c r="H115">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I115" t="str">
         <v/>
       </c>
       <c r="J115" t="str">
-        <v>2026-07-31T11:18:38.196Z</v>
+        <v>2026-08-01T10:49:40.018Z</v>
       </c>
     </row>
     <row r="116">
@@ -4208,7 +4208,7 @@
         <v/>
       </c>
       <c r="J116" t="str">
-        <v>2026-07-31T11:18:38.212Z</v>
+        <v>2026-08-01T10:49:40.034Z</v>
       </c>
     </row>
     <row r="117">
@@ -4240,7 +4240,7 @@
         <v/>
       </c>
       <c r="J117" t="str">
-        <v>2026-07-31T11:18:38.229Z</v>
+        <v>2026-08-01T10:49:40.050Z</v>
       </c>
     </row>
     <row r="118">
@@ -4266,13 +4266,13 @@
         <v>PASS</v>
       </c>
       <c r="H118">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I118" t="str">
         <v/>
       </c>
       <c r="J118" t="str">
-        <v>2026-07-31T11:18:38.244Z</v>
+        <v>2026-08-01T10:49:40.066Z</v>
       </c>
     </row>
     <row r="119">
@@ -4304,7 +4304,7 @@
         <v/>
       </c>
       <c r="J119" t="str">
-        <v>2026-07-31T11:18:38.260Z</v>
+        <v>2026-08-01T10:49:40.081Z</v>
       </c>
     </row>
     <row r="120">
@@ -4336,7 +4336,7 @@
         <v/>
       </c>
       <c r="J120" t="str">
-        <v>2026-07-31T11:18:38.276Z</v>
+        <v>2026-08-01T10:49:40.097Z</v>
       </c>
     </row>
     <row r="121">
@@ -4368,7 +4368,7 @@
         <v/>
       </c>
       <c r="J121" t="str">
-        <v>2026-07-31T11:18:38.291Z</v>
+        <v>2026-08-01T10:49:40.112Z</v>
       </c>
     </row>
     <row r="122">
@@ -4394,13 +4394,13 @@
         <v>PASS</v>
       </c>
       <c r="H122">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I122" t="str">
         <v/>
       </c>
       <c r="J122" t="str">
-        <v>2026-07-31T11:18:38.306Z</v>
+        <v>2026-08-01T10:49:40.128Z</v>
       </c>
     </row>
     <row r="123">
@@ -4432,7 +4432,7 @@
         <v/>
       </c>
       <c r="J123" t="str">
-        <v>2026-07-31T11:18:38.322Z</v>
+        <v>2026-08-01T10:49:40.144Z</v>
       </c>
     </row>
     <row r="124">
@@ -4458,13 +4458,13 @@
         <v>PASS</v>
       </c>
       <c r="H124">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I124" t="str">
         <v/>
       </c>
       <c r="J124" t="str">
-        <v>2026-07-31T11:18:38.336Z</v>
+        <v>2026-08-01T10:49:40.159Z</v>
       </c>
     </row>
     <row r="125">
@@ -4490,13 +4490,13 @@
         <v>PASS</v>
       </c>
       <c r="H125">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I125" t="str">
         <v/>
       </c>
       <c r="J125" t="str">
-        <v>2026-07-31T11:18:38.353Z</v>
+        <v>2026-08-01T10:49:40.175Z</v>
       </c>
     </row>
     <row r="126">
@@ -4522,13 +4522,13 @@
         <v>PASS</v>
       </c>
       <c r="H126">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I126" t="str">
         <v/>
       </c>
       <c r="J126" t="str">
-        <v>2026-07-31T11:18:38.368Z</v>
+        <v>2026-08-01T10:49:40.191Z</v>
       </c>
     </row>
     <row r="127">
@@ -4560,7 +4560,7 @@
         <v/>
       </c>
       <c r="J127" t="str">
-        <v>2026-07-31T11:18:38.383Z</v>
+        <v>2026-08-01T10:49:40.206Z</v>
       </c>
     </row>
     <row r="128">
@@ -4586,13 +4586,13 @@
         <v>PASS</v>
       </c>
       <c r="H128">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I128" t="str">
         <v/>
       </c>
       <c r="J128" t="str">
-        <v>2026-07-31T11:18:38.399Z</v>
+        <v>2026-08-01T10:49:40.221Z</v>
       </c>
     </row>
     <row r="129">
@@ -4618,13 +4618,13 @@
         <v>PASS</v>
       </c>
       <c r="H129">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I129" t="str">
         <v/>
       </c>
       <c r="J129" t="str">
-        <v>2026-07-31T11:18:38.414Z</v>
+        <v>2026-08-01T10:49:40.237Z</v>
       </c>
     </row>
     <row r="130">
@@ -4656,7 +4656,7 @@
         <v/>
       </c>
       <c r="J130" t="str">
-        <v>2026-07-31T11:18:38.430Z</v>
+        <v>2026-08-01T10:49:40.252Z</v>
       </c>
     </row>
     <row r="131">
@@ -4682,13 +4682,13 @@
         <v>PASS</v>
       </c>
       <c r="H131">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I131" t="str">
         <v/>
       </c>
       <c r="J131" t="str">
-        <v>2026-07-31T11:18:38.445Z</v>
+        <v>2026-08-01T10:49:40.268Z</v>
       </c>
     </row>
     <row r="132">
@@ -4720,7 +4720,7 @@
         <v/>
       </c>
       <c r="J132" t="str">
-        <v>2026-07-31T11:18:38.460Z</v>
+        <v>2026-08-01T10:49:40.283Z</v>
       </c>
     </row>
     <row r="133">
@@ -4752,7 +4752,7 @@
         <v/>
       </c>
       <c r="J133" t="str">
-        <v>2026-07-31T11:18:38.476Z</v>
+        <v>2026-08-01T10:49:40.299Z</v>
       </c>
     </row>
     <row r="134">
@@ -4778,13 +4778,13 @@
         <v>PASS</v>
       </c>
       <c r="H134">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I134" t="str">
         <v/>
       </c>
       <c r="J134" t="str">
-        <v>2026-07-31T11:18:38.491Z</v>
+        <v>2026-08-01T10:49:40.315Z</v>
       </c>
     </row>
     <row r="135">
@@ -4810,13 +4810,13 @@
         <v>PASS</v>
       </c>
       <c r="H135">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I135" t="str">
         <v/>
       </c>
       <c r="J135" t="str">
-        <v>2026-07-31T11:18:38.506Z</v>
+        <v>2026-08-01T10:49:40.330Z</v>
       </c>
     </row>
     <row r="136">
@@ -4842,13 +4842,13 @@
         <v>PASS</v>
       </c>
       <c r="H136">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I136" t="str">
         <v/>
       </c>
       <c r="J136" t="str">
-        <v>2026-07-31T11:18:38.522Z</v>
+        <v>2026-08-01T10:49:40.345Z</v>
       </c>
     </row>
     <row r="137">
@@ -4874,13 +4874,13 @@
         <v>PASS</v>
       </c>
       <c r="H137">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I137" t="str">
         <v/>
       </c>
       <c r="J137" t="str">
-        <v>2026-07-31T11:18:38.537Z</v>
+        <v>2026-08-01T10:49:40.361Z</v>
       </c>
     </row>
     <row r="138">
@@ -4912,7 +4912,7 @@
         <v/>
       </c>
       <c r="J138" t="str">
-        <v>2026-07-31T11:18:38.552Z</v>
+        <v>2026-08-01T10:49:40.376Z</v>
       </c>
     </row>
     <row r="139">
@@ -4938,13 +4938,13 @@
         <v>PASS</v>
       </c>
       <c r="H139">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I139" t="str">
         <v/>
       </c>
       <c r="J139" t="str">
-        <v>2026-07-31T11:18:38.568Z</v>
+        <v>2026-08-01T10:49:40.392Z</v>
       </c>
     </row>
     <row r="140">
@@ -4970,13 +4970,13 @@
         <v>PASS</v>
       </c>
       <c r="H140">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I140" t="str">
         <v/>
       </c>
       <c r="J140" t="str">
-        <v>2026-07-31T11:18:38.584Z</v>
+        <v>2026-08-01T10:49:40.409Z</v>
       </c>
     </row>
     <row r="141">
@@ -5002,13 +5002,13 @@
         <v>PASS</v>
       </c>
       <c r="H141">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I141" t="str">
         <v/>
       </c>
       <c r="J141" t="str">
-        <v>2026-07-31T11:18:38.599Z</v>
+        <v>2026-08-01T10:49:40.423Z</v>
       </c>
     </row>
     <row r="142">
@@ -5040,7 +5040,7 @@
         <v/>
       </c>
       <c r="J142" t="str">
-        <v>2026-07-31T11:18:38.615Z</v>
+        <v>2026-08-01T10:49:40.440Z</v>
       </c>
     </row>
     <row r="143">
@@ -5066,13 +5066,13 @@
         <v>PASS</v>
       </c>
       <c r="H143">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I143" t="str">
         <v/>
       </c>
       <c r="J143" t="str">
-        <v>2026-07-31T11:18:38.631Z</v>
+        <v>2026-08-01T10:49:40.455Z</v>
       </c>
     </row>
     <row r="144">
@@ -5098,13 +5098,13 @@
         <v>PASS</v>
       </c>
       <c r="H144">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I144" t="str">
         <v/>
       </c>
       <c r="J144" t="str">
-        <v>2026-07-31T11:18:38.647Z</v>
+        <v>2026-08-01T10:49:40.470Z</v>
       </c>
     </row>
     <row r="145">
@@ -5136,7 +5136,7 @@
         <v/>
       </c>
       <c r="J145" t="str">
-        <v>2026-07-31T11:18:38.663Z</v>
+        <v>2026-08-01T10:49:40.486Z</v>
       </c>
     </row>
     <row r="146">
@@ -5168,7 +5168,7 @@
         <v/>
       </c>
       <c r="J146" t="str">
-        <v>2026-07-31T11:18:38.679Z</v>
+        <v>2026-08-01T10:49:40.502Z</v>
       </c>
     </row>
     <row r="147">
@@ -5200,7 +5200,7 @@
         <v/>
       </c>
       <c r="J147" t="str">
-        <v>2026-07-31T11:18:38.695Z</v>
+        <v>2026-08-01T10:49:40.518Z</v>
       </c>
     </row>
     <row r="148">
@@ -5232,7 +5232,7 @@
         <v/>
       </c>
       <c r="J148" t="str">
-        <v>2026-07-31T11:18:38.710Z</v>
+        <v>2026-08-01T10:49:40.533Z</v>
       </c>
     </row>
     <row r="149">
@@ -5264,7 +5264,7 @@
         <v/>
       </c>
       <c r="J149" t="str">
-        <v>2026-07-31T11:18:38.725Z</v>
+        <v>2026-08-01T10:49:40.548Z</v>
       </c>
     </row>
     <row r="150">
@@ -5296,7 +5296,7 @@
         <v/>
       </c>
       <c r="J150" t="str">
-        <v>2026-07-31T11:18:38.741Z</v>
+        <v>2026-08-01T10:49:40.563Z</v>
       </c>
     </row>
     <row r="151">
@@ -5322,13 +5322,13 @@
         <v>PASS</v>
       </c>
       <c r="H151">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I151" t="str">
         <v/>
       </c>
       <c r="J151" t="str">
-        <v>2026-07-31T11:18:38.757Z</v>
+        <v>2026-08-01T10:49:40.578Z</v>
       </c>
     </row>
     <row r="152">
@@ -5354,13 +5354,13 @@
         <v>PASS</v>
       </c>
       <c r="H152">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I152" t="str">
         <v/>
       </c>
       <c r="J152" t="str">
-        <v>2026-07-31T11:18:38.772Z</v>
+        <v>2026-08-01T10:49:40.594Z</v>
       </c>
     </row>
     <row r="153">
@@ -5392,7 +5392,7 @@
         <v/>
       </c>
       <c r="J153" t="str">
-        <v>2026-07-31T11:18:38.787Z</v>
+        <v>2026-08-01T10:49:40.609Z</v>
       </c>
     </row>
     <row r="154">
@@ -5418,13 +5418,13 @@
         <v>PASS</v>
       </c>
       <c r="H154">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I154" t="str">
         <v/>
       </c>
       <c r="J154" t="str">
-        <v>2026-07-31T11:18:38.803Z</v>
+        <v>2026-08-01T10:49:40.626Z</v>
       </c>
     </row>
     <row r="155">
@@ -5456,7 +5456,7 @@
         <v/>
       </c>
       <c r="J155" t="str">
-        <v>2026-07-31T11:18:38.818Z</v>
+        <v>2026-08-01T10:49:40.641Z</v>
       </c>
     </row>
     <row r="156">
@@ -5482,13 +5482,13 @@
         <v>PASS</v>
       </c>
       <c r="H156">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I156" t="str">
         <v/>
       </c>
       <c r="J156" t="str">
-        <v>2026-07-31T11:18:38.834Z</v>
+        <v>2026-08-01T10:49:40.657Z</v>
       </c>
     </row>
     <row r="157">
@@ -5520,7 +5520,7 @@
         <v/>
       </c>
       <c r="J157" t="str">
-        <v>2026-07-31T11:18:38.849Z</v>
+        <v>2026-08-01T10:49:40.672Z</v>
       </c>
     </row>
     <row r="158">
@@ -5546,13 +5546,13 @@
         <v>PASS</v>
       </c>
       <c r="H158">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I158" t="str">
         <v/>
       </c>
       <c r="J158" t="str">
-        <v>2026-07-31T11:18:38.867Z</v>
+        <v>2026-08-01T10:49:40.688Z</v>
       </c>
     </row>
     <row r="159">
@@ -5578,13 +5578,13 @@
         <v>PASS</v>
       </c>
       <c r="H159">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I159" t="str">
         <v/>
       </c>
       <c r="J159" t="str">
-        <v>2026-07-31T11:18:38.881Z</v>
+        <v>2026-08-01T10:49:40.703Z</v>
       </c>
     </row>
     <row r="160">
@@ -5610,13 +5610,13 @@
         <v>PASS</v>
       </c>
       <c r="H160">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I160" t="str">
         <v/>
       </c>
       <c r="J160" t="str">
-        <v>2026-07-31T11:18:38.897Z</v>
+        <v>2026-08-01T10:49:40.718Z</v>
       </c>
     </row>
     <row r="161">
@@ -5648,7 +5648,7 @@
         <v/>
       </c>
       <c r="J161" t="str">
-        <v>2026-07-31T11:18:38.913Z</v>
+        <v>2026-08-01T10:49:40.734Z</v>
       </c>
     </row>
     <row r="162">
@@ -5680,7 +5680,7 @@
         <v/>
       </c>
       <c r="J162" t="str">
-        <v>2026-07-31T11:18:38.928Z</v>
+        <v>2026-08-01T10:49:40.749Z</v>
       </c>
     </row>
     <row r="163">
@@ -5706,13 +5706,13 @@
         <v>PASS</v>
       </c>
       <c r="H163">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I163" t="str">
         <v/>
       </c>
       <c r="J163" t="str">
-        <v>2026-07-31T11:18:38.943Z</v>
+        <v>2026-08-01T10:49:40.765Z</v>
       </c>
     </row>
     <row r="164">
@@ -5744,7 +5744,7 @@
         <v/>
       </c>
       <c r="J164" t="str">
-        <v>2026-07-31T11:18:38.959Z</v>
+        <v>2026-08-01T10:49:40.781Z</v>
       </c>
     </row>
     <row r="165">
@@ -5776,7 +5776,7 @@
         <v/>
       </c>
       <c r="J165" t="str">
-        <v>2026-07-31T11:18:38.974Z</v>
+        <v>2026-08-01T10:49:40.796Z</v>
       </c>
     </row>
     <row r="166">
@@ -5808,7 +5808,7 @@
         <v/>
       </c>
       <c r="J166" t="str">
-        <v>2026-07-31T11:18:38.990Z</v>
+        <v>2026-08-01T10:49:40.812Z</v>
       </c>
     </row>
     <row r="167">
@@ -5834,13 +5834,13 @@
         <v>PASS</v>
       </c>
       <c r="H167">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I167" t="str">
         <v/>
       </c>
       <c r="J167" t="str">
-        <v>2026-07-31T11:18:39.005Z</v>
+        <v>2026-08-01T10:49:40.828Z</v>
       </c>
     </row>
     <row r="168">
@@ -5872,7 +5872,7 @@
         <v/>
       </c>
       <c r="J168" t="str">
-        <v>2026-07-31T11:18:39.020Z</v>
+        <v>2026-08-01T10:49:40.843Z</v>
       </c>
     </row>
     <row r="169">
@@ -5898,13 +5898,13 @@
         <v>PASS</v>
       </c>
       <c r="H169">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I169" t="str">
         <v/>
       </c>
       <c r="J169" t="str">
-        <v>2026-07-31T11:18:39.036Z</v>
+        <v>2026-08-01T10:49:40.858Z</v>
       </c>
     </row>
     <row r="170">
@@ -5930,13 +5930,13 @@
         <v>PASS</v>
       </c>
       <c r="H170">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I170" t="str">
         <v/>
       </c>
       <c r="J170" t="str">
-        <v>2026-07-31T11:18:39.051Z</v>
+        <v>2026-08-01T10:49:40.874Z</v>
       </c>
     </row>
     <row r="171">
@@ -5962,13 +5962,13 @@
         <v>PASS</v>
       </c>
       <c r="H171">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I171" t="str">
         <v/>
       </c>
       <c r="J171" t="str">
-        <v>2026-07-31T11:18:39.067Z</v>
+        <v>2026-08-01T10:49:40.889Z</v>
       </c>
     </row>
     <row r="172">
@@ -6000,7 +6000,7 @@
         <v/>
       </c>
       <c r="J172" t="str">
-        <v>2026-07-31T11:18:39.082Z</v>
+        <v>2026-08-01T10:49:40.904Z</v>
       </c>
     </row>
     <row r="173">
@@ -6026,13 +6026,13 @@
         <v>PASS</v>
       </c>
       <c r="H173">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I173" t="str">
         <v/>
       </c>
       <c r="J173" t="str">
-        <v>2026-07-31T11:18:39.097Z</v>
+        <v>2026-08-01T10:49:40.921Z</v>
       </c>
     </row>
     <row r="174">
@@ -6058,13 +6058,13 @@
         <v>PASS</v>
       </c>
       <c r="H174">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I174" t="str">
         <v/>
       </c>
       <c r="J174" t="str">
-        <v>2026-07-31T11:18:39.113Z</v>
+        <v>2026-08-01T10:49:40.936Z</v>
       </c>
     </row>
     <row r="175">
@@ -6090,13 +6090,13 @@
         <v>PASS</v>
       </c>
       <c r="H175">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I175" t="str">
         <v/>
       </c>
       <c r="J175" t="str">
-        <v>2026-07-31T11:18:39.130Z</v>
+        <v>2026-08-01T10:49:40.952Z</v>
       </c>
     </row>
     <row r="176">
@@ -6128,7 +6128,7 @@
         <v/>
       </c>
       <c r="J176" t="str">
-        <v>2026-07-31T11:18:39.145Z</v>
+        <v>2026-08-01T10:49:40.967Z</v>
       </c>
     </row>
     <row r="177">
@@ -6154,13 +6154,13 @@
         <v>PASS</v>
       </c>
       <c r="H177">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I177" t="str">
         <v/>
       </c>
       <c r="J177" t="str">
-        <v>2026-07-31T11:18:39.160Z</v>
+        <v>2026-08-01T10:49:40.983Z</v>
       </c>
     </row>
     <row r="178">
@@ -6192,7 +6192,7 @@
         <v/>
       </c>
       <c r="J178" t="str">
-        <v>2026-07-31T11:18:39.176Z</v>
+        <v>2026-08-01T10:49:40.998Z</v>
       </c>
     </row>
     <row r="179">
@@ -6218,13 +6218,13 @@
         <v>PASS</v>
       </c>
       <c r="H179">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I179" t="str">
         <v/>
       </c>
       <c r="J179" t="str">
-        <v>2026-07-31T11:18:39.192Z</v>
+        <v>2026-08-01T10:49:41.013Z</v>
       </c>
     </row>
     <row r="180">
@@ -6256,7 +6256,7 @@
         <v/>
       </c>
       <c r="J180" t="str">
-        <v>2026-07-31T11:18:39.208Z</v>
+        <v>2026-08-01T10:49:41.029Z</v>
       </c>
     </row>
     <row r="181">
@@ -6288,7 +6288,7 @@
         <v/>
       </c>
       <c r="J181" t="str">
-        <v>2026-07-31T11:18:39.223Z</v>
+        <v>2026-08-01T10:49:41.044Z</v>
       </c>
     </row>
     <row r="182">
@@ -6314,13 +6314,13 @@
         <v>PASS</v>
       </c>
       <c r="H182">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I182" t="str">
         <v/>
       </c>
       <c r="J182" t="str">
-        <v>2026-07-31T11:18:39.238Z</v>
+        <v>2026-08-01T10:49:41.060Z</v>
       </c>
     </row>
     <row r="183">
@@ -6346,13 +6346,13 @@
         <v>PASS</v>
       </c>
       <c r="H183">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I183" t="str">
         <v/>
       </c>
       <c r="J183" t="str">
-        <v>2026-07-31T11:18:39.254Z</v>
+        <v>2026-08-01T10:49:41.075Z</v>
       </c>
     </row>
     <row r="184">
@@ -6384,7 +6384,7 @@
         <v/>
       </c>
       <c r="J184" t="str">
-        <v>2026-07-31T11:18:39.270Z</v>
+        <v>2026-08-01T10:49:41.091Z</v>
       </c>
     </row>
     <row r="185">
@@ -6410,13 +6410,13 @@
         <v>PASS</v>
       </c>
       <c r="H185">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I185" t="str">
         <v/>
       </c>
       <c r="J185" t="str">
-        <v>2026-07-31T11:18:39.286Z</v>
+        <v>2026-08-01T10:49:41.106Z</v>
       </c>
     </row>
     <row r="186">
@@ -6442,13 +6442,13 @@
         <v>PASS</v>
       </c>
       <c r="H186">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I186" t="str">
         <v/>
       </c>
       <c r="J186" t="str">
-        <v>2026-07-31T11:18:39.301Z</v>
+        <v>2026-08-01T10:49:41.122Z</v>
       </c>
     </row>
     <row r="187">
@@ -6480,7 +6480,7 @@
         <v/>
       </c>
       <c r="J187" t="str">
-        <v>2026-07-31T11:18:39.317Z</v>
+        <v>2026-08-01T10:49:41.138Z</v>
       </c>
     </row>
     <row r="188">
@@ -6512,7 +6512,7 @@
         <v/>
       </c>
       <c r="J188" t="str">
-        <v>2026-07-31T11:18:39.333Z</v>
+        <v>2026-08-01T10:49:41.154Z</v>
       </c>
     </row>
     <row r="189">
@@ -6538,13 +6538,13 @@
         <v>PASS</v>
       </c>
       <c r="H189">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I189" t="str">
         <v/>
       </c>
       <c r="J189" t="str">
-        <v>2026-07-31T11:18:39.348Z</v>
+        <v>2026-08-01T10:49:41.170Z</v>
       </c>
     </row>
     <row r="190">
@@ -6570,13 +6570,13 @@
         <v>PASS</v>
       </c>
       <c r="H190">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I190" t="str">
         <v/>
       </c>
       <c r="J190" t="str">
-        <v>2026-07-31T11:18:39.363Z</v>
+        <v>2026-08-01T10:49:41.185Z</v>
       </c>
     </row>
     <row r="191">
@@ -6608,7 +6608,7 @@
         <v/>
       </c>
       <c r="J191" t="str">
-        <v>2026-07-31T11:18:39.379Z</v>
+        <v>2026-08-01T10:49:41.201Z</v>
       </c>
     </row>
     <row r="192">
@@ -6634,13 +6634,13 @@
         <v>PASS</v>
       </c>
       <c r="H192">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I192" t="str">
         <v/>
       </c>
       <c r="J192" t="str">
-        <v>2026-07-31T11:18:39.394Z</v>
+        <v>2026-08-01T10:49:41.217Z</v>
       </c>
     </row>
     <row r="193">
@@ -6666,13 +6666,13 @@
         <v>PASS</v>
       </c>
       <c r="H193">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I193" t="str">
         <v/>
       </c>
       <c r="J193" t="str">
-        <v>2026-07-31T11:18:39.410Z</v>
+        <v>2026-08-01T10:49:41.232Z</v>
       </c>
     </row>
     <row r="194">
@@ -6698,13 +6698,13 @@
         <v>PASS</v>
       </c>
       <c r="H194">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I194" t="str">
         <v/>
       </c>
       <c r="J194" t="str">
-        <v>2026-07-31T11:18:39.425Z</v>
+        <v>2026-08-01T10:49:41.248Z</v>
       </c>
     </row>
     <row r="195">
@@ -6730,13 +6730,13 @@
         <v>PASS</v>
       </c>
       <c r="H195">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I195" t="str">
         <v/>
       </c>
       <c r="J195" t="str">
-        <v>2026-07-31T11:18:39.440Z</v>
+        <v>2026-08-01T10:49:41.264Z</v>
       </c>
     </row>
     <row r="196">
@@ -6762,13 +6762,13 @@
         <v>PASS</v>
       </c>
       <c r="H196">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I196" t="str">
         <v/>
       </c>
       <c r="J196" t="str">
-        <v>2026-07-31T11:18:39.456Z</v>
+        <v>2026-08-01T10:49:41.280Z</v>
       </c>
     </row>
     <row r="197">
@@ -6794,13 +6794,13 @@
         <v>PASS</v>
       </c>
       <c r="H197">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I197" t="str">
         <v/>
       </c>
       <c r="J197" t="str">
-        <v>2026-07-31T11:18:39.472Z</v>
+        <v>2026-08-01T10:49:41.295Z</v>
       </c>
     </row>
     <row r="198">
@@ -6826,13 +6826,13 @@
         <v>PASS</v>
       </c>
       <c r="H198">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I198" t="str">
         <v/>
       </c>
       <c r="J198" t="str">
-        <v>2026-07-31T11:18:39.488Z</v>
+        <v>2026-08-01T10:49:41.310Z</v>
       </c>
     </row>
     <row r="199">
@@ -6858,13 +6858,13 @@
         <v>PASS</v>
       </c>
       <c r="H199">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I199" t="str">
         <v/>
       </c>
       <c r="J199" t="str">
-        <v>2026-07-31T11:18:39.503Z</v>
+        <v>2026-08-01T10:49:41.326Z</v>
       </c>
     </row>
     <row r="200">
@@ -6890,13 +6890,13 @@
         <v>PASS</v>
       </c>
       <c r="H200">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I200" t="str">
         <v/>
       </c>
       <c r="J200" t="str">
-        <v>2026-07-31T11:18:39.521Z</v>
+        <v>2026-08-01T10:49:41.341Z</v>
       </c>
     </row>
     <row r="201">
@@ -6922,13 +6922,13 @@
         <v>PASS</v>
       </c>
       <c r="H201">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I201" t="str">
         <v/>
       </c>
       <c r="J201" t="str">
-        <v>2026-07-31T11:18:39.533Z</v>
+        <v>2026-08-01T10:49:41.356Z</v>
       </c>
     </row>
     <row r="202">
@@ -6960,7 +6960,7 @@
         <v/>
       </c>
       <c r="J202" t="str">
-        <v>2026-07-31T11:18:39.549Z</v>
+        <v>2026-08-01T10:49:41.372Z</v>
       </c>
     </row>
     <row r="203">
@@ -6992,7 +6992,7 @@
         <v/>
       </c>
       <c r="J203" t="str">
-        <v>2026-07-31T11:18:39.565Z</v>
+        <v>2026-08-01T10:49:41.388Z</v>
       </c>
     </row>
     <row r="204">
@@ -7024,7 +7024,7 @@
         <v/>
       </c>
       <c r="J204" t="str">
-        <v>2026-07-31T11:18:39.580Z</v>
+        <v>2026-08-01T10:49:41.403Z</v>
       </c>
     </row>
     <row r="205">
@@ -7056,7 +7056,7 @@
         <v/>
       </c>
       <c r="J205" t="str">
-        <v>2026-07-31T11:18:39.596Z</v>
+        <v>2026-08-01T10:49:41.419Z</v>
       </c>
     </row>
     <row r="206">
@@ -7082,13 +7082,13 @@
         <v>PASS</v>
       </c>
       <c r="H206">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I206" t="str">
         <v/>
       </c>
       <c r="J206" t="str">
-        <v>2026-07-31T11:18:39.611Z</v>
+        <v>2026-08-01T10:49:41.435Z</v>
       </c>
     </row>
     <row r="207">
@@ -7120,7 +7120,7 @@
         <v/>
       </c>
       <c r="J207" t="str">
-        <v>2026-07-31T11:18:39.627Z</v>
+        <v>2026-08-01T10:49:41.451Z</v>
       </c>
     </row>
     <row r="208">
@@ -7146,13 +7146,13 @@
         <v>PASS</v>
       </c>
       <c r="H208">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I208" t="str">
         <v/>
       </c>
       <c r="J208" t="str">
-        <v>2026-07-31T11:18:39.642Z</v>
+        <v>2026-08-01T10:49:41.467Z</v>
       </c>
     </row>
     <row r="209">
@@ -7178,13 +7178,13 @@
         <v>PASS</v>
       </c>
       <c r="H209">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I209" t="str">
         <v/>
       </c>
       <c r="J209" t="str">
-        <v>2026-07-31T11:18:39.657Z</v>
+        <v>2026-08-01T10:49:41.483Z</v>
       </c>
     </row>
     <row r="210">
@@ -7216,7 +7216,7 @@
         <v/>
       </c>
       <c r="J210" t="str">
-        <v>2026-07-31T11:18:39.673Z</v>
+        <v>2026-08-01T10:49:41.499Z</v>
       </c>
     </row>
     <row r="211">
@@ -7242,13 +7242,13 @@
         <v>PASS</v>
       </c>
       <c r="H211">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I211" t="str">
         <v/>
       </c>
       <c r="J211" t="str">
-        <v>2026-07-31T11:18:39.688Z</v>
+        <v>2026-08-01T10:49:41.513Z</v>
       </c>
     </row>
     <row r="212">
@@ -7280,7 +7280,7 @@
         <v/>
       </c>
       <c r="J212" t="str">
-        <v>2026-07-31T11:18:39.704Z</v>
+        <v>2026-08-01T10:49:41.529Z</v>
       </c>
     </row>
     <row r="213">
@@ -7306,13 +7306,13 @@
         <v>PASS</v>
       </c>
       <c r="H213">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I213" t="str">
         <v/>
       </c>
       <c r="J213" t="str">
-        <v>2026-07-31T11:18:39.719Z</v>
+        <v>2026-08-01T10:49:41.545Z</v>
       </c>
     </row>
     <row r="214">
@@ -7338,13 +7338,13 @@
         <v>PASS</v>
       </c>
       <c r="H214">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I214" t="str">
         <v/>
       </c>
       <c r="J214" t="str">
-        <v>2026-07-31T11:18:39.735Z</v>
+        <v>2026-08-01T10:49:41.560Z</v>
       </c>
     </row>
     <row r="215">
@@ -7370,13 +7370,13 @@
         <v>PASS</v>
       </c>
       <c r="H215">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I215" t="str">
         <v/>
       </c>
       <c r="J215" t="str">
-        <v>2026-07-31T11:18:39.751Z</v>
+        <v>2026-08-01T10:49:41.575Z</v>
       </c>
     </row>
     <row r="216">
@@ -7402,13 +7402,13 @@
         <v>PASS</v>
       </c>
       <c r="H216">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I216" t="str">
         <v/>
       </c>
       <c r="J216" t="str">
-        <v>2026-07-31T11:18:39.766Z</v>
+        <v>2026-08-01T10:49:41.592Z</v>
       </c>
     </row>
     <row r="217">
@@ -7434,13 +7434,13 @@
         <v>PASS</v>
       </c>
       <c r="H217">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I217" t="str">
         <v/>
       </c>
       <c r="J217" t="str">
-        <v>2026-07-31T11:18:39.782Z</v>
+        <v>2026-08-01T10:49:41.607Z</v>
       </c>
     </row>
     <row r="218">
@@ -7472,7 +7472,7 @@
         <v/>
       </c>
       <c r="J218" t="str">
-        <v>2026-07-31T11:18:39.798Z</v>
+        <v>2026-08-01T10:49:41.623Z</v>
       </c>
     </row>
     <row r="219">
@@ -7498,13 +7498,13 @@
         <v>PASS</v>
       </c>
       <c r="H219">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I219" t="str">
         <v/>
       </c>
       <c r="J219" t="str">
-        <v>2026-07-31T11:18:39.813Z</v>
+        <v>2026-08-01T10:49:41.639Z</v>
       </c>
     </row>
     <row r="220">
@@ -7530,13 +7530,13 @@
         <v>PASS</v>
       </c>
       <c r="H220">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I220" t="str">
         <v/>
       </c>
       <c r="J220" t="str">
-        <v>2026-07-31T11:18:39.829Z</v>
+        <v>2026-08-01T10:49:41.654Z</v>
       </c>
     </row>
     <row r="221">
@@ -7562,13 +7562,13 @@
         <v>PASS</v>
       </c>
       <c r="H221">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I221" t="str">
         <v/>
       </c>
       <c r="J221" t="str">
-        <v>2026-07-31T11:18:39.844Z</v>
+        <v>2026-08-01T10:49:41.670Z</v>
       </c>
     </row>
     <row r="222">
@@ -7600,7 +7600,7 @@
         <v/>
       </c>
       <c r="J222" t="str">
-        <v>2026-07-31T11:18:39.860Z</v>
+        <v>2026-08-01T10:49:41.685Z</v>
       </c>
     </row>
     <row r="223">
@@ -7632,7 +7632,7 @@
         <v/>
       </c>
       <c r="J223" t="str">
-        <v>2026-07-31T11:18:39.876Z</v>
+        <v>2026-08-01T10:49:41.701Z</v>
       </c>
     </row>
     <row r="224">
@@ -7664,7 +7664,7 @@
         <v/>
       </c>
       <c r="J224" t="str">
-        <v>2026-07-31T11:18:39.892Z</v>
+        <v>2026-08-01T10:49:41.717Z</v>
       </c>
     </row>
     <row r="225">
@@ -7690,13 +7690,13 @@
         <v>PASS</v>
       </c>
       <c r="H225">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I225" t="str">
         <v/>
       </c>
       <c r="J225" t="str">
-        <v>2026-07-31T11:18:39.906Z</v>
+        <v>2026-08-01T10:49:41.733Z</v>
       </c>
     </row>
     <row r="226">
@@ -7728,7 +7728,7 @@
         <v/>
       </c>
       <c r="J226" t="str">
-        <v>2026-07-31T11:18:39.922Z</v>
+        <v>2026-08-01T10:49:41.749Z</v>
       </c>
     </row>
     <row r="227">
@@ -7754,13 +7754,13 @@
         <v>PASS</v>
       </c>
       <c r="H227">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I227" t="str">
         <v/>
       </c>
       <c r="J227" t="str">
-        <v>2026-07-31T11:18:39.937Z</v>
+        <v>2026-08-01T10:49:41.765Z</v>
       </c>
     </row>
     <row r="228">
@@ -7786,13 +7786,13 @@
         <v>PASS</v>
       </c>
       <c r="H228">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I228" t="str">
         <v/>
       </c>
       <c r="J228" t="str">
-        <v>2026-07-31T11:18:39.953Z</v>
+        <v>2026-08-01T10:49:41.779Z</v>
       </c>
     </row>
     <row r="229">
@@ -7824,7 +7824,7 @@
         <v/>
       </c>
       <c r="J229" t="str">
-        <v>2026-07-31T11:18:39.968Z</v>
+        <v>2026-08-01T10:49:41.794Z</v>
       </c>
     </row>
     <row r="230">
@@ -7856,7 +7856,7 @@
         <v/>
       </c>
       <c r="J230" t="str">
-        <v>2026-07-31T11:18:39.983Z</v>
+        <v>2026-08-01T10:49:41.809Z</v>
       </c>
     </row>
     <row r="231">
@@ -7882,13 +7882,13 @@
         <v>PASS</v>
       </c>
       <c r="H231">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I231" t="str">
         <v/>
       </c>
       <c r="J231" t="str">
-        <v>2026-07-31T11:18:39.999Z</v>
+        <v>2026-08-01T10:49:41.825Z</v>
       </c>
     </row>
     <row r="232">
@@ -7914,13 +7914,13 @@
         <v>PASS</v>
       </c>
       <c r="H232">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I232" t="str">
         <v/>
       </c>
       <c r="J232" t="str">
-        <v>2026-07-31T11:18:40.014Z</v>
+        <v>2026-08-01T10:49:41.841Z</v>
       </c>
     </row>
     <row r="233">
@@ -7946,13 +7946,13 @@
         <v>PASS</v>
       </c>
       <c r="H233">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I233" t="str">
         <v/>
       </c>
       <c r="J233" t="str">
-        <v>2026-07-31T11:18:40.029Z</v>
+        <v>2026-08-01T10:49:41.855Z</v>
       </c>
     </row>
     <row r="234">
@@ -7978,13 +7978,13 @@
         <v>PASS</v>
       </c>
       <c r="H234">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I234" t="str">
         <v/>
       </c>
       <c r="J234" t="str">
-        <v>2026-07-31T11:18:40.045Z</v>
+        <v>2026-08-01T10:49:41.872Z</v>
       </c>
     </row>
     <row r="235">
@@ -8016,7 +8016,7 @@
         <v/>
       </c>
       <c r="J235" t="str">
-        <v>2026-07-31T11:18:40.061Z</v>
+        <v>2026-08-01T10:49:41.888Z</v>
       </c>
     </row>
     <row r="236">
@@ -8048,7 +8048,7 @@
         <v/>
       </c>
       <c r="J236" t="str">
-        <v>2026-07-31T11:18:40.076Z</v>
+        <v>2026-08-01T10:49:41.903Z</v>
       </c>
     </row>
     <row r="237">
@@ -8074,13 +8074,13 @@
         <v>PASS</v>
       </c>
       <c r="H237">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I237" t="str">
         <v/>
       </c>
       <c r="J237" t="str">
-        <v>2026-07-31T11:18:40.091Z</v>
+        <v>2026-08-01T10:49:41.919Z</v>
       </c>
     </row>
     <row r="238">
@@ -8106,13 +8106,13 @@
         <v>PASS</v>
       </c>
       <c r="H238">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I238" t="str">
         <v/>
       </c>
       <c r="J238" t="str">
-        <v>2026-07-31T11:18:40.107Z</v>
+        <v>2026-08-01T10:49:41.935Z</v>
       </c>
     </row>
     <row r="239">
@@ -8144,7 +8144,7 @@
         <v/>
       </c>
       <c r="J239" t="str">
-        <v>2026-07-31T11:18:40.122Z</v>
+        <v>2026-08-01T10:49:41.950Z</v>
       </c>
     </row>
     <row r="240">
@@ -8176,7 +8176,7 @@
         <v/>
       </c>
       <c r="J240" t="str">
-        <v>2026-07-31T11:18:40.138Z</v>
+        <v>2026-08-01T10:49:41.966Z</v>
       </c>
     </row>
     <row r="241">
@@ -8202,13 +8202,13 @@
         <v>PASS</v>
       </c>
       <c r="H241">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I241" t="str">
         <v/>
       </c>
       <c r="J241" t="str">
-        <v>2026-07-31T11:18:40.153Z</v>
+        <v>2026-08-01T10:49:41.982Z</v>
       </c>
     </row>
     <row r="242">
@@ -8234,13 +8234,13 @@
         <v>PASS</v>
       </c>
       <c r="H242">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I242" t="str">
         <v/>
       </c>
       <c r="J242" t="str">
-        <v>2026-07-31T11:18:40.170Z</v>
+        <v>2026-08-01T10:49:41.997Z</v>
       </c>
     </row>
     <row r="243">
@@ -8272,7 +8272,7 @@
         <v/>
       </c>
       <c r="J243" t="str">
-        <v>2026-07-31T11:18:40.185Z</v>
+        <v>2026-08-01T10:49:42.012Z</v>
       </c>
     </row>
     <row r="244">
@@ -8298,13 +8298,13 @@
         <v>PASS</v>
       </c>
       <c r="H244">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I244" t="str">
         <v/>
       </c>
       <c r="J244" t="str">
-        <v>2026-07-31T11:18:40.202Z</v>
+        <v>2026-08-01T10:49:42.028Z</v>
       </c>
     </row>
     <row r="245">
@@ -8330,13 +8330,13 @@
         <v>PASS</v>
       </c>
       <c r="H245">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I245" t="str">
         <v/>
       </c>
       <c r="J245" t="str">
-        <v>2026-07-31T11:18:40.217Z</v>
+        <v>2026-08-01T10:49:42.044Z</v>
       </c>
     </row>
     <row r="246">
@@ -8362,13 +8362,13 @@
         <v>PASS</v>
       </c>
       <c r="H246">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I246" t="str">
         <v/>
       </c>
       <c r="J246" t="str">
-        <v>2026-07-31T11:18:40.233Z</v>
+        <v>2026-08-01T10:49:42.059Z</v>
       </c>
     </row>
     <row r="247">
@@ -8400,7 +8400,7 @@
         <v/>
       </c>
       <c r="J247" t="str">
-        <v>2026-07-31T11:18:40.249Z</v>
+        <v>2026-08-01T10:49:42.075Z</v>
       </c>
     </row>
     <row r="248">
@@ -8432,7 +8432,7 @@
         <v/>
       </c>
       <c r="J248" t="str">
-        <v>2026-07-31T11:18:40.265Z</v>
+        <v>2026-08-01T10:49:42.090Z</v>
       </c>
     </row>
     <row r="249">
@@ -8464,7 +8464,7 @@
         <v/>
       </c>
       <c r="J249" t="str">
-        <v>2026-07-31T11:18:40.280Z</v>
+        <v>2026-08-01T10:49:42.105Z</v>
       </c>
     </row>
     <row r="250">
@@ -8490,13 +8490,13 @@
         <v>PASS</v>
       </c>
       <c r="H250">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I250" t="str">
         <v/>
       </c>
       <c r="J250" t="str">
-        <v>2026-07-31T11:18:40.295Z</v>
+        <v>2026-08-01T10:49:42.121Z</v>
       </c>
     </row>
     <row r="251">
@@ -8528,7 +8528,7 @@
         <v/>
       </c>
       <c r="J251" t="str">
-        <v>2026-07-31T11:18:40.310Z</v>
+        <v>2026-08-01T10:49:42.136Z</v>
       </c>
     </row>
     <row r="252">
@@ -8554,13 +8554,13 @@
         <v>PASS</v>
       </c>
       <c r="H252">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I252" t="str">
         <v/>
       </c>
       <c r="J252" t="str">
-        <v>2026-07-31T11:18:40.325Z</v>
+        <v>2026-08-01T10:49:42.152Z</v>
       </c>
     </row>
     <row r="253">
@@ -8592,7 +8592,7 @@
         <v/>
       </c>
       <c r="J253" t="str">
-        <v>2026-07-31T11:18:40.340Z</v>
+        <v>2026-08-01T10:49:42.167Z</v>
       </c>
     </row>
     <row r="254">
@@ -8624,7 +8624,7 @@
         <v/>
       </c>
       <c r="J254" t="str">
-        <v>2026-07-31T11:18:40.356Z</v>
+        <v>2026-08-01T10:49:42.183Z</v>
       </c>
     </row>
     <row r="255">
@@ -8650,13 +8650,13 @@
         <v>PASS</v>
       </c>
       <c r="H255">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I255" t="str">
         <v/>
       </c>
       <c r="J255" t="str">
-        <v>2026-07-31T11:18:40.371Z</v>
+        <v>2026-08-01T10:49:42.199Z</v>
       </c>
     </row>
     <row r="256">
@@ -8682,13 +8682,13 @@
         <v>PASS</v>
       </c>
       <c r="H256">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I256" t="str">
         <v/>
       </c>
       <c r="J256" t="str">
-        <v>2026-07-31T11:18:40.387Z</v>
+        <v>2026-08-01T10:49:42.214Z</v>
       </c>
     </row>
     <row r="257">
@@ -8714,13 +8714,13 @@
         <v>PASS</v>
       </c>
       <c r="H257">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I257" t="str">
         <v/>
       </c>
       <c r="J257" t="str">
-        <v>2026-07-31T11:18:40.404Z</v>
+        <v>2026-08-01T10:49:42.230Z</v>
       </c>
     </row>
     <row r="258">
@@ -8746,13 +8746,13 @@
         <v>PASS</v>
       </c>
       <c r="H258">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I258" t="str">
         <v/>
       </c>
       <c r="J258" t="str">
-        <v>2026-07-31T11:18:40.419Z</v>
+        <v>2026-08-01T10:49:42.246Z</v>
       </c>
     </row>
     <row r="259">
@@ -8778,13 +8778,13 @@
         <v>PASS</v>
       </c>
       <c r="H259">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I259" t="str">
         <v/>
       </c>
       <c r="J259" t="str">
-        <v>2026-07-31T11:18:40.433Z</v>
+        <v>2026-08-01T10:49:42.262Z</v>
       </c>
     </row>
     <row r="260">
@@ -8816,7 +8816,7 @@
         <v/>
       </c>
       <c r="J260" t="str">
-        <v>2026-07-31T11:18:40.449Z</v>
+        <v>2026-08-01T10:49:42.277Z</v>
       </c>
     </row>
     <row r="261">
@@ -8848,7 +8848,7 @@
         <v/>
       </c>
       <c r="J261" t="str">
-        <v>2026-07-31T11:18:40.465Z</v>
+        <v>2026-08-01T10:49:42.293Z</v>
       </c>
     </row>
     <row r="262">
@@ -8880,7 +8880,7 @@
         <v/>
       </c>
       <c r="J262" t="str">
-        <v>2026-07-31T11:18:40.481Z</v>
+        <v>2026-08-01T10:49:42.308Z</v>
       </c>
     </row>
     <row r="263">
@@ -8912,7 +8912,7 @@
         <v/>
       </c>
       <c r="J263" t="str">
-        <v>2026-07-31T11:18:40.497Z</v>
+        <v>2026-08-01T10:49:42.324Z</v>
       </c>
     </row>
     <row r="264">
@@ -8944,7 +8944,7 @@
         <v/>
       </c>
       <c r="J264" t="str">
-        <v>2026-07-31T11:18:40.512Z</v>
+        <v>2026-08-01T10:49:42.339Z</v>
       </c>
     </row>
     <row r="265">
@@ -8976,7 +8976,7 @@
         <v/>
       </c>
       <c r="J265" t="str">
-        <v>2026-07-31T11:18:40.528Z</v>
+        <v>2026-08-01T10:49:42.355Z</v>
       </c>
     </row>
     <row r="266">
@@ -9002,13 +9002,13 @@
         <v>PASS</v>
       </c>
       <c r="H266">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I266" t="str">
         <v/>
       </c>
       <c r="J266" t="str">
-        <v>2026-07-31T11:18:40.543Z</v>
+        <v>2026-08-01T10:49:42.372Z</v>
       </c>
     </row>
     <row r="267">
@@ -9034,13 +9034,13 @@
         <v>PASS</v>
       </c>
       <c r="H267">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I267" t="str">
         <v/>
       </c>
       <c r="J267" t="str">
-        <v>2026-07-31T11:18:40.559Z</v>
+        <v>2026-08-01T10:49:42.386Z</v>
       </c>
     </row>
     <row r="268">
@@ -9072,7 +9072,7 @@
         <v/>
       </c>
       <c r="J268" t="str">
-        <v>2026-07-31T11:18:40.575Z</v>
+        <v>2026-08-01T10:49:42.402Z</v>
       </c>
     </row>
     <row r="269">
@@ -9098,13 +9098,13 @@
         <v>PASS</v>
       </c>
       <c r="H269">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I269" t="str">
         <v/>
       </c>
       <c r="J269" t="str">
-        <v>2026-07-31T11:18:40.591Z</v>
+        <v>2026-08-01T10:49:42.417Z</v>
       </c>
     </row>
     <row r="270">
@@ -9136,7 +9136,7 @@
         <v/>
       </c>
       <c r="J270" t="str">
-        <v>2026-07-31T11:18:40.607Z</v>
+        <v>2026-08-01T10:49:42.433Z</v>
       </c>
     </row>
     <row r="271">
@@ -9162,13 +9162,13 @@
         <v>PASS</v>
       </c>
       <c r="H271">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I271" t="str">
         <v/>
       </c>
       <c r="J271" t="str">
-        <v>2026-07-31T11:18:40.621Z</v>
+        <v>2026-08-01T10:49:42.449Z</v>
       </c>
     </row>
     <row r="272">
@@ -9194,13 +9194,13 @@
         <v>PASS</v>
       </c>
       <c r="H272">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I272" t="str">
         <v/>
       </c>
       <c r="J272" t="str">
-        <v>2026-07-31T11:18:40.637Z</v>
+        <v>2026-08-01T10:49:42.464Z</v>
       </c>
     </row>
     <row r="273">
@@ -9226,13 +9226,13 @@
         <v>PASS</v>
       </c>
       <c r="H273">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I273" t="str">
         <v/>
       </c>
       <c r="J273" t="str">
-        <v>2026-07-31T11:18:40.652Z</v>
+        <v>2026-08-01T10:49:42.480Z</v>
       </c>
     </row>
     <row r="274">
@@ -9264,7 +9264,7 @@
         <v/>
       </c>
       <c r="J274" t="str">
-        <v>2026-07-31T11:18:40.667Z</v>
+        <v>2026-08-01T10:49:42.495Z</v>
       </c>
     </row>
     <row r="275">
@@ -9290,13 +9290,13 @@
         <v>PASS</v>
       </c>
       <c r="H275">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I275" t="str">
         <v/>
       </c>
       <c r="J275" t="str">
-        <v>2026-07-31T11:18:40.682Z</v>
+        <v>2026-08-01T10:49:42.511Z</v>
       </c>
     </row>
     <row r="276">
@@ -9322,13 +9322,13 @@
         <v>PASS</v>
       </c>
       <c r="H276">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I276" t="str">
         <v/>
       </c>
       <c r="J276" t="str">
-        <v>2026-07-31T11:18:40.697Z</v>
+        <v>2026-08-01T10:49:42.525Z</v>
       </c>
     </row>
     <row r="277">
@@ -9354,13 +9354,13 @@
         <v>PASS</v>
       </c>
       <c r="H277">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I277" t="str">
         <v/>
       </c>
       <c r="J277" t="str">
-        <v>2026-07-31T11:18:40.713Z</v>
+        <v>2026-08-01T10:49:42.540Z</v>
       </c>
     </row>
     <row r="278">
@@ -9392,7 +9392,7 @@
         <v/>
       </c>
       <c r="J278" t="str">
-        <v>2026-07-31T11:18:40.728Z</v>
+        <v>2026-08-01T10:49:42.555Z</v>
       </c>
     </row>
     <row r="279">
@@ -9418,13 +9418,13 @@
         <v>PASS</v>
       </c>
       <c r="H279">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I279" t="str">
         <v/>
       </c>
       <c r="J279" t="str">
-        <v>2026-07-31T11:18:40.743Z</v>
+        <v>2026-08-01T10:49:42.571Z</v>
       </c>
     </row>
     <row r="280">
@@ -9450,13 +9450,13 @@
         <v>PASS</v>
       </c>
       <c r="H280">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I280" t="str">
         <v/>
       </c>
       <c r="J280" t="str">
-        <v>2026-07-31T11:18:40.760Z</v>
+        <v>2026-08-01T10:49:42.587Z</v>
       </c>
     </row>
     <row r="281">
@@ -9488,7 +9488,7 @@
         <v/>
       </c>
       <c r="J281" t="str">
-        <v>2026-07-31T11:18:40.776Z</v>
+        <v>2026-08-01T10:49:42.603Z</v>
       </c>
     </row>
     <row r="282">
@@ -9520,7 +9520,7 @@
         <v/>
       </c>
       <c r="J282" t="str">
-        <v>2026-07-31T11:18:40.791Z</v>
+        <v>2026-08-01T10:49:42.618Z</v>
       </c>
     </row>
     <row r="283">
@@ -9546,13 +9546,13 @@
         <v>PASS</v>
       </c>
       <c r="H283">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I283" t="str">
         <v/>
       </c>
       <c r="J283" t="str">
-        <v>2026-07-31T11:18:40.807Z</v>
+        <v>2026-08-01T10:49:42.633Z</v>
       </c>
     </row>
     <row r="284">
@@ -9584,7 +9584,7 @@
         <v/>
       </c>
       <c r="J284" t="str">
-        <v>2026-07-31T11:18:40.823Z</v>
+        <v>2026-08-01T10:49:42.649Z</v>
       </c>
     </row>
     <row r="285">
@@ -9616,7 +9616,7 @@
         <v/>
       </c>
       <c r="J285" t="str">
-        <v>2026-07-31T11:18:40.838Z</v>
+        <v>2026-08-01T10:49:42.664Z</v>
       </c>
     </row>
     <row r="286">
@@ -9642,13 +9642,13 @@
         <v>PASS</v>
       </c>
       <c r="H286">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I286" t="str">
         <v/>
       </c>
       <c r="J286" t="str">
-        <v>2026-07-31T11:18:40.854Z</v>
+        <v>2026-08-01T10:49:42.680Z</v>
       </c>
     </row>
     <row r="287">
@@ -9674,13 +9674,13 @@
         <v>PASS</v>
       </c>
       <c r="H287">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I287" t="str">
         <v/>
       </c>
       <c r="J287" t="str">
-        <v>2026-07-31T11:18:40.869Z</v>
+        <v>2026-08-01T10:49:42.696Z</v>
       </c>
     </row>
     <row r="288">
@@ -9712,7 +9712,7 @@
         <v/>
       </c>
       <c r="J288" t="str">
-        <v>2026-07-31T11:18:40.884Z</v>
+        <v>2026-08-01T10:49:42.711Z</v>
       </c>
     </row>
     <row r="289">
@@ -9744,7 +9744,7 @@
         <v/>
       </c>
       <c r="J289" t="str">
-        <v>2026-07-31T11:18:40.900Z</v>
+        <v>2026-08-01T10:49:42.727Z</v>
       </c>
     </row>
     <row r="290">
@@ -9770,13 +9770,13 @@
         <v>PASS</v>
       </c>
       <c r="H290">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I290" t="str">
         <v/>
       </c>
       <c r="J290" t="str">
-        <v>2026-07-31T11:18:40.916Z</v>
+        <v>2026-08-01T10:49:42.742Z</v>
       </c>
     </row>
     <row r="291">
@@ -9808,7 +9808,7 @@
         <v/>
       </c>
       <c r="J291" t="str">
-        <v>2026-07-31T11:18:40.931Z</v>
+        <v>2026-08-01T10:49:42.758Z</v>
       </c>
     </row>
     <row r="292">
@@ -9840,7 +9840,7 @@
         <v/>
       </c>
       <c r="J292" t="str">
-        <v>2026-07-31T11:18:40.947Z</v>
+        <v>2026-08-01T10:49:42.774Z</v>
       </c>
     </row>
     <row r="293">
@@ -9872,7 +9872,7 @@
         <v/>
       </c>
       <c r="J293" t="str">
-        <v>2026-07-31T11:18:40.962Z</v>
+        <v>2026-08-01T10:49:42.789Z</v>
       </c>
     </row>
     <row r="294">
@@ -9898,13 +9898,13 @@
         <v>PASS</v>
       </c>
       <c r="H294">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I294" t="str">
         <v/>
       </c>
       <c r="J294" t="str">
-        <v>2026-07-31T11:18:40.977Z</v>
+        <v>2026-08-01T10:49:42.805Z</v>
       </c>
     </row>
     <row r="295">
@@ -9930,13 +9930,13 @@
         <v>PASS</v>
       </c>
       <c r="H295">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I295" t="str">
         <v/>
       </c>
       <c r="J295" t="str">
-        <v>2026-07-31T11:18:40.993Z</v>
+        <v>2026-08-01T10:49:42.820Z</v>
       </c>
     </row>
     <row r="296">
@@ -9962,13 +9962,13 @@
         <v>PASS</v>
       </c>
       <c r="H296">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I296" t="str">
         <v/>
       </c>
       <c r="J296" t="str">
-        <v>2026-07-31T11:18:41.009Z</v>
+        <v>2026-08-01T10:49:42.835Z</v>
       </c>
     </row>
     <row r="297">
@@ -9994,13 +9994,13 @@
         <v>PASS</v>
       </c>
       <c r="H297">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I297" t="str">
         <v/>
       </c>
       <c r="J297" t="str">
-        <v>2026-07-31T11:18:41.023Z</v>
+        <v>2026-08-01T10:49:42.851Z</v>
       </c>
     </row>
     <row r="298">
@@ -10032,7 +10032,7 @@
         <v/>
       </c>
       <c r="J298" t="str">
-        <v>2026-07-31T11:18:41.039Z</v>
+        <v>2026-08-01T10:49:42.867Z</v>
       </c>
     </row>
     <row r="299">
@@ -10058,13 +10058,13 @@
         <v>PASS</v>
       </c>
       <c r="H299">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I299" t="str">
         <v/>
       </c>
       <c r="J299" t="str">
-        <v>2026-07-31T11:18:41.054Z</v>
+        <v>2026-08-01T10:49:42.883Z</v>
       </c>
     </row>
     <row r="300">
@@ -10090,13 +10090,13 @@
         <v>PASS</v>
       </c>
       <c r="H300">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I300" t="str">
         <v/>
       </c>
       <c r="J300" t="str">
-        <v>2026-07-31T11:18:41.070Z</v>
+        <v>2026-08-01T10:49:42.898Z</v>
       </c>
     </row>
     <row r="301">
@@ -10122,13 +10122,13 @@
         <v>PASS</v>
       </c>
       <c r="H301">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I301" t="str">
         <v/>
       </c>
       <c r="J301" t="str">
-        <v>2026-07-31T11:18:41.086Z</v>
+        <v>2026-08-01T10:49:42.913Z</v>
       </c>
     </row>
     <row r="302">
@@ -10154,13 +10154,13 @@
         <v>PASS</v>
       </c>
       <c r="H302">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I302" t="str">
         <v/>
       </c>
       <c r="J302" t="str">
-        <v>2026-07-31T11:18:41.101Z</v>
+        <v>2026-08-01T10:49:42.928Z</v>
       </c>
     </row>
     <row r="303">
@@ -10192,7 +10192,7 @@
         <v/>
       </c>
       <c r="J303" t="str">
-        <v>2026-07-31T11:18:41.117Z</v>
+        <v>2026-08-01T10:49:42.944Z</v>
       </c>
     </row>
     <row r="304">
@@ -10218,13 +10218,13 @@
         <v>PASS</v>
       </c>
       <c r="H304">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I304" t="str">
         <v/>
       </c>
       <c r="J304" t="str">
-        <v>2026-07-31T11:18:41.132Z</v>
+        <v>2026-08-01T10:49:42.960Z</v>
       </c>
     </row>
     <row r="305">
@@ -10250,13 +10250,13 @@
         <v>PASS</v>
       </c>
       <c r="H305">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I305" t="str">
         <v/>
       </c>
       <c r="J305" t="str">
-        <v>2026-07-31T11:18:41.148Z</v>
+        <v>2026-08-01T10:49:42.975Z</v>
       </c>
     </row>
     <row r="306">
@@ -10282,13 +10282,13 @@
         <v>PASS</v>
       </c>
       <c r="H306">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I306" t="str">
         <v/>
       </c>
       <c r="J306" t="str">
-        <v>2026-07-31T11:18:41.163Z</v>
+        <v>2026-08-01T10:49:42.991Z</v>
       </c>
     </row>
     <row r="307">
@@ -10320,7 +10320,7 @@
         <v/>
       </c>
       <c r="J307" t="str">
-        <v>2026-07-31T11:18:41.179Z</v>
+        <v>2026-08-01T10:49:43.007Z</v>
       </c>
     </row>
     <row r="308">
@@ -10346,13 +10346,13 @@
         <v>PASS</v>
       </c>
       <c r="H308">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I308" t="str">
         <v/>
       </c>
       <c r="J308" t="str">
-        <v>2026-07-31T11:18:41.194Z</v>
+        <v>2026-08-01T10:49:43.023Z</v>
       </c>
     </row>
     <row r="309">
@@ -10378,13 +10378,13 @@
         <v>PASS</v>
       </c>
       <c r="H309">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I309" t="str">
         <v/>
       </c>
       <c r="J309" t="str">
-        <v>2026-07-31T11:18:41.209Z</v>
+        <v>2026-08-01T10:49:43.039Z</v>
       </c>
     </row>
     <row r="310">
@@ -10416,7 +10416,7 @@
         <v/>
       </c>
       <c r="J310" t="str">
-        <v>2026-07-31T11:18:41.224Z</v>
+        <v>2026-08-01T10:49:43.055Z</v>
       </c>
     </row>
     <row r="311">
@@ -10448,7 +10448,7 @@
         <v/>
       </c>
       <c r="J311" t="str">
-        <v>2026-07-31T11:18:41.239Z</v>
+        <v>2026-08-01T10:49:43.070Z</v>
       </c>
     </row>
     <row r="312">
@@ -10474,13 +10474,13 @@
         <v>PASS</v>
       </c>
       <c r="H312">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I312" t="str">
         <v/>
       </c>
       <c r="J312" t="str">
-        <v>2026-07-31T11:18:41.255Z</v>
+        <v>2026-08-01T10:49:43.086Z</v>
       </c>
     </row>
     <row r="313">
@@ -10512,7 +10512,7 @@
         <v/>
       </c>
       <c r="J313" t="str">
-        <v>2026-07-31T11:18:41.270Z</v>
+        <v>2026-08-01T10:49:43.101Z</v>
       </c>
     </row>
     <row r="314">
@@ -10544,7 +10544,7 @@
         <v/>
       </c>
       <c r="J314" t="str">
-        <v>2026-07-31T11:18:41.286Z</v>
+        <v>2026-08-01T10:49:43.117Z</v>
       </c>
     </row>
     <row r="315">
@@ -10570,13 +10570,13 @@
         <v>PASS</v>
       </c>
       <c r="H315">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I315" t="str">
         <v/>
       </c>
       <c r="J315" t="str">
-        <v>2026-07-31T11:18:41.302Z</v>
+        <v>2026-08-01T10:49:43.134Z</v>
       </c>
     </row>
     <row r="316">
@@ -10608,7 +10608,7 @@
         <v/>
       </c>
       <c r="J316" t="str">
-        <v>2026-07-31T11:18:41.317Z</v>
+        <v>2026-08-01T10:49:43.150Z</v>
       </c>
     </row>
     <row r="317">
@@ -10634,13 +10634,13 @@
         <v>PASS</v>
       </c>
       <c r="H317">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I317" t="str">
         <v/>
       </c>
       <c r="J317" t="str">
-        <v>2026-07-31T11:18:41.332Z</v>
+        <v>2026-08-01T10:49:43.164Z</v>
       </c>
     </row>
     <row r="318">
@@ -10672,7 +10672,7 @@
         <v/>
       </c>
       <c r="J318" t="str">
-        <v>2026-07-31T11:18:41.348Z</v>
+        <v>2026-08-01T10:49:43.180Z</v>
       </c>
     </row>
     <row r="319">
@@ -10698,13 +10698,13 @@
         <v>PASS</v>
       </c>
       <c r="H319">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I319" t="str">
         <v/>
       </c>
       <c r="J319" t="str">
-        <v>2026-07-31T11:18:41.363Z</v>
+        <v>2026-08-01T10:49:43.196Z</v>
       </c>
     </row>
     <row r="320">
@@ -10730,13 +10730,13 @@
         <v>PASS</v>
       </c>
       <c r="H320">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I320" t="str">
         <v/>
       </c>
       <c r="J320" t="str">
-        <v>2026-07-31T11:18:41.379Z</v>
+        <v>2026-08-01T10:49:43.211Z</v>
       </c>
     </row>
     <row r="321">
@@ -10768,7 +10768,7 @@
         <v/>
       </c>
       <c r="J321" t="str">
-        <v>2026-07-31T11:18:41.394Z</v>
+        <v>2026-08-01T10:49:43.226Z</v>
       </c>
     </row>
     <row r="322">
@@ -10800,7 +10800,7 @@
         <v/>
       </c>
       <c r="J322" t="str">
-        <v>2026-07-31T11:18:41.410Z</v>
+        <v>2026-08-01T10:49:43.242Z</v>
       </c>
     </row>
     <row r="323">
@@ -10826,13 +10826,13 @@
         <v>PASS</v>
       </c>
       <c r="H323">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I323" t="str">
         <v/>
       </c>
       <c r="J323" t="str">
-        <v>2026-07-31T11:18:41.426Z</v>
+        <v>2026-08-01T10:49:43.257Z</v>
       </c>
     </row>
     <row r="324">
@@ -10858,13 +10858,13 @@
         <v>PASS</v>
       </c>
       <c r="H324">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I324" t="str">
         <v/>
       </c>
       <c r="J324" t="str">
-        <v>2026-07-31T11:18:41.441Z</v>
+        <v>2026-08-01T10:49:43.273Z</v>
       </c>
     </row>
     <row r="325">
@@ -10896,7 +10896,7 @@
         <v/>
       </c>
       <c r="J325" t="str">
-        <v>2026-07-31T11:18:41.456Z</v>
+        <v>2026-08-01T10:49:43.289Z</v>
       </c>
     </row>
     <row r="326">
@@ -10928,7 +10928,7 @@
         <v/>
       </c>
       <c r="J326" t="str">
-        <v>2026-07-31T11:18:41.472Z</v>
+        <v>2026-08-01T10:49:43.305Z</v>
       </c>
     </row>
     <row r="327">
@@ -10954,13 +10954,13 @@
         <v>PASS</v>
       </c>
       <c r="H327">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I327" t="str">
         <v/>
       </c>
       <c r="J327" t="str">
-        <v>2026-07-31T11:18:41.488Z</v>
+        <v>2026-08-01T10:49:43.320Z</v>
       </c>
     </row>
     <row r="328">
@@ -10992,7 +10992,7 @@
         <v/>
       </c>
       <c r="J328" t="str">
-        <v>2026-07-31T11:18:41.504Z</v>
+        <v>2026-08-01T10:49:43.336Z</v>
       </c>
     </row>
     <row r="329">
@@ -11018,13 +11018,13 @@
         <v>PASS</v>
       </c>
       <c r="H329">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I329" t="str">
         <v/>
       </c>
       <c r="J329" t="str">
-        <v>2026-07-31T11:18:41.519Z</v>
+        <v>2026-08-01T10:49:43.352Z</v>
       </c>
     </row>
     <row r="330">
@@ -11050,13 +11050,13 @@
         <v>PASS</v>
       </c>
       <c r="H330">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I330" t="str">
         <v/>
       </c>
       <c r="J330" t="str">
-        <v>2026-07-31T11:18:41.536Z</v>
+        <v>2026-08-01T10:49:43.368Z</v>
       </c>
     </row>
     <row r="331">
@@ -11088,7 +11088,7 @@
         <v/>
       </c>
       <c r="J331" t="str">
-        <v>2026-07-31T11:18:41.551Z</v>
+        <v>2026-08-01T10:49:43.383Z</v>
       </c>
     </row>
     <row r="332">
@@ -11114,13 +11114,13 @@
         <v>PASS</v>
       </c>
       <c r="H332">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I332" t="str">
         <v/>
       </c>
       <c r="J332" t="str">
-        <v>2026-07-31T11:18:41.566Z</v>
+        <v>2026-08-01T10:49:43.399Z</v>
       </c>
     </row>
     <row r="333">
@@ -11152,7 +11152,7 @@
         <v/>
       </c>
       <c r="J333" t="str">
-        <v>2026-07-31T11:18:41.582Z</v>
+        <v>2026-08-01T10:49:43.414Z</v>
       </c>
     </row>
     <row r="334">
@@ -11178,13 +11178,13 @@
         <v>PASS</v>
       </c>
       <c r="H334">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I334" t="str">
         <v/>
       </c>
       <c r="J334" t="str">
-        <v>2026-07-31T11:18:41.597Z</v>
+        <v>2026-08-01T10:49:43.430Z</v>
       </c>
     </row>
     <row r="335">
@@ -11210,13 +11210,13 @@
         <v>PASS</v>
       </c>
       <c r="H335">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I335" t="str">
         <v/>
       </c>
       <c r="J335" t="str">
-        <v>2026-07-31T11:18:41.612Z</v>
+        <v>2026-08-01T10:49:43.446Z</v>
       </c>
     </row>
     <row r="336">
@@ -11242,13 +11242,13 @@
         <v>PASS</v>
       </c>
       <c r="H336">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I336" t="str">
         <v/>
       </c>
       <c r="J336" t="str">
-        <v>2026-07-31T11:18:41.628Z</v>
+        <v>2026-08-01T10:49:43.462Z</v>
       </c>
     </row>
     <row r="337">
@@ -11280,7 +11280,7 @@
         <v/>
       </c>
       <c r="J337" t="str">
-        <v>2026-07-31T11:18:41.644Z</v>
+        <v>2026-08-01T10:49:43.477Z</v>
       </c>
     </row>
     <row r="338">
@@ -11312,7 +11312,7 @@
         <v/>
       </c>
       <c r="J338" t="str">
-        <v>2026-07-31T11:18:41.659Z</v>
+        <v>2026-08-01T10:49:43.492Z</v>
       </c>
     </row>
     <row r="339">
@@ -11344,7 +11344,7 @@
         <v/>
       </c>
       <c r="J339" t="str">
-        <v>2026-07-31T11:18:41.675Z</v>
+        <v>2026-08-01T10:49:43.508Z</v>
       </c>
     </row>
     <row r="340">
@@ -11370,13 +11370,13 @@
         <v>PASS</v>
       </c>
       <c r="H340">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I340" t="str">
         <v/>
       </c>
       <c r="J340" t="str">
-        <v>2026-07-31T11:18:41.692Z</v>
+        <v>2026-08-01T10:49:43.523Z</v>
       </c>
     </row>
     <row r="341">
@@ -11402,13 +11402,13 @@
         <v>PASS</v>
       </c>
       <c r="H341">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I341" t="str">
         <v/>
       </c>
       <c r="J341" t="str">
-        <v>2026-07-31T11:18:41.707Z</v>
+        <v>2026-08-01T10:49:43.539Z</v>
       </c>
     </row>
     <row r="342">
@@ -11440,7 +11440,7 @@
         <v/>
       </c>
       <c r="J342" t="str">
-        <v>2026-07-31T11:18:41.724Z</v>
+        <v>2026-08-01T10:49:43.555Z</v>
       </c>
     </row>
     <row r="343">
@@ -11466,13 +11466,13 @@
         <v>PASS</v>
       </c>
       <c r="H343">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I343" t="str">
         <v/>
       </c>
       <c r="J343" t="str">
-        <v>2026-07-31T11:18:41.738Z</v>
+        <v>2026-08-01T10:49:43.571Z</v>
       </c>
     </row>
     <row r="344">
@@ -11504,7 +11504,7 @@
         <v/>
       </c>
       <c r="J344" t="str">
-        <v>2026-07-31T11:18:41.754Z</v>
+        <v>2026-08-01T10:49:43.587Z</v>
       </c>
     </row>
     <row r="345">
@@ -11530,13 +11530,13 @@
         <v>PASS</v>
       </c>
       <c r="H345">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I345" t="str">
         <v/>
       </c>
       <c r="J345" t="str">
-        <v>2026-07-31T11:18:41.770Z</v>
+        <v>2026-08-01T10:49:43.602Z</v>
       </c>
     </row>
     <row r="346">
@@ -11562,13 +11562,13 @@
         <v>PASS</v>
       </c>
       <c r="H346">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I346" t="str">
         <v/>
       </c>
       <c r="J346" t="str">
-        <v>2026-07-31T11:18:41.785Z</v>
+        <v>2026-08-01T10:49:43.618Z</v>
       </c>
     </row>
     <row r="347">
@@ -11594,13 +11594,13 @@
         <v>PASS</v>
       </c>
       <c r="H347">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I347" t="str">
         <v/>
       </c>
       <c r="J347" t="str">
-        <v>2026-07-31T11:18:41.801Z</v>
+        <v>2026-08-01T10:49:43.633Z</v>
       </c>
     </row>
     <row r="348">
@@ -11632,7 +11632,7 @@
         <v/>
       </c>
       <c r="J348" t="str">
-        <v>2026-07-31T11:18:41.817Z</v>
+        <v>2026-08-01T10:49:43.649Z</v>
       </c>
     </row>
     <row r="349">
@@ -11664,7 +11664,7 @@
         <v/>
       </c>
       <c r="J349" t="str">
-        <v>2026-07-31T11:18:41.833Z</v>
+        <v>2026-08-01T10:49:43.665Z</v>
       </c>
     </row>
     <row r="350">
@@ -11696,7 +11696,7 @@
         <v/>
       </c>
       <c r="J350" t="str">
-        <v>2026-07-31T11:18:41.849Z</v>
+        <v>2026-08-01T10:49:43.681Z</v>
       </c>
     </row>
     <row r="351">
@@ -11722,13 +11722,13 @@
         <v>PASS</v>
       </c>
       <c r="H351">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I351" t="str">
         <v/>
       </c>
       <c r="J351" t="str">
-        <v>2026-07-31T11:18:41.865Z</v>
+        <v>2026-08-01T10:49:43.696Z</v>
       </c>
     </row>
     <row r="352">
@@ -11754,13 +11754,13 @@
         <v>PASS</v>
       </c>
       <c r="H352">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I352" t="str">
         <v/>
       </c>
       <c r="J352" t="str">
-        <v>2026-07-31T11:18:41.880Z</v>
+        <v>2026-08-01T10:49:43.712Z</v>
       </c>
     </row>
     <row r="353">
@@ -11786,13 +11786,13 @@
         <v>PASS</v>
       </c>
       <c r="H353">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I353" t="str">
         <v/>
       </c>
       <c r="J353" t="str">
-        <v>2026-07-31T11:18:41.895Z</v>
+        <v>2026-08-01T10:49:43.728Z</v>
       </c>
     </row>
     <row r="354">
@@ -11818,13 +11818,13 @@
         <v>PASS</v>
       </c>
       <c r="H354">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I354" t="str">
         <v/>
       </c>
       <c r="J354" t="str">
-        <v>2026-07-31T11:18:41.912Z</v>
+        <v>2026-08-01T10:49:43.743Z</v>
       </c>
     </row>
     <row r="355">
@@ -11850,13 +11850,13 @@
         <v>PASS</v>
       </c>
       <c r="H355">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I355" t="str">
         <v/>
       </c>
       <c r="J355" t="str">
-        <v>2026-07-31T11:18:41.926Z</v>
+        <v>2026-08-01T10:49:43.759Z</v>
       </c>
     </row>
     <row r="356">
@@ -11882,13 +11882,13 @@
         <v>PASS</v>
       </c>
       <c r="H356">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I356" t="str">
         <v/>
       </c>
       <c r="J356" t="str">
-        <v>2026-07-31T11:18:41.943Z</v>
+        <v>2026-08-01T10:49:43.774Z</v>
       </c>
     </row>
     <row r="357">
@@ -11914,13 +11914,13 @@
         <v>PASS</v>
       </c>
       <c r="H357">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I357" t="str">
         <v/>
       </c>
       <c r="J357" t="str">
-        <v>2026-07-31T11:18:41.958Z</v>
+        <v>2026-08-01T10:49:43.790Z</v>
       </c>
     </row>
     <row r="358">
@@ -11952,7 +11952,7 @@
         <v/>
       </c>
       <c r="J358" t="str">
-        <v>2026-07-31T11:18:41.974Z</v>
+        <v>2026-08-01T10:49:43.806Z</v>
       </c>
     </row>
     <row r="359">
@@ -11984,7 +11984,7 @@
         <v/>
       </c>
       <c r="J359" t="str">
-        <v>2026-07-31T11:18:41.989Z</v>
+        <v>2026-08-01T10:49:43.821Z</v>
       </c>
     </row>
     <row r="360">
@@ -12016,7 +12016,7 @@
         <v/>
       </c>
       <c r="J360" t="str">
-        <v>2026-07-31T11:18:42.005Z</v>
+        <v>2026-08-01T10:49:43.837Z</v>
       </c>
     </row>
     <row r="361">
@@ -12048,7 +12048,7 @@
         <v/>
       </c>
       <c r="J361" t="str">
-        <v>2026-07-31T11:18:42.020Z</v>
+        <v>2026-08-01T10:49:43.852Z</v>
       </c>
     </row>
     <row r="362">
@@ -12074,13 +12074,13 @@
         <v>PASS</v>
       </c>
       <c r="H362">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I362" t="str">
         <v/>
       </c>
       <c r="J362" t="str">
-        <v>2026-07-31T11:18:42.036Z</v>
+        <v>2026-08-01T10:49:43.868Z</v>
       </c>
     </row>
     <row r="363">
@@ -12112,7 +12112,7 @@
         <v/>
       </c>
       <c r="J363" t="str">
-        <v>2026-07-31T11:18:42.052Z</v>
+        <v>2026-08-01T10:49:43.884Z</v>
       </c>
     </row>
     <row r="364">
@@ -12138,13 +12138,13 @@
         <v>PASS</v>
       </c>
       <c r="H364">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I364" t="str">
         <v/>
       </c>
       <c r="J364" t="str">
-        <v>2026-07-31T11:18:42.068Z</v>
+        <v>2026-08-01T10:49:43.899Z</v>
       </c>
     </row>
     <row r="365">
@@ -12170,13 +12170,13 @@
         <v>PASS</v>
       </c>
       <c r="H365">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I365" t="str">
         <v/>
       </c>
       <c r="J365" t="str">
-        <v>2026-07-31T11:18:42.083Z</v>
+        <v>2026-08-01T10:49:43.915Z</v>
       </c>
     </row>
     <row r="366">
@@ -12202,13 +12202,13 @@
         <v>PASS</v>
       </c>
       <c r="H366">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I366" t="str">
         <v/>
       </c>
       <c r="J366" t="str">
-        <v>2026-07-31T11:18:42.098Z</v>
+        <v>2026-08-01T10:49:43.931Z</v>
       </c>
     </row>
     <row r="367">
@@ -12240,7 +12240,7 @@
         <v/>
       </c>
       <c r="J367" t="str">
-        <v>2026-07-31T11:18:42.114Z</v>
+        <v>2026-08-01T10:49:43.947Z</v>
       </c>
     </row>
     <row r="368">
@@ -12266,13 +12266,13 @@
         <v>PASS</v>
       </c>
       <c r="H368">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I368" t="str">
         <v/>
       </c>
       <c r="J368" t="str">
-        <v>2026-07-31T11:18:42.128Z</v>
+        <v>2026-08-01T10:49:43.962Z</v>
       </c>
     </row>
     <row r="369">
@@ -12304,7 +12304,7 @@
         <v/>
       </c>
       <c r="J369" t="str">
-        <v>2026-07-31T11:18:42.144Z</v>
+        <v>2026-08-01T10:49:43.977Z</v>
       </c>
     </row>
     <row r="370">
@@ -12336,7 +12336,7 @@
         <v/>
       </c>
       <c r="J370" t="str">
-        <v>2026-07-31T11:18:42.160Z</v>
+        <v>2026-08-01T10:49:43.993Z</v>
       </c>
     </row>
     <row r="371">
@@ -12362,13 +12362,13 @@
         <v>PASS</v>
       </c>
       <c r="H371">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I371" t="str">
         <v/>
       </c>
       <c r="J371" t="str">
-        <v>2026-07-31T11:18:42.176Z</v>
+        <v>2026-08-01T10:49:44.008Z</v>
       </c>
     </row>
     <row r="372">
@@ -12394,13 +12394,13 @@
         <v>PASS</v>
       </c>
       <c r="H372">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I372" t="str">
         <v/>
       </c>
       <c r="J372" t="str">
-        <v>2026-07-31T11:18:42.192Z</v>
+        <v>2026-08-01T10:49:44.023Z</v>
       </c>
     </row>
     <row r="373">
@@ -12426,13 +12426,13 @@
         <v>PASS</v>
       </c>
       <c r="H373">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I373" t="str">
         <v/>
       </c>
       <c r="J373" t="str">
-        <v>2026-07-31T11:18:42.207Z</v>
+        <v>2026-08-01T10:49:44.039Z</v>
       </c>
     </row>
     <row r="374">
@@ -12464,7 +12464,7 @@
         <v/>
       </c>
       <c r="J374" t="str">
-        <v>2026-07-31T11:18:42.222Z</v>
+        <v>2026-08-01T10:49:44.054Z</v>
       </c>
     </row>
     <row r="375">
@@ -12496,7 +12496,7 @@
         <v/>
       </c>
       <c r="J375" t="str">
-        <v>2026-07-31T11:18:42.238Z</v>
+        <v>2026-08-01T10:49:44.070Z</v>
       </c>
     </row>
     <row r="376">
@@ -12522,13 +12522,13 @@
         <v>PASS</v>
       </c>
       <c r="H376">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I376" t="str">
         <v/>
       </c>
       <c r="J376" t="str">
-        <v>2026-07-31T11:18:42.254Z</v>
+        <v>2026-08-01T10:49:44.085Z</v>
       </c>
     </row>
     <row r="377">
@@ -12560,7 +12560,7 @@
         <v/>
       </c>
       <c r="J377" t="str">
-        <v>2026-07-31T11:18:42.270Z</v>
+        <v>2026-08-01T10:49:44.101Z</v>
       </c>
     </row>
     <row r="378">
@@ -12592,7 +12592,7 @@
         <v/>
       </c>
       <c r="J378" t="str">
-        <v>2026-07-31T11:18:42.285Z</v>
+        <v>2026-08-01T10:49:44.116Z</v>
       </c>
     </row>
     <row r="379">
@@ -12624,7 +12624,7 @@
         <v/>
       </c>
       <c r="J379" t="str">
-        <v>2026-07-31T11:18:42.301Z</v>
+        <v>2026-08-01T10:49:44.132Z</v>
       </c>
     </row>
     <row r="380">
@@ -12656,7 +12656,7 @@
         <v/>
       </c>
       <c r="J380" t="str">
-        <v>2026-07-31T11:18:42.316Z</v>
+        <v>2026-08-01T10:49:44.147Z</v>
       </c>
     </row>
     <row r="381">
@@ -12688,7 +12688,7 @@
         <v/>
       </c>
       <c r="J381" t="str">
-        <v>2026-07-31T11:18:42.332Z</v>
+        <v>2026-08-01T10:49:44.163Z</v>
       </c>
     </row>
     <row r="382">
@@ -12714,13 +12714,13 @@
         <v>PASS</v>
       </c>
       <c r="H382">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I382" t="str">
         <v/>
       </c>
       <c r="J382" t="str">
-        <v>2026-07-31T11:18:42.348Z</v>
+        <v>2026-08-01T10:49:44.178Z</v>
       </c>
     </row>
     <row r="383">
@@ -12752,7 +12752,7 @@
         <v/>
       </c>
       <c r="J383" t="str">
-        <v>2026-07-31T11:18:42.364Z</v>
+        <v>2026-08-01T10:49:44.194Z</v>
       </c>
     </row>
     <row r="384">
@@ -12778,13 +12778,13 @@
         <v>PASS</v>
       </c>
       <c r="H384">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I384" t="str">
         <v/>
       </c>
       <c r="J384" t="str">
-        <v>2026-07-31T11:18:42.379Z</v>
+        <v>2026-08-01T10:49:44.210Z</v>
       </c>
     </row>
     <row r="385">
@@ -12810,13 +12810,13 @@
         <v>PASS</v>
       </c>
       <c r="H385">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I385" t="str">
         <v/>
       </c>
       <c r="J385" t="str">
-        <v>2026-07-31T11:18:42.395Z</v>
+        <v>2026-08-01T10:49:44.225Z</v>
       </c>
     </row>
     <row r="386">
@@ -12842,13 +12842,13 @@
         <v>PASS</v>
       </c>
       <c r="H386">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I386" t="str">
         <v/>
       </c>
       <c r="J386" t="str">
-        <v>2026-07-31T11:18:42.411Z</v>
+        <v>2026-08-01T10:49:44.240Z</v>
       </c>
     </row>
     <row r="387">
@@ -12880,7 +12880,7 @@
         <v/>
       </c>
       <c r="J387" t="str">
-        <v>2026-07-31T11:18:42.426Z</v>
+        <v>2026-08-01T10:49:44.255Z</v>
       </c>
     </row>
     <row r="388">
@@ -12912,7 +12912,7 @@
         <v/>
       </c>
       <c r="J388" t="str">
-        <v>2026-07-31T11:18:42.442Z</v>
+        <v>2026-08-01T10:49:44.271Z</v>
       </c>
     </row>
     <row r="389">
@@ -12938,13 +12938,13 @@
         <v>PASS</v>
       </c>
       <c r="H389">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I389" t="str">
         <v/>
       </c>
       <c r="J389" t="str">
-        <v>2026-07-31T11:18:42.458Z</v>
+        <v>2026-08-01T10:49:44.286Z</v>
       </c>
     </row>
     <row r="390">
@@ -12976,7 +12976,7 @@
         <v/>
       </c>
       <c r="J390" t="str">
-        <v>2026-07-31T11:18:42.474Z</v>
+        <v>2026-08-01T10:49:44.302Z</v>
       </c>
     </row>
     <row r="391">
@@ -13002,13 +13002,13 @@
         <v>PASS</v>
       </c>
       <c r="H391">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I391" t="str">
         <v/>
       </c>
       <c r="J391" t="str">
-        <v>2026-07-31T11:18:42.489Z</v>
+        <v>2026-08-01T10:49:44.318Z</v>
       </c>
     </row>
     <row r="392">
@@ -13040,7 +13040,7 @@
         <v/>
       </c>
       <c r="J392" t="str">
-        <v>2026-07-31T11:18:42.505Z</v>
+        <v>2026-08-01T10:49:44.334Z</v>
       </c>
     </row>
     <row r="393">
@@ -13066,13 +13066,13 @@
         <v>PASS</v>
       </c>
       <c r="H393">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I393" t="str">
         <v/>
       </c>
       <c r="J393" t="str">
-        <v>2026-07-31T11:18:42.521Z</v>
+        <v>2026-08-01T10:49:44.348Z</v>
       </c>
     </row>
     <row r="394">
@@ -13098,13 +13098,13 @@
         <v>PASS</v>
       </c>
       <c r="H394">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I394" t="str">
         <v/>
       </c>
       <c r="J394" t="str">
-        <v>2026-07-31T11:18:42.537Z</v>
+        <v>2026-08-01T10:49:44.363Z</v>
       </c>
     </row>
     <row r="395">
@@ -13130,13 +13130,13 @@
         <v>PASS</v>
       </c>
       <c r="H395">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I395" t="str">
         <v/>
       </c>
       <c r="J395" t="str">
-        <v>2026-07-31T11:18:42.553Z</v>
+        <v>2026-08-01T10:49:44.378Z</v>
       </c>
     </row>
     <row r="396">
@@ -13162,13 +13162,13 @@
         <v>PASS</v>
       </c>
       <c r="H396">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I396" t="str">
         <v/>
       </c>
       <c r="J396" t="str">
-        <v>2026-07-31T11:18:42.568Z</v>
+        <v>2026-08-01T10:49:44.394Z</v>
       </c>
     </row>
     <row r="397">
@@ -13200,7 +13200,7 @@
         <v/>
       </c>
       <c r="J397" t="str">
-        <v>2026-07-31T11:18:42.583Z</v>
+        <v>2026-08-01T10:49:44.409Z</v>
       </c>
     </row>
     <row r="398">
@@ -13232,7 +13232,7 @@
         <v/>
       </c>
       <c r="J398" t="str">
-        <v>2026-07-31T11:18:42.599Z</v>
+        <v>2026-08-01T10:49:44.425Z</v>
       </c>
     </row>
     <row r="399">
@@ -13258,13 +13258,13 @@
         <v>PASS</v>
       </c>
       <c r="H399">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I399" t="str">
         <v/>
       </c>
       <c r="J399" t="str">
-        <v>2026-07-31T11:18:42.615Z</v>
+        <v>2026-08-01T10:49:44.440Z</v>
       </c>
     </row>
     <row r="400">
@@ -13296,7 +13296,7 @@
         <v/>
       </c>
       <c r="J400" t="str">
-        <v>2026-07-31T11:18:42.631Z</v>
+        <v>2026-08-01T10:49:44.456Z</v>
       </c>
     </row>
     <row r="401">
@@ -13322,13 +13322,13 @@
         <v>PASS</v>
       </c>
       <c r="H401">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I401" t="str">
         <v/>
       </c>
       <c r="J401" t="str">
-        <v>2026-07-31T11:18:42.647Z</v>
+        <v>2026-08-01T10:49:44.471Z</v>
       </c>
     </row>
   </sheetData>

--- a/appium-tests/reports/appium-mobile-test-report-400.xlsx
+++ b/appium-tests/reports/appium-mobile-test-report-400.xlsx
@@ -473,7 +473,7 @@
         <v>Generated At</v>
       </c>
       <c r="B9" t="str">
-        <v>1/8/2026, 4:19:44 pm</v>
+        <v>8/8/2026, 12:43:24 pm</v>
       </c>
     </row>
   </sheetData>
@@ -554,13 +554,13 @@
         <v>PASS</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I2" t="str">
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>2026-08-01T10:49:38.258Z</v>
+        <v>2026-08-08T07:13:18.018Z</v>
       </c>
     </row>
     <row r="3">
@@ -586,13 +586,13 @@
         <v>PASS</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I3" t="str">
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>2026-08-01T10:49:38.275Z</v>
+        <v>2026-08-08T07:13:18.023Z</v>
       </c>
     </row>
     <row r="4">
@@ -618,13 +618,13 @@
         <v>PASS</v>
       </c>
       <c r="H4">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>2026-08-01T10:49:38.290Z</v>
+        <v>2026-08-08T07:13:18.028Z</v>
       </c>
     </row>
     <row r="5">
@@ -650,13 +650,13 @@
         <v>PASS</v>
       </c>
       <c r="H5">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I5" t="str">
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>2026-08-01T10:49:38.306Z</v>
+        <v>2026-08-08T07:13:18.040Z</v>
       </c>
     </row>
     <row r="6">
@@ -682,13 +682,13 @@
         <v>PASS</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I6" t="str">
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>2026-08-01T10:49:38.322Z</v>
+        <v>2026-08-08T07:13:18.059Z</v>
       </c>
     </row>
     <row r="7">
@@ -714,13 +714,13 @@
         <v>PASS</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I7" t="str">
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>2026-08-01T10:49:38.338Z</v>
+        <v>2026-08-08T07:13:18.074Z</v>
       </c>
     </row>
     <row r="8">
@@ -746,13 +746,13 @@
         <v>PASS</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8" t="str">
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>2026-08-01T10:49:38.353Z</v>
+        <v>2026-08-08T07:13:18.090Z</v>
       </c>
     </row>
     <row r="9">
@@ -784,7 +784,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>2026-08-01T10:49:38.369Z</v>
+        <v>2026-08-08T07:13:18.106Z</v>
       </c>
     </row>
     <row r="10">
@@ -816,7 +816,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>2026-08-01T10:49:38.385Z</v>
+        <v>2026-08-08T07:13:18.122Z</v>
       </c>
     </row>
     <row r="11">
@@ -848,7 +848,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>2026-08-01T10:49:38.400Z</v>
+        <v>2026-08-08T07:13:18.137Z</v>
       </c>
     </row>
     <row r="12">
@@ -874,13 +874,13 @@
         <v>PASS</v>
       </c>
       <c r="H12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I12" t="str">
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>2026-08-01T10:49:38.415Z</v>
+        <v>2026-08-08T07:13:18.153Z</v>
       </c>
     </row>
     <row r="13">
@@ -906,13 +906,13 @@
         <v>PASS</v>
       </c>
       <c r="H13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I13" t="str">
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>2026-08-01T10:49:38.432Z</v>
+        <v>2026-08-08T07:13:18.169Z</v>
       </c>
     </row>
     <row r="14">
@@ -938,13 +938,13 @@
         <v>PASS</v>
       </c>
       <c r="H14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I14" t="str">
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>2026-08-01T10:49:38.448Z</v>
+        <v>2026-08-08T07:13:18.184Z</v>
       </c>
     </row>
     <row r="15">
@@ -970,13 +970,13 @@
         <v>PASS</v>
       </c>
       <c r="H15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I15" t="str">
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>2026-08-01T10:49:38.463Z</v>
+        <v>2026-08-08T07:13:18.200Z</v>
       </c>
     </row>
     <row r="16">
@@ -1002,13 +1002,13 @@
         <v>PASS</v>
       </c>
       <c r="H16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I16" t="str">
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>2026-08-01T10:49:38.477Z</v>
+        <v>2026-08-08T07:13:18.215Z</v>
       </c>
     </row>
     <row r="17">
@@ -1040,7 +1040,7 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>2026-08-01T10:49:38.493Z</v>
+        <v>2026-08-08T07:13:18.231Z</v>
       </c>
     </row>
     <row r="18">
@@ -1066,13 +1066,13 @@
         <v>PASS</v>
       </c>
       <c r="H18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I18" t="str">
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>2026-08-01T10:49:38.509Z</v>
+        <v>2026-08-08T07:13:18.246Z</v>
       </c>
     </row>
     <row r="19">
@@ -1098,13 +1098,13 @@
         <v>PASS</v>
       </c>
       <c r="H19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I19" t="str">
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>2026-08-01T10:49:38.524Z</v>
+        <v>2026-08-08T07:13:18.262Z</v>
       </c>
     </row>
     <row r="20">
@@ -1130,13 +1130,13 @@
         <v>PASS</v>
       </c>
       <c r="H20">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" t="str">
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>2026-08-01T10:49:38.539Z</v>
+        <v>2026-08-08T07:13:18.278Z</v>
       </c>
     </row>
     <row r="21">
@@ -1168,7 +1168,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>2026-08-01T10:49:38.555Z</v>
+        <v>2026-08-08T07:13:18.294Z</v>
       </c>
     </row>
     <row r="22">
@@ -1194,13 +1194,13 @@
         <v>PASS</v>
       </c>
       <c r="H22">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I22" t="str">
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>2026-08-01T10:49:38.570Z</v>
+        <v>2026-08-08T07:13:18.310Z</v>
       </c>
     </row>
     <row r="23">
@@ -1226,13 +1226,13 @@
         <v>PASS</v>
       </c>
       <c r="H23">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I23" t="str">
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>2026-08-01T10:49:38.586Z</v>
+        <v>2026-08-08T07:13:18.325Z</v>
       </c>
     </row>
     <row r="24">
@@ -1264,7 +1264,7 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>2026-08-01T10:49:38.602Z</v>
+        <v>2026-08-08T07:13:18.341Z</v>
       </c>
     </row>
     <row r="25">
@@ -1296,7 +1296,7 @@
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>2026-08-01T10:49:38.618Z</v>
+        <v>2026-08-08T07:13:18.357Z</v>
       </c>
     </row>
     <row r="26">
@@ -1322,13 +1322,13 @@
         <v>PASS</v>
       </c>
       <c r="H26">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>2026-08-01T10:49:38.633Z</v>
+        <v>2026-08-08T07:13:18.373Z</v>
       </c>
     </row>
     <row r="27">
@@ -1360,7 +1360,7 @@
         <v/>
       </c>
       <c r="J27" t="str">
-        <v>2026-08-01T10:49:38.649Z</v>
+        <v>2026-08-08T07:13:18.389Z</v>
       </c>
     </row>
     <row r="28">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="J28" t="str">
-        <v>2026-08-01T10:49:38.664Z</v>
+        <v>2026-08-08T07:13:18.404Z</v>
       </c>
     </row>
     <row r="29">
@@ -1418,13 +1418,13 @@
         <v>PASS</v>
       </c>
       <c r="H29">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I29" t="str">
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>2026-08-01T10:49:38.679Z</v>
+        <v>2026-08-08T07:13:18.420Z</v>
       </c>
     </row>
     <row r="30">
@@ -1456,7 +1456,7 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>2026-08-01T10:49:38.695Z</v>
+        <v>2026-08-08T07:13:18.436Z</v>
       </c>
     </row>
     <row r="31">
@@ -1482,13 +1482,13 @@
         <v>PASS</v>
       </c>
       <c r="H31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I31" t="str">
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>2026-08-01T10:49:38.710Z</v>
+        <v>2026-08-08T07:13:18.452Z</v>
       </c>
     </row>
     <row r="32">
@@ -1514,13 +1514,13 @@
         <v>PASS</v>
       </c>
       <c r="H32">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I32" t="str">
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>2026-08-01T10:49:38.726Z</v>
+        <v>2026-08-08T07:13:18.468Z</v>
       </c>
     </row>
     <row r="33">
@@ -1546,13 +1546,13 @@
         <v>PASS</v>
       </c>
       <c r="H33">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I33" t="str">
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>2026-08-01T10:49:38.741Z</v>
+        <v>2026-08-08T07:13:18.484Z</v>
       </c>
     </row>
     <row r="34">
@@ -1578,13 +1578,13 @@
         <v>PASS</v>
       </c>
       <c r="H34">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I34" t="str">
         <v/>
       </c>
       <c r="J34" t="str">
-        <v>2026-08-01T10:49:38.758Z</v>
+        <v>2026-08-08T07:13:18.500Z</v>
       </c>
     </row>
     <row r="35">
@@ -1610,13 +1610,13 @@
         <v>PASS</v>
       </c>
       <c r="H35">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I35" t="str">
         <v/>
       </c>
       <c r="J35" t="str">
-        <v>2026-08-01T10:49:38.773Z</v>
+        <v>2026-08-08T07:13:18.516Z</v>
       </c>
     </row>
     <row r="36">
@@ -1642,13 +1642,13 @@
         <v>PASS</v>
       </c>
       <c r="H36">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I36" t="str">
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>2026-08-01T10:49:38.788Z</v>
+        <v>2026-08-08T07:13:18.532Z</v>
       </c>
     </row>
     <row r="37">
@@ -1674,13 +1674,13 @@
         <v>PASS</v>
       </c>
       <c r="H37">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I37" t="str">
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>2026-08-01T10:49:38.804Z</v>
+        <v>2026-08-08T07:13:18.547Z</v>
       </c>
     </row>
     <row r="38">
@@ -1712,7 +1712,7 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>2026-08-01T10:49:38.820Z</v>
+        <v>2026-08-08T07:13:18.563Z</v>
       </c>
     </row>
     <row r="39">
@@ -1738,13 +1738,13 @@
         <v>PASS</v>
       </c>
       <c r="H39">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I39" t="str">
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>2026-08-01T10:49:38.835Z</v>
+        <v>2026-08-08T07:13:18.579Z</v>
       </c>
     </row>
     <row r="40">
@@ -1776,7 +1776,7 @@
         <v/>
       </c>
       <c r="J40" t="str">
-        <v>2026-08-01T10:49:38.850Z</v>
+        <v>2026-08-08T07:13:18.594Z</v>
       </c>
     </row>
     <row r="41">
@@ -1802,13 +1802,13 @@
         <v>PASS</v>
       </c>
       <c r="H41">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I41" t="str">
         <v/>
       </c>
       <c r="J41" t="str">
-        <v>2026-08-01T10:49:38.867Z</v>
+        <v>2026-08-08T07:13:18.609Z</v>
       </c>
     </row>
     <row r="42">
@@ -1834,13 +1834,13 @@
         <v>PASS</v>
       </c>
       <c r="H42">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I42" t="str">
         <v/>
       </c>
       <c r="J42" t="str">
-        <v>2026-08-01T10:49:38.883Z</v>
+        <v>2026-08-08T07:13:18.625Z</v>
       </c>
     </row>
     <row r="43">
@@ -1866,13 +1866,13 @@
         <v>PASS</v>
       </c>
       <c r="H43">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I43" t="str">
         <v/>
       </c>
       <c r="J43" t="str">
-        <v>2026-08-01T10:49:38.899Z</v>
+        <v>2026-08-08T07:13:18.640Z</v>
       </c>
     </row>
     <row r="44">
@@ -1898,13 +1898,13 @@
         <v>PASS</v>
       </c>
       <c r="H44">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I44" t="str">
         <v/>
       </c>
       <c r="J44" t="str">
-        <v>2026-08-01T10:49:38.913Z</v>
+        <v>2026-08-08T07:13:18.656Z</v>
       </c>
     </row>
     <row r="45">
@@ -1930,13 +1930,13 @@
         <v>PASS</v>
       </c>
       <c r="H45">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I45" t="str">
         <v/>
       </c>
       <c r="J45" t="str">
-        <v>2026-08-01T10:49:38.929Z</v>
+        <v>2026-08-08T07:13:18.671Z</v>
       </c>
     </row>
     <row r="46">
@@ -1968,7 +1968,7 @@
         <v/>
       </c>
       <c r="J46" t="str">
-        <v>2026-08-01T10:49:38.945Z</v>
+        <v>2026-08-08T07:13:18.687Z</v>
       </c>
     </row>
     <row r="47">
@@ -2000,7 +2000,7 @@
         <v/>
       </c>
       <c r="J47" t="str">
-        <v>2026-08-01T10:49:38.960Z</v>
+        <v>2026-08-08T07:13:18.702Z</v>
       </c>
     </row>
     <row r="48">
@@ -2032,7 +2032,7 @@
         <v/>
       </c>
       <c r="J48" t="str">
-        <v>2026-08-01T10:49:38.976Z</v>
+        <v>2026-08-08T07:13:18.718Z</v>
       </c>
     </row>
     <row r="49">
@@ -2064,7 +2064,7 @@
         <v/>
       </c>
       <c r="J49" t="str">
-        <v>2026-08-01T10:49:38.991Z</v>
+        <v>2026-08-08T07:13:18.733Z</v>
       </c>
     </row>
     <row r="50">
@@ -2090,13 +2090,13 @@
         <v>PASS</v>
       </c>
       <c r="H50">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I50" t="str">
         <v/>
       </c>
       <c r="J50" t="str">
-        <v>2026-08-01T10:49:39.007Z</v>
+        <v>2026-08-08T07:13:18.750Z</v>
       </c>
     </row>
     <row r="51">
@@ -2122,13 +2122,13 @@
         <v>PASS</v>
       </c>
       <c r="H51">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I51" t="str">
         <v/>
       </c>
       <c r="J51" t="str">
-        <v>2026-08-01T10:49:39.023Z</v>
+        <v>2026-08-08T07:13:18.765Z</v>
       </c>
     </row>
     <row r="52">
@@ -2160,7 +2160,7 @@
         <v/>
       </c>
       <c r="J52" t="str">
-        <v>2026-08-01T10:49:39.038Z</v>
+        <v>2026-08-08T07:13:18.781Z</v>
       </c>
     </row>
     <row r="53">
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="J53" t="str">
-        <v>2026-08-01T10:49:39.054Z</v>
+        <v>2026-08-08T07:13:18.797Z</v>
       </c>
     </row>
     <row r="54">
@@ -2218,13 +2218,13 @@
         <v>PASS</v>
       </c>
       <c r="H54">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I54" t="str">
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>2026-08-01T10:49:39.070Z</v>
+        <v>2026-08-08T07:13:18.814Z</v>
       </c>
     </row>
     <row r="55">
@@ -2250,13 +2250,13 @@
         <v>PASS</v>
       </c>
       <c r="H55">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I55" t="str">
         <v/>
       </c>
       <c r="J55" t="str">
-        <v>2026-08-01T10:49:39.086Z</v>
+        <v>2026-08-08T07:13:18.828Z</v>
       </c>
     </row>
     <row r="56">
@@ -2282,13 +2282,13 @@
         <v>PASS</v>
       </c>
       <c r="H56">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I56" t="str">
         <v/>
       </c>
       <c r="J56" t="str">
-        <v>2026-08-01T10:49:39.101Z</v>
+        <v>2026-08-08T07:13:18.844Z</v>
       </c>
     </row>
     <row r="57">
@@ -2314,13 +2314,13 @@
         <v>PASS</v>
       </c>
       <c r="H57">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I57" t="str">
         <v/>
       </c>
       <c r="J57" t="str">
-        <v>2026-08-01T10:49:39.117Z</v>
+        <v>2026-08-08T07:13:18.859Z</v>
       </c>
     </row>
     <row r="58">
@@ -2346,13 +2346,13 @@
         <v>PASS</v>
       </c>
       <c r="H58">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I58" t="str">
         <v/>
       </c>
       <c r="J58" t="str">
-        <v>2026-08-01T10:49:39.132Z</v>
+        <v>2026-08-08T07:13:18.875Z</v>
       </c>
     </row>
     <row r="59">
@@ -2384,7 +2384,7 @@
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>2026-08-01T10:49:39.147Z</v>
+        <v>2026-08-08T07:13:18.890Z</v>
       </c>
     </row>
     <row r="60">
@@ -2410,13 +2410,13 @@
         <v>PASS</v>
       </c>
       <c r="H60">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I60" t="str">
         <v/>
       </c>
       <c r="J60" t="str">
-        <v>2026-08-01T10:49:39.162Z</v>
+        <v>2026-08-08T07:13:18.906Z</v>
       </c>
     </row>
     <row r="61">
@@ -2442,13 +2442,13 @@
         <v>PASS</v>
       </c>
       <c r="H61">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I61" t="str">
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>2026-08-01T10:49:39.177Z</v>
+        <v>2026-08-08T07:13:18.922Z</v>
       </c>
     </row>
     <row r="62">
@@ -2474,13 +2474,13 @@
         <v>PASS</v>
       </c>
       <c r="H62">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I62" t="str">
         <v/>
       </c>
       <c r="J62" t="str">
-        <v>2026-08-01T10:49:39.193Z</v>
+        <v>2026-08-08T07:13:18.938Z</v>
       </c>
     </row>
     <row r="63">
@@ -2506,13 +2506,13 @@
         <v>PASS</v>
       </c>
       <c r="H63">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I63" t="str">
         <v/>
       </c>
       <c r="J63" t="str">
-        <v>2026-08-01T10:49:39.209Z</v>
+        <v>2026-08-08T07:13:18.954Z</v>
       </c>
     </row>
     <row r="64">
@@ -2538,13 +2538,13 @@
         <v>PASS</v>
       </c>
       <c r="H64">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I64" t="str">
         <v/>
       </c>
       <c r="J64" t="str">
-        <v>2026-08-01T10:49:39.225Z</v>
+        <v>2026-08-08T07:13:18.969Z</v>
       </c>
     </row>
     <row r="65">
@@ -2570,13 +2570,13 @@
         <v>PASS</v>
       </c>
       <c r="H65">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I65" t="str">
         <v/>
       </c>
       <c r="J65" t="str">
-        <v>2026-08-01T10:49:39.240Z</v>
+        <v>2026-08-08T07:13:18.985Z</v>
       </c>
     </row>
     <row r="66">
@@ -2608,7 +2608,7 @@
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>2026-08-01T10:49:39.255Z</v>
+        <v>2026-08-08T07:13:19.000Z</v>
       </c>
     </row>
     <row r="67">
@@ -2640,7 +2640,7 @@
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>2026-08-01T10:49:39.271Z</v>
+        <v>2026-08-08T07:13:19.015Z</v>
       </c>
     </row>
     <row r="68">
@@ -2672,7 +2672,7 @@
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>2026-08-01T10:49:39.287Z</v>
+        <v>2026-08-08T07:13:19.031Z</v>
       </c>
     </row>
     <row r="69">
@@ -2704,7 +2704,7 @@
         <v/>
       </c>
       <c r="J69" t="str">
-        <v>2026-08-01T10:49:39.303Z</v>
+        <v>2026-08-08T07:13:19.047Z</v>
       </c>
     </row>
     <row r="70">
@@ -2730,13 +2730,13 @@
         <v>PASS</v>
       </c>
       <c r="H70">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I70" t="str">
         <v/>
       </c>
       <c r="J70" t="str">
-        <v>2026-08-01T10:49:39.318Z</v>
+        <v>2026-08-08T07:13:19.063Z</v>
       </c>
     </row>
     <row r="71">
@@ -2768,7 +2768,7 @@
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>2026-08-01T10:49:39.334Z</v>
+        <v>2026-08-08T07:13:19.079Z</v>
       </c>
     </row>
     <row r="72">
@@ -2794,13 +2794,13 @@
         <v>PASS</v>
       </c>
       <c r="H72">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I72" t="str">
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>2026-08-01T10:49:39.348Z</v>
+        <v>2026-08-08T07:13:19.095Z</v>
       </c>
     </row>
     <row r="73">
@@ -2826,13 +2826,13 @@
         <v>PASS</v>
       </c>
       <c r="H73">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I73" t="str">
         <v/>
       </c>
       <c r="J73" t="str">
-        <v>2026-08-01T10:49:39.364Z</v>
+        <v>2026-08-08T07:13:19.110Z</v>
       </c>
     </row>
     <row r="74">
@@ -2858,13 +2858,13 @@
         <v>PASS</v>
       </c>
       <c r="H74">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I74" t="str">
         <v/>
       </c>
       <c r="J74" t="str">
-        <v>2026-08-01T10:49:39.380Z</v>
+        <v>2026-08-08T07:13:19.125Z</v>
       </c>
     </row>
     <row r="75">
@@ -2896,7 +2896,7 @@
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>2026-08-01T10:49:39.396Z</v>
+        <v>2026-08-08T07:13:19.141Z</v>
       </c>
     </row>
     <row r="76">
@@ -2928,7 +2928,7 @@
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>2026-08-01T10:49:39.411Z</v>
+        <v>2026-08-08T07:13:19.156Z</v>
       </c>
     </row>
     <row r="77">
@@ -2960,7 +2960,7 @@
         <v/>
       </c>
       <c r="J77" t="str">
-        <v>2026-08-01T10:49:39.427Z</v>
+        <v>2026-08-08T07:13:19.172Z</v>
       </c>
     </row>
     <row r="78">
@@ -2986,13 +2986,13 @@
         <v>PASS</v>
       </c>
       <c r="H78">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I78" t="str">
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>2026-08-01T10:49:39.443Z</v>
+        <v>2026-08-08T07:13:19.187Z</v>
       </c>
     </row>
     <row r="79">
@@ -3024,7 +3024,7 @@
         <v/>
       </c>
       <c r="J79" t="str">
-        <v>2026-08-01T10:49:39.459Z</v>
+        <v>2026-08-08T07:13:19.203Z</v>
       </c>
     </row>
     <row r="80">
@@ -3056,7 +3056,7 @@
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>2026-08-01T10:49:39.474Z</v>
+        <v>2026-08-08T07:13:19.218Z</v>
       </c>
     </row>
     <row r="81">
@@ -3088,7 +3088,7 @@
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>2026-08-01T10:49:39.490Z</v>
+        <v>2026-08-08T07:13:19.234Z</v>
       </c>
     </row>
     <row r="82">
@@ -3114,13 +3114,13 @@
         <v>PASS</v>
       </c>
       <c r="H82">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I82" t="str">
         <v/>
       </c>
       <c r="J82" t="str">
-        <v>2026-08-01T10:49:39.505Z</v>
+        <v>2026-08-08T07:13:19.249Z</v>
       </c>
     </row>
     <row r="83">
@@ -3152,7 +3152,7 @@
         <v/>
       </c>
       <c r="J83" t="str">
-        <v>2026-08-01T10:49:39.522Z</v>
+        <v>2026-08-08T07:13:19.265Z</v>
       </c>
     </row>
     <row r="84">
@@ -3184,7 +3184,7 @@
         <v/>
       </c>
       <c r="J84" t="str">
-        <v>2026-08-01T10:49:39.537Z</v>
+        <v>2026-08-08T07:13:19.280Z</v>
       </c>
     </row>
     <row r="85">
@@ -3210,13 +3210,13 @@
         <v>PASS</v>
       </c>
       <c r="H85">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I85" t="str">
         <v/>
       </c>
       <c r="J85" t="str">
-        <v>2026-08-01T10:49:39.552Z</v>
+        <v>2026-08-08T07:13:19.296Z</v>
       </c>
     </row>
     <row r="86">
@@ -3248,7 +3248,7 @@
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>2026-08-01T10:49:39.569Z</v>
+        <v>2026-08-08T07:13:19.312Z</v>
       </c>
     </row>
     <row r="87">
@@ -3274,13 +3274,13 @@
         <v>PASS</v>
       </c>
       <c r="H87">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I87" t="str">
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>2026-08-01T10:49:39.583Z</v>
+        <v>2026-08-08T07:13:19.327Z</v>
       </c>
     </row>
     <row r="88">
@@ -3312,7 +3312,7 @@
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>2026-08-01T10:49:39.599Z</v>
+        <v>2026-08-08T07:13:19.343Z</v>
       </c>
     </row>
     <row r="89">
@@ -3344,7 +3344,7 @@
         <v/>
       </c>
       <c r="J89" t="str">
-        <v>2026-08-01T10:49:39.614Z</v>
+        <v>2026-08-08T07:13:19.358Z</v>
       </c>
     </row>
     <row r="90">
@@ -3370,13 +3370,13 @@
         <v>PASS</v>
       </c>
       <c r="H90">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I90" t="str">
         <v/>
       </c>
       <c r="J90" t="str">
-        <v>2026-08-01T10:49:39.631Z</v>
+        <v>2026-08-08T07:13:19.374Z</v>
       </c>
     </row>
     <row r="91">
@@ -3402,13 +3402,13 @@
         <v>PASS</v>
       </c>
       <c r="H91">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I91" t="str">
         <v/>
       </c>
       <c r="J91" t="str">
-        <v>2026-08-01T10:49:39.646Z</v>
+        <v>2026-08-08T07:13:19.389Z</v>
       </c>
     </row>
     <row r="92">
@@ -3440,7 +3440,7 @@
         <v/>
       </c>
       <c r="J92" t="str">
-        <v>2026-08-01T10:49:39.661Z</v>
+        <v>2026-08-08T07:13:19.405Z</v>
       </c>
     </row>
     <row r="93">
@@ -3472,7 +3472,7 @@
         <v/>
       </c>
       <c r="J93" t="str">
-        <v>2026-08-01T10:49:39.677Z</v>
+        <v>2026-08-08T07:13:19.422Z</v>
       </c>
     </row>
     <row r="94">
@@ -3504,7 +3504,7 @@
         <v/>
       </c>
       <c r="J94" t="str">
-        <v>2026-08-01T10:49:39.693Z</v>
+        <v>2026-08-08T07:13:19.438Z</v>
       </c>
     </row>
     <row r="95">
@@ -3530,13 +3530,13 @@
         <v>PASS</v>
       </c>
       <c r="H95">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I95" t="str">
         <v/>
       </c>
       <c r="J95" t="str">
-        <v>2026-08-01T10:49:39.707Z</v>
+        <v>2026-08-08T07:13:19.454Z</v>
       </c>
     </row>
     <row r="96">
@@ -3562,13 +3562,13 @@
         <v>PASS</v>
       </c>
       <c r="H96">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I96" t="str">
         <v/>
       </c>
       <c r="J96" t="str">
-        <v>2026-08-01T10:49:39.723Z</v>
+        <v>2026-08-08T07:13:19.469Z</v>
       </c>
     </row>
     <row r="97">
@@ -3600,7 +3600,7 @@
         <v/>
       </c>
       <c r="J97" t="str">
-        <v>2026-08-01T10:49:39.738Z</v>
+        <v>2026-08-08T07:13:19.484Z</v>
       </c>
     </row>
     <row r="98">
@@ -3626,13 +3626,13 @@
         <v>PASS</v>
       </c>
       <c r="H98">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I98" t="str">
         <v/>
       </c>
       <c r="J98" t="str">
-        <v>2026-08-01T10:49:39.754Z</v>
+        <v>2026-08-08T07:13:19.500Z</v>
       </c>
     </row>
     <row r="99">
@@ -3658,13 +3658,13 @@
         <v>PASS</v>
       </c>
       <c r="H99">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I99" t="str">
         <v/>
       </c>
       <c r="J99" t="str">
-        <v>2026-08-01T10:49:39.770Z</v>
+        <v>2026-08-08T07:13:19.515Z</v>
       </c>
     </row>
     <row r="100">
@@ -3690,13 +3690,13 @@
         <v>PASS</v>
       </c>
       <c r="H100">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I100" t="str">
         <v/>
       </c>
       <c r="J100" t="str">
-        <v>2026-08-01T10:49:39.785Z</v>
+        <v>2026-08-08T07:13:19.531Z</v>
       </c>
     </row>
     <row r="101">
@@ -3728,7 +3728,7 @@
         <v/>
       </c>
       <c r="J101" t="str">
-        <v>2026-08-01T10:49:39.800Z</v>
+        <v>2026-08-08T07:13:19.546Z</v>
       </c>
     </row>
     <row r="102">
@@ -3754,13 +3754,13 @@
         <v>PASS</v>
       </c>
       <c r="H102">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I102" t="str">
         <v/>
       </c>
       <c r="J102" t="str">
-        <v>2026-08-01T10:49:39.816Z</v>
+        <v>2026-08-08T07:13:19.561Z</v>
       </c>
     </row>
     <row r="103">
@@ -3786,13 +3786,13 @@
         <v>PASS</v>
       </c>
       <c r="H103">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I103" t="str">
         <v/>
       </c>
       <c r="J103" t="str">
-        <v>2026-08-01T10:49:39.831Z</v>
+        <v>2026-08-08T07:13:19.577Z</v>
       </c>
     </row>
     <row r="104">
@@ -3824,7 +3824,7 @@
         <v/>
       </c>
       <c r="J104" t="str">
-        <v>2026-08-01T10:49:39.847Z</v>
+        <v>2026-08-08T07:13:19.593Z</v>
       </c>
     </row>
     <row r="105">
@@ -3850,13 +3850,13 @@
         <v>PASS</v>
       </c>
       <c r="H105">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I105" t="str">
         <v/>
       </c>
       <c r="J105" t="str">
-        <v>2026-08-01T10:49:39.863Z</v>
+        <v>2026-08-08T07:13:19.608Z</v>
       </c>
     </row>
     <row r="106">
@@ -3882,13 +3882,13 @@
         <v>PASS</v>
       </c>
       <c r="H106">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I106" t="str">
         <v/>
       </c>
       <c r="J106" t="str">
-        <v>2026-08-01T10:49:39.878Z</v>
+        <v>2026-08-08T07:13:19.624Z</v>
       </c>
     </row>
     <row r="107">
@@ -3920,7 +3920,7 @@
         <v/>
       </c>
       <c r="J107" t="str">
-        <v>2026-08-01T10:49:39.894Z</v>
+        <v>2026-08-08T07:13:19.640Z</v>
       </c>
     </row>
     <row r="108">
@@ -3952,7 +3952,7 @@
         <v/>
       </c>
       <c r="J108" t="str">
-        <v>2026-08-01T10:49:39.909Z</v>
+        <v>2026-08-08T07:13:19.655Z</v>
       </c>
     </row>
     <row r="109">
@@ -3984,7 +3984,7 @@
         <v/>
       </c>
       <c r="J109" t="str">
-        <v>2026-08-01T10:49:39.924Z</v>
+        <v>2026-08-08T07:13:19.670Z</v>
       </c>
     </row>
     <row r="110">
@@ -4016,7 +4016,7 @@
         <v/>
       </c>
       <c r="J110" t="str">
-        <v>2026-08-01T10:49:39.940Z</v>
+        <v>2026-08-08T07:13:19.686Z</v>
       </c>
     </row>
     <row r="111">
@@ -4048,7 +4048,7 @@
         <v/>
       </c>
       <c r="J111" t="str">
-        <v>2026-08-01T10:49:39.955Z</v>
+        <v>2026-08-08T07:13:19.701Z</v>
       </c>
     </row>
     <row r="112">
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="J112" t="str">
-        <v>2026-08-01T10:49:39.970Z</v>
+        <v>2026-08-08T07:13:19.717Z</v>
       </c>
     </row>
     <row r="113">
@@ -4106,13 +4106,13 @@
         <v>PASS</v>
       </c>
       <c r="H113">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I113" t="str">
         <v/>
       </c>
       <c r="J113" t="str">
-        <v>2026-08-01T10:49:39.986Z</v>
+        <v>2026-08-08T07:13:19.733Z</v>
       </c>
     </row>
     <row r="114">
@@ -4138,13 +4138,13 @@
         <v>PASS</v>
       </c>
       <c r="H114">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I114" t="str">
         <v/>
       </c>
       <c r="J114" t="str">
-        <v>2026-08-01T10:49:40.002Z</v>
+        <v>2026-08-08T07:13:19.748Z</v>
       </c>
     </row>
     <row r="115">
@@ -4176,7 +4176,7 @@
         <v/>
       </c>
       <c r="J115" t="str">
-        <v>2026-08-01T10:49:40.018Z</v>
+        <v>2026-08-08T07:13:19.764Z</v>
       </c>
     </row>
     <row r="116">
@@ -4208,7 +4208,7 @@
         <v/>
       </c>
       <c r="J116" t="str">
-        <v>2026-08-01T10:49:40.034Z</v>
+        <v>2026-08-08T07:13:19.780Z</v>
       </c>
     </row>
     <row r="117">
@@ -4240,7 +4240,7 @@
         <v/>
       </c>
       <c r="J117" t="str">
-        <v>2026-08-01T10:49:40.050Z</v>
+        <v>2026-08-08T07:13:19.796Z</v>
       </c>
     </row>
     <row r="118">
@@ -4266,13 +4266,13 @@
         <v>PASS</v>
       </c>
       <c r="H118">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I118" t="str">
         <v/>
       </c>
       <c r="J118" t="str">
-        <v>2026-08-01T10:49:40.066Z</v>
+        <v>2026-08-08T07:13:19.812Z</v>
       </c>
     </row>
     <row r="119">
@@ -4304,7 +4304,7 @@
         <v/>
       </c>
       <c r="J119" t="str">
-        <v>2026-08-01T10:49:40.081Z</v>
+        <v>2026-08-08T07:13:19.827Z</v>
       </c>
     </row>
     <row r="120">
@@ -4330,13 +4330,13 @@
         <v>PASS</v>
       </c>
       <c r="H120">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I120" t="str">
         <v/>
       </c>
       <c r="J120" t="str">
-        <v>2026-08-01T10:49:40.097Z</v>
+        <v>2026-08-08T07:13:19.842Z</v>
       </c>
     </row>
     <row r="121">
@@ -4362,13 +4362,13 @@
         <v>PASS</v>
       </c>
       <c r="H121">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I121" t="str">
         <v/>
       </c>
       <c r="J121" t="str">
-        <v>2026-08-01T10:49:40.112Z</v>
+        <v>2026-08-08T07:13:19.858Z</v>
       </c>
     </row>
     <row r="122">
@@ -4394,13 +4394,13 @@
         <v>PASS</v>
       </c>
       <c r="H122">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I122" t="str">
         <v/>
       </c>
       <c r="J122" t="str">
-        <v>2026-08-01T10:49:40.128Z</v>
+        <v>2026-08-08T07:13:19.873Z</v>
       </c>
     </row>
     <row r="123">
@@ -4432,7 +4432,7 @@
         <v/>
       </c>
       <c r="J123" t="str">
-        <v>2026-08-01T10:49:40.144Z</v>
+        <v>2026-08-08T07:13:19.889Z</v>
       </c>
     </row>
     <row r="124">
@@ -4458,13 +4458,13 @@
         <v>PASS</v>
       </c>
       <c r="H124">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I124" t="str">
         <v/>
       </c>
       <c r="J124" t="str">
-        <v>2026-08-01T10:49:40.159Z</v>
+        <v>2026-08-08T07:13:19.905Z</v>
       </c>
     </row>
     <row r="125">
@@ -4496,7 +4496,7 @@
         <v/>
       </c>
       <c r="J125" t="str">
-        <v>2026-08-01T10:49:40.175Z</v>
+        <v>2026-08-08T07:13:19.921Z</v>
       </c>
     </row>
     <row r="126">
@@ -4522,13 +4522,13 @@
         <v>PASS</v>
       </c>
       <c r="H126">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I126" t="str">
         <v/>
       </c>
       <c r="J126" t="str">
-        <v>2026-08-01T10:49:40.191Z</v>
+        <v>2026-08-08T07:13:19.936Z</v>
       </c>
     </row>
     <row r="127">
@@ -4560,7 +4560,7 @@
         <v/>
       </c>
       <c r="J127" t="str">
-        <v>2026-08-01T10:49:40.206Z</v>
+        <v>2026-08-08T07:13:19.951Z</v>
       </c>
     </row>
     <row r="128">
@@ -4592,7 +4592,7 @@
         <v/>
       </c>
       <c r="J128" t="str">
-        <v>2026-08-01T10:49:40.221Z</v>
+        <v>2026-08-08T07:13:19.967Z</v>
       </c>
     </row>
     <row r="129">
@@ -4624,7 +4624,7 @@
         <v/>
       </c>
       <c r="J129" t="str">
-        <v>2026-08-01T10:49:40.237Z</v>
+        <v>2026-08-08T07:13:19.983Z</v>
       </c>
     </row>
     <row r="130">
@@ -4650,13 +4650,13 @@
         <v>PASS</v>
       </c>
       <c r="H130">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I130" t="str">
         <v/>
       </c>
       <c r="J130" t="str">
-        <v>2026-08-01T10:49:40.252Z</v>
+        <v>2026-08-08T07:13:19.999Z</v>
       </c>
     </row>
     <row r="131">
@@ -4682,13 +4682,13 @@
         <v>PASS</v>
       </c>
       <c r="H131">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I131" t="str">
         <v/>
       </c>
       <c r="J131" t="str">
-        <v>2026-08-01T10:49:40.268Z</v>
+        <v>2026-08-08T07:13:20.013Z</v>
       </c>
     </row>
     <row r="132">
@@ -4714,13 +4714,13 @@
         <v>PASS</v>
       </c>
       <c r="H132">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I132" t="str">
         <v/>
       </c>
       <c r="J132" t="str">
-        <v>2026-08-01T10:49:40.283Z</v>
+        <v>2026-08-08T07:13:20.029Z</v>
       </c>
     </row>
     <row r="133">
@@ -4746,13 +4746,13 @@
         <v>PASS</v>
       </c>
       <c r="H133">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I133" t="str">
         <v/>
       </c>
       <c r="J133" t="str">
-        <v>2026-08-01T10:49:40.299Z</v>
+        <v>2026-08-08T07:13:20.044Z</v>
       </c>
     </row>
     <row r="134">
@@ -4784,7 +4784,7 @@
         <v/>
       </c>
       <c r="J134" t="str">
-        <v>2026-08-01T10:49:40.315Z</v>
+        <v>2026-08-08T07:13:20.060Z</v>
       </c>
     </row>
     <row r="135">
@@ -4810,13 +4810,13 @@
         <v>PASS</v>
       </c>
       <c r="H135">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I135" t="str">
         <v/>
       </c>
       <c r="J135" t="str">
-        <v>2026-08-01T10:49:40.330Z</v>
+        <v>2026-08-08T07:13:20.077Z</v>
       </c>
     </row>
     <row r="136">
@@ -4848,7 +4848,7 @@
         <v/>
       </c>
       <c r="J136" t="str">
-        <v>2026-08-01T10:49:40.345Z</v>
+        <v>2026-08-08T07:13:20.092Z</v>
       </c>
     </row>
     <row r="137">
@@ -4874,13 +4874,13 @@
         <v>PASS</v>
       </c>
       <c r="H137">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I137" t="str">
         <v/>
       </c>
       <c r="J137" t="str">
-        <v>2026-08-01T10:49:40.361Z</v>
+        <v>2026-08-08T07:13:20.107Z</v>
       </c>
     </row>
     <row r="138">
@@ -4912,7 +4912,7 @@
         <v/>
       </c>
       <c r="J138" t="str">
-        <v>2026-08-01T10:49:40.376Z</v>
+        <v>2026-08-08T07:13:20.122Z</v>
       </c>
     </row>
     <row r="139">
@@ -4944,7 +4944,7 @@
         <v/>
       </c>
       <c r="J139" t="str">
-        <v>2026-08-01T10:49:40.392Z</v>
+        <v>2026-08-08T07:13:20.138Z</v>
       </c>
     </row>
     <row r="140">
@@ -4970,13 +4970,13 @@
         <v>PASS</v>
       </c>
       <c r="H140">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I140" t="str">
         <v/>
       </c>
       <c r="J140" t="str">
-        <v>2026-08-01T10:49:40.409Z</v>
+        <v>2026-08-08T07:13:20.153Z</v>
       </c>
     </row>
     <row r="141">
@@ -5002,13 +5002,13 @@
         <v>PASS</v>
       </c>
       <c r="H141">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I141" t="str">
         <v/>
       </c>
       <c r="J141" t="str">
-        <v>2026-08-01T10:49:40.423Z</v>
+        <v>2026-08-08T07:13:20.169Z</v>
       </c>
     </row>
     <row r="142">
@@ -5040,7 +5040,7 @@
         <v/>
       </c>
       <c r="J142" t="str">
-        <v>2026-08-01T10:49:40.440Z</v>
+        <v>2026-08-08T07:13:20.185Z</v>
       </c>
     </row>
     <row r="143">
@@ -5072,7 +5072,7 @@
         <v/>
       </c>
       <c r="J143" t="str">
-        <v>2026-08-01T10:49:40.455Z</v>
+        <v>2026-08-08T07:13:20.200Z</v>
       </c>
     </row>
     <row r="144">
@@ -5098,13 +5098,13 @@
         <v>PASS</v>
       </c>
       <c r="H144">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I144" t="str">
         <v/>
       </c>
       <c r="J144" t="str">
-        <v>2026-08-01T10:49:40.470Z</v>
+        <v>2026-08-08T07:13:20.216Z</v>
       </c>
     </row>
     <row r="145">
@@ -5130,13 +5130,13 @@
         <v>PASS</v>
       </c>
       <c r="H145">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I145" t="str">
         <v/>
       </c>
       <c r="J145" t="str">
-        <v>2026-08-01T10:49:40.486Z</v>
+        <v>2026-08-08T07:13:20.231Z</v>
       </c>
     </row>
     <row r="146">
@@ -5168,7 +5168,7 @@
         <v/>
       </c>
       <c r="J146" t="str">
-        <v>2026-08-01T10:49:40.502Z</v>
+        <v>2026-08-08T07:13:20.247Z</v>
       </c>
     </row>
     <row r="147">
@@ -5194,13 +5194,13 @@
         <v>PASS</v>
       </c>
       <c r="H147">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I147" t="str">
         <v/>
       </c>
       <c r="J147" t="str">
-        <v>2026-08-01T10:49:40.518Z</v>
+        <v>2026-08-08T07:13:20.264Z</v>
       </c>
     </row>
     <row r="148">
@@ -5232,7 +5232,7 @@
         <v/>
       </c>
       <c r="J148" t="str">
-        <v>2026-08-01T10:49:40.533Z</v>
+        <v>2026-08-08T07:13:20.279Z</v>
       </c>
     </row>
     <row r="149">
@@ -5264,7 +5264,7 @@
         <v/>
       </c>
       <c r="J149" t="str">
-        <v>2026-08-01T10:49:40.548Z</v>
+        <v>2026-08-08T07:13:20.294Z</v>
       </c>
     </row>
     <row r="150">
@@ -5290,13 +5290,13 @@
         <v>PASS</v>
       </c>
       <c r="H150">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I150" t="str">
         <v/>
       </c>
       <c r="J150" t="str">
-        <v>2026-08-01T10:49:40.563Z</v>
+        <v>2026-08-08T07:13:20.312Z</v>
       </c>
     </row>
     <row r="151">
@@ -5322,13 +5322,13 @@
         <v>PASS</v>
       </c>
       <c r="H151">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I151" t="str">
         <v/>
       </c>
       <c r="J151" t="str">
-        <v>2026-08-01T10:49:40.578Z</v>
+        <v>2026-08-08T07:13:20.326Z</v>
       </c>
     </row>
     <row r="152">
@@ -5360,7 +5360,7 @@
         <v/>
       </c>
       <c r="J152" t="str">
-        <v>2026-08-01T10:49:40.594Z</v>
+        <v>2026-08-08T07:13:20.342Z</v>
       </c>
     </row>
     <row r="153">
@@ -5386,13 +5386,13 @@
         <v>PASS</v>
       </c>
       <c r="H153">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I153" t="str">
         <v/>
       </c>
       <c r="J153" t="str">
-        <v>2026-08-01T10:49:40.609Z</v>
+        <v>2026-08-08T07:13:20.358Z</v>
       </c>
     </row>
     <row r="154">
@@ -5418,13 +5418,13 @@
         <v>PASS</v>
       </c>
       <c r="H154">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I154" t="str">
         <v/>
       </c>
       <c r="J154" t="str">
-        <v>2026-08-01T10:49:40.626Z</v>
+        <v>2026-08-08T07:13:20.373Z</v>
       </c>
     </row>
     <row r="155">
@@ -5450,13 +5450,13 @@
         <v>PASS</v>
       </c>
       <c r="H155">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I155" t="str">
         <v/>
       </c>
       <c r="J155" t="str">
-        <v>2026-08-01T10:49:40.641Z</v>
+        <v>2026-08-08T07:13:20.389Z</v>
       </c>
     </row>
     <row r="156">
@@ -5488,7 +5488,7 @@
         <v/>
       </c>
       <c r="J156" t="str">
-        <v>2026-08-01T10:49:40.657Z</v>
+        <v>2026-08-08T07:13:20.404Z</v>
       </c>
     </row>
     <row r="157">
@@ -5514,13 +5514,13 @@
         <v>PASS</v>
       </c>
       <c r="H157">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I157" t="str">
         <v/>
       </c>
       <c r="J157" t="str">
-        <v>2026-08-01T10:49:40.672Z</v>
+        <v>2026-08-08T07:13:20.420Z</v>
       </c>
     </row>
     <row r="158">
@@ -5552,7 +5552,7 @@
         <v/>
       </c>
       <c r="J158" t="str">
-        <v>2026-08-01T10:49:40.688Z</v>
+        <v>2026-08-08T07:13:20.435Z</v>
       </c>
     </row>
     <row r="159">
@@ -5584,7 +5584,7 @@
         <v/>
       </c>
       <c r="J159" t="str">
-        <v>2026-08-01T10:49:40.703Z</v>
+        <v>2026-08-08T07:13:20.450Z</v>
       </c>
     </row>
     <row r="160">
@@ -5610,13 +5610,13 @@
         <v>PASS</v>
       </c>
       <c r="H160">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I160" t="str">
         <v/>
       </c>
       <c r="J160" t="str">
-        <v>2026-08-01T10:49:40.718Z</v>
+        <v>2026-08-08T07:13:20.466Z</v>
       </c>
     </row>
     <row r="161">
@@ -5648,7 +5648,7 @@
         <v/>
       </c>
       <c r="J161" t="str">
-        <v>2026-08-01T10:49:40.734Z</v>
+        <v>2026-08-08T07:13:20.482Z</v>
       </c>
     </row>
     <row r="162">
@@ -5674,13 +5674,13 @@
         <v>PASS</v>
       </c>
       <c r="H162">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I162" t="str">
         <v/>
       </c>
       <c r="J162" t="str">
-        <v>2026-08-01T10:49:40.749Z</v>
+        <v>2026-08-08T07:13:20.498Z</v>
       </c>
     </row>
     <row r="163">
@@ -5706,13 +5706,13 @@
         <v>PASS</v>
       </c>
       <c r="H163">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I163" t="str">
         <v/>
       </c>
       <c r="J163" t="str">
-        <v>2026-08-01T10:49:40.765Z</v>
+        <v>2026-08-08T07:13:20.512Z</v>
       </c>
     </row>
     <row r="164">
@@ -5738,13 +5738,13 @@
         <v>PASS</v>
       </c>
       <c r="H164">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I164" t="str">
         <v/>
       </c>
       <c r="J164" t="str">
-        <v>2026-08-01T10:49:40.781Z</v>
+        <v>2026-08-08T07:13:20.529Z</v>
       </c>
     </row>
     <row r="165">
@@ -5770,13 +5770,13 @@
         <v>PASS</v>
       </c>
       <c r="H165">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I165" t="str">
         <v/>
       </c>
       <c r="J165" t="str">
-        <v>2026-08-01T10:49:40.796Z</v>
+        <v>2026-08-08T07:13:20.543Z</v>
       </c>
     </row>
     <row r="166">
@@ -5808,7 +5808,7 @@
         <v/>
       </c>
       <c r="J166" t="str">
-        <v>2026-08-01T10:49:40.812Z</v>
+        <v>2026-08-08T07:13:20.559Z</v>
       </c>
     </row>
     <row r="167">
@@ -5834,13 +5834,13 @@
         <v>PASS</v>
       </c>
       <c r="H167">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I167" t="str">
         <v/>
       </c>
       <c r="J167" t="str">
-        <v>2026-08-01T10:49:40.828Z</v>
+        <v>2026-08-08T07:13:20.574Z</v>
       </c>
     </row>
     <row r="168">
@@ -5872,7 +5872,7 @@
         <v/>
       </c>
       <c r="J168" t="str">
-        <v>2026-08-01T10:49:40.843Z</v>
+        <v>2026-08-08T07:13:20.589Z</v>
       </c>
     </row>
     <row r="169">
@@ -5898,13 +5898,13 @@
         <v>PASS</v>
       </c>
       <c r="H169">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I169" t="str">
         <v/>
       </c>
       <c r="J169" t="str">
-        <v>2026-08-01T10:49:40.858Z</v>
+        <v>2026-08-08T07:13:20.605Z</v>
       </c>
     </row>
     <row r="170">
@@ -5936,7 +5936,7 @@
         <v/>
       </c>
       <c r="J170" t="str">
-        <v>2026-08-01T10:49:40.874Z</v>
+        <v>2026-08-08T07:13:20.621Z</v>
       </c>
     </row>
     <row r="171">
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="J171" t="str">
-        <v>2026-08-01T10:49:40.889Z</v>
+        <v>2026-08-08T07:13:20.636Z</v>
       </c>
     </row>
     <row r="172">
@@ -6000,7 +6000,7 @@
         <v/>
       </c>
       <c r="J172" t="str">
-        <v>2026-08-01T10:49:40.904Z</v>
+        <v>2026-08-08T07:13:20.651Z</v>
       </c>
     </row>
     <row r="173">
@@ -6026,13 +6026,13 @@
         <v>PASS</v>
       </c>
       <c r="H173">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I173" t="str">
         <v/>
       </c>
       <c r="J173" t="str">
-        <v>2026-08-01T10:49:40.921Z</v>
+        <v>2026-08-08T07:13:20.667Z</v>
       </c>
     </row>
     <row r="174">
@@ -6058,13 +6058,13 @@
         <v>PASS</v>
       </c>
       <c r="H174">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I174" t="str">
         <v/>
       </c>
       <c r="J174" t="str">
-        <v>2026-08-01T10:49:40.936Z</v>
+        <v>2026-08-08T07:13:20.683Z</v>
       </c>
     </row>
     <row r="175">
@@ -6096,7 +6096,7 @@
         <v/>
       </c>
       <c r="J175" t="str">
-        <v>2026-08-01T10:49:40.952Z</v>
+        <v>2026-08-08T07:13:20.699Z</v>
       </c>
     </row>
     <row r="176">
@@ -6122,13 +6122,13 @@
         <v>PASS</v>
       </c>
       <c r="H176">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I176" t="str">
         <v/>
       </c>
       <c r="J176" t="str">
-        <v>2026-08-01T10:49:40.967Z</v>
+        <v>2026-08-08T07:13:20.714Z</v>
       </c>
     </row>
     <row r="177">
@@ -6154,13 +6154,13 @@
         <v>PASS</v>
       </c>
       <c r="H177">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I177" t="str">
         <v/>
       </c>
       <c r="J177" t="str">
-        <v>2026-08-01T10:49:40.983Z</v>
+        <v>2026-08-08T07:13:20.729Z</v>
       </c>
     </row>
     <row r="178">
@@ -6186,13 +6186,13 @@
         <v>PASS</v>
       </c>
       <c r="H178">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I178" t="str">
         <v/>
       </c>
       <c r="J178" t="str">
-        <v>2026-08-01T10:49:40.998Z</v>
+        <v>2026-08-08T07:13:20.745Z</v>
       </c>
     </row>
     <row r="179">
@@ -6224,7 +6224,7 @@
         <v/>
       </c>
       <c r="J179" t="str">
-        <v>2026-08-01T10:49:41.013Z</v>
+        <v>2026-08-08T07:13:20.760Z</v>
       </c>
     </row>
     <row r="180">
@@ -6256,7 +6256,7 @@
         <v/>
       </c>
       <c r="J180" t="str">
-        <v>2026-08-01T10:49:41.029Z</v>
+        <v>2026-08-08T07:13:20.776Z</v>
       </c>
     </row>
     <row r="181">
@@ -6288,7 +6288,7 @@
         <v/>
       </c>
       <c r="J181" t="str">
-        <v>2026-08-01T10:49:41.044Z</v>
+        <v>2026-08-08T07:13:20.791Z</v>
       </c>
     </row>
     <row r="182">
@@ -6320,7 +6320,7 @@
         <v/>
       </c>
       <c r="J182" t="str">
-        <v>2026-08-01T10:49:41.060Z</v>
+        <v>2026-08-08T07:13:20.808Z</v>
       </c>
     </row>
     <row r="183">
@@ -6346,13 +6346,13 @@
         <v>PASS</v>
       </c>
       <c r="H183">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I183" t="str">
         <v/>
       </c>
       <c r="J183" t="str">
-        <v>2026-08-01T10:49:41.075Z</v>
+        <v>2026-08-08T07:13:20.824Z</v>
       </c>
     </row>
     <row r="184">
@@ -6384,7 +6384,7 @@
         <v/>
       </c>
       <c r="J184" t="str">
-        <v>2026-08-01T10:49:41.091Z</v>
+        <v>2026-08-08T07:13:20.840Z</v>
       </c>
     </row>
     <row r="185">
@@ -6416,7 +6416,7 @@
         <v/>
       </c>
       <c r="J185" t="str">
-        <v>2026-08-01T10:49:41.106Z</v>
+        <v>2026-08-08T07:13:20.855Z</v>
       </c>
     </row>
     <row r="186">
@@ -6448,7 +6448,7 @@
         <v/>
       </c>
       <c r="J186" t="str">
-        <v>2026-08-01T10:49:41.122Z</v>
+        <v>2026-08-08T07:13:20.871Z</v>
       </c>
     </row>
     <row r="187">
@@ -6474,13 +6474,13 @@
         <v>PASS</v>
       </c>
       <c r="H187">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I187" t="str">
         <v/>
       </c>
       <c r="J187" t="str">
-        <v>2026-08-01T10:49:41.138Z</v>
+        <v>2026-08-08T07:13:20.886Z</v>
       </c>
     </row>
     <row r="188">
@@ -6506,13 +6506,13 @@
         <v>PASS</v>
       </c>
       <c r="H188">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I188" t="str">
         <v/>
       </c>
       <c r="J188" t="str">
-        <v>2026-08-01T10:49:41.154Z</v>
+        <v>2026-08-08T07:13:20.903Z</v>
       </c>
     </row>
     <row r="189">
@@ -6538,13 +6538,13 @@
         <v>PASS</v>
       </c>
       <c r="H189">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I189" t="str">
         <v/>
       </c>
       <c r="J189" t="str">
-        <v>2026-08-01T10:49:41.170Z</v>
+        <v>2026-08-08T07:13:20.918Z</v>
       </c>
     </row>
     <row r="190">
@@ -6576,7 +6576,7 @@
         <v/>
       </c>
       <c r="J190" t="str">
-        <v>2026-08-01T10:49:41.185Z</v>
+        <v>2026-08-08T07:13:20.933Z</v>
       </c>
     </row>
     <row r="191">
@@ -6602,13 +6602,13 @@
         <v>PASS</v>
       </c>
       <c r="H191">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I191" t="str">
         <v/>
       </c>
       <c r="J191" t="str">
-        <v>2026-08-01T10:49:41.201Z</v>
+        <v>2026-08-08T07:13:20.949Z</v>
       </c>
     </row>
     <row r="192">
@@ -6640,7 +6640,7 @@
         <v/>
       </c>
       <c r="J192" t="str">
-        <v>2026-08-01T10:49:41.217Z</v>
+        <v>2026-08-08T07:13:20.965Z</v>
       </c>
     </row>
     <row r="193">
@@ -6666,13 +6666,13 @@
         <v>PASS</v>
       </c>
       <c r="H193">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I193" t="str">
         <v/>
       </c>
       <c r="J193" t="str">
-        <v>2026-08-01T10:49:41.232Z</v>
+        <v>2026-08-08T07:13:20.981Z</v>
       </c>
     </row>
     <row r="194">
@@ -6698,13 +6698,13 @@
         <v>PASS</v>
       </c>
       <c r="H194">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I194" t="str">
         <v/>
       </c>
       <c r="J194" t="str">
-        <v>2026-08-01T10:49:41.248Z</v>
+        <v>2026-08-08T07:13:20.996Z</v>
       </c>
     </row>
     <row r="195">
@@ -6730,13 +6730,13 @@
         <v>PASS</v>
       </c>
       <c r="H195">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I195" t="str">
         <v/>
       </c>
       <c r="J195" t="str">
-        <v>2026-08-01T10:49:41.264Z</v>
+        <v>2026-08-08T07:13:21.011Z</v>
       </c>
     </row>
     <row r="196">
@@ -6762,13 +6762,13 @@
         <v>PASS</v>
       </c>
       <c r="H196">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I196" t="str">
         <v/>
       </c>
       <c r="J196" t="str">
-        <v>2026-08-01T10:49:41.280Z</v>
+        <v>2026-08-08T07:13:21.027Z</v>
       </c>
     </row>
     <row r="197">
@@ -6794,13 +6794,13 @@
         <v>PASS</v>
       </c>
       <c r="H197">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I197" t="str">
         <v/>
       </c>
       <c r="J197" t="str">
-        <v>2026-08-01T10:49:41.295Z</v>
+        <v>2026-08-08T07:13:21.043Z</v>
       </c>
     </row>
     <row r="198">
@@ -6832,7 +6832,7 @@
         <v/>
       </c>
       <c r="J198" t="str">
-        <v>2026-08-01T10:49:41.310Z</v>
+        <v>2026-08-08T07:13:21.058Z</v>
       </c>
     </row>
     <row r="199">
@@ -6858,13 +6858,13 @@
         <v>PASS</v>
       </c>
       <c r="H199">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I199" t="str">
         <v/>
       </c>
       <c r="J199" t="str">
-        <v>2026-08-01T10:49:41.326Z</v>
+        <v>2026-08-08T07:13:21.075Z</v>
       </c>
     </row>
     <row r="200">
@@ -6896,7 +6896,7 @@
         <v/>
       </c>
       <c r="J200" t="str">
-        <v>2026-08-01T10:49:41.341Z</v>
+        <v>2026-08-08T07:13:21.090Z</v>
       </c>
     </row>
     <row r="201">
@@ -6928,7 +6928,7 @@
         <v/>
       </c>
       <c r="J201" t="str">
-        <v>2026-08-01T10:49:41.356Z</v>
+        <v>2026-08-08T07:13:21.105Z</v>
       </c>
     </row>
     <row r="202">
@@ -6954,13 +6954,13 @@
         <v>PASS</v>
       </c>
       <c r="H202">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I202" t="str">
         <v/>
       </c>
       <c r="J202" t="str">
-        <v>2026-08-01T10:49:41.372Z</v>
+        <v>2026-08-08T07:13:21.120Z</v>
       </c>
     </row>
     <row r="203">
@@ -6992,7 +6992,7 @@
         <v/>
       </c>
       <c r="J203" t="str">
-        <v>2026-08-01T10:49:41.388Z</v>
+        <v>2026-08-08T07:13:21.136Z</v>
       </c>
     </row>
     <row r="204">
@@ -7024,7 +7024,7 @@
         <v/>
       </c>
       <c r="J204" t="str">
-        <v>2026-08-01T10:49:41.403Z</v>
+        <v>2026-08-08T07:13:21.151Z</v>
       </c>
     </row>
     <row r="205">
@@ -7056,7 +7056,7 @@
         <v/>
       </c>
       <c r="J205" t="str">
-        <v>2026-08-01T10:49:41.419Z</v>
+        <v>2026-08-08T07:13:21.167Z</v>
       </c>
     </row>
     <row r="206">
@@ -7082,13 +7082,13 @@
         <v>PASS</v>
       </c>
       <c r="H206">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I206" t="str">
         <v/>
       </c>
       <c r="J206" t="str">
-        <v>2026-08-01T10:49:41.435Z</v>
+        <v>2026-08-08T07:13:21.182Z</v>
       </c>
     </row>
     <row r="207">
@@ -7120,7 +7120,7 @@
         <v/>
       </c>
       <c r="J207" t="str">
-        <v>2026-08-01T10:49:41.451Z</v>
+        <v>2026-08-08T07:13:21.198Z</v>
       </c>
     </row>
     <row r="208">
@@ -7146,13 +7146,13 @@
         <v>PASS</v>
       </c>
       <c r="H208">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I208" t="str">
         <v/>
       </c>
       <c r="J208" t="str">
-        <v>2026-08-01T10:49:41.467Z</v>
+        <v>2026-08-08T07:13:21.215Z</v>
       </c>
     </row>
     <row r="209">
@@ -7178,13 +7178,13 @@
         <v>PASS</v>
       </c>
       <c r="H209">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I209" t="str">
         <v/>
       </c>
       <c r="J209" t="str">
-        <v>2026-08-01T10:49:41.483Z</v>
+        <v>2026-08-08T07:13:21.233Z</v>
       </c>
     </row>
     <row r="210">
@@ -7210,13 +7210,13 @@
         <v>PASS</v>
       </c>
       <c r="H210">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I210" t="str">
         <v/>
       </c>
       <c r="J210" t="str">
-        <v>2026-08-01T10:49:41.499Z</v>
+        <v>2026-08-08T07:13:21.248Z</v>
       </c>
     </row>
     <row r="211">
@@ -7242,13 +7242,13 @@
         <v>PASS</v>
       </c>
       <c r="H211">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I211" t="str">
         <v/>
       </c>
       <c r="J211" t="str">
-        <v>2026-08-01T10:49:41.513Z</v>
+        <v>2026-08-08T07:13:21.263Z</v>
       </c>
     </row>
     <row r="212">
@@ -7274,13 +7274,13 @@
         <v>PASS</v>
       </c>
       <c r="H212">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I212" t="str">
         <v/>
       </c>
       <c r="J212" t="str">
-        <v>2026-08-01T10:49:41.529Z</v>
+        <v>2026-08-08T07:13:21.278Z</v>
       </c>
     </row>
     <row r="213">
@@ -7312,7 +7312,7 @@
         <v/>
       </c>
       <c r="J213" t="str">
-        <v>2026-08-01T10:49:41.545Z</v>
+        <v>2026-08-08T07:13:21.294Z</v>
       </c>
     </row>
     <row r="214">
@@ -7344,7 +7344,7 @@
         <v/>
       </c>
       <c r="J214" t="str">
-        <v>2026-08-01T10:49:41.560Z</v>
+        <v>2026-08-08T07:13:21.309Z</v>
       </c>
     </row>
     <row r="215">
@@ -7370,13 +7370,13 @@
         <v>PASS</v>
       </c>
       <c r="H215">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I215" t="str">
         <v/>
       </c>
       <c r="J215" t="str">
-        <v>2026-08-01T10:49:41.575Z</v>
+        <v>2026-08-08T07:13:21.325Z</v>
       </c>
     </row>
     <row r="216">
@@ -7402,13 +7402,13 @@
         <v>PASS</v>
       </c>
       <c r="H216">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I216" t="str">
         <v/>
       </c>
       <c r="J216" t="str">
-        <v>2026-08-01T10:49:41.592Z</v>
+        <v>2026-08-08T07:13:21.341Z</v>
       </c>
     </row>
     <row r="217">
@@ -7434,13 +7434,13 @@
         <v>PASS</v>
       </c>
       <c r="H217">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I217" t="str">
         <v/>
       </c>
       <c r="J217" t="str">
-        <v>2026-08-01T10:49:41.607Z</v>
+        <v>2026-08-08T07:13:21.357Z</v>
       </c>
     </row>
     <row r="218">
@@ -7472,7 +7472,7 @@
         <v/>
       </c>
       <c r="J218" t="str">
-        <v>2026-08-01T10:49:41.623Z</v>
+        <v>2026-08-08T07:13:21.373Z</v>
       </c>
     </row>
     <row r="219">
@@ -7504,7 +7504,7 @@
         <v/>
       </c>
       <c r="J219" t="str">
-        <v>2026-08-01T10:49:41.639Z</v>
+        <v>2026-08-08T07:13:21.389Z</v>
       </c>
     </row>
     <row r="220">
@@ -7536,7 +7536,7 @@
         <v/>
       </c>
       <c r="J220" t="str">
-        <v>2026-08-01T10:49:41.654Z</v>
+        <v>2026-08-08T07:13:21.404Z</v>
       </c>
     </row>
     <row r="221">
@@ -7568,7 +7568,7 @@
         <v/>
       </c>
       <c r="J221" t="str">
-        <v>2026-08-01T10:49:41.670Z</v>
+        <v>2026-08-08T07:13:21.420Z</v>
       </c>
     </row>
     <row r="222">
@@ -7594,13 +7594,13 @@
         <v>PASS</v>
       </c>
       <c r="H222">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I222" t="str">
         <v/>
       </c>
       <c r="J222" t="str">
-        <v>2026-08-01T10:49:41.685Z</v>
+        <v>2026-08-08T07:13:21.436Z</v>
       </c>
     </row>
     <row r="223">
@@ -7632,7 +7632,7 @@
         <v/>
       </c>
       <c r="J223" t="str">
-        <v>2026-08-01T10:49:41.701Z</v>
+        <v>2026-08-08T07:13:21.452Z</v>
       </c>
     </row>
     <row r="224">
@@ -7658,13 +7658,13 @@
         <v>PASS</v>
       </c>
       <c r="H224">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I224" t="str">
         <v/>
       </c>
       <c r="J224" t="str">
-        <v>2026-08-01T10:49:41.717Z</v>
+        <v>2026-08-08T07:13:21.467Z</v>
       </c>
     </row>
     <row r="225">
@@ -7690,13 +7690,13 @@
         <v>PASS</v>
       </c>
       <c r="H225">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I225" t="str">
         <v/>
       </c>
       <c r="J225" t="str">
-        <v>2026-08-01T10:49:41.733Z</v>
+        <v>2026-08-08T07:13:21.482Z</v>
       </c>
     </row>
     <row r="226">
@@ -7728,7 +7728,7 @@
         <v/>
       </c>
       <c r="J226" t="str">
-        <v>2026-08-01T10:49:41.749Z</v>
+        <v>2026-08-08T07:13:21.498Z</v>
       </c>
     </row>
     <row r="227">
@@ -7754,13 +7754,13 @@
         <v>PASS</v>
       </c>
       <c r="H227">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I227" t="str">
         <v/>
       </c>
       <c r="J227" t="str">
-        <v>2026-08-01T10:49:41.765Z</v>
+        <v>2026-08-08T07:13:21.513Z</v>
       </c>
     </row>
     <row r="228">
@@ -7786,13 +7786,13 @@
         <v>PASS</v>
       </c>
       <c r="H228">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I228" t="str">
         <v/>
       </c>
       <c r="J228" t="str">
-        <v>2026-08-01T10:49:41.779Z</v>
+        <v>2026-08-08T07:13:21.528Z</v>
       </c>
     </row>
     <row r="229">
@@ -7818,13 +7818,13 @@
         <v>PASS</v>
       </c>
       <c r="H229">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I229" t="str">
         <v/>
       </c>
       <c r="J229" t="str">
-        <v>2026-08-01T10:49:41.794Z</v>
+        <v>2026-08-08T07:13:21.544Z</v>
       </c>
     </row>
     <row r="230">
@@ -7856,7 +7856,7 @@
         <v/>
       </c>
       <c r="J230" t="str">
-        <v>2026-08-01T10:49:41.809Z</v>
+        <v>2026-08-08T07:13:21.559Z</v>
       </c>
     </row>
     <row r="231">
@@ -7888,7 +7888,7 @@
         <v/>
       </c>
       <c r="J231" t="str">
-        <v>2026-08-01T10:49:41.825Z</v>
+        <v>2026-08-08T07:13:21.574Z</v>
       </c>
     </row>
     <row r="232">
@@ -7920,7 +7920,7 @@
         <v/>
       </c>
       <c r="J232" t="str">
-        <v>2026-08-01T10:49:41.841Z</v>
+        <v>2026-08-08T07:13:21.590Z</v>
       </c>
     </row>
     <row r="233">
@@ -7946,13 +7946,13 @@
         <v>PASS</v>
       </c>
       <c r="H233">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I233" t="str">
         <v/>
       </c>
       <c r="J233" t="str">
-        <v>2026-08-01T10:49:41.855Z</v>
+        <v>2026-08-08T07:13:21.605Z</v>
       </c>
     </row>
     <row r="234">
@@ -7978,13 +7978,13 @@
         <v>PASS</v>
       </c>
       <c r="H234">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I234" t="str">
         <v/>
       </c>
       <c r="J234" t="str">
-        <v>2026-08-01T10:49:41.872Z</v>
+        <v>2026-08-08T07:13:21.620Z</v>
       </c>
     </row>
     <row r="235">
@@ -8016,7 +8016,7 @@
         <v/>
       </c>
       <c r="J235" t="str">
-        <v>2026-08-01T10:49:41.888Z</v>
+        <v>2026-08-08T07:13:21.636Z</v>
       </c>
     </row>
     <row r="236">
@@ -8042,13 +8042,13 @@
         <v>PASS</v>
       </c>
       <c r="H236">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I236" t="str">
         <v/>
       </c>
       <c r="J236" t="str">
-        <v>2026-08-01T10:49:41.903Z</v>
+        <v>2026-08-08T07:13:21.652Z</v>
       </c>
     </row>
     <row r="237">
@@ -8080,7 +8080,7 @@
         <v/>
       </c>
       <c r="J237" t="str">
-        <v>2026-08-01T10:49:41.919Z</v>
+        <v>2026-08-08T07:13:21.668Z</v>
       </c>
     </row>
     <row r="238">
@@ -8106,13 +8106,13 @@
         <v>PASS</v>
       </c>
       <c r="H238">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I238" t="str">
         <v/>
       </c>
       <c r="J238" t="str">
-        <v>2026-08-01T10:49:41.935Z</v>
+        <v>2026-08-08T07:13:21.685Z</v>
       </c>
     </row>
     <row r="239">
@@ -8144,7 +8144,7 @@
         <v/>
       </c>
       <c r="J239" t="str">
-        <v>2026-08-01T10:49:41.950Z</v>
+        <v>2026-08-08T07:13:21.700Z</v>
       </c>
     </row>
     <row r="240">
@@ -8176,7 +8176,7 @@
         <v/>
       </c>
       <c r="J240" t="str">
-        <v>2026-08-01T10:49:41.966Z</v>
+        <v>2026-08-08T07:13:21.716Z</v>
       </c>
     </row>
     <row r="241">
@@ -8208,7 +8208,7 @@
         <v/>
       </c>
       <c r="J241" t="str">
-        <v>2026-08-01T10:49:41.982Z</v>
+        <v>2026-08-08T07:13:21.732Z</v>
       </c>
     </row>
     <row r="242">
@@ -8234,13 +8234,13 @@
         <v>PASS</v>
       </c>
       <c r="H242">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I242" t="str">
         <v/>
       </c>
       <c r="J242" t="str">
-        <v>2026-08-01T10:49:41.997Z</v>
+        <v>2026-08-08T07:13:21.748Z</v>
       </c>
     </row>
     <row r="243">
@@ -8272,7 +8272,7 @@
         <v/>
       </c>
       <c r="J243" t="str">
-        <v>2026-08-01T10:49:42.012Z</v>
+        <v>2026-08-08T07:13:21.763Z</v>
       </c>
     </row>
     <row r="244">
@@ -8298,13 +8298,13 @@
         <v>PASS</v>
       </c>
       <c r="H244">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I244" t="str">
         <v/>
       </c>
       <c r="J244" t="str">
-        <v>2026-08-01T10:49:42.028Z</v>
+        <v>2026-08-08T07:13:21.778Z</v>
       </c>
     </row>
     <row r="245">
@@ -8330,13 +8330,13 @@
         <v>PASS</v>
       </c>
       <c r="H245">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I245" t="str">
         <v/>
       </c>
       <c r="J245" t="str">
-        <v>2026-08-01T10:49:42.044Z</v>
+        <v>2026-08-08T07:13:21.795Z</v>
       </c>
     </row>
     <row r="246">
@@ -8368,7 +8368,7 @@
         <v/>
       </c>
       <c r="J246" t="str">
-        <v>2026-08-01T10:49:42.059Z</v>
+        <v>2026-08-08T07:13:21.810Z</v>
       </c>
     </row>
     <row r="247">
@@ -8394,13 +8394,13 @@
         <v>PASS</v>
       </c>
       <c r="H247">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I247" t="str">
         <v/>
       </c>
       <c r="J247" t="str">
-        <v>2026-08-01T10:49:42.075Z</v>
+        <v>2026-08-08T07:13:21.825Z</v>
       </c>
     </row>
     <row r="248">
@@ -8426,13 +8426,13 @@
         <v>PASS</v>
       </c>
       <c r="H248">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I248" t="str">
         <v/>
       </c>
       <c r="J248" t="str">
-        <v>2026-08-01T10:49:42.090Z</v>
+        <v>2026-08-08T07:13:21.842Z</v>
       </c>
     </row>
     <row r="249">
@@ -8458,13 +8458,13 @@
         <v>PASS</v>
       </c>
       <c r="H249">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I249" t="str">
         <v/>
       </c>
       <c r="J249" t="str">
-        <v>2026-08-01T10:49:42.105Z</v>
+        <v>2026-08-08T07:13:21.856Z</v>
       </c>
     </row>
     <row r="250">
@@ -8490,13 +8490,13 @@
         <v>PASS</v>
       </c>
       <c r="H250">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I250" t="str">
         <v/>
       </c>
       <c r="J250" t="str">
-        <v>2026-08-01T10:49:42.121Z</v>
+        <v>2026-08-08T07:13:21.873Z</v>
       </c>
     </row>
     <row r="251">
@@ -8522,13 +8522,13 @@
         <v>PASS</v>
       </c>
       <c r="H251">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I251" t="str">
         <v/>
       </c>
       <c r="J251" t="str">
-        <v>2026-08-01T10:49:42.136Z</v>
+        <v>2026-08-08T07:13:21.889Z</v>
       </c>
     </row>
     <row r="252">
@@ -8554,13 +8554,13 @@
         <v>PASS</v>
       </c>
       <c r="H252">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I252" t="str">
         <v/>
       </c>
       <c r="J252" t="str">
-        <v>2026-08-01T10:49:42.152Z</v>
+        <v>2026-08-08T07:13:21.905Z</v>
       </c>
     </row>
     <row r="253">
@@ -8592,7 +8592,7 @@
         <v/>
       </c>
       <c r="J253" t="str">
-        <v>2026-08-01T10:49:42.167Z</v>
+        <v>2026-08-08T07:13:21.920Z</v>
       </c>
     </row>
     <row r="254">
@@ -8624,7 +8624,7 @@
         <v/>
       </c>
       <c r="J254" t="str">
-        <v>2026-08-01T10:49:42.183Z</v>
+        <v>2026-08-08T07:13:21.936Z</v>
       </c>
     </row>
     <row r="255">
@@ -8656,7 +8656,7 @@
         <v/>
       </c>
       <c r="J255" t="str">
-        <v>2026-08-01T10:49:42.199Z</v>
+        <v>2026-08-08T07:13:21.952Z</v>
       </c>
     </row>
     <row r="256">
@@ -8688,7 +8688,7 @@
         <v/>
       </c>
       <c r="J256" t="str">
-        <v>2026-08-01T10:49:42.214Z</v>
+        <v>2026-08-08T07:13:21.967Z</v>
       </c>
     </row>
     <row r="257">
@@ -8714,13 +8714,13 @@
         <v>PASS</v>
       </c>
       <c r="H257">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I257" t="str">
         <v/>
       </c>
       <c r="J257" t="str">
-        <v>2026-08-01T10:49:42.230Z</v>
+        <v>2026-08-08T07:13:21.984Z</v>
       </c>
     </row>
     <row r="258">
@@ -8746,13 +8746,13 @@
         <v>PASS</v>
       </c>
       <c r="H258">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I258" t="str">
         <v/>
       </c>
       <c r="J258" t="str">
-        <v>2026-08-01T10:49:42.246Z</v>
+        <v>2026-08-08T07:13:21.999Z</v>
       </c>
     </row>
     <row r="259">
@@ -8778,13 +8778,13 @@
         <v>PASS</v>
       </c>
       <c r="H259">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I259" t="str">
         <v/>
       </c>
       <c r="J259" t="str">
-        <v>2026-08-01T10:49:42.262Z</v>
+        <v>2026-08-08T07:13:22.014Z</v>
       </c>
     </row>
     <row r="260">
@@ -8816,7 +8816,7 @@
         <v/>
       </c>
       <c r="J260" t="str">
-        <v>2026-08-01T10:49:42.277Z</v>
+        <v>2026-08-08T07:13:22.029Z</v>
       </c>
     </row>
     <row r="261">
@@ -8848,7 +8848,7 @@
         <v/>
       </c>
       <c r="J261" t="str">
-        <v>2026-08-01T10:49:42.293Z</v>
+        <v>2026-08-08T07:13:22.045Z</v>
       </c>
     </row>
     <row r="262">
@@ -8880,7 +8880,7 @@
         <v/>
       </c>
       <c r="J262" t="str">
-        <v>2026-08-01T10:49:42.308Z</v>
+        <v>2026-08-08T07:13:22.061Z</v>
       </c>
     </row>
     <row r="263">
@@ -8912,7 +8912,7 @@
         <v/>
       </c>
       <c r="J263" t="str">
-        <v>2026-08-01T10:49:42.324Z</v>
+        <v>2026-08-08T07:13:22.077Z</v>
       </c>
     </row>
     <row r="264">
@@ -8944,7 +8944,7 @@
         <v/>
       </c>
       <c r="J264" t="str">
-        <v>2026-08-01T10:49:42.339Z</v>
+        <v>2026-08-08T07:13:22.092Z</v>
       </c>
     </row>
     <row r="265">
@@ -8976,7 +8976,7 @@
         <v/>
       </c>
       <c r="J265" t="str">
-        <v>2026-08-01T10:49:42.355Z</v>
+        <v>2026-08-08T07:13:22.108Z</v>
       </c>
     </row>
     <row r="266">
@@ -9002,13 +9002,13 @@
         <v>PASS</v>
       </c>
       <c r="H266">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I266" t="str">
         <v/>
       </c>
       <c r="J266" t="str">
-        <v>2026-08-01T10:49:42.372Z</v>
+        <v>2026-08-08T07:13:22.123Z</v>
       </c>
     </row>
     <row r="267">
@@ -9034,13 +9034,13 @@
         <v>PASS</v>
       </c>
       <c r="H267">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I267" t="str">
         <v/>
       </c>
       <c r="J267" t="str">
-        <v>2026-08-01T10:49:42.386Z</v>
+        <v>2026-08-08T07:13:22.138Z</v>
       </c>
     </row>
     <row r="268">
@@ -9072,7 +9072,7 @@
         <v/>
       </c>
       <c r="J268" t="str">
-        <v>2026-08-01T10:49:42.402Z</v>
+        <v>2026-08-08T07:13:22.154Z</v>
       </c>
     </row>
     <row r="269">
@@ -9104,7 +9104,7 @@
         <v/>
       </c>
       <c r="J269" t="str">
-        <v>2026-08-01T10:49:42.417Z</v>
+        <v>2026-08-08T07:13:22.169Z</v>
       </c>
     </row>
     <row r="270">
@@ -9136,7 +9136,7 @@
         <v/>
       </c>
       <c r="J270" t="str">
-        <v>2026-08-01T10:49:42.433Z</v>
+        <v>2026-08-08T07:13:22.185Z</v>
       </c>
     </row>
     <row r="271">
@@ -9162,13 +9162,13 @@
         <v>PASS</v>
       </c>
       <c r="H271">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I271" t="str">
         <v/>
       </c>
       <c r="J271" t="str">
-        <v>2026-08-01T10:49:42.449Z</v>
+        <v>2026-08-08T07:13:22.200Z</v>
       </c>
     </row>
     <row r="272">
@@ -9200,7 +9200,7 @@
         <v/>
       </c>
       <c r="J272" t="str">
-        <v>2026-08-01T10:49:42.464Z</v>
+        <v>2026-08-08T07:13:22.216Z</v>
       </c>
     </row>
     <row r="273">
@@ -9226,13 +9226,13 @@
         <v>PASS</v>
       </c>
       <c r="H273">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I273" t="str">
         <v/>
       </c>
       <c r="J273" t="str">
-        <v>2026-08-01T10:49:42.480Z</v>
+        <v>2026-08-08T07:13:22.231Z</v>
       </c>
     </row>
     <row r="274">
@@ -9264,7 +9264,7 @@
         <v/>
       </c>
       <c r="J274" t="str">
-        <v>2026-08-01T10:49:42.495Z</v>
+        <v>2026-08-08T07:13:22.247Z</v>
       </c>
     </row>
     <row r="275">
@@ -9290,13 +9290,13 @@
         <v>PASS</v>
       </c>
       <c r="H275">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I275" t="str">
         <v/>
       </c>
       <c r="J275" t="str">
-        <v>2026-08-01T10:49:42.511Z</v>
+        <v>2026-08-08T07:13:22.262Z</v>
       </c>
     </row>
     <row r="276">
@@ -9322,13 +9322,13 @@
         <v>PASS</v>
       </c>
       <c r="H276">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I276" t="str">
         <v/>
       </c>
       <c r="J276" t="str">
-        <v>2026-08-01T10:49:42.525Z</v>
+        <v>2026-08-08T07:13:22.278Z</v>
       </c>
     </row>
     <row r="277">
@@ -9360,7 +9360,7 @@
         <v/>
       </c>
       <c r="J277" t="str">
-        <v>2026-08-01T10:49:42.540Z</v>
+        <v>2026-08-08T07:13:22.294Z</v>
       </c>
     </row>
     <row r="278">
@@ -9392,7 +9392,7 @@
         <v/>
       </c>
       <c r="J278" t="str">
-        <v>2026-08-01T10:49:42.555Z</v>
+        <v>2026-08-08T07:13:22.309Z</v>
       </c>
     </row>
     <row r="279">
@@ -9418,13 +9418,13 @@
         <v>PASS</v>
       </c>
       <c r="H279">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I279" t="str">
         <v/>
       </c>
       <c r="J279" t="str">
-        <v>2026-08-01T10:49:42.571Z</v>
+        <v>2026-08-08T07:13:22.325Z</v>
       </c>
     </row>
     <row r="280">
@@ -9450,13 +9450,13 @@
         <v>PASS</v>
       </c>
       <c r="H280">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I280" t="str">
         <v/>
       </c>
       <c r="J280" t="str">
-        <v>2026-08-01T10:49:42.587Z</v>
+        <v>2026-08-08T07:13:22.341Z</v>
       </c>
     </row>
     <row r="281">
@@ -9482,13 +9482,13 @@
         <v>PASS</v>
       </c>
       <c r="H281">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I281" t="str">
         <v/>
       </c>
       <c r="J281" t="str">
-        <v>2026-08-01T10:49:42.603Z</v>
+        <v>2026-08-08T07:13:22.356Z</v>
       </c>
     </row>
     <row r="282">
@@ -9520,7 +9520,7 @@
         <v/>
       </c>
       <c r="J282" t="str">
-        <v>2026-08-01T10:49:42.618Z</v>
+        <v>2026-08-08T07:13:22.371Z</v>
       </c>
     </row>
     <row r="283">
@@ -9546,13 +9546,13 @@
         <v>PASS</v>
       </c>
       <c r="H283">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I283" t="str">
         <v/>
       </c>
       <c r="J283" t="str">
-        <v>2026-08-01T10:49:42.633Z</v>
+        <v>2026-08-08T07:13:22.387Z</v>
       </c>
     </row>
     <row r="284">
@@ -9584,7 +9584,7 @@
         <v/>
       </c>
       <c r="J284" t="str">
-        <v>2026-08-01T10:49:42.649Z</v>
+        <v>2026-08-08T07:13:22.403Z</v>
       </c>
     </row>
     <row r="285">
@@ -9610,13 +9610,13 @@
         <v>PASS</v>
       </c>
       <c r="H285">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I285" t="str">
         <v/>
       </c>
       <c r="J285" t="str">
-        <v>2026-08-01T10:49:42.664Z</v>
+        <v>2026-08-08T07:13:22.419Z</v>
       </c>
     </row>
     <row r="286">
@@ -9648,7 +9648,7 @@
         <v/>
       </c>
       <c r="J286" t="str">
-        <v>2026-08-01T10:49:42.680Z</v>
+        <v>2026-08-08T07:13:22.435Z</v>
       </c>
     </row>
     <row r="287">
@@ -9674,13 +9674,13 @@
         <v>PASS</v>
       </c>
       <c r="H287">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I287" t="str">
         <v/>
       </c>
       <c r="J287" t="str">
-        <v>2026-08-01T10:49:42.696Z</v>
+        <v>2026-08-08T07:13:22.450Z</v>
       </c>
     </row>
     <row r="288">
@@ -9706,13 +9706,13 @@
         <v>PASS</v>
       </c>
       <c r="H288">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I288" t="str">
         <v/>
       </c>
       <c r="J288" t="str">
-        <v>2026-08-01T10:49:42.711Z</v>
+        <v>2026-08-08T07:13:22.466Z</v>
       </c>
     </row>
     <row r="289">
@@ -9744,7 +9744,7 @@
         <v/>
       </c>
       <c r="J289" t="str">
-        <v>2026-08-01T10:49:42.727Z</v>
+        <v>2026-08-08T07:13:22.482Z</v>
       </c>
     </row>
     <row r="290">
@@ -9776,7 +9776,7 @@
         <v/>
       </c>
       <c r="J290" t="str">
-        <v>2026-08-01T10:49:42.742Z</v>
+        <v>2026-08-08T07:13:22.497Z</v>
       </c>
     </row>
     <row r="291">
@@ -9802,13 +9802,13 @@
         <v>PASS</v>
       </c>
       <c r="H291">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I291" t="str">
         <v/>
       </c>
       <c r="J291" t="str">
-        <v>2026-08-01T10:49:42.758Z</v>
+        <v>2026-08-08T07:13:22.513Z</v>
       </c>
     </row>
     <row r="292">
@@ -9840,7 +9840,7 @@
         <v/>
       </c>
       <c r="J292" t="str">
-        <v>2026-08-01T10:49:42.774Z</v>
+        <v>2026-08-08T07:13:22.528Z</v>
       </c>
     </row>
     <row r="293">
@@ -9866,13 +9866,13 @@
         <v>PASS</v>
       </c>
       <c r="H293">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I293" t="str">
         <v/>
       </c>
       <c r="J293" t="str">
-        <v>2026-08-01T10:49:42.789Z</v>
+        <v>2026-08-08T07:13:22.544Z</v>
       </c>
     </row>
     <row r="294">
@@ -9904,7 +9904,7 @@
         <v/>
       </c>
       <c r="J294" t="str">
-        <v>2026-08-01T10:49:42.805Z</v>
+        <v>2026-08-08T07:13:22.560Z</v>
       </c>
     </row>
     <row r="295">
@@ -9930,13 +9930,13 @@
         <v>PASS</v>
       </c>
       <c r="H295">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I295" t="str">
         <v/>
       </c>
       <c r="J295" t="str">
-        <v>2026-08-01T10:49:42.820Z</v>
+        <v>2026-08-08T07:13:22.575Z</v>
       </c>
     </row>
     <row r="296">
@@ -9962,13 +9962,13 @@
         <v>PASS</v>
       </c>
       <c r="H296">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I296" t="str">
         <v/>
       </c>
       <c r="J296" t="str">
-        <v>2026-08-01T10:49:42.835Z</v>
+        <v>2026-08-08T07:13:22.591Z</v>
       </c>
     </row>
     <row r="297">
@@ -9994,13 +9994,13 @@
         <v>PASS</v>
       </c>
       <c r="H297">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I297" t="str">
         <v/>
       </c>
       <c r="J297" t="str">
-        <v>2026-08-01T10:49:42.851Z</v>
+        <v>2026-08-08T07:13:22.606Z</v>
       </c>
     </row>
     <row r="298">
@@ -10032,7 +10032,7 @@
         <v/>
       </c>
       <c r="J298" t="str">
-        <v>2026-08-01T10:49:42.867Z</v>
+        <v>2026-08-08T07:13:22.622Z</v>
       </c>
     </row>
     <row r="299">
@@ -10058,13 +10058,13 @@
         <v>PASS</v>
       </c>
       <c r="H299">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I299" t="str">
         <v/>
       </c>
       <c r="J299" t="str">
-        <v>2026-08-01T10:49:42.883Z</v>
+        <v>2026-08-08T07:13:22.637Z</v>
       </c>
     </row>
     <row r="300">
@@ -10090,13 +10090,13 @@
         <v>PASS</v>
       </c>
       <c r="H300">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I300" t="str">
         <v/>
       </c>
       <c r="J300" t="str">
-        <v>2026-08-01T10:49:42.898Z</v>
+        <v>2026-08-08T07:13:22.654Z</v>
       </c>
     </row>
     <row r="301">
@@ -10128,7 +10128,7 @@
         <v/>
       </c>
       <c r="J301" t="str">
-        <v>2026-08-01T10:49:42.913Z</v>
+        <v>2026-08-08T07:13:22.669Z</v>
       </c>
     </row>
     <row r="302">
@@ -10154,13 +10154,13 @@
         <v>PASS</v>
       </c>
       <c r="H302">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I302" t="str">
         <v/>
       </c>
       <c r="J302" t="str">
-        <v>2026-08-01T10:49:42.928Z</v>
+        <v>2026-08-08T07:13:22.684Z</v>
       </c>
     </row>
     <row r="303">
@@ -10192,7 +10192,7 @@
         <v/>
       </c>
       <c r="J303" t="str">
-        <v>2026-08-01T10:49:42.944Z</v>
+        <v>2026-08-08T07:13:22.700Z</v>
       </c>
     </row>
     <row r="304">
@@ -10218,13 +10218,13 @@
         <v>PASS</v>
       </c>
       <c r="H304">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I304" t="str">
         <v/>
       </c>
       <c r="J304" t="str">
-        <v>2026-08-01T10:49:42.960Z</v>
+        <v>2026-08-08T07:13:22.715Z</v>
       </c>
     </row>
     <row r="305">
@@ -10250,13 +10250,13 @@
         <v>PASS</v>
       </c>
       <c r="H305">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I305" t="str">
         <v/>
       </c>
       <c r="J305" t="str">
-        <v>2026-08-01T10:49:42.975Z</v>
+        <v>2026-08-08T07:13:22.732Z</v>
       </c>
     </row>
     <row r="306">
@@ -10282,13 +10282,13 @@
         <v>PASS</v>
       </c>
       <c r="H306">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I306" t="str">
         <v/>
       </c>
       <c r="J306" t="str">
-        <v>2026-08-01T10:49:42.991Z</v>
+        <v>2026-08-08T07:13:22.747Z</v>
       </c>
     </row>
     <row r="307">
@@ -10320,7 +10320,7 @@
         <v/>
       </c>
       <c r="J307" t="str">
-        <v>2026-08-01T10:49:43.007Z</v>
+        <v>2026-08-08T07:13:22.763Z</v>
       </c>
     </row>
     <row r="308">
@@ -10346,13 +10346,13 @@
         <v>PASS</v>
       </c>
       <c r="H308">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I308" t="str">
         <v/>
       </c>
       <c r="J308" t="str">
-        <v>2026-08-01T10:49:43.023Z</v>
+        <v>2026-08-08T07:13:22.778Z</v>
       </c>
     </row>
     <row r="309">
@@ -10384,7 +10384,7 @@
         <v/>
       </c>
       <c r="J309" t="str">
-        <v>2026-08-01T10:49:43.039Z</v>
+        <v>2026-08-08T07:13:22.794Z</v>
       </c>
     </row>
     <row r="310">
@@ -10416,7 +10416,7 @@
         <v/>
       </c>
       <c r="J310" t="str">
-        <v>2026-08-01T10:49:43.055Z</v>
+        <v>2026-08-08T07:13:22.809Z</v>
       </c>
     </row>
     <row r="311">
@@ -10442,13 +10442,13 @@
         <v>PASS</v>
       </c>
       <c r="H311">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I311" t="str">
         <v/>
       </c>
       <c r="J311" t="str">
-        <v>2026-08-01T10:49:43.070Z</v>
+        <v>2026-08-08T07:13:22.825Z</v>
       </c>
     </row>
     <row r="312">
@@ -10474,13 +10474,13 @@
         <v>PASS</v>
       </c>
       <c r="H312">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I312" t="str">
         <v/>
       </c>
       <c r="J312" t="str">
-        <v>2026-08-01T10:49:43.086Z</v>
+        <v>2026-08-08T07:13:22.840Z</v>
       </c>
     </row>
     <row r="313">
@@ -10512,7 +10512,7 @@
         <v/>
       </c>
       <c r="J313" t="str">
-        <v>2026-08-01T10:49:43.101Z</v>
+        <v>2026-08-08T07:13:22.855Z</v>
       </c>
     </row>
     <row r="314">
@@ -10538,13 +10538,13 @@
         <v>PASS</v>
       </c>
       <c r="H314">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I314" t="str">
         <v/>
       </c>
       <c r="J314" t="str">
-        <v>2026-08-01T10:49:43.117Z</v>
+        <v>2026-08-08T07:13:22.872Z</v>
       </c>
     </row>
     <row r="315">
@@ -10570,13 +10570,13 @@
         <v>PASS</v>
       </c>
       <c r="H315">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I315" t="str">
         <v/>
       </c>
       <c r="J315" t="str">
-        <v>2026-08-01T10:49:43.134Z</v>
+        <v>2026-08-08T07:13:22.887Z</v>
       </c>
     </row>
     <row r="316">
@@ -10602,13 +10602,13 @@
         <v>PASS</v>
       </c>
       <c r="H316">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I316" t="str">
         <v/>
       </c>
       <c r="J316" t="str">
-        <v>2026-08-01T10:49:43.150Z</v>
+        <v>2026-08-08T07:13:22.903Z</v>
       </c>
     </row>
     <row r="317">
@@ -10634,13 +10634,13 @@
         <v>PASS</v>
       </c>
       <c r="H317">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I317" t="str">
         <v/>
       </c>
       <c r="J317" t="str">
-        <v>2026-08-01T10:49:43.164Z</v>
+        <v>2026-08-08T07:13:22.919Z</v>
       </c>
     </row>
     <row r="318">
@@ -10672,7 +10672,7 @@
         <v/>
       </c>
       <c r="J318" t="str">
-        <v>2026-08-01T10:49:43.180Z</v>
+        <v>2026-08-08T07:13:22.935Z</v>
       </c>
     </row>
     <row r="319">
@@ -10698,13 +10698,13 @@
         <v>PASS</v>
       </c>
       <c r="H319">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I319" t="str">
         <v/>
       </c>
       <c r="J319" t="str">
-        <v>2026-08-01T10:49:43.196Z</v>
+        <v>2026-08-08T07:13:22.950Z</v>
       </c>
     </row>
     <row r="320">
@@ -10730,13 +10730,13 @@
         <v>PASS</v>
       </c>
       <c r="H320">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I320" t="str">
         <v/>
       </c>
       <c r="J320" t="str">
-        <v>2026-08-01T10:49:43.211Z</v>
+        <v>2026-08-08T07:13:22.966Z</v>
       </c>
     </row>
     <row r="321">
@@ -10768,7 +10768,7 @@
         <v/>
       </c>
       <c r="J321" t="str">
-        <v>2026-08-01T10:49:43.226Z</v>
+        <v>2026-08-08T07:13:22.981Z</v>
       </c>
     </row>
     <row r="322">
@@ -10794,13 +10794,13 @@
         <v>PASS</v>
       </c>
       <c r="H322">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I322" t="str">
         <v/>
       </c>
       <c r="J322" t="str">
-        <v>2026-08-01T10:49:43.242Z</v>
+        <v>2026-08-08T07:13:22.997Z</v>
       </c>
     </row>
     <row r="323">
@@ -10826,13 +10826,13 @@
         <v>PASS</v>
       </c>
       <c r="H323">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I323" t="str">
         <v/>
       </c>
       <c r="J323" t="str">
-        <v>2026-08-01T10:49:43.257Z</v>
+        <v>2026-08-08T07:13:23.013Z</v>
       </c>
     </row>
     <row r="324">
@@ -10858,13 +10858,13 @@
         <v>PASS</v>
       </c>
       <c r="H324">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I324" t="str">
         <v/>
       </c>
       <c r="J324" t="str">
-        <v>2026-08-01T10:49:43.273Z</v>
+        <v>2026-08-08T07:13:23.028Z</v>
       </c>
     </row>
     <row r="325">
@@ -10890,13 +10890,13 @@
         <v>PASS</v>
       </c>
       <c r="H325">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I325" t="str">
         <v/>
       </c>
       <c r="J325" t="str">
-        <v>2026-08-01T10:49:43.289Z</v>
+        <v>2026-08-08T07:13:23.044Z</v>
       </c>
     </row>
     <row r="326">
@@ -10928,7 +10928,7 @@
         <v/>
       </c>
       <c r="J326" t="str">
-        <v>2026-08-01T10:49:43.305Z</v>
+        <v>2026-08-08T07:13:23.060Z</v>
       </c>
     </row>
     <row r="327">
@@ -10960,7 +10960,7 @@
         <v/>
       </c>
       <c r="J327" t="str">
-        <v>2026-08-01T10:49:43.320Z</v>
+        <v>2026-08-08T07:13:23.075Z</v>
       </c>
     </row>
     <row r="328">
@@ -10986,13 +10986,13 @@
         <v>PASS</v>
       </c>
       <c r="H328">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I328" t="str">
         <v/>
       </c>
       <c r="J328" t="str">
-        <v>2026-08-01T10:49:43.336Z</v>
+        <v>2026-08-08T07:13:23.090Z</v>
       </c>
     </row>
     <row r="329">
@@ -11024,7 +11024,7 @@
         <v/>
       </c>
       <c r="J329" t="str">
-        <v>2026-08-01T10:49:43.352Z</v>
+        <v>2026-08-08T07:13:23.106Z</v>
       </c>
     </row>
     <row r="330">
@@ -11050,13 +11050,13 @@
         <v>PASS</v>
       </c>
       <c r="H330">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I330" t="str">
         <v/>
       </c>
       <c r="J330" t="str">
-        <v>2026-08-01T10:49:43.368Z</v>
+        <v>2026-08-08T07:13:23.121Z</v>
       </c>
     </row>
     <row r="331">
@@ -11082,13 +11082,13 @@
         <v>PASS</v>
       </c>
       <c r="H331">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I331" t="str">
         <v/>
       </c>
       <c r="J331" t="str">
-        <v>2026-08-01T10:49:43.383Z</v>
+        <v>2026-08-08T07:13:23.136Z</v>
       </c>
     </row>
     <row r="332">
@@ -11114,13 +11114,13 @@
         <v>PASS</v>
       </c>
       <c r="H332">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I332" t="str">
         <v/>
       </c>
       <c r="J332" t="str">
-        <v>2026-08-01T10:49:43.399Z</v>
+        <v>2026-08-08T07:13:23.152Z</v>
       </c>
     </row>
     <row r="333">
@@ -11146,13 +11146,13 @@
         <v>PASS</v>
       </c>
       <c r="H333">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I333" t="str">
         <v/>
       </c>
       <c r="J333" t="str">
-        <v>2026-08-01T10:49:43.414Z</v>
+        <v>2026-08-08T07:13:23.168Z</v>
       </c>
     </row>
     <row r="334">
@@ -11178,13 +11178,13 @@
         <v>PASS</v>
       </c>
       <c r="H334">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I334" t="str">
         <v/>
       </c>
       <c r="J334" t="str">
-        <v>2026-08-01T10:49:43.430Z</v>
+        <v>2026-08-08T07:13:23.183Z</v>
       </c>
     </row>
     <row r="335">
@@ -11216,7 +11216,7 @@
         <v/>
       </c>
       <c r="J335" t="str">
-        <v>2026-08-01T10:49:43.446Z</v>
+        <v>2026-08-08T07:13:23.199Z</v>
       </c>
     </row>
     <row r="336">
@@ -11242,13 +11242,13 @@
         <v>PASS</v>
       </c>
       <c r="H336">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I336" t="str">
         <v/>
       </c>
       <c r="J336" t="str">
-        <v>2026-08-01T10:49:43.462Z</v>
+        <v>2026-08-08T07:13:23.214Z</v>
       </c>
     </row>
     <row r="337">
@@ -11274,13 +11274,13 @@
         <v>PASS</v>
       </c>
       <c r="H337">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I337" t="str">
         <v/>
       </c>
       <c r="J337" t="str">
-        <v>2026-08-01T10:49:43.477Z</v>
+        <v>2026-08-08T07:13:23.230Z</v>
       </c>
     </row>
     <row r="338">
@@ -11306,13 +11306,13 @@
         <v>PASS</v>
       </c>
       <c r="H338">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I338" t="str">
         <v/>
       </c>
       <c r="J338" t="str">
-        <v>2026-08-01T10:49:43.492Z</v>
+        <v>2026-08-08T07:13:23.247Z</v>
       </c>
     </row>
     <row r="339">
@@ -11338,13 +11338,13 @@
         <v>PASS</v>
       </c>
       <c r="H339">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I339" t="str">
         <v/>
       </c>
       <c r="J339" t="str">
-        <v>2026-08-01T10:49:43.508Z</v>
+        <v>2026-08-08T07:13:23.265Z</v>
       </c>
     </row>
     <row r="340">
@@ -11370,13 +11370,13 @@
         <v>PASS</v>
       </c>
       <c r="H340">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I340" t="str">
         <v/>
       </c>
       <c r="J340" t="str">
-        <v>2026-08-01T10:49:43.523Z</v>
+        <v>2026-08-08T07:13:23.278Z</v>
       </c>
     </row>
     <row r="341">
@@ -11402,13 +11402,13 @@
         <v>PASS</v>
       </c>
       <c r="H341">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I341" t="str">
         <v/>
       </c>
       <c r="J341" t="str">
-        <v>2026-08-01T10:49:43.539Z</v>
+        <v>2026-08-08T07:13:23.293Z</v>
       </c>
     </row>
     <row r="342">
@@ -11434,13 +11434,13 @@
         <v>PASS</v>
       </c>
       <c r="H342">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I342" t="str">
         <v/>
       </c>
       <c r="J342" t="str">
-        <v>2026-08-01T10:49:43.555Z</v>
+        <v>2026-08-08T07:13:23.308Z</v>
       </c>
     </row>
     <row r="343">
@@ -11472,7 +11472,7 @@
         <v/>
       </c>
       <c r="J343" t="str">
-        <v>2026-08-01T10:49:43.571Z</v>
+        <v>2026-08-08T07:13:23.324Z</v>
       </c>
     </row>
     <row r="344">
@@ -11498,13 +11498,13 @@
         <v>PASS</v>
       </c>
       <c r="H344">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I344" t="str">
         <v/>
       </c>
       <c r="J344" t="str">
-        <v>2026-08-01T10:49:43.587Z</v>
+        <v>2026-08-08T07:13:23.343Z</v>
       </c>
     </row>
     <row r="345">
@@ -11530,13 +11530,13 @@
         <v>PASS</v>
       </c>
       <c r="H345">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I345" t="str">
         <v/>
       </c>
       <c r="J345" t="str">
-        <v>2026-08-01T10:49:43.602Z</v>
+        <v>2026-08-08T07:13:23.356Z</v>
       </c>
     </row>
     <row r="346">
@@ -11562,13 +11562,13 @@
         <v>PASS</v>
       </c>
       <c r="H346">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I346" t="str">
         <v/>
       </c>
       <c r="J346" t="str">
-        <v>2026-08-01T10:49:43.618Z</v>
+        <v>2026-08-08T07:13:23.371Z</v>
       </c>
     </row>
     <row r="347">
@@ -11594,13 +11594,13 @@
         <v>PASS</v>
       </c>
       <c r="H347">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I347" t="str">
         <v/>
       </c>
       <c r="J347" t="str">
-        <v>2026-08-01T10:49:43.633Z</v>
+        <v>2026-08-08T07:13:23.387Z</v>
       </c>
     </row>
     <row r="348">
@@ -11626,13 +11626,13 @@
         <v>PASS</v>
       </c>
       <c r="H348">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I348" t="str">
         <v/>
       </c>
       <c r="J348" t="str">
-        <v>2026-08-01T10:49:43.649Z</v>
+        <v>2026-08-08T07:13:23.401Z</v>
       </c>
     </row>
     <row r="349">
@@ -11664,7 +11664,7 @@
         <v/>
       </c>
       <c r="J349" t="str">
-        <v>2026-08-01T10:49:43.665Z</v>
+        <v>2026-08-08T07:13:23.418Z</v>
       </c>
     </row>
     <row r="350">
@@ -11696,7 +11696,7 @@
         <v/>
       </c>
       <c r="J350" t="str">
-        <v>2026-08-01T10:49:43.681Z</v>
+        <v>2026-08-08T07:13:23.434Z</v>
       </c>
     </row>
     <row r="351">
@@ -11728,7 +11728,7 @@
         <v/>
       </c>
       <c r="J351" t="str">
-        <v>2026-08-01T10:49:43.696Z</v>
+        <v>2026-08-08T07:13:23.449Z</v>
       </c>
     </row>
     <row r="352">
@@ -11760,7 +11760,7 @@
         <v/>
       </c>
       <c r="J352" t="str">
-        <v>2026-08-01T10:49:43.712Z</v>
+        <v>2026-08-08T07:13:23.465Z</v>
       </c>
     </row>
     <row r="353">
@@ -11786,13 +11786,13 @@
         <v>PASS</v>
       </c>
       <c r="H353">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I353" t="str">
         <v/>
       </c>
       <c r="J353" t="str">
-        <v>2026-08-01T10:49:43.728Z</v>
+        <v>2026-08-08T07:13:23.479Z</v>
       </c>
     </row>
     <row r="354">
@@ -11818,13 +11818,13 @@
         <v>PASS</v>
       </c>
       <c r="H354">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I354" t="str">
         <v/>
       </c>
       <c r="J354" t="str">
-        <v>2026-08-01T10:49:43.743Z</v>
+        <v>2026-08-08T07:13:23.495Z</v>
       </c>
     </row>
     <row r="355">
@@ -11856,7 +11856,7 @@
         <v/>
       </c>
       <c r="J355" t="str">
-        <v>2026-08-01T10:49:43.759Z</v>
+        <v>2026-08-08T07:13:23.511Z</v>
       </c>
     </row>
     <row r="356">
@@ -11882,13 +11882,13 @@
         <v>PASS</v>
       </c>
       <c r="H356">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I356" t="str">
         <v/>
       </c>
       <c r="J356" t="str">
-        <v>2026-08-01T10:49:43.774Z</v>
+        <v>2026-08-08T07:13:23.527Z</v>
       </c>
     </row>
     <row r="357">
@@ -11920,7 +11920,7 @@
         <v/>
       </c>
       <c r="J357" t="str">
-        <v>2026-08-01T10:49:43.790Z</v>
+        <v>2026-08-08T07:13:23.543Z</v>
       </c>
     </row>
     <row r="358">
@@ -11946,13 +11946,13 @@
         <v>PASS</v>
       </c>
       <c r="H358">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I358" t="str">
         <v/>
       </c>
       <c r="J358" t="str">
-        <v>2026-08-01T10:49:43.806Z</v>
+        <v>2026-08-08T07:13:23.558Z</v>
       </c>
     </row>
     <row r="359">
@@ -11984,7 +11984,7 @@
         <v/>
       </c>
       <c r="J359" t="str">
-        <v>2026-08-01T10:49:43.821Z</v>
+        <v>2026-08-08T07:13:23.573Z</v>
       </c>
     </row>
     <row r="360">
@@ -12016,7 +12016,7 @@
         <v/>
       </c>
       <c r="J360" t="str">
-        <v>2026-08-01T10:49:43.837Z</v>
+        <v>2026-08-08T07:13:23.589Z</v>
       </c>
     </row>
     <row r="361">
@@ -12042,13 +12042,13 @@
         <v>PASS</v>
       </c>
       <c r="H361">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I361" t="str">
         <v/>
       </c>
       <c r="J361" t="str">
-        <v>2026-08-01T10:49:43.852Z</v>
+        <v>2026-08-08T07:13:23.605Z</v>
       </c>
     </row>
     <row r="362">
@@ -12080,7 +12080,7 @@
         <v/>
       </c>
       <c r="J362" t="str">
-        <v>2026-08-01T10:49:43.868Z</v>
+        <v>2026-08-08T07:13:23.621Z</v>
       </c>
     </row>
     <row r="363">
@@ -12112,7 +12112,7 @@
         <v/>
       </c>
       <c r="J363" t="str">
-        <v>2026-08-01T10:49:43.884Z</v>
+        <v>2026-08-08T07:13:23.637Z</v>
       </c>
     </row>
     <row r="364">
@@ -12144,7 +12144,7 @@
         <v/>
       </c>
       <c r="J364" t="str">
-        <v>2026-08-01T10:49:43.899Z</v>
+        <v>2026-08-08T07:13:23.652Z</v>
       </c>
     </row>
     <row r="365">
@@ -12170,13 +12170,13 @@
         <v>PASS</v>
       </c>
       <c r="H365">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I365" t="str">
         <v/>
       </c>
       <c r="J365" t="str">
-        <v>2026-08-01T10:49:43.915Z</v>
+        <v>2026-08-08T07:13:23.667Z</v>
       </c>
     </row>
     <row r="366">
@@ -12202,13 +12202,13 @@
         <v>PASS</v>
       </c>
       <c r="H366">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I366" t="str">
         <v/>
       </c>
       <c r="J366" t="str">
-        <v>2026-08-01T10:49:43.931Z</v>
+        <v>2026-08-08T07:13:23.682Z</v>
       </c>
     </row>
     <row r="367">
@@ -12240,7 +12240,7 @@
         <v/>
       </c>
       <c r="J367" t="str">
-        <v>2026-08-01T10:49:43.947Z</v>
+        <v>2026-08-08T07:13:23.698Z</v>
       </c>
     </row>
     <row r="368">
@@ -12266,13 +12266,13 @@
         <v>PASS</v>
       </c>
       <c r="H368">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I368" t="str">
         <v/>
       </c>
       <c r="J368" t="str">
-        <v>2026-08-01T10:49:43.962Z</v>
+        <v>2026-08-08T07:13:23.714Z</v>
       </c>
     </row>
     <row r="369">
@@ -12304,7 +12304,7 @@
         <v/>
       </c>
       <c r="J369" t="str">
-        <v>2026-08-01T10:49:43.977Z</v>
+        <v>2026-08-08T07:13:23.729Z</v>
       </c>
     </row>
     <row r="370">
@@ -12330,13 +12330,13 @@
         <v>PASS</v>
       </c>
       <c r="H370">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I370" t="str">
         <v/>
       </c>
       <c r="J370" t="str">
-        <v>2026-08-01T10:49:43.993Z</v>
+        <v>2026-08-08T07:13:23.746Z</v>
       </c>
     </row>
     <row r="371">
@@ -12362,13 +12362,13 @@
         <v>PASS</v>
       </c>
       <c r="H371">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I371" t="str">
         <v/>
       </c>
       <c r="J371" t="str">
-        <v>2026-08-01T10:49:44.008Z</v>
+        <v>2026-08-08T07:13:23.763Z</v>
       </c>
     </row>
     <row r="372">
@@ -12394,13 +12394,13 @@
         <v>PASS</v>
       </c>
       <c r="H372">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I372" t="str">
         <v/>
       </c>
       <c r="J372" t="str">
-        <v>2026-08-01T10:49:44.023Z</v>
+        <v>2026-08-08T07:13:23.777Z</v>
       </c>
     </row>
     <row r="373">
@@ -12432,7 +12432,7 @@
         <v/>
       </c>
       <c r="J373" t="str">
-        <v>2026-08-01T10:49:44.039Z</v>
+        <v>2026-08-08T07:13:23.793Z</v>
       </c>
     </row>
     <row r="374">
@@ -12458,13 +12458,13 @@
         <v>PASS</v>
       </c>
       <c r="H374">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I374" t="str">
         <v/>
       </c>
       <c r="J374" t="str">
-        <v>2026-08-01T10:49:44.054Z</v>
+        <v>2026-08-08T07:13:23.809Z</v>
       </c>
     </row>
     <row r="375">
@@ -12490,13 +12490,13 @@
         <v>PASS</v>
       </c>
       <c r="H375">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I375" t="str">
         <v/>
       </c>
       <c r="J375" t="str">
-        <v>2026-08-01T10:49:44.070Z</v>
+        <v>2026-08-08T07:13:23.824Z</v>
       </c>
     </row>
     <row r="376">
@@ -12522,13 +12522,13 @@
         <v>PASS</v>
       </c>
       <c r="H376">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I376" t="str">
         <v/>
       </c>
       <c r="J376" t="str">
-        <v>2026-08-01T10:49:44.085Z</v>
+        <v>2026-08-08T07:13:23.839Z</v>
       </c>
     </row>
     <row r="377">
@@ -12554,13 +12554,13 @@
         <v>PASS</v>
       </c>
       <c r="H377">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I377" t="str">
         <v/>
       </c>
       <c r="J377" t="str">
-        <v>2026-08-01T10:49:44.101Z</v>
+        <v>2026-08-08T07:13:23.854Z</v>
       </c>
     </row>
     <row r="378">
@@ -12592,7 +12592,7 @@
         <v/>
       </c>
       <c r="J378" t="str">
-        <v>2026-08-01T10:49:44.116Z</v>
+        <v>2026-08-08T07:13:23.870Z</v>
       </c>
     </row>
     <row r="379">
@@ -12624,7 +12624,7 @@
         <v/>
       </c>
       <c r="J379" t="str">
-        <v>2026-08-01T10:49:44.132Z</v>
+        <v>2026-08-08T07:13:23.886Z</v>
       </c>
     </row>
     <row r="380">
@@ -12650,13 +12650,13 @@
         <v>PASS</v>
       </c>
       <c r="H380">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I380" t="str">
         <v/>
       </c>
       <c r="J380" t="str">
-        <v>2026-08-01T10:49:44.147Z</v>
+        <v>2026-08-08T07:13:23.900Z</v>
       </c>
     </row>
     <row r="381">
@@ -12682,13 +12682,13 @@
         <v>PASS</v>
       </c>
       <c r="H381">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I381" t="str">
         <v/>
       </c>
       <c r="J381" t="str">
-        <v>2026-08-01T10:49:44.163Z</v>
+        <v>2026-08-08T07:13:23.915Z</v>
       </c>
     </row>
     <row r="382">
@@ -12714,13 +12714,13 @@
         <v>PASS</v>
       </c>
       <c r="H382">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I382" t="str">
         <v/>
       </c>
       <c r="J382" t="str">
-        <v>2026-08-01T10:49:44.178Z</v>
+        <v>2026-08-08T07:13:23.932Z</v>
       </c>
     </row>
     <row r="383">
@@ -12746,13 +12746,13 @@
         <v>PASS</v>
       </c>
       <c r="H383">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I383" t="str">
         <v/>
       </c>
       <c r="J383" t="str">
-        <v>2026-08-01T10:49:44.194Z</v>
+        <v>2026-08-08T07:13:23.947Z</v>
       </c>
     </row>
     <row r="384">
@@ -12778,13 +12778,13 @@
         <v>PASS</v>
       </c>
       <c r="H384">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I384" t="str">
         <v/>
       </c>
       <c r="J384" t="str">
-        <v>2026-08-01T10:49:44.210Z</v>
+        <v>2026-08-08T07:13:23.963Z</v>
       </c>
     </row>
     <row r="385">
@@ -12810,13 +12810,13 @@
         <v>PASS</v>
       </c>
       <c r="H385">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I385" t="str">
         <v/>
       </c>
       <c r="J385" t="str">
-        <v>2026-08-01T10:49:44.225Z</v>
+        <v>2026-08-08T07:13:23.979Z</v>
       </c>
     </row>
     <row r="386">
@@ -12842,13 +12842,13 @@
         <v>PASS</v>
       </c>
       <c r="H386">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I386" t="str">
         <v/>
       </c>
       <c r="J386" t="str">
-        <v>2026-08-01T10:49:44.240Z</v>
+        <v>2026-08-08T07:13:23.995Z</v>
       </c>
     </row>
     <row r="387">
@@ -12874,13 +12874,13 @@
         <v>PASS</v>
       </c>
       <c r="H387">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I387" t="str">
         <v/>
       </c>
       <c r="J387" t="str">
-        <v>2026-08-01T10:49:44.255Z</v>
+        <v>2026-08-08T07:13:24.011Z</v>
       </c>
     </row>
     <row r="388">
@@ -12906,13 +12906,13 @@
         <v>PASS</v>
       </c>
       <c r="H388">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I388" t="str">
         <v/>
       </c>
       <c r="J388" t="str">
-        <v>2026-08-01T10:49:44.271Z</v>
+        <v>2026-08-08T07:13:24.026Z</v>
       </c>
     </row>
     <row r="389">
@@ -12938,13 +12938,13 @@
         <v>PASS</v>
       </c>
       <c r="H389">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I389" t="str">
         <v/>
       </c>
       <c r="J389" t="str">
-        <v>2026-08-01T10:49:44.286Z</v>
+        <v>2026-08-08T07:13:24.043Z</v>
       </c>
     </row>
     <row r="390">
@@ -12970,13 +12970,13 @@
         <v>PASS</v>
       </c>
       <c r="H390">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I390" t="str">
         <v/>
       </c>
       <c r="J390" t="str">
-        <v>2026-08-01T10:49:44.302Z</v>
+        <v>2026-08-08T07:13:24.059Z</v>
       </c>
     </row>
     <row r="391">
@@ -13002,13 +13002,13 @@
         <v>PASS</v>
       </c>
       <c r="H391">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I391" t="str">
         <v/>
       </c>
       <c r="J391" t="str">
-        <v>2026-08-01T10:49:44.318Z</v>
+        <v>2026-08-08T07:13:24.073Z</v>
       </c>
     </row>
     <row r="392">
@@ -13040,7 +13040,7 @@
         <v/>
       </c>
       <c r="J392" t="str">
-        <v>2026-08-01T10:49:44.334Z</v>
+        <v>2026-08-08T07:13:24.089Z</v>
       </c>
     </row>
     <row r="393">
@@ -13066,13 +13066,13 @@
         <v>PASS</v>
       </c>
       <c r="H393">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I393" t="str">
         <v/>
       </c>
       <c r="J393" t="str">
-        <v>2026-08-01T10:49:44.348Z</v>
+        <v>2026-08-08T07:13:24.104Z</v>
       </c>
     </row>
     <row r="394">
@@ -13098,13 +13098,13 @@
         <v>PASS</v>
       </c>
       <c r="H394">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I394" t="str">
         <v/>
       </c>
       <c r="J394" t="str">
-        <v>2026-08-01T10:49:44.363Z</v>
+        <v>2026-08-08T07:13:24.120Z</v>
       </c>
     </row>
     <row r="395">
@@ -13136,7 +13136,7 @@
         <v/>
       </c>
       <c r="J395" t="str">
-        <v>2026-08-01T10:49:44.378Z</v>
+        <v>2026-08-08T07:13:24.135Z</v>
       </c>
     </row>
     <row r="396">
@@ -13168,7 +13168,7 @@
         <v/>
       </c>
       <c r="J396" t="str">
-        <v>2026-08-01T10:49:44.394Z</v>
+        <v>2026-08-08T07:13:24.151Z</v>
       </c>
     </row>
     <row r="397">
@@ -13200,7 +13200,7 @@
         <v/>
       </c>
       <c r="J397" t="str">
-        <v>2026-08-01T10:49:44.409Z</v>
+        <v>2026-08-08T07:13:24.166Z</v>
       </c>
     </row>
     <row r="398">
@@ -13232,7 +13232,7 @@
         <v/>
       </c>
       <c r="J398" t="str">
-        <v>2026-08-01T10:49:44.425Z</v>
+        <v>2026-08-08T07:13:24.182Z</v>
       </c>
     </row>
     <row r="399">
@@ -13264,7 +13264,7 @@
         <v/>
       </c>
       <c r="J399" t="str">
-        <v>2026-08-01T10:49:44.440Z</v>
+        <v>2026-08-08T07:13:24.197Z</v>
       </c>
     </row>
     <row r="400">
@@ -13296,7 +13296,7 @@
         <v/>
       </c>
       <c r="J400" t="str">
-        <v>2026-08-01T10:49:44.456Z</v>
+        <v>2026-08-08T07:13:24.214Z</v>
       </c>
     </row>
     <row r="401">
@@ -13328,7 +13328,7 @@
         <v/>
       </c>
       <c r="J401" t="str">
-        <v>2026-08-01T10:49:44.471Z</v>
+        <v>2026-08-08T07:13:24.229Z</v>
       </c>
     </row>
   </sheetData>

--- a/appium-tests/reports/appium-mobile-test-report-400.xlsx
+++ b/appium-tests/reports/appium-mobile-test-report-400.xlsx
@@ -449,7 +449,7 @@
         <v>Suite Duration (seconds)</v>
       </c>
       <c r="B6">
-        <v>6.22</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="7">
@@ -473,7 +473,7 @@
         <v>Generated At</v>
       </c>
       <c r="B9" t="str">
-        <v>8/8/2026, 12:43:24 pm</v>
+        <v>9/8/2026, 11:49:41 pm</v>
       </c>
     </row>
   </sheetData>
@@ -554,13 +554,13 @@
         <v>PASS</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I2" t="str">
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>2026-08-08T07:13:18.018Z</v>
+        <v>2026-08-09T18:19:35.426Z</v>
       </c>
     </row>
     <row r="3">
@@ -586,13 +586,13 @@
         <v>PASS</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" t="str">
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>2026-08-08T07:13:18.023Z</v>
+        <v>2026-08-09T18:19:35.432Z</v>
       </c>
     </row>
     <row r="4">
@@ -618,13 +618,13 @@
         <v>PASS</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>2026-08-08T07:13:18.028Z</v>
+        <v>2026-08-09T18:19:35.446Z</v>
       </c>
     </row>
     <row r="5">
@@ -650,13 +650,13 @@
         <v>PASS</v>
       </c>
       <c r="H5">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I5" t="str">
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>2026-08-08T07:13:18.040Z</v>
+        <v>2026-08-09T18:19:35.462Z</v>
       </c>
     </row>
     <row r="6">
@@ -682,13 +682,13 @@
         <v>PASS</v>
       </c>
       <c r="H6">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I6" t="str">
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>2026-08-08T07:13:18.059Z</v>
+        <v>2026-08-09T18:19:35.477Z</v>
       </c>
     </row>
     <row r="7">
@@ -720,7 +720,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>2026-08-08T07:13:18.074Z</v>
+        <v>2026-08-09T18:19:35.492Z</v>
       </c>
     </row>
     <row r="8">
@@ -752,7 +752,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>2026-08-08T07:13:18.090Z</v>
+        <v>2026-08-09T18:19:35.508Z</v>
       </c>
     </row>
     <row r="9">
@@ -784,7 +784,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>2026-08-08T07:13:18.106Z</v>
+        <v>2026-08-09T18:19:35.524Z</v>
       </c>
     </row>
     <row r="10">
@@ -810,13 +810,13 @@
         <v>PASS</v>
       </c>
       <c r="H10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I10" t="str">
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>2026-08-08T07:13:18.122Z</v>
+        <v>2026-08-09T18:19:35.539Z</v>
       </c>
     </row>
     <row r="11">
@@ -848,7 +848,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>2026-08-08T07:13:18.137Z</v>
+        <v>2026-08-09T18:19:35.554Z</v>
       </c>
     </row>
     <row r="12">
@@ -880,7 +880,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>2026-08-08T07:13:18.153Z</v>
+        <v>2026-08-09T18:19:35.570Z</v>
       </c>
     </row>
     <row r="13">
@@ -906,13 +906,13 @@
         <v>PASS</v>
       </c>
       <c r="H13">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I13" t="str">
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>2026-08-08T07:13:18.169Z</v>
+        <v>2026-08-09T18:19:35.586Z</v>
       </c>
     </row>
     <row r="14">
@@ -938,13 +938,13 @@
         <v>PASS</v>
       </c>
       <c r="H14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I14" t="str">
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>2026-08-08T07:13:18.184Z</v>
+        <v>2026-08-09T18:19:35.602Z</v>
       </c>
     </row>
     <row r="15">
@@ -970,13 +970,13 @@
         <v>PASS</v>
       </c>
       <c r="H15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I15" t="str">
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>2026-08-08T07:13:18.200Z</v>
+        <v>2026-08-09T18:19:35.617Z</v>
       </c>
     </row>
     <row r="16">
@@ -1002,13 +1002,13 @@
         <v>PASS</v>
       </c>
       <c r="H16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I16" t="str">
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>2026-08-08T07:13:18.215Z</v>
+        <v>2026-08-09T18:19:35.633Z</v>
       </c>
     </row>
     <row r="17">
@@ -1034,13 +1034,13 @@
         <v>PASS</v>
       </c>
       <c r="H17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I17" t="str">
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>2026-08-08T07:13:18.231Z</v>
+        <v>2026-08-09T18:19:35.648Z</v>
       </c>
     </row>
     <row r="18">
@@ -1072,7 +1072,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>2026-08-08T07:13:18.246Z</v>
+        <v>2026-08-09T18:19:35.663Z</v>
       </c>
     </row>
     <row r="19">
@@ -1098,13 +1098,13 @@
         <v>PASS</v>
       </c>
       <c r="H19">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I19" t="str">
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>2026-08-08T07:13:18.262Z</v>
+        <v>2026-08-09T18:19:35.681Z</v>
       </c>
     </row>
     <row r="20">
@@ -1130,13 +1130,13 @@
         <v>PASS</v>
       </c>
       <c r="H20">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I20" t="str">
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>2026-08-08T07:13:18.278Z</v>
+        <v>2026-08-09T18:19:35.695Z</v>
       </c>
     </row>
     <row r="21">
@@ -1162,13 +1162,13 @@
         <v>PASS</v>
       </c>
       <c r="H21">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I21" t="str">
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>2026-08-08T07:13:18.294Z</v>
+        <v>2026-08-09T18:19:35.710Z</v>
       </c>
     </row>
     <row r="22">
@@ -1194,13 +1194,13 @@
         <v>PASS</v>
       </c>
       <c r="H22">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I22" t="str">
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>2026-08-08T07:13:18.310Z</v>
+        <v>2026-08-09T18:19:35.726Z</v>
       </c>
     </row>
     <row r="23">
@@ -1232,7 +1232,7 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>2026-08-08T07:13:18.325Z</v>
+        <v>2026-08-09T18:19:35.741Z</v>
       </c>
     </row>
     <row r="24">
@@ -1258,13 +1258,13 @@
         <v>PASS</v>
       </c>
       <c r="H24">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I24" t="str">
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>2026-08-08T07:13:18.341Z</v>
+        <v>2026-08-09T18:19:35.756Z</v>
       </c>
     </row>
     <row r="25">
@@ -1290,13 +1290,13 @@
         <v>PASS</v>
       </c>
       <c r="H25">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" t="str">
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>2026-08-08T07:13:18.357Z</v>
+        <v>2026-08-09T18:19:35.773Z</v>
       </c>
     </row>
     <row r="26">
@@ -1322,13 +1322,13 @@
         <v>PASS</v>
       </c>
       <c r="H26">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>2026-08-08T07:13:18.373Z</v>
+        <v>2026-08-09T18:19:35.788Z</v>
       </c>
     </row>
     <row r="27">
@@ -1360,7 +1360,7 @@
         <v/>
       </c>
       <c r="J27" t="str">
-        <v>2026-08-08T07:13:18.389Z</v>
+        <v>2026-08-09T18:19:35.804Z</v>
       </c>
     </row>
     <row r="28">
@@ -1386,13 +1386,13 @@
         <v>PASS</v>
       </c>
       <c r="H28">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I28" t="str">
         <v/>
       </c>
       <c r="J28" t="str">
-        <v>2026-08-08T07:13:18.404Z</v>
+        <v>2026-08-09T18:19:35.820Z</v>
       </c>
     </row>
     <row r="29">
@@ -1418,13 +1418,13 @@
         <v>PASS</v>
       </c>
       <c r="H29">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I29" t="str">
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>2026-08-08T07:13:18.420Z</v>
+        <v>2026-08-09T18:19:35.835Z</v>
       </c>
     </row>
     <row r="30">
@@ -1456,7 +1456,7 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>2026-08-08T07:13:18.436Z</v>
+        <v>2026-08-09T18:19:35.851Z</v>
       </c>
     </row>
     <row r="31">
@@ -1488,7 +1488,7 @@
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>2026-08-08T07:13:18.452Z</v>
+        <v>2026-08-09T18:19:35.867Z</v>
       </c>
     </row>
     <row r="32">
@@ -1514,13 +1514,13 @@
         <v>PASS</v>
       </c>
       <c r="H32">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I32" t="str">
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>2026-08-08T07:13:18.468Z</v>
+        <v>2026-08-09T18:19:35.882Z</v>
       </c>
     </row>
     <row r="33">
@@ -1546,13 +1546,13 @@
         <v>PASS</v>
       </c>
       <c r="H33">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I33" t="str">
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>2026-08-08T07:13:18.484Z</v>
+        <v>2026-08-09T18:19:35.897Z</v>
       </c>
     </row>
     <row r="34">
@@ -1578,13 +1578,13 @@
         <v>PASS</v>
       </c>
       <c r="H34">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I34" t="str">
         <v/>
       </c>
       <c r="J34" t="str">
-        <v>2026-08-08T07:13:18.500Z</v>
+        <v>2026-08-09T18:19:35.912Z</v>
       </c>
     </row>
     <row r="35">
@@ -1610,13 +1610,13 @@
         <v>PASS</v>
       </c>
       <c r="H35">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I35" t="str">
         <v/>
       </c>
       <c r="J35" t="str">
-        <v>2026-08-08T07:13:18.516Z</v>
+        <v>2026-08-09T18:19:35.927Z</v>
       </c>
     </row>
     <row r="36">
@@ -1642,13 +1642,13 @@
         <v>PASS</v>
       </c>
       <c r="H36">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I36" t="str">
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>2026-08-08T07:13:18.532Z</v>
+        <v>2026-08-09T18:19:35.942Z</v>
       </c>
     </row>
     <row r="37">
@@ -1674,13 +1674,13 @@
         <v>PASS</v>
       </c>
       <c r="H37">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I37" t="str">
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>2026-08-08T07:13:18.547Z</v>
+        <v>2026-08-09T18:19:35.957Z</v>
       </c>
     </row>
     <row r="38">
@@ -1706,13 +1706,13 @@
         <v>PASS</v>
       </c>
       <c r="H38">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I38" t="str">
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>2026-08-08T07:13:18.563Z</v>
+        <v>2026-08-09T18:19:35.972Z</v>
       </c>
     </row>
     <row r="39">
@@ -1738,13 +1738,13 @@
         <v>PASS</v>
       </c>
       <c r="H39">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I39" t="str">
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>2026-08-08T07:13:18.579Z</v>
+        <v>2026-08-09T18:19:35.987Z</v>
       </c>
     </row>
     <row r="40">
@@ -1770,13 +1770,13 @@
         <v>PASS</v>
       </c>
       <c r="H40">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I40" t="str">
         <v/>
       </c>
       <c r="J40" t="str">
-        <v>2026-08-08T07:13:18.594Z</v>
+        <v>2026-08-09T18:19:36.003Z</v>
       </c>
     </row>
     <row r="41">
@@ -1802,13 +1802,13 @@
         <v>PASS</v>
       </c>
       <c r="H41">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I41" t="str">
         <v/>
       </c>
       <c r="J41" t="str">
-        <v>2026-08-08T07:13:18.609Z</v>
+        <v>2026-08-09T18:19:36.019Z</v>
       </c>
     </row>
     <row r="42">
@@ -1834,13 +1834,13 @@
         <v>PASS</v>
       </c>
       <c r="H42">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I42" t="str">
         <v/>
       </c>
       <c r="J42" t="str">
-        <v>2026-08-08T07:13:18.625Z</v>
+        <v>2026-08-09T18:19:36.034Z</v>
       </c>
     </row>
     <row r="43">
@@ -1872,7 +1872,7 @@
         <v/>
       </c>
       <c r="J43" t="str">
-        <v>2026-08-08T07:13:18.640Z</v>
+        <v>2026-08-09T18:19:36.049Z</v>
       </c>
     </row>
     <row r="44">
@@ -1904,7 +1904,7 @@
         <v/>
       </c>
       <c r="J44" t="str">
-        <v>2026-08-08T07:13:18.656Z</v>
+        <v>2026-08-09T18:19:36.065Z</v>
       </c>
     </row>
     <row r="45">
@@ -1930,13 +1930,13 @@
         <v>PASS</v>
       </c>
       <c r="H45">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I45" t="str">
         <v/>
       </c>
       <c r="J45" t="str">
-        <v>2026-08-08T07:13:18.671Z</v>
+        <v>2026-08-09T18:19:36.081Z</v>
       </c>
     </row>
     <row r="46">
@@ -1968,7 +1968,7 @@
         <v/>
       </c>
       <c r="J46" t="str">
-        <v>2026-08-08T07:13:18.687Z</v>
+        <v>2026-08-09T18:19:36.097Z</v>
       </c>
     </row>
     <row r="47">
@@ -2000,7 +2000,7 @@
         <v/>
       </c>
       <c r="J47" t="str">
-        <v>2026-08-08T07:13:18.702Z</v>
+        <v>2026-08-09T18:19:36.112Z</v>
       </c>
     </row>
     <row r="48">
@@ -2032,7 +2032,7 @@
         <v/>
       </c>
       <c r="J48" t="str">
-        <v>2026-08-08T07:13:18.718Z</v>
+        <v>2026-08-09T18:19:36.128Z</v>
       </c>
     </row>
     <row r="49">
@@ -2058,13 +2058,13 @@
         <v>PASS</v>
       </c>
       <c r="H49">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I49" t="str">
         <v/>
       </c>
       <c r="J49" t="str">
-        <v>2026-08-08T07:13:18.733Z</v>
+        <v>2026-08-09T18:19:36.144Z</v>
       </c>
     </row>
     <row r="50">
@@ -2090,13 +2090,13 @@
         <v>PASS</v>
       </c>
       <c r="H50">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I50" t="str">
         <v/>
       </c>
       <c r="J50" t="str">
-        <v>2026-08-08T07:13:18.750Z</v>
+        <v>2026-08-09T18:19:36.160Z</v>
       </c>
     </row>
     <row r="51">
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="J51" t="str">
-        <v>2026-08-08T07:13:18.765Z</v>
+        <v>2026-08-09T18:19:36.176Z</v>
       </c>
     </row>
     <row r="52">
@@ -2154,13 +2154,13 @@
         <v>PASS</v>
       </c>
       <c r="H52">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I52" t="str">
         <v/>
       </c>
       <c r="J52" t="str">
-        <v>2026-08-08T07:13:18.781Z</v>
+        <v>2026-08-09T18:19:36.190Z</v>
       </c>
     </row>
     <row r="53">
@@ -2186,13 +2186,13 @@
         <v>PASS</v>
       </c>
       <c r="H53">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I53" t="str">
         <v/>
       </c>
       <c r="J53" t="str">
-        <v>2026-08-08T07:13:18.797Z</v>
+        <v>2026-08-09T18:19:36.205Z</v>
       </c>
     </row>
     <row r="54">
@@ -2218,13 +2218,13 @@
         <v>PASS</v>
       </c>
       <c r="H54">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I54" t="str">
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>2026-08-08T07:13:18.814Z</v>
+        <v>2026-08-09T18:19:36.221Z</v>
       </c>
     </row>
     <row r="55">
@@ -2250,13 +2250,13 @@
         <v>PASS</v>
       </c>
       <c r="H55">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I55" t="str">
         <v/>
       </c>
       <c r="J55" t="str">
-        <v>2026-08-08T07:13:18.828Z</v>
+        <v>2026-08-09T18:19:36.237Z</v>
       </c>
     </row>
     <row r="56">
@@ -2288,7 +2288,7 @@
         <v/>
       </c>
       <c r="J56" t="str">
-        <v>2026-08-08T07:13:18.844Z</v>
+        <v>2026-08-09T18:19:36.253Z</v>
       </c>
     </row>
     <row r="57">
@@ -2314,13 +2314,13 @@
         <v>PASS</v>
       </c>
       <c r="H57">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I57" t="str">
         <v/>
       </c>
       <c r="J57" t="str">
-        <v>2026-08-08T07:13:18.859Z</v>
+        <v>2026-08-09T18:19:36.269Z</v>
       </c>
     </row>
     <row r="58">
@@ -2352,7 +2352,7 @@
         <v/>
       </c>
       <c r="J58" t="str">
-        <v>2026-08-08T07:13:18.875Z</v>
+        <v>2026-08-09T18:19:36.285Z</v>
       </c>
     </row>
     <row r="59">
@@ -2378,13 +2378,13 @@
         <v>PASS</v>
       </c>
       <c r="H59">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I59" t="str">
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>2026-08-08T07:13:18.890Z</v>
+        <v>2026-08-09T18:19:36.301Z</v>
       </c>
     </row>
     <row r="60">
@@ -2416,7 +2416,7 @@
         <v/>
       </c>
       <c r="J60" t="str">
-        <v>2026-08-08T07:13:18.906Z</v>
+        <v>2026-08-09T18:19:36.317Z</v>
       </c>
     </row>
     <row r="61">
@@ -2448,7 +2448,7 @@
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>2026-08-08T07:13:18.922Z</v>
+        <v>2026-08-09T18:19:36.333Z</v>
       </c>
     </row>
     <row r="62">
@@ -2474,13 +2474,13 @@
         <v>PASS</v>
       </c>
       <c r="H62">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I62" t="str">
         <v/>
       </c>
       <c r="J62" t="str">
-        <v>2026-08-08T07:13:18.938Z</v>
+        <v>2026-08-09T18:19:36.347Z</v>
       </c>
     </row>
     <row r="63">
@@ -2512,7 +2512,7 @@
         <v/>
       </c>
       <c r="J63" t="str">
-        <v>2026-08-08T07:13:18.954Z</v>
+        <v>2026-08-09T18:19:36.364Z</v>
       </c>
     </row>
     <row r="64">
@@ -2544,7 +2544,7 @@
         <v/>
       </c>
       <c r="J64" t="str">
-        <v>2026-08-08T07:13:18.969Z</v>
+        <v>2026-08-09T18:19:36.379Z</v>
       </c>
     </row>
     <row r="65">
@@ -2570,13 +2570,13 @@
         <v>PASS</v>
       </c>
       <c r="H65">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I65" t="str">
         <v/>
       </c>
       <c r="J65" t="str">
-        <v>2026-08-08T07:13:18.985Z</v>
+        <v>2026-08-09T18:19:36.394Z</v>
       </c>
     </row>
     <row r="66">
@@ -2602,13 +2602,13 @@
         <v>PASS</v>
       </c>
       <c r="H66">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I66" t="str">
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>2026-08-08T07:13:19.000Z</v>
+        <v>2026-08-09T18:19:36.411Z</v>
       </c>
     </row>
     <row r="67">
@@ -2634,13 +2634,13 @@
         <v>PASS</v>
       </c>
       <c r="H67">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I67" t="str">
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>2026-08-08T07:13:19.015Z</v>
+        <v>2026-08-09T18:19:36.424Z</v>
       </c>
     </row>
     <row r="68">
@@ -2672,7 +2672,7 @@
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>2026-08-08T07:13:19.031Z</v>
+        <v>2026-08-09T18:19:36.440Z</v>
       </c>
     </row>
     <row r="69">
@@ -2698,13 +2698,13 @@
         <v>PASS</v>
       </c>
       <c r="H69">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I69" t="str">
         <v/>
       </c>
       <c r="J69" t="str">
-        <v>2026-08-08T07:13:19.047Z</v>
+        <v>2026-08-09T18:19:36.455Z</v>
       </c>
     </row>
     <row r="70">
@@ -2736,7 +2736,7 @@
         <v/>
       </c>
       <c r="J70" t="str">
-        <v>2026-08-08T07:13:19.063Z</v>
+        <v>2026-08-09T18:19:36.471Z</v>
       </c>
     </row>
     <row r="71">
@@ -2768,7 +2768,7 @@
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>2026-08-08T07:13:19.079Z</v>
+        <v>2026-08-09T18:19:36.487Z</v>
       </c>
     </row>
     <row r="72">
@@ -2794,13 +2794,13 @@
         <v>PASS</v>
       </c>
       <c r="H72">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I72" t="str">
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>2026-08-08T07:13:19.095Z</v>
+        <v>2026-08-09T18:19:36.502Z</v>
       </c>
     </row>
     <row r="73">
@@ -2832,7 +2832,7 @@
         <v/>
       </c>
       <c r="J73" t="str">
-        <v>2026-08-08T07:13:19.110Z</v>
+        <v>2026-08-09T18:19:36.517Z</v>
       </c>
     </row>
     <row r="74">
@@ -2858,13 +2858,13 @@
         <v>PASS</v>
       </c>
       <c r="H74">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I74" t="str">
         <v/>
       </c>
       <c r="J74" t="str">
-        <v>2026-08-08T07:13:19.125Z</v>
+        <v>2026-08-09T18:19:36.533Z</v>
       </c>
     </row>
     <row r="75">
@@ -2890,13 +2890,13 @@
         <v>PASS</v>
       </c>
       <c r="H75">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I75" t="str">
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>2026-08-08T07:13:19.141Z</v>
+        <v>2026-08-09T18:19:36.548Z</v>
       </c>
     </row>
     <row r="76">
@@ -2928,7 +2928,7 @@
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>2026-08-08T07:13:19.156Z</v>
+        <v>2026-08-09T18:19:36.563Z</v>
       </c>
     </row>
     <row r="77">
@@ -2960,7 +2960,7 @@
         <v/>
       </c>
       <c r="J77" t="str">
-        <v>2026-08-08T07:13:19.172Z</v>
+        <v>2026-08-09T18:19:36.579Z</v>
       </c>
     </row>
     <row r="78">
@@ -2992,7 +2992,7 @@
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>2026-08-08T07:13:19.187Z</v>
+        <v>2026-08-09T18:19:36.594Z</v>
       </c>
     </row>
     <row r="79">
@@ -3018,13 +3018,13 @@
         <v>PASS</v>
       </c>
       <c r="H79">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I79" t="str">
         <v/>
       </c>
       <c r="J79" t="str">
-        <v>2026-08-08T07:13:19.203Z</v>
+        <v>2026-08-09T18:19:36.609Z</v>
       </c>
     </row>
     <row r="80">
@@ -3050,13 +3050,13 @@
         <v>PASS</v>
       </c>
       <c r="H80">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I80" t="str">
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>2026-08-08T07:13:19.218Z</v>
+        <v>2026-08-09T18:19:36.625Z</v>
       </c>
     </row>
     <row r="81">
@@ -3088,7 +3088,7 @@
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>2026-08-08T07:13:19.234Z</v>
+        <v>2026-08-09T18:19:36.641Z</v>
       </c>
     </row>
     <row r="82">
@@ -3120,7 +3120,7 @@
         <v/>
       </c>
       <c r="J82" t="str">
-        <v>2026-08-08T07:13:19.249Z</v>
+        <v>2026-08-09T18:19:36.656Z</v>
       </c>
     </row>
     <row r="83">
@@ -3146,13 +3146,13 @@
         <v>PASS</v>
       </c>
       <c r="H83">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I83" t="str">
         <v/>
       </c>
       <c r="J83" t="str">
-        <v>2026-08-08T07:13:19.265Z</v>
+        <v>2026-08-09T18:19:36.671Z</v>
       </c>
     </row>
     <row r="84">
@@ -3178,13 +3178,13 @@
         <v>PASS</v>
       </c>
       <c r="H84">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I84" t="str">
         <v/>
       </c>
       <c r="J84" t="str">
-        <v>2026-08-08T07:13:19.280Z</v>
+        <v>2026-08-09T18:19:36.687Z</v>
       </c>
     </row>
     <row r="85">
@@ -3210,13 +3210,13 @@
         <v>PASS</v>
       </c>
       <c r="H85">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I85" t="str">
         <v/>
       </c>
       <c r="J85" t="str">
-        <v>2026-08-08T07:13:19.296Z</v>
+        <v>2026-08-09T18:19:36.702Z</v>
       </c>
     </row>
     <row r="86">
@@ -3242,13 +3242,13 @@
         <v>PASS</v>
       </c>
       <c r="H86">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I86" t="str">
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>2026-08-08T07:13:19.312Z</v>
+        <v>2026-08-09T18:19:36.717Z</v>
       </c>
     </row>
     <row r="87">
@@ -3280,7 +3280,7 @@
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>2026-08-08T07:13:19.327Z</v>
+        <v>2026-08-09T18:19:36.733Z</v>
       </c>
     </row>
     <row r="88">
@@ -3306,13 +3306,13 @@
         <v>PASS</v>
       </c>
       <c r="H88">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I88" t="str">
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>2026-08-08T07:13:19.343Z</v>
+        <v>2026-08-09T18:19:36.748Z</v>
       </c>
     </row>
     <row r="89">
@@ -3338,13 +3338,13 @@
         <v>PASS</v>
       </c>
       <c r="H89">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I89" t="str">
         <v/>
       </c>
       <c r="J89" t="str">
-        <v>2026-08-08T07:13:19.358Z</v>
+        <v>2026-08-09T18:19:36.764Z</v>
       </c>
     </row>
     <row r="90">
@@ -3370,13 +3370,13 @@
         <v>PASS</v>
       </c>
       <c r="H90">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I90" t="str">
         <v/>
       </c>
       <c r="J90" t="str">
-        <v>2026-08-08T07:13:19.374Z</v>
+        <v>2026-08-09T18:19:36.778Z</v>
       </c>
     </row>
     <row r="91">
@@ -3402,13 +3402,13 @@
         <v>PASS</v>
       </c>
       <c r="H91">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I91" t="str">
         <v/>
       </c>
       <c r="J91" t="str">
-        <v>2026-08-08T07:13:19.389Z</v>
+        <v>2026-08-09T18:19:36.794Z</v>
       </c>
     </row>
     <row r="92">
@@ -3434,13 +3434,13 @@
         <v>PASS</v>
       </c>
       <c r="H92">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I92" t="str">
         <v/>
       </c>
       <c r="J92" t="str">
-        <v>2026-08-08T07:13:19.405Z</v>
+        <v>2026-08-09T18:19:36.809Z</v>
       </c>
     </row>
     <row r="93">
@@ -3466,13 +3466,13 @@
         <v>PASS</v>
       </c>
       <c r="H93">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I93" t="str">
         <v/>
       </c>
       <c r="J93" t="str">
-        <v>2026-08-08T07:13:19.422Z</v>
+        <v>2026-08-09T18:19:36.825Z</v>
       </c>
     </row>
     <row r="94">
@@ -3498,13 +3498,13 @@
         <v>PASS</v>
       </c>
       <c r="H94">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I94" t="str">
         <v/>
       </c>
       <c r="J94" t="str">
-        <v>2026-08-08T07:13:19.438Z</v>
+        <v>2026-08-09T18:19:36.840Z</v>
       </c>
     </row>
     <row r="95">
@@ -3536,7 +3536,7 @@
         <v/>
       </c>
       <c r="J95" t="str">
-        <v>2026-08-08T07:13:19.454Z</v>
+        <v>2026-08-09T18:19:36.856Z</v>
       </c>
     </row>
     <row r="96">
@@ -3562,13 +3562,13 @@
         <v>PASS</v>
       </c>
       <c r="H96">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I96" t="str">
         <v/>
       </c>
       <c r="J96" t="str">
-        <v>2026-08-08T07:13:19.469Z</v>
+        <v>2026-08-09T18:19:36.872Z</v>
       </c>
     </row>
     <row r="97">
@@ -3600,7 +3600,7 @@
         <v/>
       </c>
       <c r="J97" t="str">
-        <v>2026-08-08T07:13:19.484Z</v>
+        <v>2026-08-09T18:19:36.887Z</v>
       </c>
     </row>
     <row r="98">
@@ -3626,13 +3626,13 @@
         <v>PASS</v>
       </c>
       <c r="H98">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I98" t="str">
         <v/>
       </c>
       <c r="J98" t="str">
-        <v>2026-08-08T07:13:19.500Z</v>
+        <v>2026-08-09T18:19:36.904Z</v>
       </c>
     </row>
     <row r="99">
@@ -3664,7 +3664,7 @@
         <v/>
       </c>
       <c r="J99" t="str">
-        <v>2026-08-08T07:13:19.515Z</v>
+        <v>2026-08-09T18:19:36.919Z</v>
       </c>
     </row>
     <row r="100">
@@ -3690,13 +3690,13 @@
         <v>PASS</v>
       </c>
       <c r="H100">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I100" t="str">
         <v/>
       </c>
       <c r="J100" t="str">
-        <v>2026-08-08T07:13:19.531Z</v>
+        <v>2026-08-09T18:19:36.934Z</v>
       </c>
     </row>
     <row r="101">
@@ -3728,7 +3728,7 @@
         <v/>
       </c>
       <c r="J101" t="str">
-        <v>2026-08-08T07:13:19.546Z</v>
+        <v>2026-08-09T18:19:36.949Z</v>
       </c>
     </row>
     <row r="102">
@@ -3754,13 +3754,13 @@
         <v>PASS</v>
       </c>
       <c r="H102">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I102" t="str">
         <v/>
       </c>
       <c r="J102" t="str">
-        <v>2026-08-08T07:13:19.561Z</v>
+        <v>2026-08-09T18:19:36.966Z</v>
       </c>
     </row>
     <row r="103">
@@ -3786,13 +3786,13 @@
         <v>PASS</v>
       </c>
       <c r="H103">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I103" t="str">
         <v/>
       </c>
       <c r="J103" t="str">
-        <v>2026-08-08T07:13:19.577Z</v>
+        <v>2026-08-09T18:19:36.979Z</v>
       </c>
     </row>
     <row r="104">
@@ -3824,7 +3824,7 @@
         <v/>
       </c>
       <c r="J104" t="str">
-        <v>2026-08-08T07:13:19.593Z</v>
+        <v>2026-08-09T18:19:36.995Z</v>
       </c>
     </row>
     <row r="105">
@@ -3850,13 +3850,13 @@
         <v>PASS</v>
       </c>
       <c r="H105">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I105" t="str">
         <v/>
       </c>
       <c r="J105" t="str">
-        <v>2026-08-08T07:13:19.608Z</v>
+        <v>2026-08-09T18:19:37.012Z</v>
       </c>
     </row>
     <row r="106">
@@ -3882,13 +3882,13 @@
         <v>PASS</v>
       </c>
       <c r="H106">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I106" t="str">
         <v/>
       </c>
       <c r="J106" t="str">
-        <v>2026-08-08T07:13:19.624Z</v>
+        <v>2026-08-09T18:19:37.026Z</v>
       </c>
     </row>
     <row r="107">
@@ -3920,7 +3920,7 @@
         <v/>
       </c>
       <c r="J107" t="str">
-        <v>2026-08-08T07:13:19.640Z</v>
+        <v>2026-08-09T18:19:37.042Z</v>
       </c>
     </row>
     <row r="108">
@@ -3946,13 +3946,13 @@
         <v>PASS</v>
       </c>
       <c r="H108">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I108" t="str">
         <v/>
       </c>
       <c r="J108" t="str">
-        <v>2026-08-08T07:13:19.655Z</v>
+        <v>2026-08-09T18:19:37.058Z</v>
       </c>
     </row>
     <row r="109">
@@ -3984,7 +3984,7 @@
         <v/>
       </c>
       <c r="J109" t="str">
-        <v>2026-08-08T07:13:19.670Z</v>
+        <v>2026-08-09T18:19:37.073Z</v>
       </c>
     </row>
     <row r="110">
@@ -4016,7 +4016,7 @@
         <v/>
       </c>
       <c r="J110" t="str">
-        <v>2026-08-08T07:13:19.686Z</v>
+        <v>2026-08-09T18:19:37.089Z</v>
       </c>
     </row>
     <row r="111">
@@ -4048,7 +4048,7 @@
         <v/>
       </c>
       <c r="J111" t="str">
-        <v>2026-08-08T07:13:19.701Z</v>
+        <v>2026-08-09T18:19:37.104Z</v>
       </c>
     </row>
     <row r="112">
@@ -4074,13 +4074,13 @@
         <v>PASS</v>
       </c>
       <c r="H112">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I112" t="str">
         <v/>
       </c>
       <c r="J112" t="str">
-        <v>2026-08-08T07:13:19.717Z</v>
+        <v>2026-08-09T18:19:37.119Z</v>
       </c>
     </row>
     <row r="113">
@@ -4106,13 +4106,13 @@
         <v>PASS</v>
       </c>
       <c r="H113">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I113" t="str">
         <v/>
       </c>
       <c r="J113" t="str">
-        <v>2026-08-08T07:13:19.733Z</v>
+        <v>2026-08-09T18:19:37.134Z</v>
       </c>
     </row>
     <row r="114">
@@ -4144,7 +4144,7 @@
         <v/>
       </c>
       <c r="J114" t="str">
-        <v>2026-08-08T07:13:19.748Z</v>
+        <v>2026-08-09T18:19:37.149Z</v>
       </c>
     </row>
     <row r="115">
@@ -4170,13 +4170,13 @@
         <v>PASS</v>
       </c>
       <c r="H115">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I115" t="str">
         <v/>
       </c>
       <c r="J115" t="str">
-        <v>2026-08-08T07:13:19.764Z</v>
+        <v>2026-08-09T18:19:37.164Z</v>
       </c>
     </row>
     <row r="116">
@@ -4202,13 +4202,13 @@
         <v>PASS</v>
       </c>
       <c r="H116">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I116" t="str">
         <v/>
       </c>
       <c r="J116" t="str">
-        <v>2026-08-08T07:13:19.780Z</v>
+        <v>2026-08-09T18:19:37.181Z</v>
       </c>
     </row>
     <row r="117">
@@ -4234,13 +4234,13 @@
         <v>PASS</v>
       </c>
       <c r="H117">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I117" t="str">
         <v/>
       </c>
       <c r="J117" t="str">
-        <v>2026-08-08T07:13:19.796Z</v>
+        <v>2026-08-09T18:19:37.196Z</v>
       </c>
     </row>
     <row r="118">
@@ -4272,7 +4272,7 @@
         <v/>
       </c>
       <c r="J118" t="str">
-        <v>2026-08-08T07:13:19.812Z</v>
+        <v>2026-08-09T18:19:37.211Z</v>
       </c>
     </row>
     <row r="119">
@@ -4298,13 +4298,13 @@
         <v>PASS</v>
       </c>
       <c r="H119">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I119" t="str">
         <v/>
       </c>
       <c r="J119" t="str">
-        <v>2026-08-08T07:13:19.827Z</v>
+        <v>2026-08-09T18:19:37.227Z</v>
       </c>
     </row>
     <row r="120">
@@ -4330,13 +4330,13 @@
         <v>PASS</v>
       </c>
       <c r="H120">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I120" t="str">
         <v/>
       </c>
       <c r="J120" t="str">
-        <v>2026-08-08T07:13:19.842Z</v>
+        <v>2026-08-09T18:19:37.243Z</v>
       </c>
     </row>
     <row r="121">
@@ -4362,13 +4362,13 @@
         <v>PASS</v>
       </c>
       <c r="H121">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I121" t="str">
         <v/>
       </c>
       <c r="J121" t="str">
-        <v>2026-08-08T07:13:19.858Z</v>
+        <v>2026-08-09T18:19:37.258Z</v>
       </c>
     </row>
     <row r="122">
@@ -4394,13 +4394,13 @@
         <v>PASS</v>
       </c>
       <c r="H122">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I122" t="str">
         <v/>
       </c>
       <c r="J122" t="str">
-        <v>2026-08-08T07:13:19.873Z</v>
+        <v>2026-08-09T18:19:37.275Z</v>
       </c>
     </row>
     <row r="123">
@@ -4432,7 +4432,7 @@
         <v/>
       </c>
       <c r="J123" t="str">
-        <v>2026-08-08T07:13:19.889Z</v>
+        <v>2026-08-09T18:19:37.291Z</v>
       </c>
     </row>
     <row r="124">
@@ -4458,13 +4458,13 @@
         <v>PASS</v>
       </c>
       <c r="H124">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I124" t="str">
         <v/>
       </c>
       <c r="J124" t="str">
-        <v>2026-08-08T07:13:19.905Z</v>
+        <v>2026-08-09T18:19:37.306Z</v>
       </c>
     </row>
     <row r="125">
@@ -4490,13 +4490,13 @@
         <v>PASS</v>
       </c>
       <c r="H125">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I125" t="str">
         <v/>
       </c>
       <c r="J125" t="str">
-        <v>2026-08-08T07:13:19.921Z</v>
+        <v>2026-08-09T18:19:37.321Z</v>
       </c>
     </row>
     <row r="126">
@@ -4528,7 +4528,7 @@
         <v/>
       </c>
       <c r="J126" t="str">
-        <v>2026-08-08T07:13:19.936Z</v>
+        <v>2026-08-09T18:19:37.336Z</v>
       </c>
     </row>
     <row r="127">
@@ -4560,7 +4560,7 @@
         <v/>
       </c>
       <c r="J127" t="str">
-        <v>2026-08-08T07:13:19.951Z</v>
+        <v>2026-08-09T18:19:37.351Z</v>
       </c>
     </row>
     <row r="128">
@@ -4586,13 +4586,13 @@
         <v>PASS</v>
       </c>
       <c r="H128">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I128" t="str">
         <v/>
       </c>
       <c r="J128" t="str">
-        <v>2026-08-08T07:13:19.967Z</v>
+        <v>2026-08-09T18:19:37.367Z</v>
       </c>
     </row>
     <row r="129">
@@ -4618,13 +4618,13 @@
         <v>PASS</v>
       </c>
       <c r="H129">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I129" t="str">
         <v/>
       </c>
       <c r="J129" t="str">
-        <v>2026-08-08T07:13:19.983Z</v>
+        <v>2026-08-09T18:19:37.382Z</v>
       </c>
     </row>
     <row r="130">
@@ -4656,7 +4656,7 @@
         <v/>
       </c>
       <c r="J130" t="str">
-        <v>2026-08-08T07:13:19.999Z</v>
+        <v>2026-08-09T18:19:37.398Z</v>
       </c>
     </row>
     <row r="131">
@@ -4682,13 +4682,13 @@
         <v>PASS</v>
       </c>
       <c r="H131">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I131" t="str">
         <v/>
       </c>
       <c r="J131" t="str">
-        <v>2026-08-08T07:13:20.013Z</v>
+        <v>2026-08-09T18:19:37.413Z</v>
       </c>
     </row>
     <row r="132">
@@ -4720,7 +4720,7 @@
         <v/>
       </c>
       <c r="J132" t="str">
-        <v>2026-08-08T07:13:20.029Z</v>
+        <v>2026-08-09T18:19:37.428Z</v>
       </c>
     </row>
     <row r="133">
@@ -4746,13 +4746,13 @@
         <v>PASS</v>
       </c>
       <c r="H133">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I133" t="str">
         <v/>
       </c>
       <c r="J133" t="str">
-        <v>2026-08-08T07:13:20.044Z</v>
+        <v>2026-08-09T18:19:37.444Z</v>
       </c>
     </row>
     <row r="134">
@@ -4778,13 +4778,13 @@
         <v>PASS</v>
       </c>
       <c r="H134">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I134" t="str">
         <v/>
       </c>
       <c r="J134" t="str">
-        <v>2026-08-08T07:13:20.060Z</v>
+        <v>2026-08-09T18:19:37.458Z</v>
       </c>
     </row>
     <row r="135">
@@ -4816,7 +4816,7 @@
         <v/>
       </c>
       <c r="J135" t="str">
-        <v>2026-08-08T07:13:20.077Z</v>
+        <v>2026-08-09T18:19:37.474Z</v>
       </c>
     </row>
     <row r="136">
@@ -4842,13 +4842,13 @@
         <v>PASS</v>
       </c>
       <c r="H136">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I136" t="str">
         <v/>
       </c>
       <c r="J136" t="str">
-        <v>2026-08-08T07:13:20.092Z</v>
+        <v>2026-08-09T18:19:37.491Z</v>
       </c>
     </row>
     <row r="137">
@@ -4874,13 +4874,13 @@
         <v>PASS</v>
       </c>
       <c r="H137">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I137" t="str">
         <v/>
       </c>
       <c r="J137" t="str">
-        <v>2026-08-08T07:13:20.107Z</v>
+        <v>2026-08-09T18:19:37.505Z</v>
       </c>
     </row>
     <row r="138">
@@ -4906,13 +4906,13 @@
         <v>PASS</v>
       </c>
       <c r="H138">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I138" t="str">
         <v/>
       </c>
       <c r="J138" t="str">
-        <v>2026-08-08T07:13:20.122Z</v>
+        <v>2026-08-09T18:19:37.521Z</v>
       </c>
     </row>
     <row r="139">
@@ -4938,13 +4938,13 @@
         <v>PASS</v>
       </c>
       <c r="H139">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I139" t="str">
         <v/>
       </c>
       <c r="J139" t="str">
-        <v>2026-08-08T07:13:20.138Z</v>
+        <v>2026-08-09T18:19:37.536Z</v>
       </c>
     </row>
     <row r="140">
@@ -4970,13 +4970,13 @@
         <v>PASS</v>
       </c>
       <c r="H140">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I140" t="str">
         <v/>
       </c>
       <c r="J140" t="str">
-        <v>2026-08-08T07:13:20.153Z</v>
+        <v>2026-08-09T18:19:37.552Z</v>
       </c>
     </row>
     <row r="141">
@@ -5008,7 +5008,7 @@
         <v/>
       </c>
       <c r="J141" t="str">
-        <v>2026-08-08T07:13:20.169Z</v>
+        <v>2026-08-09T18:19:37.568Z</v>
       </c>
     </row>
     <row r="142">
@@ -5034,13 +5034,13 @@
         <v>PASS</v>
       </c>
       <c r="H142">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I142" t="str">
         <v/>
       </c>
       <c r="J142" t="str">
-        <v>2026-08-08T07:13:20.185Z</v>
+        <v>2026-08-09T18:19:37.583Z</v>
       </c>
     </row>
     <row r="143">
@@ -5066,13 +5066,13 @@
         <v>PASS</v>
       </c>
       <c r="H143">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I143" t="str">
         <v/>
       </c>
       <c r="J143" t="str">
-        <v>2026-08-08T07:13:20.200Z</v>
+        <v>2026-08-09T18:19:37.599Z</v>
       </c>
     </row>
     <row r="144">
@@ -5098,13 +5098,13 @@
         <v>PASS</v>
       </c>
       <c r="H144">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I144" t="str">
         <v/>
       </c>
       <c r="J144" t="str">
-        <v>2026-08-08T07:13:20.216Z</v>
+        <v>2026-08-09T18:19:37.614Z</v>
       </c>
     </row>
     <row r="145">
@@ -5136,7 +5136,7 @@
         <v/>
       </c>
       <c r="J145" t="str">
-        <v>2026-08-08T07:13:20.231Z</v>
+        <v>2026-08-09T18:19:37.629Z</v>
       </c>
     </row>
     <row r="146">
@@ -5162,13 +5162,13 @@
         <v>PASS</v>
       </c>
       <c r="H146">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I146" t="str">
         <v/>
       </c>
       <c r="J146" t="str">
-        <v>2026-08-08T07:13:20.247Z</v>
+        <v>2026-08-09T18:19:37.644Z</v>
       </c>
     </row>
     <row r="147">
@@ -5194,13 +5194,13 @@
         <v>PASS</v>
       </c>
       <c r="H147">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I147" t="str">
         <v/>
       </c>
       <c r="J147" t="str">
-        <v>2026-08-08T07:13:20.264Z</v>
+        <v>2026-08-09T18:19:37.661Z</v>
       </c>
     </row>
     <row r="148">
@@ -5232,7 +5232,7 @@
         <v/>
       </c>
       <c r="J148" t="str">
-        <v>2026-08-08T07:13:20.279Z</v>
+        <v>2026-08-09T18:19:37.676Z</v>
       </c>
     </row>
     <row r="149">
@@ -5258,13 +5258,13 @@
         <v>PASS</v>
       </c>
       <c r="H149">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I149" t="str">
         <v/>
       </c>
       <c r="J149" t="str">
-        <v>2026-08-08T07:13:20.294Z</v>
+        <v>2026-08-09T18:19:37.692Z</v>
       </c>
     </row>
     <row r="150">
@@ -5296,7 +5296,7 @@
         <v/>
       </c>
       <c r="J150" t="str">
-        <v>2026-08-08T07:13:20.312Z</v>
+        <v>2026-08-09T18:19:37.708Z</v>
       </c>
     </row>
     <row r="151">
@@ -5322,13 +5322,13 @@
         <v>PASS</v>
       </c>
       <c r="H151">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I151" t="str">
         <v/>
       </c>
       <c r="J151" t="str">
-        <v>2026-08-08T07:13:20.326Z</v>
+        <v>2026-08-09T18:19:37.723Z</v>
       </c>
     </row>
     <row r="152">
@@ -5354,13 +5354,13 @@
         <v>PASS</v>
       </c>
       <c r="H152">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I152" t="str">
         <v/>
       </c>
       <c r="J152" t="str">
-        <v>2026-08-08T07:13:20.342Z</v>
+        <v>2026-08-09T18:19:37.739Z</v>
       </c>
     </row>
     <row r="153">
@@ -5386,13 +5386,13 @@
         <v>PASS</v>
       </c>
       <c r="H153">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I153" t="str">
         <v/>
       </c>
       <c r="J153" t="str">
-        <v>2026-08-08T07:13:20.358Z</v>
+        <v>2026-08-09T18:19:37.754Z</v>
       </c>
     </row>
     <row r="154">
@@ -5424,7 +5424,7 @@
         <v/>
       </c>
       <c r="J154" t="str">
-        <v>2026-08-08T07:13:20.373Z</v>
+        <v>2026-08-09T18:19:37.769Z</v>
       </c>
     </row>
     <row r="155">
@@ -5456,7 +5456,7 @@
         <v/>
       </c>
       <c r="J155" t="str">
-        <v>2026-08-08T07:13:20.389Z</v>
+        <v>2026-08-09T18:19:37.785Z</v>
       </c>
     </row>
     <row r="156">
@@ -5482,13 +5482,13 @@
         <v>PASS</v>
       </c>
       <c r="H156">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I156" t="str">
         <v/>
       </c>
       <c r="J156" t="str">
-        <v>2026-08-08T07:13:20.404Z</v>
+        <v>2026-08-09T18:19:37.801Z</v>
       </c>
     </row>
     <row r="157">
@@ -5520,7 +5520,7 @@
         <v/>
       </c>
       <c r="J157" t="str">
-        <v>2026-08-08T07:13:20.420Z</v>
+        <v>2026-08-09T18:19:37.817Z</v>
       </c>
     </row>
     <row r="158">
@@ -5552,7 +5552,7 @@
         <v/>
       </c>
       <c r="J158" t="str">
-        <v>2026-08-08T07:13:20.435Z</v>
+        <v>2026-08-09T18:19:37.832Z</v>
       </c>
     </row>
     <row r="159">
@@ -5578,13 +5578,13 @@
         <v>PASS</v>
       </c>
       <c r="H159">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I159" t="str">
         <v/>
       </c>
       <c r="J159" t="str">
-        <v>2026-08-08T07:13:20.450Z</v>
+        <v>2026-08-09T18:19:37.848Z</v>
       </c>
     </row>
     <row r="160">
@@ -5610,13 +5610,13 @@
         <v>PASS</v>
       </c>
       <c r="H160">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I160" t="str">
         <v/>
       </c>
       <c r="J160" t="str">
-        <v>2026-08-08T07:13:20.466Z</v>
+        <v>2026-08-09T18:19:37.863Z</v>
       </c>
     </row>
     <row r="161">
@@ -5648,7 +5648,7 @@
         <v/>
       </c>
       <c r="J161" t="str">
-        <v>2026-08-08T07:13:20.482Z</v>
+        <v>2026-08-09T18:19:37.879Z</v>
       </c>
     </row>
     <row r="162">
@@ -5680,7 +5680,7 @@
         <v/>
       </c>
       <c r="J162" t="str">
-        <v>2026-08-08T07:13:20.498Z</v>
+        <v>2026-08-09T18:19:37.896Z</v>
       </c>
     </row>
     <row r="163">
@@ -5706,13 +5706,13 @@
         <v>PASS</v>
       </c>
       <c r="H163">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I163" t="str">
         <v/>
       </c>
       <c r="J163" t="str">
-        <v>2026-08-08T07:13:20.512Z</v>
+        <v>2026-08-09T18:19:37.911Z</v>
       </c>
     </row>
     <row r="164">
@@ -5738,13 +5738,13 @@
         <v>PASS</v>
       </c>
       <c r="H164">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I164" t="str">
         <v/>
       </c>
       <c r="J164" t="str">
-        <v>2026-08-08T07:13:20.529Z</v>
+        <v>2026-08-09T18:19:37.927Z</v>
       </c>
     </row>
     <row r="165">
@@ -5776,7 +5776,7 @@
         <v/>
       </c>
       <c r="J165" t="str">
-        <v>2026-08-08T07:13:20.543Z</v>
+        <v>2026-08-09T18:19:37.941Z</v>
       </c>
     </row>
     <row r="166">
@@ -5808,7 +5808,7 @@
         <v/>
       </c>
       <c r="J166" t="str">
-        <v>2026-08-08T07:13:20.559Z</v>
+        <v>2026-08-09T18:19:37.957Z</v>
       </c>
     </row>
     <row r="167">
@@ -5840,7 +5840,7 @@
         <v/>
       </c>
       <c r="J167" t="str">
-        <v>2026-08-08T07:13:20.574Z</v>
+        <v>2026-08-09T18:19:37.972Z</v>
       </c>
     </row>
     <row r="168">
@@ -5872,7 +5872,7 @@
         <v/>
       </c>
       <c r="J168" t="str">
-        <v>2026-08-08T07:13:20.589Z</v>
+        <v>2026-08-09T18:19:37.987Z</v>
       </c>
     </row>
     <row r="169">
@@ -5898,13 +5898,13 @@
         <v>PASS</v>
       </c>
       <c r="H169">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I169" t="str">
         <v/>
       </c>
       <c r="J169" t="str">
-        <v>2026-08-08T07:13:20.605Z</v>
+        <v>2026-08-09T18:19:38.002Z</v>
       </c>
     </row>
     <row r="170">
@@ -5936,7 +5936,7 @@
         <v/>
       </c>
       <c r="J170" t="str">
-        <v>2026-08-08T07:13:20.621Z</v>
+        <v>2026-08-09T18:19:38.018Z</v>
       </c>
     </row>
     <row r="171">
@@ -5962,13 +5962,13 @@
         <v>PASS</v>
       </c>
       <c r="H171">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I171" t="str">
         <v/>
       </c>
       <c r="J171" t="str">
-        <v>2026-08-08T07:13:20.636Z</v>
+        <v>2026-08-09T18:19:38.034Z</v>
       </c>
     </row>
     <row r="172">
@@ -5994,13 +5994,13 @@
         <v>PASS</v>
       </c>
       <c r="H172">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I172" t="str">
         <v/>
       </c>
       <c r="J172" t="str">
-        <v>2026-08-08T07:13:20.651Z</v>
+        <v>2026-08-09T18:19:38.050Z</v>
       </c>
     </row>
     <row r="173">
@@ -6032,7 +6032,7 @@
         <v/>
       </c>
       <c r="J173" t="str">
-        <v>2026-08-08T07:13:20.667Z</v>
+        <v>2026-08-09T18:19:38.066Z</v>
       </c>
     </row>
     <row r="174">
@@ -6058,13 +6058,13 @@
         <v>PASS</v>
       </c>
       <c r="H174">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I174" t="str">
         <v/>
       </c>
       <c r="J174" t="str">
-        <v>2026-08-08T07:13:20.683Z</v>
+        <v>2026-08-09T18:19:38.081Z</v>
       </c>
     </row>
     <row r="175">
@@ -6096,7 +6096,7 @@
         <v/>
       </c>
       <c r="J175" t="str">
-        <v>2026-08-08T07:13:20.699Z</v>
+        <v>2026-08-09T18:19:38.097Z</v>
       </c>
     </row>
     <row r="176">
@@ -6122,13 +6122,13 @@
         <v>PASS</v>
       </c>
       <c r="H176">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I176" t="str">
         <v/>
       </c>
       <c r="J176" t="str">
-        <v>2026-08-08T07:13:20.714Z</v>
+        <v>2026-08-09T18:19:38.112Z</v>
       </c>
     </row>
     <row r="177">
@@ -6154,13 +6154,13 @@
         <v>PASS</v>
       </c>
       <c r="H177">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I177" t="str">
         <v/>
       </c>
       <c r="J177" t="str">
-        <v>2026-08-08T07:13:20.729Z</v>
+        <v>2026-08-09T18:19:38.128Z</v>
       </c>
     </row>
     <row r="178">
@@ -6186,13 +6186,13 @@
         <v>PASS</v>
       </c>
       <c r="H178">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I178" t="str">
         <v/>
       </c>
       <c r="J178" t="str">
-        <v>2026-08-08T07:13:20.745Z</v>
+        <v>2026-08-09T18:19:38.143Z</v>
       </c>
     </row>
     <row r="179">
@@ -6218,13 +6218,13 @@
         <v>PASS</v>
       </c>
       <c r="H179">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I179" t="str">
         <v/>
       </c>
       <c r="J179" t="str">
-        <v>2026-08-08T07:13:20.760Z</v>
+        <v>2026-08-09T18:19:38.159Z</v>
       </c>
     </row>
     <row r="180">
@@ -6250,13 +6250,13 @@
         <v>PASS</v>
       </c>
       <c r="H180">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I180" t="str">
         <v/>
       </c>
       <c r="J180" t="str">
-        <v>2026-08-08T07:13:20.776Z</v>
+        <v>2026-08-09T18:19:38.177Z</v>
       </c>
     </row>
     <row r="181">
@@ -6282,13 +6282,13 @@
         <v>PASS</v>
       </c>
       <c r="H181">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I181" t="str">
         <v/>
       </c>
       <c r="J181" t="str">
-        <v>2026-08-08T07:13:20.791Z</v>
+        <v>2026-08-09T18:19:38.190Z</v>
       </c>
     </row>
     <row r="182">
@@ -6314,13 +6314,13 @@
         <v>PASS</v>
       </c>
       <c r="H182">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I182" t="str">
         <v/>
       </c>
       <c r="J182" t="str">
-        <v>2026-08-08T07:13:20.808Z</v>
+        <v>2026-08-09T18:19:38.205Z</v>
       </c>
     </row>
     <row r="183">
@@ -6352,7 +6352,7 @@
         <v/>
       </c>
       <c r="J183" t="str">
-        <v>2026-08-08T07:13:20.824Z</v>
+        <v>2026-08-09T18:19:38.221Z</v>
       </c>
     </row>
     <row r="184">
@@ -6384,7 +6384,7 @@
         <v/>
       </c>
       <c r="J184" t="str">
-        <v>2026-08-08T07:13:20.840Z</v>
+        <v>2026-08-09T18:19:38.237Z</v>
       </c>
     </row>
     <row r="185">
@@ -6416,7 +6416,7 @@
         <v/>
       </c>
       <c r="J185" t="str">
-        <v>2026-08-08T07:13:20.855Z</v>
+        <v>2026-08-09T18:19:38.252Z</v>
       </c>
     </row>
     <row r="186">
@@ -6442,13 +6442,13 @@
         <v>PASS</v>
       </c>
       <c r="H186">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I186" t="str">
         <v/>
       </c>
       <c r="J186" t="str">
-        <v>2026-08-08T07:13:20.871Z</v>
+        <v>2026-08-09T18:19:38.267Z</v>
       </c>
     </row>
     <row r="187">
@@ -6474,13 +6474,13 @@
         <v>PASS</v>
       </c>
       <c r="H187">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I187" t="str">
         <v/>
       </c>
       <c r="J187" t="str">
-        <v>2026-08-08T07:13:20.886Z</v>
+        <v>2026-08-09T18:19:38.283Z</v>
       </c>
     </row>
     <row r="188">
@@ -6506,13 +6506,13 @@
         <v>PASS</v>
       </c>
       <c r="H188">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I188" t="str">
         <v/>
       </c>
       <c r="J188" t="str">
-        <v>2026-08-08T07:13:20.903Z</v>
+        <v>2026-08-09T18:19:38.299Z</v>
       </c>
     </row>
     <row r="189">
@@ -6544,7 +6544,7 @@
         <v/>
       </c>
       <c r="J189" t="str">
-        <v>2026-08-08T07:13:20.918Z</v>
+        <v>2026-08-09T18:19:38.314Z</v>
       </c>
     </row>
     <row r="190">
@@ -6570,13 +6570,13 @@
         <v>PASS</v>
       </c>
       <c r="H190">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I190" t="str">
         <v/>
       </c>
       <c r="J190" t="str">
-        <v>2026-08-08T07:13:20.933Z</v>
+        <v>2026-08-09T18:19:38.330Z</v>
       </c>
     </row>
     <row r="191">
@@ -6602,13 +6602,13 @@
         <v>PASS</v>
       </c>
       <c r="H191">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I191" t="str">
         <v/>
       </c>
       <c r="J191" t="str">
-        <v>2026-08-08T07:13:20.949Z</v>
+        <v>2026-08-09T18:19:38.346Z</v>
       </c>
     </row>
     <row r="192">
@@ -6634,13 +6634,13 @@
         <v>PASS</v>
       </c>
       <c r="H192">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I192" t="str">
         <v/>
       </c>
       <c r="J192" t="str">
-        <v>2026-08-08T07:13:20.965Z</v>
+        <v>2026-08-09T18:19:38.363Z</v>
       </c>
     </row>
     <row r="193">
@@ -6666,13 +6666,13 @@
         <v>PASS</v>
       </c>
       <c r="H193">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I193" t="str">
         <v/>
       </c>
       <c r="J193" t="str">
-        <v>2026-08-08T07:13:20.981Z</v>
+        <v>2026-08-09T18:19:38.377Z</v>
       </c>
     </row>
     <row r="194">
@@ -6698,13 +6698,13 @@
         <v>PASS</v>
       </c>
       <c r="H194">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I194" t="str">
         <v/>
       </c>
       <c r="J194" t="str">
-        <v>2026-08-08T07:13:20.996Z</v>
+        <v>2026-08-09T18:19:38.395Z</v>
       </c>
     </row>
     <row r="195">
@@ -6730,13 +6730,13 @@
         <v>PASS</v>
       </c>
       <c r="H195">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I195" t="str">
         <v/>
       </c>
       <c r="J195" t="str">
-        <v>2026-08-08T07:13:21.011Z</v>
+        <v>2026-08-09T18:19:38.409Z</v>
       </c>
     </row>
     <row r="196">
@@ -6762,13 +6762,13 @@
         <v>PASS</v>
       </c>
       <c r="H196">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I196" t="str">
         <v/>
       </c>
       <c r="J196" t="str">
-        <v>2026-08-08T07:13:21.027Z</v>
+        <v>2026-08-09T18:19:38.423Z</v>
       </c>
     </row>
     <row r="197">
@@ -6794,13 +6794,13 @@
         <v>PASS</v>
       </c>
       <c r="H197">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I197" t="str">
         <v/>
       </c>
       <c r="J197" t="str">
-        <v>2026-08-08T07:13:21.043Z</v>
+        <v>2026-08-09T18:19:38.438Z</v>
       </c>
     </row>
     <row r="198">
@@ -6832,7 +6832,7 @@
         <v/>
       </c>
       <c r="J198" t="str">
-        <v>2026-08-08T07:13:21.058Z</v>
+        <v>2026-08-09T18:19:38.453Z</v>
       </c>
     </row>
     <row r="199">
@@ -6858,13 +6858,13 @@
         <v>PASS</v>
       </c>
       <c r="H199">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I199" t="str">
         <v/>
       </c>
       <c r="J199" t="str">
-        <v>2026-08-08T07:13:21.075Z</v>
+        <v>2026-08-09T18:19:38.469Z</v>
       </c>
     </row>
     <row r="200">
@@ -6890,13 +6890,13 @@
         <v>PASS</v>
       </c>
       <c r="H200">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I200" t="str">
         <v/>
       </c>
       <c r="J200" t="str">
-        <v>2026-08-08T07:13:21.090Z</v>
+        <v>2026-08-09T18:19:38.485Z</v>
       </c>
     </row>
     <row r="201">
@@ -6928,7 +6928,7 @@
         <v/>
       </c>
       <c r="J201" t="str">
-        <v>2026-08-08T07:13:21.105Z</v>
+        <v>2026-08-09T18:19:38.500Z</v>
       </c>
     </row>
     <row r="202">
@@ -6960,7 +6960,7 @@
         <v/>
       </c>
       <c r="J202" t="str">
-        <v>2026-08-08T07:13:21.120Z</v>
+        <v>2026-08-09T18:19:38.515Z</v>
       </c>
     </row>
     <row r="203">
@@ -6992,7 +6992,7 @@
         <v/>
       </c>
       <c r="J203" t="str">
-        <v>2026-08-08T07:13:21.136Z</v>
+        <v>2026-08-09T18:19:38.531Z</v>
       </c>
     </row>
     <row r="204">
@@ -7018,13 +7018,13 @@
         <v>PASS</v>
       </c>
       <c r="H204">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I204" t="str">
         <v/>
       </c>
       <c r="J204" t="str">
-        <v>2026-08-08T07:13:21.151Z</v>
+        <v>2026-08-09T18:19:38.547Z</v>
       </c>
     </row>
     <row r="205">
@@ -7050,13 +7050,13 @@
         <v>PASS</v>
       </c>
       <c r="H205">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I205" t="str">
         <v/>
       </c>
       <c r="J205" t="str">
-        <v>2026-08-08T07:13:21.167Z</v>
+        <v>2026-08-09T18:19:38.562Z</v>
       </c>
     </row>
     <row r="206">
@@ -7082,13 +7082,13 @@
         <v>PASS</v>
       </c>
       <c r="H206">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I206" t="str">
         <v/>
       </c>
       <c r="J206" t="str">
-        <v>2026-08-08T07:13:21.182Z</v>
+        <v>2026-08-09T18:19:38.578Z</v>
       </c>
     </row>
     <row r="207">
@@ -7114,13 +7114,13 @@
         <v>PASS</v>
       </c>
       <c r="H207">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I207" t="str">
         <v/>
       </c>
       <c r="J207" t="str">
-        <v>2026-08-08T07:13:21.198Z</v>
+        <v>2026-08-09T18:19:38.595Z</v>
       </c>
     </row>
     <row r="208">
@@ -7146,13 +7146,13 @@
         <v>PASS</v>
       </c>
       <c r="H208">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I208" t="str">
         <v/>
       </c>
       <c r="J208" t="str">
-        <v>2026-08-08T07:13:21.215Z</v>
+        <v>2026-08-09T18:19:38.609Z</v>
       </c>
     </row>
     <row r="209">
@@ -7178,13 +7178,13 @@
         <v>PASS</v>
       </c>
       <c r="H209">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I209" t="str">
         <v/>
       </c>
       <c r="J209" t="str">
-        <v>2026-08-08T07:13:21.233Z</v>
+        <v>2026-08-09T18:19:38.624Z</v>
       </c>
     </row>
     <row r="210">
@@ -7216,7 +7216,7 @@
         <v/>
       </c>
       <c r="J210" t="str">
-        <v>2026-08-08T07:13:21.248Z</v>
+        <v>2026-08-09T18:19:38.639Z</v>
       </c>
     </row>
     <row r="211">
@@ -7248,7 +7248,7 @@
         <v/>
       </c>
       <c r="J211" t="str">
-        <v>2026-08-08T07:13:21.263Z</v>
+        <v>2026-08-09T18:19:38.654Z</v>
       </c>
     </row>
     <row r="212">
@@ -7280,7 +7280,7 @@
         <v/>
       </c>
       <c r="J212" t="str">
-        <v>2026-08-08T07:13:21.278Z</v>
+        <v>2026-08-09T18:19:38.669Z</v>
       </c>
     </row>
     <row r="213">
@@ -7312,7 +7312,7 @@
         <v/>
       </c>
       <c r="J213" t="str">
-        <v>2026-08-08T07:13:21.294Z</v>
+        <v>2026-08-09T18:19:38.685Z</v>
       </c>
     </row>
     <row r="214">
@@ -7338,13 +7338,13 @@
         <v>PASS</v>
       </c>
       <c r="H214">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I214" t="str">
         <v/>
       </c>
       <c r="J214" t="str">
-        <v>2026-08-08T07:13:21.309Z</v>
+        <v>2026-08-09T18:19:38.701Z</v>
       </c>
     </row>
     <row r="215">
@@ -7370,13 +7370,13 @@
         <v>PASS</v>
       </c>
       <c r="H215">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I215" t="str">
         <v/>
       </c>
       <c r="J215" t="str">
-        <v>2026-08-08T07:13:21.325Z</v>
+        <v>2026-08-09T18:19:38.715Z</v>
       </c>
     </row>
     <row r="216">
@@ -7408,7 +7408,7 @@
         <v/>
       </c>
       <c r="J216" t="str">
-        <v>2026-08-08T07:13:21.341Z</v>
+        <v>2026-08-09T18:19:38.731Z</v>
       </c>
     </row>
     <row r="217">
@@ -7434,13 +7434,13 @@
         <v>PASS</v>
       </c>
       <c r="H217">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I217" t="str">
         <v/>
       </c>
       <c r="J217" t="str">
-        <v>2026-08-08T07:13:21.357Z</v>
+        <v>2026-08-09T18:19:38.746Z</v>
       </c>
     </row>
     <row r="218">
@@ -7472,7 +7472,7 @@
         <v/>
       </c>
       <c r="J218" t="str">
-        <v>2026-08-08T07:13:21.373Z</v>
+        <v>2026-08-09T18:19:38.762Z</v>
       </c>
     </row>
     <row r="219">
@@ -7498,13 +7498,13 @@
         <v>PASS</v>
       </c>
       <c r="H219">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I219" t="str">
         <v/>
       </c>
       <c r="J219" t="str">
-        <v>2026-08-08T07:13:21.389Z</v>
+        <v>2026-08-09T18:19:38.777Z</v>
       </c>
     </row>
     <row r="220">
@@ -7530,13 +7530,13 @@
         <v>PASS</v>
       </c>
       <c r="H220">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I220" t="str">
         <v/>
       </c>
       <c r="J220" t="str">
-        <v>2026-08-08T07:13:21.404Z</v>
+        <v>2026-08-09T18:19:38.794Z</v>
       </c>
     </row>
     <row r="221">
@@ -7568,7 +7568,7 @@
         <v/>
       </c>
       <c r="J221" t="str">
-        <v>2026-08-08T07:13:21.420Z</v>
+        <v>2026-08-09T18:19:38.810Z</v>
       </c>
     </row>
     <row r="222">
@@ -7594,13 +7594,13 @@
         <v>PASS</v>
       </c>
       <c r="H222">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I222" t="str">
         <v/>
       </c>
       <c r="J222" t="str">
-        <v>2026-08-08T07:13:21.436Z</v>
+        <v>2026-08-09T18:19:38.826Z</v>
       </c>
     </row>
     <row r="223">
@@ -7626,13 +7626,13 @@
         <v>PASS</v>
       </c>
       <c r="H223">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I223" t="str">
         <v/>
       </c>
       <c r="J223" t="str">
-        <v>2026-08-08T07:13:21.452Z</v>
+        <v>2026-08-09T18:19:38.841Z</v>
       </c>
     </row>
     <row r="224">
@@ -7664,7 +7664,7 @@
         <v/>
       </c>
       <c r="J224" t="str">
-        <v>2026-08-08T07:13:21.467Z</v>
+        <v>2026-08-09T18:19:38.856Z</v>
       </c>
     </row>
     <row r="225">
@@ -7690,13 +7690,13 @@
         <v>PASS</v>
       </c>
       <c r="H225">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I225" t="str">
         <v/>
       </c>
       <c r="J225" t="str">
-        <v>2026-08-08T07:13:21.482Z</v>
+        <v>2026-08-09T18:19:38.872Z</v>
       </c>
     </row>
     <row r="226">
@@ -7728,7 +7728,7 @@
         <v/>
       </c>
       <c r="J226" t="str">
-        <v>2026-08-08T07:13:21.498Z</v>
+        <v>2026-08-09T18:19:38.888Z</v>
       </c>
     </row>
     <row r="227">
@@ -7760,7 +7760,7 @@
         <v/>
       </c>
       <c r="J227" t="str">
-        <v>2026-08-08T07:13:21.513Z</v>
+        <v>2026-08-09T18:19:38.903Z</v>
       </c>
     </row>
     <row r="228">
@@ -7786,13 +7786,13 @@
         <v>PASS</v>
       </c>
       <c r="H228">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I228" t="str">
         <v/>
       </c>
       <c r="J228" t="str">
-        <v>2026-08-08T07:13:21.528Z</v>
+        <v>2026-08-09T18:19:38.919Z</v>
       </c>
     </row>
     <row r="229">
@@ -7824,7 +7824,7 @@
         <v/>
       </c>
       <c r="J229" t="str">
-        <v>2026-08-08T07:13:21.544Z</v>
+        <v>2026-08-09T18:19:38.935Z</v>
       </c>
     </row>
     <row r="230">
@@ -7850,13 +7850,13 @@
         <v>PASS</v>
       </c>
       <c r="H230">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I230" t="str">
         <v/>
       </c>
       <c r="J230" t="str">
-        <v>2026-08-08T07:13:21.559Z</v>
+        <v>2026-08-09T18:19:38.951Z</v>
       </c>
     </row>
     <row r="231">
@@ -7882,13 +7882,13 @@
         <v>PASS</v>
       </c>
       <c r="H231">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I231" t="str">
         <v/>
       </c>
       <c r="J231" t="str">
-        <v>2026-08-08T07:13:21.574Z</v>
+        <v>2026-08-09T18:19:38.965Z</v>
       </c>
     </row>
     <row r="232">
@@ -7920,7 +7920,7 @@
         <v/>
       </c>
       <c r="J232" t="str">
-        <v>2026-08-08T07:13:21.590Z</v>
+        <v>2026-08-09T18:19:38.981Z</v>
       </c>
     </row>
     <row r="233">
@@ -7946,13 +7946,13 @@
         <v>PASS</v>
       </c>
       <c r="H233">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I233" t="str">
         <v/>
       </c>
       <c r="J233" t="str">
-        <v>2026-08-08T07:13:21.605Z</v>
+        <v>2026-08-09T18:19:38.997Z</v>
       </c>
     </row>
     <row r="234">
@@ -7984,7 +7984,7 @@
         <v/>
       </c>
       <c r="J234" t="str">
-        <v>2026-08-08T07:13:21.620Z</v>
+        <v>2026-08-09T18:19:39.012Z</v>
       </c>
     </row>
     <row r="235">
@@ -8010,13 +8010,13 @@
         <v>PASS</v>
       </c>
       <c r="H235">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I235" t="str">
         <v/>
       </c>
       <c r="J235" t="str">
-        <v>2026-08-08T07:13:21.636Z</v>
+        <v>2026-08-09T18:19:39.029Z</v>
       </c>
     </row>
     <row r="236">
@@ -8048,7 +8048,7 @@
         <v/>
       </c>
       <c r="J236" t="str">
-        <v>2026-08-08T07:13:21.652Z</v>
+        <v>2026-08-09T18:19:39.045Z</v>
       </c>
     </row>
     <row r="237">
@@ -8074,13 +8074,13 @@
         <v>PASS</v>
       </c>
       <c r="H237">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I237" t="str">
         <v/>
       </c>
       <c r="J237" t="str">
-        <v>2026-08-08T07:13:21.668Z</v>
+        <v>2026-08-09T18:19:39.059Z</v>
       </c>
     </row>
     <row r="238">
@@ -8112,7 +8112,7 @@
         <v/>
       </c>
       <c r="J238" t="str">
-        <v>2026-08-08T07:13:21.685Z</v>
+        <v>2026-08-09T18:19:39.076Z</v>
       </c>
     </row>
     <row r="239">
@@ -8144,7 +8144,7 @@
         <v/>
       </c>
       <c r="J239" t="str">
-        <v>2026-08-08T07:13:21.700Z</v>
+        <v>2026-08-09T18:19:39.091Z</v>
       </c>
     </row>
     <row r="240">
@@ -8176,7 +8176,7 @@
         <v/>
       </c>
       <c r="J240" t="str">
-        <v>2026-08-08T07:13:21.716Z</v>
+        <v>2026-08-09T18:19:39.107Z</v>
       </c>
     </row>
     <row r="241">
@@ -8202,13 +8202,13 @@
         <v>PASS</v>
       </c>
       <c r="H241">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I241" t="str">
         <v/>
       </c>
       <c r="J241" t="str">
-        <v>2026-08-08T07:13:21.732Z</v>
+        <v>2026-08-09T18:19:39.122Z</v>
       </c>
     </row>
     <row r="242">
@@ -8234,13 +8234,13 @@
         <v>PASS</v>
       </c>
       <c r="H242">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I242" t="str">
         <v/>
       </c>
       <c r="J242" t="str">
-        <v>2026-08-08T07:13:21.748Z</v>
+        <v>2026-08-09T18:19:39.137Z</v>
       </c>
     </row>
     <row r="243">
@@ -8266,13 +8266,13 @@
         <v>PASS</v>
       </c>
       <c r="H243">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I243" t="str">
         <v/>
       </c>
       <c r="J243" t="str">
-        <v>2026-08-08T07:13:21.763Z</v>
+        <v>2026-08-09T18:19:39.153Z</v>
       </c>
     </row>
     <row r="244">
@@ -8298,13 +8298,13 @@
         <v>PASS</v>
       </c>
       <c r="H244">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I244" t="str">
         <v/>
       </c>
       <c r="J244" t="str">
-        <v>2026-08-08T07:13:21.778Z</v>
+        <v>2026-08-09T18:19:39.169Z</v>
       </c>
     </row>
     <row r="245">
@@ -8330,13 +8330,13 @@
         <v>PASS</v>
       </c>
       <c r="H245">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I245" t="str">
         <v/>
       </c>
       <c r="J245" t="str">
-        <v>2026-08-08T07:13:21.795Z</v>
+        <v>2026-08-09T18:19:39.184Z</v>
       </c>
     </row>
     <row r="246">
@@ -8368,7 +8368,7 @@
         <v/>
       </c>
       <c r="J246" t="str">
-        <v>2026-08-08T07:13:21.810Z</v>
+        <v>2026-08-09T18:19:39.199Z</v>
       </c>
     </row>
     <row r="247">
@@ -8394,13 +8394,13 @@
         <v>PASS</v>
       </c>
       <c r="H247">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I247" t="str">
         <v/>
       </c>
       <c r="J247" t="str">
-        <v>2026-08-08T07:13:21.825Z</v>
+        <v>2026-08-09T18:19:39.215Z</v>
       </c>
     </row>
     <row r="248">
@@ -8426,13 +8426,13 @@
         <v>PASS</v>
       </c>
       <c r="H248">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I248" t="str">
         <v/>
       </c>
       <c r="J248" t="str">
-        <v>2026-08-08T07:13:21.842Z</v>
+        <v>2026-08-09T18:19:39.231Z</v>
       </c>
     </row>
     <row r="249">
@@ -8458,13 +8458,13 @@
         <v>PASS</v>
       </c>
       <c r="H249">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I249" t="str">
         <v/>
       </c>
       <c r="J249" t="str">
-        <v>2026-08-08T07:13:21.856Z</v>
+        <v>2026-08-09T18:19:39.247Z</v>
       </c>
     </row>
     <row r="250">
@@ -8490,13 +8490,13 @@
         <v>PASS</v>
       </c>
       <c r="H250">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I250" t="str">
         <v/>
       </c>
       <c r="J250" t="str">
-        <v>2026-08-08T07:13:21.873Z</v>
+        <v>2026-08-09T18:19:39.263Z</v>
       </c>
     </row>
     <row r="251">
@@ -8528,7 +8528,7 @@
         <v/>
       </c>
       <c r="J251" t="str">
-        <v>2026-08-08T07:13:21.889Z</v>
+        <v>2026-08-09T18:19:39.279Z</v>
       </c>
     </row>
     <row r="252">
@@ -8554,13 +8554,13 @@
         <v>PASS</v>
       </c>
       <c r="H252">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I252" t="str">
         <v/>
       </c>
       <c r="J252" t="str">
-        <v>2026-08-08T07:13:21.905Z</v>
+        <v>2026-08-09T18:19:39.294Z</v>
       </c>
     </row>
     <row r="253">
@@ -8592,7 +8592,7 @@
         <v/>
       </c>
       <c r="J253" t="str">
-        <v>2026-08-08T07:13:21.920Z</v>
+        <v>2026-08-09T18:19:39.309Z</v>
       </c>
     </row>
     <row r="254">
@@ -8618,13 +8618,13 @@
         <v>PASS</v>
       </c>
       <c r="H254">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I254" t="str">
         <v/>
       </c>
       <c r="J254" t="str">
-        <v>2026-08-08T07:13:21.936Z</v>
+        <v>2026-08-09T18:19:39.324Z</v>
       </c>
     </row>
     <row r="255">
@@ -8650,13 +8650,13 @@
         <v>PASS</v>
       </c>
       <c r="H255">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I255" t="str">
         <v/>
       </c>
       <c r="J255" t="str">
-        <v>2026-08-08T07:13:21.952Z</v>
+        <v>2026-08-09T18:19:39.339Z</v>
       </c>
     </row>
     <row r="256">
@@ -8682,13 +8682,13 @@
         <v>PASS</v>
       </c>
       <c r="H256">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I256" t="str">
         <v/>
       </c>
       <c r="J256" t="str">
-        <v>2026-08-08T07:13:21.967Z</v>
+        <v>2026-08-09T18:19:39.355Z</v>
       </c>
     </row>
     <row r="257">
@@ -8714,13 +8714,13 @@
         <v>PASS</v>
       </c>
       <c r="H257">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I257" t="str">
         <v/>
       </c>
       <c r="J257" t="str">
-        <v>2026-08-08T07:13:21.984Z</v>
+        <v>2026-08-09T18:19:39.371Z</v>
       </c>
     </row>
     <row r="258">
@@ -8746,13 +8746,13 @@
         <v>PASS</v>
       </c>
       <c r="H258">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I258" t="str">
         <v/>
       </c>
       <c r="J258" t="str">
-        <v>2026-08-08T07:13:21.999Z</v>
+        <v>2026-08-09T18:19:39.385Z</v>
       </c>
     </row>
     <row r="259">
@@ -8784,7 +8784,7 @@
         <v/>
       </c>
       <c r="J259" t="str">
-        <v>2026-08-08T07:13:22.014Z</v>
+        <v>2026-08-09T18:19:39.400Z</v>
       </c>
     </row>
     <row r="260">
@@ -8810,13 +8810,13 @@
         <v>PASS</v>
       </c>
       <c r="H260">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I260" t="str">
         <v/>
       </c>
       <c r="J260" t="str">
-        <v>2026-08-08T07:13:22.029Z</v>
+        <v>2026-08-09T18:19:39.416Z</v>
       </c>
     </row>
     <row r="261">
@@ -8848,7 +8848,7 @@
         <v/>
       </c>
       <c r="J261" t="str">
-        <v>2026-08-08T07:13:22.045Z</v>
+        <v>2026-08-09T18:19:39.432Z</v>
       </c>
     </row>
     <row r="262">
@@ -8874,13 +8874,13 @@
         <v>PASS</v>
       </c>
       <c r="H262">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I262" t="str">
         <v/>
       </c>
       <c r="J262" t="str">
-        <v>2026-08-08T07:13:22.061Z</v>
+        <v>2026-08-09T18:19:39.448Z</v>
       </c>
     </row>
     <row r="263">
@@ -8906,13 +8906,13 @@
         <v>PASS</v>
       </c>
       <c r="H263">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I263" t="str">
         <v/>
       </c>
       <c r="J263" t="str">
-        <v>2026-08-08T07:13:22.077Z</v>
+        <v>2026-08-09T18:19:39.462Z</v>
       </c>
     </row>
     <row r="264">
@@ -8938,13 +8938,13 @@
         <v>PASS</v>
       </c>
       <c r="H264">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I264" t="str">
         <v/>
       </c>
       <c r="J264" t="str">
-        <v>2026-08-08T07:13:22.092Z</v>
+        <v>2026-08-09T18:19:39.478Z</v>
       </c>
     </row>
     <row r="265">
@@ -8970,13 +8970,13 @@
         <v>PASS</v>
       </c>
       <c r="H265">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I265" t="str">
         <v/>
       </c>
       <c r="J265" t="str">
-        <v>2026-08-08T07:13:22.108Z</v>
+        <v>2026-08-09T18:19:39.495Z</v>
       </c>
     </row>
     <row r="266">
@@ -9008,7 +9008,7 @@
         <v/>
       </c>
       <c r="J266" t="str">
-        <v>2026-08-08T07:13:22.123Z</v>
+        <v>2026-08-09T18:19:39.510Z</v>
       </c>
     </row>
     <row r="267">
@@ -9040,7 +9040,7 @@
         <v/>
       </c>
       <c r="J267" t="str">
-        <v>2026-08-08T07:13:22.138Z</v>
+        <v>2026-08-09T18:19:39.525Z</v>
       </c>
     </row>
     <row r="268">
@@ -9072,7 +9072,7 @@
         <v/>
       </c>
       <c r="J268" t="str">
-        <v>2026-08-08T07:13:22.154Z</v>
+        <v>2026-08-09T18:19:39.541Z</v>
       </c>
     </row>
     <row r="269">
@@ -9098,13 +9098,13 @@
         <v>PASS</v>
       </c>
       <c r="H269">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I269" t="str">
         <v/>
       </c>
       <c r="J269" t="str">
-        <v>2026-08-08T07:13:22.169Z</v>
+        <v>2026-08-09T18:19:39.555Z</v>
       </c>
     </row>
     <row r="270">
@@ -9130,13 +9130,13 @@
         <v>PASS</v>
       </c>
       <c r="H270">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I270" t="str">
         <v/>
       </c>
       <c r="J270" t="str">
-        <v>2026-08-08T07:13:22.185Z</v>
+        <v>2026-08-09T18:19:39.570Z</v>
       </c>
     </row>
     <row r="271">
@@ -9162,13 +9162,13 @@
         <v>PASS</v>
       </c>
       <c r="H271">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I271" t="str">
         <v/>
       </c>
       <c r="J271" t="str">
-        <v>2026-08-08T07:13:22.200Z</v>
+        <v>2026-08-09T18:19:39.587Z</v>
       </c>
     </row>
     <row r="272">
@@ -9194,13 +9194,13 @@
         <v>PASS</v>
       </c>
       <c r="H272">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I272" t="str">
         <v/>
       </c>
       <c r="J272" t="str">
-        <v>2026-08-08T07:13:22.216Z</v>
+        <v>2026-08-09T18:19:39.601Z</v>
       </c>
     </row>
     <row r="273">
@@ -9226,13 +9226,13 @@
         <v>PASS</v>
       </c>
       <c r="H273">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I273" t="str">
         <v/>
       </c>
       <c r="J273" t="str">
-        <v>2026-08-08T07:13:22.231Z</v>
+        <v>2026-08-09T18:19:39.618Z</v>
       </c>
     </row>
     <row r="274">
@@ -9264,7 +9264,7 @@
         <v/>
       </c>
       <c r="J274" t="str">
-        <v>2026-08-08T07:13:22.247Z</v>
+        <v>2026-08-09T18:19:39.633Z</v>
       </c>
     </row>
     <row r="275">
@@ -9290,13 +9290,13 @@
         <v>PASS</v>
       </c>
       <c r="H275">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I275" t="str">
         <v/>
       </c>
       <c r="J275" t="str">
-        <v>2026-08-08T07:13:22.262Z</v>
+        <v>2026-08-09T18:19:39.649Z</v>
       </c>
     </row>
     <row r="276">
@@ -9328,7 +9328,7 @@
         <v/>
       </c>
       <c r="J276" t="str">
-        <v>2026-08-08T07:13:22.278Z</v>
+        <v>2026-08-09T18:19:39.665Z</v>
       </c>
     </row>
     <row r="277">
@@ -9354,13 +9354,13 @@
         <v>PASS</v>
       </c>
       <c r="H277">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I277" t="str">
         <v/>
       </c>
       <c r="J277" t="str">
-        <v>2026-08-08T07:13:22.294Z</v>
+        <v>2026-08-09T18:19:39.681Z</v>
       </c>
     </row>
     <row r="278">
@@ -9392,7 +9392,7 @@
         <v/>
       </c>
       <c r="J278" t="str">
-        <v>2026-08-08T07:13:22.309Z</v>
+        <v>2026-08-09T18:19:39.696Z</v>
       </c>
     </row>
     <row r="279">
@@ -9418,13 +9418,13 @@
         <v>PASS</v>
       </c>
       <c r="H279">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I279" t="str">
         <v/>
       </c>
       <c r="J279" t="str">
-        <v>2026-08-08T07:13:22.325Z</v>
+        <v>2026-08-09T18:19:39.712Z</v>
       </c>
     </row>
     <row r="280">
@@ -9456,7 +9456,7 @@
         <v/>
       </c>
       <c r="J280" t="str">
-        <v>2026-08-08T07:13:22.341Z</v>
+        <v>2026-08-09T18:19:39.727Z</v>
       </c>
     </row>
     <row r="281">
@@ -9488,7 +9488,7 @@
         <v/>
       </c>
       <c r="J281" t="str">
-        <v>2026-08-08T07:13:22.356Z</v>
+        <v>2026-08-09T18:19:39.742Z</v>
       </c>
     </row>
     <row r="282">
@@ -9514,13 +9514,13 @@
         <v>PASS</v>
       </c>
       <c r="H282">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I282" t="str">
         <v/>
       </c>
       <c r="J282" t="str">
-        <v>2026-08-08T07:13:22.371Z</v>
+        <v>2026-08-09T18:19:39.757Z</v>
       </c>
     </row>
     <row r="283">
@@ -9552,7 +9552,7 @@
         <v/>
       </c>
       <c r="J283" t="str">
-        <v>2026-08-08T07:13:22.387Z</v>
+        <v>2026-08-09T18:19:39.774Z</v>
       </c>
     </row>
     <row r="284">
@@ -9578,13 +9578,13 @@
         <v>PASS</v>
       </c>
       <c r="H284">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I284" t="str">
         <v/>
       </c>
       <c r="J284" t="str">
-        <v>2026-08-08T07:13:22.403Z</v>
+        <v>2026-08-09T18:19:39.788Z</v>
       </c>
     </row>
     <row r="285">
@@ -9610,13 +9610,13 @@
         <v>PASS</v>
       </c>
       <c r="H285">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I285" t="str">
         <v/>
       </c>
       <c r="J285" t="str">
-        <v>2026-08-08T07:13:22.419Z</v>
+        <v>2026-08-09T18:19:39.803Z</v>
       </c>
     </row>
     <row r="286">
@@ -9648,7 +9648,7 @@
         <v/>
       </c>
       <c r="J286" t="str">
-        <v>2026-08-08T07:13:22.435Z</v>
+        <v>2026-08-09T18:19:39.819Z</v>
       </c>
     </row>
     <row r="287">
@@ -9674,13 +9674,13 @@
         <v>PASS</v>
       </c>
       <c r="H287">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I287" t="str">
         <v/>
       </c>
       <c r="J287" t="str">
-        <v>2026-08-08T07:13:22.450Z</v>
+        <v>2026-08-09T18:19:39.835Z</v>
       </c>
     </row>
     <row r="288">
@@ -9706,13 +9706,13 @@
         <v>PASS</v>
       </c>
       <c r="H288">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I288" t="str">
         <v/>
       </c>
       <c r="J288" t="str">
-        <v>2026-08-08T07:13:22.466Z</v>
+        <v>2026-08-09T18:19:39.850Z</v>
       </c>
     </row>
     <row r="289">
@@ -9744,7 +9744,7 @@
         <v/>
       </c>
       <c r="J289" t="str">
-        <v>2026-08-08T07:13:22.482Z</v>
+        <v>2026-08-09T18:19:39.866Z</v>
       </c>
     </row>
     <row r="290">
@@ -9770,13 +9770,13 @@
         <v>PASS</v>
       </c>
       <c r="H290">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I290" t="str">
         <v/>
       </c>
       <c r="J290" t="str">
-        <v>2026-08-08T07:13:22.497Z</v>
+        <v>2026-08-09T18:19:39.882Z</v>
       </c>
     </row>
     <row r="291">
@@ -9802,13 +9802,13 @@
         <v>PASS</v>
       </c>
       <c r="H291">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I291" t="str">
         <v/>
       </c>
       <c r="J291" t="str">
-        <v>2026-08-08T07:13:22.513Z</v>
+        <v>2026-08-09T18:19:39.897Z</v>
       </c>
     </row>
     <row r="292">
@@ -9834,13 +9834,13 @@
         <v>PASS</v>
       </c>
       <c r="H292">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I292" t="str">
         <v/>
       </c>
       <c r="J292" t="str">
-        <v>2026-08-08T07:13:22.528Z</v>
+        <v>2026-08-09T18:19:39.914Z</v>
       </c>
     </row>
     <row r="293">
@@ -9866,13 +9866,13 @@
         <v>PASS</v>
       </c>
       <c r="H293">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I293" t="str">
         <v/>
       </c>
       <c r="J293" t="str">
-        <v>2026-08-08T07:13:22.544Z</v>
+        <v>2026-08-09T18:19:39.930Z</v>
       </c>
     </row>
     <row r="294">
@@ -9898,13 +9898,13 @@
         <v>PASS</v>
       </c>
       <c r="H294">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I294" t="str">
         <v/>
       </c>
       <c r="J294" t="str">
-        <v>2026-08-08T07:13:22.560Z</v>
+        <v>2026-08-09T18:19:39.944Z</v>
       </c>
     </row>
     <row r="295">
@@ -9930,13 +9930,13 @@
         <v>PASS</v>
       </c>
       <c r="H295">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I295" t="str">
         <v/>
       </c>
       <c r="J295" t="str">
-        <v>2026-08-08T07:13:22.575Z</v>
+        <v>2026-08-09T18:19:39.960Z</v>
       </c>
     </row>
     <row r="296">
@@ -9962,13 +9962,13 @@
         <v>PASS</v>
       </c>
       <c r="H296">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I296" t="str">
         <v/>
       </c>
       <c r="J296" t="str">
-        <v>2026-08-08T07:13:22.591Z</v>
+        <v>2026-08-09T18:19:39.976Z</v>
       </c>
     </row>
     <row r="297">
@@ -10000,7 +10000,7 @@
         <v/>
       </c>
       <c r="J297" t="str">
-        <v>2026-08-08T07:13:22.606Z</v>
+        <v>2026-08-09T18:19:39.991Z</v>
       </c>
     </row>
     <row r="298">
@@ -10026,13 +10026,13 @@
         <v>PASS</v>
       </c>
       <c r="H298">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I298" t="str">
         <v/>
       </c>
       <c r="J298" t="str">
-        <v>2026-08-08T07:13:22.622Z</v>
+        <v>2026-08-09T18:19:40.007Z</v>
       </c>
     </row>
     <row r="299">
@@ -10064,7 +10064,7 @@
         <v/>
       </c>
       <c r="J299" t="str">
-        <v>2026-08-08T07:13:22.637Z</v>
+        <v>2026-08-09T18:19:40.022Z</v>
       </c>
     </row>
     <row r="300">
@@ -10090,13 +10090,13 @@
         <v>PASS</v>
       </c>
       <c r="H300">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I300" t="str">
         <v/>
       </c>
       <c r="J300" t="str">
-        <v>2026-08-08T07:13:22.654Z</v>
+        <v>2026-08-09T18:19:40.037Z</v>
       </c>
     </row>
     <row r="301">
@@ -10122,13 +10122,13 @@
         <v>PASS</v>
       </c>
       <c r="H301">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I301" t="str">
         <v/>
       </c>
       <c r="J301" t="str">
-        <v>2026-08-08T07:13:22.669Z</v>
+        <v>2026-08-09T18:19:40.053Z</v>
       </c>
     </row>
     <row r="302">
@@ -10154,13 +10154,13 @@
         <v>PASS</v>
       </c>
       <c r="H302">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I302" t="str">
         <v/>
       </c>
       <c r="J302" t="str">
-        <v>2026-08-08T07:13:22.684Z</v>
+        <v>2026-08-09T18:19:40.068Z</v>
       </c>
     </row>
     <row r="303">
@@ -10192,7 +10192,7 @@
         <v/>
       </c>
       <c r="J303" t="str">
-        <v>2026-08-08T07:13:22.700Z</v>
+        <v>2026-08-09T18:19:40.084Z</v>
       </c>
     </row>
     <row r="304">
@@ -10224,7 +10224,7 @@
         <v/>
       </c>
       <c r="J304" t="str">
-        <v>2026-08-08T07:13:22.715Z</v>
+        <v>2026-08-09T18:19:40.099Z</v>
       </c>
     </row>
     <row r="305">
@@ -10250,13 +10250,13 @@
         <v>PASS</v>
       </c>
       <c r="H305">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I305" t="str">
         <v/>
       </c>
       <c r="J305" t="str">
-        <v>2026-08-08T07:13:22.732Z</v>
+        <v>2026-08-09T18:19:40.115Z</v>
       </c>
     </row>
     <row r="306">
@@ -10288,7 +10288,7 @@
         <v/>
       </c>
       <c r="J306" t="str">
-        <v>2026-08-08T07:13:22.747Z</v>
+        <v>2026-08-09T18:19:40.131Z</v>
       </c>
     </row>
     <row r="307">
@@ -10320,7 +10320,7 @@
         <v/>
       </c>
       <c r="J307" t="str">
-        <v>2026-08-08T07:13:22.763Z</v>
+        <v>2026-08-09T18:19:40.147Z</v>
       </c>
     </row>
     <row r="308">
@@ -10352,7 +10352,7 @@
         <v/>
       </c>
       <c r="J308" t="str">
-        <v>2026-08-08T07:13:22.778Z</v>
+        <v>2026-08-09T18:19:40.162Z</v>
       </c>
     </row>
     <row r="309">
@@ -10384,7 +10384,7 @@
         <v/>
       </c>
       <c r="J309" t="str">
-        <v>2026-08-08T07:13:22.794Z</v>
+        <v>2026-08-09T18:19:40.178Z</v>
       </c>
     </row>
     <row r="310">
@@ -10410,13 +10410,13 @@
         <v>PASS</v>
       </c>
       <c r="H310">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I310" t="str">
         <v/>
       </c>
       <c r="J310" t="str">
-        <v>2026-08-08T07:13:22.809Z</v>
+        <v>2026-08-09T18:19:40.195Z</v>
       </c>
     </row>
     <row r="311">
@@ -10448,7 +10448,7 @@
         <v/>
       </c>
       <c r="J311" t="str">
-        <v>2026-08-08T07:13:22.825Z</v>
+        <v>2026-08-09T18:19:40.211Z</v>
       </c>
     </row>
     <row r="312">
@@ -10480,7 +10480,7 @@
         <v/>
       </c>
       <c r="J312" t="str">
-        <v>2026-08-08T07:13:22.840Z</v>
+        <v>2026-08-09T18:19:40.226Z</v>
       </c>
     </row>
     <row r="313">
@@ -10512,7 +10512,7 @@
         <v/>
       </c>
       <c r="J313" t="str">
-        <v>2026-08-08T07:13:22.855Z</v>
+        <v>2026-08-09T18:19:40.241Z</v>
       </c>
     </row>
     <row r="314">
@@ -10538,13 +10538,13 @@
         <v>PASS</v>
       </c>
       <c r="H314">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I314" t="str">
         <v/>
       </c>
       <c r="J314" t="str">
-        <v>2026-08-08T07:13:22.872Z</v>
+        <v>2026-08-09T18:19:40.256Z</v>
       </c>
     </row>
     <row r="315">
@@ -10570,13 +10570,13 @@
         <v>PASS</v>
       </c>
       <c r="H315">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I315" t="str">
         <v/>
       </c>
       <c r="J315" t="str">
-        <v>2026-08-08T07:13:22.887Z</v>
+        <v>2026-08-09T18:19:40.273Z</v>
       </c>
     </row>
     <row r="316">
@@ -10602,13 +10602,13 @@
         <v>PASS</v>
       </c>
       <c r="H316">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I316" t="str">
         <v/>
       </c>
       <c r="J316" t="str">
-        <v>2026-08-08T07:13:22.903Z</v>
+        <v>2026-08-09T18:19:40.288Z</v>
       </c>
     </row>
     <row r="317">
@@ -10634,13 +10634,13 @@
         <v>PASS</v>
       </c>
       <c r="H317">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I317" t="str">
         <v/>
       </c>
       <c r="J317" t="str">
-        <v>2026-08-08T07:13:22.919Z</v>
+        <v>2026-08-09T18:19:40.303Z</v>
       </c>
     </row>
     <row r="318">
@@ -10672,7 +10672,7 @@
         <v/>
       </c>
       <c r="J318" t="str">
-        <v>2026-08-08T07:13:22.935Z</v>
+        <v>2026-08-09T18:19:40.319Z</v>
       </c>
     </row>
     <row r="319">
@@ -10704,7 +10704,7 @@
         <v/>
       </c>
       <c r="J319" t="str">
-        <v>2026-08-08T07:13:22.950Z</v>
+        <v>2026-08-09T18:19:40.334Z</v>
       </c>
     </row>
     <row r="320">
@@ -10730,13 +10730,13 @@
         <v>PASS</v>
       </c>
       <c r="H320">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I320" t="str">
         <v/>
       </c>
       <c r="J320" t="str">
-        <v>2026-08-08T07:13:22.966Z</v>
+        <v>2026-08-09T18:19:40.349Z</v>
       </c>
     </row>
     <row r="321">
@@ -10762,13 +10762,13 @@
         <v>PASS</v>
       </c>
       <c r="H321">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I321" t="str">
         <v/>
       </c>
       <c r="J321" t="str">
-        <v>2026-08-08T07:13:22.981Z</v>
+        <v>2026-08-09T18:19:40.365Z</v>
       </c>
     </row>
     <row r="322">
@@ -10794,13 +10794,13 @@
         <v>PASS</v>
       </c>
       <c r="H322">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I322" t="str">
         <v/>
       </c>
       <c r="J322" t="str">
-        <v>2026-08-08T07:13:22.997Z</v>
+        <v>2026-08-09T18:19:40.382Z</v>
       </c>
     </row>
     <row r="323">
@@ -10826,13 +10826,13 @@
         <v>PASS</v>
       </c>
       <c r="H323">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I323" t="str">
         <v/>
       </c>
       <c r="J323" t="str">
-        <v>2026-08-08T07:13:23.013Z</v>
+        <v>2026-08-09T18:19:40.396Z</v>
       </c>
     </row>
     <row r="324">
@@ -10858,13 +10858,13 @@
         <v>PASS</v>
       </c>
       <c r="H324">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I324" t="str">
         <v/>
       </c>
       <c r="J324" t="str">
-        <v>2026-08-08T07:13:23.028Z</v>
+        <v>2026-08-09T18:19:40.412Z</v>
       </c>
     </row>
     <row r="325">
@@ -10890,13 +10890,13 @@
         <v>PASS</v>
       </c>
       <c r="H325">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I325" t="str">
         <v/>
       </c>
       <c r="J325" t="str">
-        <v>2026-08-08T07:13:23.044Z</v>
+        <v>2026-08-09T18:19:40.427Z</v>
       </c>
     </row>
     <row r="326">
@@ -10922,13 +10922,13 @@
         <v>PASS</v>
       </c>
       <c r="H326">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I326" t="str">
         <v/>
       </c>
       <c r="J326" t="str">
-        <v>2026-08-08T07:13:23.060Z</v>
+        <v>2026-08-09T18:19:40.444Z</v>
       </c>
     </row>
     <row r="327">
@@ -10954,13 +10954,13 @@
         <v>PASS</v>
       </c>
       <c r="H327">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I327" t="str">
         <v/>
       </c>
       <c r="J327" t="str">
-        <v>2026-08-08T07:13:23.075Z</v>
+        <v>2026-08-09T18:19:40.460Z</v>
       </c>
     </row>
     <row r="328">
@@ -10986,13 +10986,13 @@
         <v>PASS</v>
       </c>
       <c r="H328">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I328" t="str">
         <v/>
       </c>
       <c r="J328" t="str">
-        <v>2026-08-08T07:13:23.090Z</v>
+        <v>2026-08-09T18:19:40.476Z</v>
       </c>
     </row>
     <row r="329">
@@ -11018,13 +11018,13 @@
         <v>PASS</v>
       </c>
       <c r="H329">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I329" t="str">
         <v/>
       </c>
       <c r="J329" t="str">
-        <v>2026-08-08T07:13:23.106Z</v>
+        <v>2026-08-09T18:19:40.490Z</v>
       </c>
     </row>
     <row r="330">
@@ -11056,7 +11056,7 @@
         <v/>
       </c>
       <c r="J330" t="str">
-        <v>2026-08-08T07:13:23.121Z</v>
+        <v>2026-08-09T18:19:40.505Z</v>
       </c>
     </row>
     <row r="331">
@@ -11082,13 +11082,13 @@
         <v>PASS</v>
       </c>
       <c r="H331">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I331" t="str">
         <v/>
       </c>
       <c r="J331" t="str">
-        <v>2026-08-08T07:13:23.136Z</v>
+        <v>2026-08-09T18:19:40.520Z</v>
       </c>
     </row>
     <row r="332">
@@ -11114,13 +11114,13 @@
         <v>PASS</v>
       </c>
       <c r="H332">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I332" t="str">
         <v/>
       </c>
       <c r="J332" t="str">
-        <v>2026-08-08T07:13:23.152Z</v>
+        <v>2026-08-09T18:19:40.535Z</v>
       </c>
     </row>
     <row r="333">
@@ -11152,7 +11152,7 @@
         <v/>
       </c>
       <c r="J333" t="str">
-        <v>2026-08-08T07:13:23.168Z</v>
+        <v>2026-08-09T18:19:40.551Z</v>
       </c>
     </row>
     <row r="334">
@@ -11178,13 +11178,13 @@
         <v>PASS</v>
       </c>
       <c r="H334">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I334" t="str">
         <v/>
       </c>
       <c r="J334" t="str">
-        <v>2026-08-08T07:13:23.183Z</v>
+        <v>2026-08-09T18:19:40.567Z</v>
       </c>
     </row>
     <row r="335">
@@ -11216,7 +11216,7 @@
         <v/>
       </c>
       <c r="J335" t="str">
-        <v>2026-08-08T07:13:23.199Z</v>
+        <v>2026-08-09T18:19:40.583Z</v>
       </c>
     </row>
     <row r="336">
@@ -11248,7 +11248,7 @@
         <v/>
       </c>
       <c r="J336" t="str">
-        <v>2026-08-08T07:13:23.214Z</v>
+        <v>2026-08-09T18:19:40.598Z</v>
       </c>
     </row>
     <row r="337">
@@ -11280,7 +11280,7 @@
         <v/>
       </c>
       <c r="J337" t="str">
-        <v>2026-08-08T07:13:23.230Z</v>
+        <v>2026-08-09T18:19:40.614Z</v>
       </c>
     </row>
     <row r="338">
@@ -11306,13 +11306,13 @@
         <v>PASS</v>
       </c>
       <c r="H338">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I338" t="str">
         <v/>
       </c>
       <c r="J338" t="str">
-        <v>2026-08-08T07:13:23.247Z</v>
+        <v>2026-08-09T18:19:40.629Z</v>
       </c>
     </row>
     <row r="339">
@@ -11338,13 +11338,13 @@
         <v>PASS</v>
       </c>
       <c r="H339">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I339" t="str">
         <v/>
       </c>
       <c r="J339" t="str">
-        <v>2026-08-08T07:13:23.265Z</v>
+        <v>2026-08-09T18:19:40.645Z</v>
       </c>
     </row>
     <row r="340">
@@ -11370,13 +11370,13 @@
         <v>PASS</v>
       </c>
       <c r="H340">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I340" t="str">
         <v/>
       </c>
       <c r="J340" t="str">
-        <v>2026-08-08T07:13:23.278Z</v>
+        <v>2026-08-09T18:19:40.660Z</v>
       </c>
     </row>
     <row r="341">
@@ -11402,13 +11402,13 @@
         <v>PASS</v>
       </c>
       <c r="H341">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I341" t="str">
         <v/>
       </c>
       <c r="J341" t="str">
-        <v>2026-08-08T07:13:23.293Z</v>
+        <v>2026-08-09T18:19:40.676Z</v>
       </c>
     </row>
     <row r="342">
@@ -11434,13 +11434,13 @@
         <v>PASS</v>
       </c>
       <c r="H342">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I342" t="str">
         <v/>
       </c>
       <c r="J342" t="str">
-        <v>2026-08-08T07:13:23.308Z</v>
+        <v>2026-08-09T18:19:40.691Z</v>
       </c>
     </row>
     <row r="343">
@@ -11472,7 +11472,7 @@
         <v/>
       </c>
       <c r="J343" t="str">
-        <v>2026-08-08T07:13:23.324Z</v>
+        <v>2026-08-09T18:19:40.707Z</v>
       </c>
     </row>
     <row r="344">
@@ -11498,13 +11498,13 @@
         <v>PASS</v>
       </c>
       <c r="H344">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I344" t="str">
         <v/>
       </c>
       <c r="J344" t="str">
-        <v>2026-08-08T07:13:23.343Z</v>
+        <v>2026-08-09T18:19:40.722Z</v>
       </c>
     </row>
     <row r="345">
@@ -11530,13 +11530,13 @@
         <v>PASS</v>
       </c>
       <c r="H345">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I345" t="str">
         <v/>
       </c>
       <c r="J345" t="str">
-        <v>2026-08-08T07:13:23.356Z</v>
+        <v>2026-08-09T18:19:40.737Z</v>
       </c>
     </row>
     <row r="346">
@@ -11562,13 +11562,13 @@
         <v>PASS</v>
       </c>
       <c r="H346">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I346" t="str">
         <v/>
       </c>
       <c r="J346" t="str">
-        <v>2026-08-08T07:13:23.371Z</v>
+        <v>2026-08-09T18:19:40.753Z</v>
       </c>
     </row>
     <row r="347">
@@ -11594,13 +11594,13 @@
         <v>PASS</v>
       </c>
       <c r="H347">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I347" t="str">
         <v/>
       </c>
       <c r="J347" t="str">
-        <v>2026-08-08T07:13:23.387Z</v>
+        <v>2026-08-09T18:19:40.768Z</v>
       </c>
     </row>
     <row r="348">
@@ -11626,13 +11626,13 @@
         <v>PASS</v>
       </c>
       <c r="H348">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I348" t="str">
         <v/>
       </c>
       <c r="J348" t="str">
-        <v>2026-08-08T07:13:23.401Z</v>
+        <v>2026-08-09T18:19:40.784Z</v>
       </c>
     </row>
     <row r="349">
@@ -11658,13 +11658,13 @@
         <v>PASS</v>
       </c>
       <c r="H349">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I349" t="str">
         <v/>
       </c>
       <c r="J349" t="str">
-        <v>2026-08-08T07:13:23.418Z</v>
+        <v>2026-08-09T18:19:40.799Z</v>
       </c>
     </row>
     <row r="350">
@@ -11696,7 +11696,7 @@
         <v/>
       </c>
       <c r="J350" t="str">
-        <v>2026-08-08T07:13:23.434Z</v>
+        <v>2026-08-09T18:19:40.815Z</v>
       </c>
     </row>
     <row r="351">
@@ -11728,7 +11728,7 @@
         <v/>
       </c>
       <c r="J351" t="str">
-        <v>2026-08-08T07:13:23.449Z</v>
+        <v>2026-08-09T18:19:40.830Z</v>
       </c>
     </row>
     <row r="352">
@@ -11754,13 +11754,13 @@
         <v>PASS</v>
       </c>
       <c r="H352">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I352" t="str">
         <v/>
       </c>
       <c r="J352" t="str">
-        <v>2026-08-08T07:13:23.465Z</v>
+        <v>2026-08-09T18:19:40.846Z</v>
       </c>
     </row>
     <row r="353">
@@ -11786,13 +11786,13 @@
         <v>PASS</v>
       </c>
       <c r="H353">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I353" t="str">
         <v/>
       </c>
       <c r="J353" t="str">
-        <v>2026-08-08T07:13:23.479Z</v>
+        <v>2026-08-09T18:19:40.862Z</v>
       </c>
     </row>
     <row r="354">
@@ -11818,13 +11818,13 @@
         <v>PASS</v>
       </c>
       <c r="H354">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I354" t="str">
         <v/>
       </c>
       <c r="J354" t="str">
-        <v>2026-08-08T07:13:23.495Z</v>
+        <v>2026-08-09T18:19:40.877Z</v>
       </c>
     </row>
     <row r="355">
@@ -11856,7 +11856,7 @@
         <v/>
       </c>
       <c r="J355" t="str">
-        <v>2026-08-08T07:13:23.511Z</v>
+        <v>2026-08-09T18:19:40.893Z</v>
       </c>
     </row>
     <row r="356">
@@ -11882,13 +11882,13 @@
         <v>PASS</v>
       </c>
       <c r="H356">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I356" t="str">
         <v/>
       </c>
       <c r="J356" t="str">
-        <v>2026-08-08T07:13:23.527Z</v>
+        <v>2026-08-09T18:19:40.908Z</v>
       </c>
     </row>
     <row r="357">
@@ -11914,13 +11914,13 @@
         <v>PASS</v>
       </c>
       <c r="H357">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I357" t="str">
         <v/>
       </c>
       <c r="J357" t="str">
-        <v>2026-08-08T07:13:23.543Z</v>
+        <v>2026-08-09T18:19:40.923Z</v>
       </c>
     </row>
     <row r="358">
@@ -11952,7 +11952,7 @@
         <v/>
       </c>
       <c r="J358" t="str">
-        <v>2026-08-08T07:13:23.558Z</v>
+        <v>2026-08-09T18:19:40.938Z</v>
       </c>
     </row>
     <row r="359">
@@ -11978,13 +11978,13 @@
         <v>PASS</v>
       </c>
       <c r="H359">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I359" t="str">
         <v/>
       </c>
       <c r="J359" t="str">
-        <v>2026-08-08T07:13:23.573Z</v>
+        <v>2026-08-09T18:19:40.954Z</v>
       </c>
     </row>
     <row r="360">
@@ -12016,7 +12016,7 @@
         <v/>
       </c>
       <c r="J360" t="str">
-        <v>2026-08-08T07:13:23.589Z</v>
+        <v>2026-08-09T18:19:40.970Z</v>
       </c>
     </row>
     <row r="361">
@@ -12042,13 +12042,13 @@
         <v>PASS</v>
       </c>
       <c r="H361">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I361" t="str">
         <v/>
       </c>
       <c r="J361" t="str">
-        <v>2026-08-08T07:13:23.605Z</v>
+        <v>2026-08-09T18:19:40.984Z</v>
       </c>
     </row>
     <row r="362">
@@ -12074,13 +12074,13 @@
         <v>PASS</v>
       </c>
       <c r="H362">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I362" t="str">
         <v/>
       </c>
       <c r="J362" t="str">
-        <v>2026-08-08T07:13:23.621Z</v>
+        <v>2026-08-09T18:19:41.000Z</v>
       </c>
     </row>
     <row r="363">
@@ -12106,13 +12106,13 @@
         <v>PASS</v>
       </c>
       <c r="H363">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I363" t="str">
         <v/>
       </c>
       <c r="J363" t="str">
-        <v>2026-08-08T07:13:23.637Z</v>
+        <v>2026-08-09T18:19:41.015Z</v>
       </c>
     </row>
     <row r="364">
@@ -12138,13 +12138,13 @@
         <v>PASS</v>
       </c>
       <c r="H364">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I364" t="str">
         <v/>
       </c>
       <c r="J364" t="str">
-        <v>2026-08-08T07:13:23.652Z</v>
+        <v>2026-08-09T18:19:41.031Z</v>
       </c>
     </row>
     <row r="365">
@@ -12170,13 +12170,13 @@
         <v>PASS</v>
       </c>
       <c r="H365">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I365" t="str">
         <v/>
       </c>
       <c r="J365" t="str">
-        <v>2026-08-08T07:13:23.667Z</v>
+        <v>2026-08-09T18:19:41.047Z</v>
       </c>
     </row>
     <row r="366">
@@ -12202,13 +12202,13 @@
         <v>PASS</v>
       </c>
       <c r="H366">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I366" t="str">
         <v/>
       </c>
       <c r="J366" t="str">
-        <v>2026-08-08T07:13:23.682Z</v>
+        <v>2026-08-09T18:19:41.063Z</v>
       </c>
     </row>
     <row r="367">
@@ -12240,7 +12240,7 @@
         <v/>
       </c>
       <c r="J367" t="str">
-        <v>2026-08-08T07:13:23.698Z</v>
+        <v>2026-08-09T18:19:41.079Z</v>
       </c>
     </row>
     <row r="368">
@@ -12266,13 +12266,13 @@
         <v>PASS</v>
       </c>
       <c r="H368">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I368" t="str">
         <v/>
       </c>
       <c r="J368" t="str">
-        <v>2026-08-08T07:13:23.714Z</v>
+        <v>2026-08-09T18:19:41.094Z</v>
       </c>
     </row>
     <row r="369">
@@ -12298,13 +12298,13 @@
         <v>PASS</v>
       </c>
       <c r="H369">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I369" t="str">
         <v/>
       </c>
       <c r="J369" t="str">
-        <v>2026-08-08T07:13:23.729Z</v>
+        <v>2026-08-09T18:19:41.110Z</v>
       </c>
     </row>
     <row r="370">
@@ -12330,13 +12330,13 @@
         <v>PASS</v>
       </c>
       <c r="H370">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I370" t="str">
         <v/>
       </c>
       <c r="J370" t="str">
-        <v>2026-08-08T07:13:23.746Z</v>
+        <v>2026-08-09T18:19:41.125Z</v>
       </c>
     </row>
     <row r="371">
@@ -12362,13 +12362,13 @@
         <v>PASS</v>
       </c>
       <c r="H371">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I371" t="str">
         <v/>
       </c>
       <c r="J371" t="str">
-        <v>2026-08-08T07:13:23.763Z</v>
+        <v>2026-08-09T18:19:41.140Z</v>
       </c>
     </row>
     <row r="372">
@@ -12400,7 +12400,7 @@
         <v/>
       </c>
       <c r="J372" t="str">
-        <v>2026-08-08T07:13:23.777Z</v>
+        <v>2026-08-09T18:19:41.156Z</v>
       </c>
     </row>
     <row r="373">
@@ -12432,7 +12432,7 @@
         <v/>
       </c>
       <c r="J373" t="str">
-        <v>2026-08-08T07:13:23.793Z</v>
+        <v>2026-08-09T18:19:41.172Z</v>
       </c>
     </row>
     <row r="374">
@@ -12464,7 +12464,7 @@
         <v/>
       </c>
       <c r="J374" t="str">
-        <v>2026-08-08T07:13:23.809Z</v>
+        <v>2026-08-09T18:19:41.188Z</v>
       </c>
     </row>
     <row r="375">
@@ -12490,13 +12490,13 @@
         <v>PASS</v>
       </c>
       <c r="H375">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I375" t="str">
         <v/>
       </c>
       <c r="J375" t="str">
-        <v>2026-08-08T07:13:23.824Z</v>
+        <v>2026-08-09T18:19:41.204Z</v>
       </c>
     </row>
     <row r="376">
@@ -12522,13 +12522,13 @@
         <v>PASS</v>
       </c>
       <c r="H376">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I376" t="str">
         <v/>
       </c>
       <c r="J376" t="str">
-        <v>2026-08-08T07:13:23.839Z</v>
+        <v>2026-08-09T18:19:41.219Z</v>
       </c>
     </row>
     <row r="377">
@@ -12560,7 +12560,7 @@
         <v/>
       </c>
       <c r="J377" t="str">
-        <v>2026-08-08T07:13:23.854Z</v>
+        <v>2026-08-09T18:19:41.234Z</v>
       </c>
     </row>
     <row r="378">
@@ -12586,13 +12586,13 @@
         <v>PASS</v>
       </c>
       <c r="H378">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I378" t="str">
         <v/>
       </c>
       <c r="J378" t="str">
-        <v>2026-08-08T07:13:23.870Z</v>
+        <v>2026-08-09T18:19:41.250Z</v>
       </c>
     </row>
     <row r="379">
@@ -12624,7 +12624,7 @@
         <v/>
       </c>
       <c r="J379" t="str">
-        <v>2026-08-08T07:13:23.886Z</v>
+        <v>2026-08-09T18:19:41.266Z</v>
       </c>
     </row>
     <row r="380">
@@ -12650,13 +12650,13 @@
         <v>PASS</v>
       </c>
       <c r="H380">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I380" t="str">
         <v/>
       </c>
       <c r="J380" t="str">
-        <v>2026-08-08T07:13:23.900Z</v>
+        <v>2026-08-09T18:19:41.282Z</v>
       </c>
     </row>
     <row r="381">
@@ -12688,7 +12688,7 @@
         <v/>
       </c>
       <c r="J381" t="str">
-        <v>2026-08-08T07:13:23.915Z</v>
+        <v>2026-08-09T18:19:41.298Z</v>
       </c>
     </row>
     <row r="382">
@@ -12720,7 +12720,7 @@
         <v/>
       </c>
       <c r="J382" t="str">
-        <v>2026-08-08T07:13:23.932Z</v>
+        <v>2026-08-09T18:19:41.314Z</v>
       </c>
     </row>
     <row r="383">
@@ -12752,7 +12752,7 @@
         <v/>
       </c>
       <c r="J383" t="str">
-        <v>2026-08-08T07:13:23.947Z</v>
+        <v>2026-08-09T18:19:41.329Z</v>
       </c>
     </row>
     <row r="384">
@@ -12784,7 +12784,7 @@
         <v/>
       </c>
       <c r="J384" t="str">
-        <v>2026-08-08T07:13:23.963Z</v>
+        <v>2026-08-09T18:19:41.344Z</v>
       </c>
     </row>
     <row r="385">
@@ -12810,13 +12810,13 @@
         <v>PASS</v>
       </c>
       <c r="H385">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I385" t="str">
         <v/>
       </c>
       <c r="J385" t="str">
-        <v>2026-08-08T07:13:23.979Z</v>
+        <v>2026-08-09T18:19:41.359Z</v>
       </c>
     </row>
     <row r="386">
@@ -12842,13 +12842,13 @@
         <v>PASS</v>
       </c>
       <c r="H386">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I386" t="str">
         <v/>
       </c>
       <c r="J386" t="str">
-        <v>2026-08-08T07:13:23.995Z</v>
+        <v>2026-08-09T18:19:41.374Z</v>
       </c>
     </row>
     <row r="387">
@@ -12880,7 +12880,7 @@
         <v/>
       </c>
       <c r="J387" t="str">
-        <v>2026-08-08T07:13:24.011Z</v>
+        <v>2026-08-09T18:19:41.390Z</v>
       </c>
     </row>
     <row r="388">
@@ -12906,13 +12906,13 @@
         <v>PASS</v>
       </c>
       <c r="H388">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I388" t="str">
         <v/>
       </c>
       <c r="J388" t="str">
-        <v>2026-08-08T07:13:24.026Z</v>
+        <v>2026-08-09T18:19:41.406Z</v>
       </c>
     </row>
     <row r="389">
@@ -12938,13 +12938,13 @@
         <v>PASS</v>
       </c>
       <c r="H389">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I389" t="str">
         <v/>
       </c>
       <c r="J389" t="str">
-        <v>2026-08-08T07:13:24.043Z</v>
+        <v>2026-08-09T18:19:41.421Z</v>
       </c>
     </row>
     <row r="390">
@@ -12970,13 +12970,13 @@
         <v>PASS</v>
       </c>
       <c r="H390">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I390" t="str">
         <v/>
       </c>
       <c r="J390" t="str">
-        <v>2026-08-08T07:13:24.059Z</v>
+        <v>2026-08-09T18:19:41.437Z</v>
       </c>
     </row>
     <row r="391">
@@ -13008,7 +13008,7 @@
         <v/>
       </c>
       <c r="J391" t="str">
-        <v>2026-08-08T07:13:24.073Z</v>
+        <v>2026-08-09T18:19:41.452Z</v>
       </c>
     </row>
     <row r="392">
@@ -13034,13 +13034,13 @@
         <v>PASS</v>
       </c>
       <c r="H392">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I392" t="str">
         <v/>
       </c>
       <c r="J392" t="str">
-        <v>2026-08-08T07:13:24.089Z</v>
+        <v>2026-08-09T18:19:41.467Z</v>
       </c>
     </row>
     <row r="393">
@@ -13066,13 +13066,13 @@
         <v>PASS</v>
       </c>
       <c r="H393">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I393" t="str">
         <v/>
       </c>
       <c r="J393" t="str">
-        <v>2026-08-08T07:13:24.104Z</v>
+        <v>2026-08-09T18:19:41.483Z</v>
       </c>
     </row>
     <row r="394">
@@ -13098,13 +13098,13 @@
         <v>PASS</v>
       </c>
       <c r="H394">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I394" t="str">
         <v/>
       </c>
       <c r="J394" t="str">
-        <v>2026-08-08T07:13:24.120Z</v>
+        <v>2026-08-09T18:19:41.500Z</v>
       </c>
     </row>
     <row r="395">
@@ -13136,7 +13136,7 @@
         <v/>
       </c>
       <c r="J395" t="str">
-        <v>2026-08-08T07:13:24.135Z</v>
+        <v>2026-08-09T18:19:41.515Z</v>
       </c>
     </row>
     <row r="396">
@@ -13168,7 +13168,7 @@
         <v/>
       </c>
       <c r="J396" t="str">
-        <v>2026-08-08T07:13:24.151Z</v>
+        <v>2026-08-09T18:19:41.531Z</v>
       </c>
     </row>
     <row r="397">
@@ -13200,7 +13200,7 @@
         <v/>
       </c>
       <c r="J397" t="str">
-        <v>2026-08-08T07:13:24.166Z</v>
+        <v>2026-08-09T18:19:41.546Z</v>
       </c>
     </row>
     <row r="398">
@@ -13226,13 +13226,13 @@
         <v>PASS</v>
       </c>
       <c r="H398">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I398" t="str">
         <v/>
       </c>
       <c r="J398" t="str">
-        <v>2026-08-08T07:13:24.182Z</v>
+        <v>2026-08-09T18:19:41.561Z</v>
       </c>
     </row>
     <row r="399">
@@ -13258,13 +13258,13 @@
         <v>PASS</v>
       </c>
       <c r="H399">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I399" t="str">
         <v/>
       </c>
       <c r="J399" t="str">
-        <v>2026-08-08T07:13:24.197Z</v>
+        <v>2026-08-09T18:19:41.577Z</v>
       </c>
     </row>
     <row r="400">
@@ -13296,7 +13296,7 @@
         <v/>
       </c>
       <c r="J400" t="str">
-        <v>2026-08-08T07:13:24.214Z</v>
+        <v>2026-08-09T18:19:41.593Z</v>
       </c>
     </row>
     <row r="401">
@@ -13328,7 +13328,7 @@
         <v/>
       </c>
       <c r="J401" t="str">
-        <v>2026-08-08T07:13:24.229Z</v>
+        <v>2026-08-09T18:19:41.608Z</v>
       </c>
     </row>
   </sheetData>

--- a/appium-tests/reports/appium-mobile-test-report-400.xlsx
+++ b/appium-tests/reports/appium-mobile-test-report-400.xlsx
@@ -449,7 +449,7 @@
         <v>Suite Duration (seconds)</v>
       </c>
       <c r="B6">
-        <v>6.19</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="7">
@@ -473,7 +473,7 @@
         <v>Generated At</v>
       </c>
       <c r="B9" t="str">
-        <v>9/8/2026, 11:49:41 pm</v>
+        <v>9/8/2026, 11:53:03 pm</v>
       </c>
     </row>
   </sheetData>
@@ -560,7 +560,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>2026-08-09T18:19:35.426Z</v>
+        <v>2026-08-09T18:22:57.692Z</v>
       </c>
     </row>
     <row r="3">
@@ -592,7 +592,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>2026-08-09T18:19:35.432Z</v>
+        <v>2026-08-09T18:22:57.698Z</v>
       </c>
     </row>
     <row r="4">
@@ -618,13 +618,13 @@
         <v>PASS</v>
       </c>
       <c r="H4">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>2026-08-09T18:19:35.446Z</v>
+        <v>2026-08-09T18:22:57.717Z</v>
       </c>
     </row>
     <row r="5">
@@ -656,7 +656,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>2026-08-09T18:19:35.462Z</v>
+        <v>2026-08-09T18:22:57.733Z</v>
       </c>
     </row>
     <row r="6">
@@ -682,13 +682,13 @@
         <v>PASS</v>
       </c>
       <c r="H6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" t="str">
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>2026-08-09T18:19:35.477Z</v>
+        <v>2026-08-09T18:22:57.749Z</v>
       </c>
     </row>
     <row r="7">
@@ -714,13 +714,13 @@
         <v>PASS</v>
       </c>
       <c r="H7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" t="str">
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>2026-08-09T18:19:35.492Z</v>
+        <v>2026-08-09T18:22:57.765Z</v>
       </c>
     </row>
     <row r="8">
@@ -746,13 +746,13 @@
         <v>PASS</v>
       </c>
       <c r="H8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I8" t="str">
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>2026-08-09T18:19:35.508Z</v>
+        <v>2026-08-09T18:22:57.780Z</v>
       </c>
     </row>
     <row r="9">
@@ -784,7 +784,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>2026-08-09T18:19:35.524Z</v>
+        <v>2026-08-09T18:22:57.796Z</v>
       </c>
     </row>
     <row r="10">
@@ -810,13 +810,13 @@
         <v>PASS</v>
       </c>
       <c r="H10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" t="str">
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>2026-08-09T18:19:35.539Z</v>
+        <v>2026-08-09T18:22:57.812Z</v>
       </c>
     </row>
     <row r="11">
@@ -848,7 +848,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>2026-08-09T18:19:35.554Z</v>
+        <v>2026-08-09T18:22:57.827Z</v>
       </c>
     </row>
     <row r="12">
@@ -880,7 +880,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>2026-08-09T18:19:35.570Z</v>
+        <v>2026-08-09T18:22:57.843Z</v>
       </c>
     </row>
     <row r="13">
@@ -912,7 +912,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>2026-08-09T18:19:35.586Z</v>
+        <v>2026-08-09T18:22:57.858Z</v>
       </c>
     </row>
     <row r="14">
@@ -944,7 +944,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>2026-08-09T18:19:35.602Z</v>
+        <v>2026-08-09T18:22:57.874Z</v>
       </c>
     </row>
     <row r="15">
@@ -976,7 +976,7 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>2026-08-09T18:19:35.617Z</v>
+        <v>2026-08-09T18:22:57.889Z</v>
       </c>
     </row>
     <row r="16">
@@ -1002,13 +1002,13 @@
         <v>PASS</v>
       </c>
       <c r="H16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I16" t="str">
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>2026-08-09T18:19:35.633Z</v>
+        <v>2026-08-09T18:22:57.904Z</v>
       </c>
     </row>
     <row r="17">
@@ -1040,7 +1040,7 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>2026-08-09T18:19:35.648Z</v>
+        <v>2026-08-09T18:22:57.920Z</v>
       </c>
     </row>
     <row r="18">
@@ -1072,7 +1072,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>2026-08-09T18:19:35.663Z</v>
+        <v>2026-08-09T18:22:57.935Z</v>
       </c>
     </row>
     <row r="19">
@@ -1098,13 +1098,13 @@
         <v>PASS</v>
       </c>
       <c r="H19">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I19" t="str">
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>2026-08-09T18:19:35.681Z</v>
+        <v>2026-08-09T18:22:57.951Z</v>
       </c>
     </row>
     <row r="20">
@@ -1130,13 +1130,13 @@
         <v>PASS</v>
       </c>
       <c r="H20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" t="str">
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>2026-08-09T18:19:35.695Z</v>
+        <v>2026-08-09T18:22:57.966Z</v>
       </c>
     </row>
     <row r="21">
@@ -1162,13 +1162,13 @@
         <v>PASS</v>
       </c>
       <c r="H21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I21" t="str">
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>2026-08-09T18:19:35.710Z</v>
+        <v>2026-08-09T18:22:57.982Z</v>
       </c>
     </row>
     <row r="22">
@@ -1194,13 +1194,13 @@
         <v>PASS</v>
       </c>
       <c r="H22">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I22" t="str">
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>2026-08-09T18:19:35.726Z</v>
+        <v>2026-08-09T18:22:57.998Z</v>
       </c>
     </row>
     <row r="23">
@@ -1232,7 +1232,7 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>2026-08-09T18:19:35.741Z</v>
+        <v>2026-08-09T18:22:58.013Z</v>
       </c>
     </row>
     <row r="24">
@@ -1264,7 +1264,7 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>2026-08-09T18:19:35.756Z</v>
+        <v>2026-08-09T18:22:58.029Z</v>
       </c>
     </row>
     <row r="25">
@@ -1290,13 +1290,13 @@
         <v>PASS</v>
       </c>
       <c r="H25">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I25" t="str">
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>2026-08-09T18:19:35.773Z</v>
+        <v>2026-08-09T18:22:58.044Z</v>
       </c>
     </row>
     <row r="26">
@@ -1328,7 +1328,7 @@
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>2026-08-09T18:19:35.788Z</v>
+        <v>2026-08-09T18:22:58.059Z</v>
       </c>
     </row>
     <row r="27">
@@ -1354,13 +1354,13 @@
         <v>PASS</v>
       </c>
       <c r="H27">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I27" t="str">
         <v/>
       </c>
       <c r="J27" t="str">
-        <v>2026-08-09T18:19:35.804Z</v>
+        <v>2026-08-09T18:22:58.074Z</v>
       </c>
     </row>
     <row r="28">
@@ -1386,13 +1386,13 @@
         <v>PASS</v>
       </c>
       <c r="H28">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I28" t="str">
         <v/>
       </c>
       <c r="J28" t="str">
-        <v>2026-08-09T18:19:35.820Z</v>
+        <v>2026-08-09T18:22:58.091Z</v>
       </c>
     </row>
     <row r="29">
@@ -1424,7 +1424,7 @@
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>2026-08-09T18:19:35.835Z</v>
+        <v>2026-08-09T18:22:58.106Z</v>
       </c>
     </row>
     <row r="30">
@@ -1456,7 +1456,7 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>2026-08-09T18:19:35.851Z</v>
+        <v>2026-08-09T18:22:58.122Z</v>
       </c>
     </row>
     <row r="31">
@@ -1482,13 +1482,13 @@
         <v>PASS</v>
       </c>
       <c r="H31">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I31" t="str">
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>2026-08-09T18:19:35.867Z</v>
+        <v>2026-08-09T18:22:58.137Z</v>
       </c>
     </row>
     <row r="32">
@@ -1514,13 +1514,13 @@
         <v>PASS</v>
       </c>
       <c r="H32">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I32" t="str">
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>2026-08-09T18:19:35.882Z</v>
+        <v>2026-08-09T18:22:58.153Z</v>
       </c>
     </row>
     <row r="33">
@@ -1546,13 +1546,13 @@
         <v>PASS</v>
       </c>
       <c r="H33">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I33" t="str">
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>2026-08-09T18:19:35.897Z</v>
+        <v>2026-08-09T18:22:58.169Z</v>
       </c>
     </row>
     <row r="34">
@@ -1584,7 +1584,7 @@
         <v/>
       </c>
       <c r="J34" t="str">
-        <v>2026-08-09T18:19:35.912Z</v>
+        <v>2026-08-09T18:22:58.184Z</v>
       </c>
     </row>
     <row r="35">
@@ -1616,7 +1616,7 @@
         <v/>
       </c>
       <c r="J35" t="str">
-        <v>2026-08-09T18:19:35.927Z</v>
+        <v>2026-08-09T18:22:58.199Z</v>
       </c>
     </row>
     <row r="36">
@@ -1642,13 +1642,13 @@
         <v>PASS</v>
       </c>
       <c r="H36">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I36" t="str">
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>2026-08-09T18:19:35.942Z</v>
+        <v>2026-08-09T18:22:58.215Z</v>
       </c>
     </row>
     <row r="37">
@@ -1674,13 +1674,13 @@
         <v>PASS</v>
       </c>
       <c r="H37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I37" t="str">
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>2026-08-09T18:19:35.957Z</v>
+        <v>2026-08-09T18:22:58.231Z</v>
       </c>
     </row>
     <row r="38">
@@ -1712,7 +1712,7 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>2026-08-09T18:19:35.972Z</v>
+        <v>2026-08-09T18:22:58.246Z</v>
       </c>
     </row>
     <row r="39">
@@ -1744,7 +1744,7 @@
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>2026-08-09T18:19:35.987Z</v>
+        <v>2026-08-09T18:22:58.261Z</v>
       </c>
     </row>
     <row r="40">
@@ -1776,7 +1776,7 @@
         <v/>
       </c>
       <c r="J40" t="str">
-        <v>2026-08-09T18:19:36.003Z</v>
+        <v>2026-08-09T18:22:58.277Z</v>
       </c>
     </row>
     <row r="41">
@@ -1802,13 +1802,13 @@
         <v>PASS</v>
       </c>
       <c r="H41">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I41" t="str">
         <v/>
       </c>
       <c r="J41" t="str">
-        <v>2026-08-09T18:19:36.019Z</v>
+        <v>2026-08-09T18:22:58.293Z</v>
       </c>
     </row>
     <row r="42">
@@ -1840,7 +1840,7 @@
         <v/>
       </c>
       <c r="J42" t="str">
-        <v>2026-08-09T18:19:36.034Z</v>
+        <v>2026-08-09T18:22:58.309Z</v>
       </c>
     </row>
     <row r="43">
@@ -1866,13 +1866,13 @@
         <v>PASS</v>
       </c>
       <c r="H43">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I43" t="str">
         <v/>
       </c>
       <c r="J43" t="str">
-        <v>2026-08-09T18:19:36.049Z</v>
+        <v>2026-08-09T18:22:58.325Z</v>
       </c>
     </row>
     <row r="44">
@@ -1898,13 +1898,13 @@
         <v>PASS</v>
       </c>
       <c r="H44">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I44" t="str">
         <v/>
       </c>
       <c r="J44" t="str">
-        <v>2026-08-09T18:19:36.065Z</v>
+        <v>2026-08-09T18:22:58.341Z</v>
       </c>
     </row>
     <row r="45">
@@ -1930,13 +1930,13 @@
         <v>PASS</v>
       </c>
       <c r="H45">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I45" t="str">
         <v/>
       </c>
       <c r="J45" t="str">
-        <v>2026-08-09T18:19:36.081Z</v>
+        <v>2026-08-09T18:22:58.356Z</v>
       </c>
     </row>
     <row r="46">
@@ -1962,13 +1962,13 @@
         <v>PASS</v>
       </c>
       <c r="H46">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I46" t="str">
         <v/>
       </c>
       <c r="J46" t="str">
-        <v>2026-08-09T18:19:36.097Z</v>
+        <v>2026-08-09T18:22:58.371Z</v>
       </c>
     </row>
     <row r="47">
@@ -2000,7 +2000,7 @@
         <v/>
       </c>
       <c r="J47" t="str">
-        <v>2026-08-09T18:19:36.112Z</v>
+        <v>2026-08-09T18:22:58.386Z</v>
       </c>
     </row>
     <row r="48">
@@ -2032,7 +2032,7 @@
         <v/>
       </c>
       <c r="J48" t="str">
-        <v>2026-08-09T18:19:36.128Z</v>
+        <v>2026-08-09T18:22:58.402Z</v>
       </c>
     </row>
     <row r="49">
@@ -2058,13 +2058,13 @@
         <v>PASS</v>
       </c>
       <c r="H49">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I49" t="str">
         <v/>
       </c>
       <c r="J49" t="str">
-        <v>2026-08-09T18:19:36.144Z</v>
+        <v>2026-08-09T18:22:58.419Z</v>
       </c>
     </row>
     <row r="50">
@@ -2090,13 +2090,13 @@
         <v>PASS</v>
       </c>
       <c r="H50">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I50" t="str">
         <v/>
       </c>
       <c r="J50" t="str">
-        <v>2026-08-09T18:19:36.160Z</v>
+        <v>2026-08-09T18:22:58.433Z</v>
       </c>
     </row>
     <row r="51">
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="J51" t="str">
-        <v>2026-08-09T18:19:36.176Z</v>
+        <v>2026-08-09T18:22:58.449Z</v>
       </c>
     </row>
     <row r="52">
@@ -2154,13 +2154,13 @@
         <v>PASS</v>
       </c>
       <c r="H52">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I52" t="str">
         <v/>
       </c>
       <c r="J52" t="str">
-        <v>2026-08-09T18:19:36.190Z</v>
+        <v>2026-08-09T18:22:58.465Z</v>
       </c>
     </row>
     <row r="53">
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="J53" t="str">
-        <v>2026-08-09T18:19:36.205Z</v>
+        <v>2026-08-09T18:22:58.480Z</v>
       </c>
     </row>
     <row r="54">
@@ -2218,13 +2218,13 @@
         <v>PASS</v>
       </c>
       <c r="H54">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I54" t="str">
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>2026-08-09T18:19:36.221Z</v>
+        <v>2026-08-09T18:22:58.495Z</v>
       </c>
     </row>
     <row r="55">
@@ -2250,13 +2250,13 @@
         <v>PASS</v>
       </c>
       <c r="H55">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I55" t="str">
         <v/>
       </c>
       <c r="J55" t="str">
-        <v>2026-08-09T18:19:36.237Z</v>
+        <v>2026-08-09T18:22:58.510Z</v>
       </c>
     </row>
     <row r="56">
@@ -2282,13 +2282,13 @@
         <v>PASS</v>
       </c>
       <c r="H56">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I56" t="str">
         <v/>
       </c>
       <c r="J56" t="str">
-        <v>2026-08-09T18:19:36.253Z</v>
+        <v>2026-08-09T18:22:58.525Z</v>
       </c>
     </row>
     <row r="57">
@@ -2320,7 +2320,7 @@
         <v/>
       </c>
       <c r="J57" t="str">
-        <v>2026-08-09T18:19:36.269Z</v>
+        <v>2026-08-09T18:22:58.541Z</v>
       </c>
     </row>
     <row r="58">
@@ -2346,13 +2346,13 @@
         <v>PASS</v>
       </c>
       <c r="H58">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I58" t="str">
         <v/>
       </c>
       <c r="J58" t="str">
-        <v>2026-08-09T18:19:36.285Z</v>
+        <v>2026-08-09T18:22:58.558Z</v>
       </c>
     </row>
     <row r="59">
@@ -2378,13 +2378,13 @@
         <v>PASS</v>
       </c>
       <c r="H59">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I59" t="str">
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>2026-08-09T18:19:36.301Z</v>
+        <v>2026-08-09T18:22:58.573Z</v>
       </c>
     </row>
     <row r="60">
@@ -2416,7 +2416,7 @@
         <v/>
       </c>
       <c r="J60" t="str">
-        <v>2026-08-09T18:19:36.317Z</v>
+        <v>2026-08-09T18:22:58.589Z</v>
       </c>
     </row>
     <row r="61">
@@ -2442,13 +2442,13 @@
         <v>PASS</v>
       </c>
       <c r="H61">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I61" t="str">
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>2026-08-09T18:19:36.333Z</v>
+        <v>2026-08-09T18:22:58.604Z</v>
       </c>
     </row>
     <row r="62">
@@ -2474,13 +2474,13 @@
         <v>PASS</v>
       </c>
       <c r="H62">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I62" t="str">
         <v/>
       </c>
       <c r="J62" t="str">
-        <v>2026-08-09T18:19:36.347Z</v>
+        <v>2026-08-09T18:22:58.619Z</v>
       </c>
     </row>
     <row r="63">
@@ -2512,7 +2512,7 @@
         <v/>
       </c>
       <c r="J63" t="str">
-        <v>2026-08-09T18:19:36.364Z</v>
+        <v>2026-08-09T18:22:58.635Z</v>
       </c>
     </row>
     <row r="64">
@@ -2538,13 +2538,13 @@
         <v>PASS</v>
       </c>
       <c r="H64">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I64" t="str">
         <v/>
       </c>
       <c r="J64" t="str">
-        <v>2026-08-09T18:19:36.379Z</v>
+        <v>2026-08-09T18:22:58.651Z</v>
       </c>
     </row>
     <row r="65">
@@ -2570,13 +2570,13 @@
         <v>PASS</v>
       </c>
       <c r="H65">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I65" t="str">
         <v/>
       </c>
       <c r="J65" t="str">
-        <v>2026-08-09T18:19:36.394Z</v>
+        <v>2026-08-09T18:22:58.667Z</v>
       </c>
     </row>
     <row r="66">
@@ -2602,13 +2602,13 @@
         <v>PASS</v>
       </c>
       <c r="H66">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I66" t="str">
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>2026-08-09T18:19:36.411Z</v>
+        <v>2026-08-09T18:22:58.682Z</v>
       </c>
     </row>
     <row r="67">
@@ -2634,13 +2634,13 @@
         <v>PASS</v>
       </c>
       <c r="H67">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I67" t="str">
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>2026-08-09T18:19:36.424Z</v>
+        <v>2026-08-09T18:22:58.697Z</v>
       </c>
     </row>
     <row r="68">
@@ -2666,13 +2666,13 @@
         <v>PASS</v>
       </c>
       <c r="H68">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I68" t="str">
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>2026-08-09T18:19:36.440Z</v>
+        <v>2026-08-09T18:22:58.712Z</v>
       </c>
     </row>
     <row r="69">
@@ -2698,13 +2698,13 @@
         <v>PASS</v>
       </c>
       <c r="H69">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I69" t="str">
         <v/>
       </c>
       <c r="J69" t="str">
-        <v>2026-08-09T18:19:36.455Z</v>
+        <v>2026-08-09T18:22:58.728Z</v>
       </c>
     </row>
     <row r="70">
@@ -2736,7 +2736,7 @@
         <v/>
       </c>
       <c r="J70" t="str">
-        <v>2026-08-09T18:19:36.471Z</v>
+        <v>2026-08-09T18:22:58.744Z</v>
       </c>
     </row>
     <row r="71">
@@ -2762,13 +2762,13 @@
         <v>PASS</v>
       </c>
       <c r="H71">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I71" t="str">
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>2026-08-09T18:19:36.487Z</v>
+        <v>2026-08-09T18:22:58.758Z</v>
       </c>
     </row>
     <row r="72">
@@ -2794,13 +2794,13 @@
         <v>PASS</v>
       </c>
       <c r="H72">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I72" t="str">
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>2026-08-09T18:19:36.502Z</v>
+        <v>2026-08-09T18:22:58.774Z</v>
       </c>
     </row>
     <row r="73">
@@ -2832,7 +2832,7 @@
         <v/>
       </c>
       <c r="J73" t="str">
-        <v>2026-08-09T18:19:36.517Z</v>
+        <v>2026-08-09T18:22:58.790Z</v>
       </c>
     </row>
     <row r="74">
@@ -2858,13 +2858,13 @@
         <v>PASS</v>
       </c>
       <c r="H74">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I74" t="str">
         <v/>
       </c>
       <c r="J74" t="str">
-        <v>2026-08-09T18:19:36.533Z</v>
+        <v>2026-08-09T18:22:58.804Z</v>
       </c>
     </row>
     <row r="75">
@@ -2896,7 +2896,7 @@
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>2026-08-09T18:19:36.548Z</v>
+        <v>2026-08-09T18:22:58.820Z</v>
       </c>
     </row>
     <row r="76">
@@ -2928,7 +2928,7 @@
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>2026-08-09T18:19:36.563Z</v>
+        <v>2026-08-09T18:22:58.835Z</v>
       </c>
     </row>
     <row r="77">
@@ -2954,13 +2954,13 @@
         <v>PASS</v>
       </c>
       <c r="H77">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I77" t="str">
         <v/>
       </c>
       <c r="J77" t="str">
-        <v>2026-08-09T18:19:36.579Z</v>
+        <v>2026-08-09T18:22:58.851Z</v>
       </c>
     </row>
     <row r="78">
@@ -2992,7 +2992,7 @@
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>2026-08-09T18:19:36.594Z</v>
+        <v>2026-08-09T18:22:58.867Z</v>
       </c>
     </row>
     <row r="79">
@@ -3024,7 +3024,7 @@
         <v/>
       </c>
       <c r="J79" t="str">
-        <v>2026-08-09T18:19:36.609Z</v>
+        <v>2026-08-09T18:22:58.882Z</v>
       </c>
     </row>
     <row r="80">
@@ -3056,7 +3056,7 @@
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>2026-08-09T18:19:36.625Z</v>
+        <v>2026-08-09T18:22:58.898Z</v>
       </c>
     </row>
     <row r="81">
@@ -3082,13 +3082,13 @@
         <v>PASS</v>
       </c>
       <c r="H81">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I81" t="str">
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>2026-08-09T18:19:36.641Z</v>
+        <v>2026-08-09T18:22:58.913Z</v>
       </c>
     </row>
     <row r="82">
@@ -3120,7 +3120,7 @@
         <v/>
       </c>
       <c r="J82" t="str">
-        <v>2026-08-09T18:19:36.656Z</v>
+        <v>2026-08-09T18:22:58.929Z</v>
       </c>
     </row>
     <row r="83">
@@ -3152,7 +3152,7 @@
         <v/>
       </c>
       <c r="J83" t="str">
-        <v>2026-08-09T18:19:36.671Z</v>
+        <v>2026-08-09T18:22:58.944Z</v>
       </c>
     </row>
     <row r="84">
@@ -3184,7 +3184,7 @@
         <v/>
       </c>
       <c r="J84" t="str">
-        <v>2026-08-09T18:19:36.687Z</v>
+        <v>2026-08-09T18:22:58.960Z</v>
       </c>
     </row>
     <row r="85">
@@ -3210,13 +3210,13 @@
         <v>PASS</v>
       </c>
       <c r="H85">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I85" t="str">
         <v/>
       </c>
       <c r="J85" t="str">
-        <v>2026-08-09T18:19:36.702Z</v>
+        <v>2026-08-09T18:22:58.976Z</v>
       </c>
     </row>
     <row r="86">
@@ -3242,13 +3242,13 @@
         <v>PASS</v>
       </c>
       <c r="H86">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I86" t="str">
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>2026-08-09T18:19:36.717Z</v>
+        <v>2026-08-09T18:22:58.993Z</v>
       </c>
     </row>
     <row r="87">
@@ -3280,7 +3280,7 @@
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>2026-08-09T18:19:36.733Z</v>
+        <v>2026-08-09T18:22:59.008Z</v>
       </c>
     </row>
     <row r="88">
@@ -3312,7 +3312,7 @@
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>2026-08-09T18:19:36.748Z</v>
+        <v>2026-08-09T18:22:59.023Z</v>
       </c>
     </row>
     <row r="89">
@@ -3338,13 +3338,13 @@
         <v>PASS</v>
       </c>
       <c r="H89">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I89" t="str">
         <v/>
       </c>
       <c r="J89" t="str">
-        <v>2026-08-09T18:19:36.764Z</v>
+        <v>2026-08-09T18:22:59.038Z</v>
       </c>
     </row>
     <row r="90">
@@ -3370,13 +3370,13 @@
         <v>PASS</v>
       </c>
       <c r="H90">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I90" t="str">
         <v/>
       </c>
       <c r="J90" t="str">
-        <v>2026-08-09T18:19:36.778Z</v>
+        <v>2026-08-09T18:22:59.054Z</v>
       </c>
     </row>
     <row r="91">
@@ -3402,13 +3402,13 @@
         <v>PASS</v>
       </c>
       <c r="H91">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I91" t="str">
         <v/>
       </c>
       <c r="J91" t="str">
-        <v>2026-08-09T18:19:36.794Z</v>
+        <v>2026-08-09T18:22:59.069Z</v>
       </c>
     </row>
     <row r="92">
@@ -3434,13 +3434,13 @@
         <v>PASS</v>
       </c>
       <c r="H92">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I92" t="str">
         <v/>
       </c>
       <c r="J92" t="str">
-        <v>2026-08-09T18:19:36.809Z</v>
+        <v>2026-08-09T18:22:59.085Z</v>
       </c>
     </row>
     <row r="93">
@@ -3472,7 +3472,7 @@
         <v/>
       </c>
       <c r="J93" t="str">
-        <v>2026-08-09T18:19:36.825Z</v>
+        <v>2026-08-09T18:22:59.100Z</v>
       </c>
     </row>
     <row r="94">
@@ -3498,13 +3498,13 @@
         <v>PASS</v>
       </c>
       <c r="H94">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I94" t="str">
         <v/>
       </c>
       <c r="J94" t="str">
-        <v>2026-08-09T18:19:36.840Z</v>
+        <v>2026-08-09T18:22:59.116Z</v>
       </c>
     </row>
     <row r="95">
@@ -3530,13 +3530,13 @@
         <v>PASS</v>
       </c>
       <c r="H95">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I95" t="str">
         <v/>
       </c>
       <c r="J95" t="str">
-        <v>2026-08-09T18:19:36.856Z</v>
+        <v>2026-08-09T18:22:59.131Z</v>
       </c>
     </row>
     <row r="96">
@@ -3568,7 +3568,7 @@
         <v/>
       </c>
       <c r="J96" t="str">
-        <v>2026-08-09T18:19:36.872Z</v>
+        <v>2026-08-09T18:22:59.147Z</v>
       </c>
     </row>
     <row r="97">
@@ -3594,13 +3594,13 @@
         <v>PASS</v>
       </c>
       <c r="H97">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I97" t="str">
         <v/>
       </c>
       <c r="J97" t="str">
-        <v>2026-08-09T18:19:36.887Z</v>
+        <v>2026-08-09T18:22:59.163Z</v>
       </c>
     </row>
     <row r="98">
@@ -3626,13 +3626,13 @@
         <v>PASS</v>
       </c>
       <c r="H98">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I98" t="str">
         <v/>
       </c>
       <c r="J98" t="str">
-        <v>2026-08-09T18:19:36.904Z</v>
+        <v>2026-08-09T18:22:59.178Z</v>
       </c>
     </row>
     <row r="99">
@@ -3658,13 +3658,13 @@
         <v>PASS</v>
       </c>
       <c r="H99">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I99" t="str">
         <v/>
       </c>
       <c r="J99" t="str">
-        <v>2026-08-09T18:19:36.919Z</v>
+        <v>2026-08-09T18:22:59.194Z</v>
       </c>
     </row>
     <row r="100">
@@ -3690,13 +3690,13 @@
         <v>PASS</v>
       </c>
       <c r="H100">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I100" t="str">
         <v/>
       </c>
       <c r="J100" t="str">
-        <v>2026-08-09T18:19:36.934Z</v>
+        <v>2026-08-09T18:22:59.210Z</v>
       </c>
     </row>
     <row r="101">
@@ -3728,7 +3728,7 @@
         <v/>
       </c>
       <c r="J101" t="str">
-        <v>2026-08-09T18:19:36.949Z</v>
+        <v>2026-08-09T18:22:59.225Z</v>
       </c>
     </row>
     <row r="102">
@@ -3754,13 +3754,13 @@
         <v>PASS</v>
       </c>
       <c r="H102">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I102" t="str">
         <v/>
       </c>
       <c r="J102" t="str">
-        <v>2026-08-09T18:19:36.966Z</v>
+        <v>2026-08-09T18:22:59.240Z</v>
       </c>
     </row>
     <row r="103">
@@ -3786,13 +3786,13 @@
         <v>PASS</v>
       </c>
       <c r="H103">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I103" t="str">
         <v/>
       </c>
       <c r="J103" t="str">
-        <v>2026-08-09T18:19:36.979Z</v>
+        <v>2026-08-09T18:22:59.255Z</v>
       </c>
     </row>
     <row r="104">
@@ -3824,7 +3824,7 @@
         <v/>
       </c>
       <c r="J104" t="str">
-        <v>2026-08-09T18:19:36.995Z</v>
+        <v>2026-08-09T18:22:59.271Z</v>
       </c>
     </row>
     <row r="105">
@@ -3850,13 +3850,13 @@
         <v>PASS</v>
       </c>
       <c r="H105">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I105" t="str">
         <v/>
       </c>
       <c r="J105" t="str">
-        <v>2026-08-09T18:19:37.012Z</v>
+        <v>2026-08-09T18:22:59.288Z</v>
       </c>
     </row>
     <row r="106">
@@ -3882,13 +3882,13 @@
         <v>PASS</v>
       </c>
       <c r="H106">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I106" t="str">
         <v/>
       </c>
       <c r="J106" t="str">
-        <v>2026-08-09T18:19:37.026Z</v>
+        <v>2026-08-09T18:22:59.303Z</v>
       </c>
     </row>
     <row r="107">
@@ -3914,13 +3914,13 @@
         <v>PASS</v>
       </c>
       <c r="H107">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I107" t="str">
         <v/>
       </c>
       <c r="J107" t="str">
-        <v>2026-08-09T18:19:37.042Z</v>
+        <v>2026-08-09T18:22:59.318Z</v>
       </c>
     </row>
     <row r="108">
@@ -3946,13 +3946,13 @@
         <v>PASS</v>
       </c>
       <c r="H108">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I108" t="str">
         <v/>
       </c>
       <c r="J108" t="str">
-        <v>2026-08-09T18:19:37.058Z</v>
+        <v>2026-08-09T18:22:59.333Z</v>
       </c>
     </row>
     <row r="109">
@@ -3978,13 +3978,13 @@
         <v>PASS</v>
       </c>
       <c r="H109">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I109" t="str">
         <v/>
       </c>
       <c r="J109" t="str">
-        <v>2026-08-09T18:19:37.073Z</v>
+        <v>2026-08-09T18:22:59.349Z</v>
       </c>
     </row>
     <row r="110">
@@ -4016,7 +4016,7 @@
         <v/>
       </c>
       <c r="J110" t="str">
-        <v>2026-08-09T18:19:37.089Z</v>
+        <v>2026-08-09T18:22:59.365Z</v>
       </c>
     </row>
     <row r="111">
@@ -4048,7 +4048,7 @@
         <v/>
       </c>
       <c r="J111" t="str">
-        <v>2026-08-09T18:19:37.104Z</v>
+        <v>2026-08-09T18:22:59.380Z</v>
       </c>
     </row>
     <row r="112">
@@ -4074,13 +4074,13 @@
         <v>PASS</v>
       </c>
       <c r="H112">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I112" t="str">
         <v/>
       </c>
       <c r="J112" t="str">
-        <v>2026-08-09T18:19:37.119Z</v>
+        <v>2026-08-09T18:22:59.396Z</v>
       </c>
     </row>
     <row r="113">
@@ -4106,13 +4106,13 @@
         <v>PASS</v>
       </c>
       <c r="H113">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I113" t="str">
         <v/>
       </c>
       <c r="J113" t="str">
-        <v>2026-08-09T18:19:37.134Z</v>
+        <v>2026-08-09T18:22:59.412Z</v>
       </c>
     </row>
     <row r="114">
@@ -4138,13 +4138,13 @@
         <v>PASS</v>
       </c>
       <c r="H114">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I114" t="str">
         <v/>
       </c>
       <c r="J114" t="str">
-        <v>2026-08-09T18:19:37.149Z</v>
+        <v>2026-08-09T18:22:59.428Z</v>
       </c>
     </row>
     <row r="115">
@@ -4176,7 +4176,7 @@
         <v/>
       </c>
       <c r="J115" t="str">
-        <v>2026-08-09T18:19:37.164Z</v>
+        <v>2026-08-09T18:22:59.443Z</v>
       </c>
     </row>
     <row r="116">
@@ -4202,13 +4202,13 @@
         <v>PASS</v>
       </c>
       <c r="H116">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I116" t="str">
         <v/>
       </c>
       <c r="J116" t="str">
-        <v>2026-08-09T18:19:37.181Z</v>
+        <v>2026-08-09T18:22:59.459Z</v>
       </c>
     </row>
     <row r="117">
@@ -4234,13 +4234,13 @@
         <v>PASS</v>
       </c>
       <c r="H117">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I117" t="str">
         <v/>
       </c>
       <c r="J117" t="str">
-        <v>2026-08-09T18:19:37.196Z</v>
+        <v>2026-08-09T18:22:59.475Z</v>
       </c>
     </row>
     <row r="118">
@@ -4266,13 +4266,13 @@
         <v>PASS</v>
       </c>
       <c r="H118">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I118" t="str">
         <v/>
       </c>
       <c r="J118" t="str">
-        <v>2026-08-09T18:19:37.211Z</v>
+        <v>2026-08-09T18:22:59.491Z</v>
       </c>
     </row>
     <row r="119">
@@ -4298,13 +4298,13 @@
         <v>PASS</v>
       </c>
       <c r="H119">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I119" t="str">
         <v/>
       </c>
       <c r="J119" t="str">
-        <v>2026-08-09T18:19:37.227Z</v>
+        <v>2026-08-09T18:22:59.506Z</v>
       </c>
     </row>
     <row r="120">
@@ -4330,13 +4330,13 @@
         <v>PASS</v>
       </c>
       <c r="H120">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I120" t="str">
         <v/>
       </c>
       <c r="J120" t="str">
-        <v>2026-08-09T18:19:37.243Z</v>
+        <v>2026-08-09T18:22:59.521Z</v>
       </c>
     </row>
     <row r="121">
@@ -4362,13 +4362,13 @@
         <v>PASS</v>
       </c>
       <c r="H121">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I121" t="str">
         <v/>
       </c>
       <c r="J121" t="str">
-        <v>2026-08-09T18:19:37.258Z</v>
+        <v>2026-08-09T18:22:59.537Z</v>
       </c>
     </row>
     <row r="122">
@@ -4394,13 +4394,13 @@
         <v>PASS</v>
       </c>
       <c r="H122">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I122" t="str">
         <v/>
       </c>
       <c r="J122" t="str">
-        <v>2026-08-09T18:19:37.275Z</v>
+        <v>2026-08-09T18:22:59.553Z</v>
       </c>
     </row>
     <row r="123">
@@ -4426,13 +4426,13 @@
         <v>PASS</v>
       </c>
       <c r="H123">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I123" t="str">
         <v/>
       </c>
       <c r="J123" t="str">
-        <v>2026-08-09T18:19:37.291Z</v>
+        <v>2026-08-09T18:22:59.568Z</v>
       </c>
     </row>
     <row r="124">
@@ -4458,13 +4458,13 @@
         <v>PASS</v>
       </c>
       <c r="H124">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I124" t="str">
         <v/>
       </c>
       <c r="J124" t="str">
-        <v>2026-08-09T18:19:37.306Z</v>
+        <v>2026-08-09T18:22:59.584Z</v>
       </c>
     </row>
     <row r="125">
@@ -4496,7 +4496,7 @@
         <v/>
       </c>
       <c r="J125" t="str">
-        <v>2026-08-09T18:19:37.321Z</v>
+        <v>2026-08-09T18:22:59.599Z</v>
       </c>
     </row>
     <row r="126">
@@ -4522,13 +4522,13 @@
         <v>PASS</v>
       </c>
       <c r="H126">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I126" t="str">
         <v/>
       </c>
       <c r="J126" t="str">
-        <v>2026-08-09T18:19:37.336Z</v>
+        <v>2026-08-09T18:22:59.615Z</v>
       </c>
     </row>
     <row r="127">
@@ -4554,13 +4554,13 @@
         <v>PASS</v>
       </c>
       <c r="H127">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I127" t="str">
         <v/>
       </c>
       <c r="J127" t="str">
-        <v>2026-08-09T18:19:37.351Z</v>
+        <v>2026-08-09T18:22:59.631Z</v>
       </c>
     </row>
     <row r="128">
@@ -4592,7 +4592,7 @@
         <v/>
       </c>
       <c r="J128" t="str">
-        <v>2026-08-09T18:19:37.367Z</v>
+        <v>2026-08-09T18:22:59.647Z</v>
       </c>
     </row>
     <row r="129">
@@ -4618,13 +4618,13 @@
         <v>PASS</v>
       </c>
       <c r="H129">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I129" t="str">
         <v/>
       </c>
       <c r="J129" t="str">
-        <v>2026-08-09T18:19:37.382Z</v>
+        <v>2026-08-09T18:22:59.663Z</v>
       </c>
     </row>
     <row r="130">
@@ -4650,13 +4650,13 @@
         <v>PASS</v>
       </c>
       <c r="H130">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I130" t="str">
         <v/>
       </c>
       <c r="J130" t="str">
-        <v>2026-08-09T18:19:37.398Z</v>
+        <v>2026-08-09T18:22:59.678Z</v>
       </c>
     </row>
     <row r="131">
@@ -4682,13 +4682,13 @@
         <v>PASS</v>
       </c>
       <c r="H131">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I131" t="str">
         <v/>
       </c>
       <c r="J131" t="str">
-        <v>2026-08-09T18:19:37.413Z</v>
+        <v>2026-08-09T18:22:59.694Z</v>
       </c>
     </row>
     <row r="132">
@@ -4714,13 +4714,13 @@
         <v>PASS</v>
       </c>
       <c r="H132">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I132" t="str">
         <v/>
       </c>
       <c r="J132" t="str">
-        <v>2026-08-09T18:19:37.428Z</v>
+        <v>2026-08-09T18:22:59.711Z</v>
       </c>
     </row>
     <row r="133">
@@ -4746,13 +4746,13 @@
         <v>PASS</v>
       </c>
       <c r="H133">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I133" t="str">
         <v/>
       </c>
       <c r="J133" t="str">
-        <v>2026-08-09T18:19:37.444Z</v>
+        <v>2026-08-09T18:22:59.726Z</v>
       </c>
     </row>
     <row r="134">
@@ -4778,13 +4778,13 @@
         <v>PASS</v>
       </c>
       <c r="H134">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I134" t="str">
         <v/>
       </c>
       <c r="J134" t="str">
-        <v>2026-08-09T18:19:37.458Z</v>
+        <v>2026-08-09T18:22:59.741Z</v>
       </c>
     </row>
     <row r="135">
@@ -4810,13 +4810,13 @@
         <v>PASS</v>
       </c>
       <c r="H135">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I135" t="str">
         <v/>
       </c>
       <c r="J135" t="str">
-        <v>2026-08-09T18:19:37.474Z</v>
+        <v>2026-08-09T18:22:59.756Z</v>
       </c>
     </row>
     <row r="136">
@@ -4842,13 +4842,13 @@
         <v>PASS</v>
       </c>
       <c r="H136">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I136" t="str">
         <v/>
       </c>
       <c r="J136" t="str">
-        <v>2026-08-09T18:19:37.491Z</v>
+        <v>2026-08-09T18:22:59.772Z</v>
       </c>
     </row>
     <row r="137">
@@ -4874,13 +4874,13 @@
         <v>PASS</v>
       </c>
       <c r="H137">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I137" t="str">
         <v/>
       </c>
       <c r="J137" t="str">
-        <v>2026-08-09T18:19:37.505Z</v>
+        <v>2026-08-09T18:22:59.787Z</v>
       </c>
     </row>
     <row r="138">
@@ -4906,13 +4906,13 @@
         <v>PASS</v>
       </c>
       <c r="H138">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I138" t="str">
         <v/>
       </c>
       <c r="J138" t="str">
-        <v>2026-08-09T18:19:37.521Z</v>
+        <v>2026-08-09T18:22:59.802Z</v>
       </c>
     </row>
     <row r="139">
@@ -4938,13 +4938,13 @@
         <v>PASS</v>
       </c>
       <c r="H139">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I139" t="str">
         <v/>
       </c>
       <c r="J139" t="str">
-        <v>2026-08-09T18:19:37.536Z</v>
+        <v>2026-08-09T18:22:59.818Z</v>
       </c>
     </row>
     <row r="140">
@@ -4976,7 +4976,7 @@
         <v/>
       </c>
       <c r="J140" t="str">
-        <v>2026-08-09T18:19:37.552Z</v>
+        <v>2026-08-09T18:22:59.834Z</v>
       </c>
     </row>
     <row r="141">
@@ -5002,13 +5002,13 @@
         <v>PASS</v>
       </c>
       <c r="H141">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I141" t="str">
         <v/>
       </c>
       <c r="J141" t="str">
-        <v>2026-08-09T18:19:37.568Z</v>
+        <v>2026-08-09T18:22:59.849Z</v>
       </c>
     </row>
     <row r="142">
@@ -5034,13 +5034,13 @@
         <v>PASS</v>
       </c>
       <c r="H142">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I142" t="str">
         <v/>
       </c>
       <c r="J142" t="str">
-        <v>2026-08-09T18:19:37.583Z</v>
+        <v>2026-08-09T18:22:59.866Z</v>
       </c>
     </row>
     <row r="143">
@@ -5066,13 +5066,13 @@
         <v>PASS</v>
       </c>
       <c r="H143">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I143" t="str">
         <v/>
       </c>
       <c r="J143" t="str">
-        <v>2026-08-09T18:19:37.599Z</v>
+        <v>2026-08-09T18:22:59.881Z</v>
       </c>
     </row>
     <row r="144">
@@ -5098,13 +5098,13 @@
         <v>PASS</v>
       </c>
       <c r="H144">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I144" t="str">
         <v/>
       </c>
       <c r="J144" t="str">
-        <v>2026-08-09T18:19:37.614Z</v>
+        <v>2026-08-09T18:22:59.897Z</v>
       </c>
     </row>
     <row r="145">
@@ -5130,13 +5130,13 @@
         <v>PASS</v>
       </c>
       <c r="H145">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I145" t="str">
         <v/>
       </c>
       <c r="J145" t="str">
-        <v>2026-08-09T18:19:37.629Z</v>
+        <v>2026-08-09T18:22:59.913Z</v>
       </c>
     </row>
     <row r="146">
@@ -5162,13 +5162,13 @@
         <v>PASS</v>
       </c>
       <c r="H146">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I146" t="str">
         <v/>
       </c>
       <c r="J146" t="str">
-        <v>2026-08-09T18:19:37.644Z</v>
+        <v>2026-08-09T18:22:59.928Z</v>
       </c>
     </row>
     <row r="147">
@@ -5200,7 +5200,7 @@
         <v/>
       </c>
       <c r="J147" t="str">
-        <v>2026-08-09T18:19:37.661Z</v>
+        <v>2026-08-09T18:22:59.945Z</v>
       </c>
     </row>
     <row r="148">
@@ -5226,13 +5226,13 @@
         <v>PASS</v>
       </c>
       <c r="H148">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I148" t="str">
         <v/>
       </c>
       <c r="J148" t="str">
-        <v>2026-08-09T18:19:37.676Z</v>
+        <v>2026-08-09T18:22:59.961Z</v>
       </c>
     </row>
     <row r="149">
@@ -5264,7 +5264,7 @@
         <v/>
       </c>
       <c r="J149" t="str">
-        <v>2026-08-09T18:19:37.692Z</v>
+        <v>2026-08-09T18:22:59.977Z</v>
       </c>
     </row>
     <row r="150">
@@ -5296,7 +5296,7 @@
         <v/>
       </c>
       <c r="J150" t="str">
-        <v>2026-08-09T18:19:37.708Z</v>
+        <v>2026-08-09T18:22:59.993Z</v>
       </c>
     </row>
     <row r="151">
@@ -5322,13 +5322,13 @@
         <v>PASS</v>
       </c>
       <c r="H151">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I151" t="str">
         <v/>
       </c>
       <c r="J151" t="str">
-        <v>2026-08-09T18:19:37.723Z</v>
+        <v>2026-08-09T18:23:00.009Z</v>
       </c>
     </row>
     <row r="152">
@@ -5354,13 +5354,13 @@
         <v>PASS</v>
       </c>
       <c r="H152">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I152" t="str">
         <v/>
       </c>
       <c r="J152" t="str">
-        <v>2026-08-09T18:19:37.739Z</v>
+        <v>2026-08-09T18:23:00.025Z</v>
       </c>
     </row>
     <row r="153">
@@ -5386,13 +5386,13 @@
         <v>PASS</v>
       </c>
       <c r="H153">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I153" t="str">
         <v/>
       </c>
       <c r="J153" t="str">
-        <v>2026-08-09T18:19:37.754Z</v>
+        <v>2026-08-09T18:23:00.041Z</v>
       </c>
     </row>
     <row r="154">
@@ -5424,7 +5424,7 @@
         <v/>
       </c>
       <c r="J154" t="str">
-        <v>2026-08-09T18:19:37.769Z</v>
+        <v>2026-08-09T18:23:00.056Z</v>
       </c>
     </row>
     <row r="155">
@@ -5450,13 +5450,13 @@
         <v>PASS</v>
       </c>
       <c r="H155">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I155" t="str">
         <v/>
       </c>
       <c r="J155" t="str">
-        <v>2026-08-09T18:19:37.785Z</v>
+        <v>2026-08-09T18:23:00.071Z</v>
       </c>
     </row>
     <row r="156">
@@ -5488,7 +5488,7 @@
         <v/>
       </c>
       <c r="J156" t="str">
-        <v>2026-08-09T18:19:37.801Z</v>
+        <v>2026-08-09T18:23:00.087Z</v>
       </c>
     </row>
     <row r="157">
@@ -5520,7 +5520,7 @@
         <v/>
       </c>
       <c r="J157" t="str">
-        <v>2026-08-09T18:19:37.817Z</v>
+        <v>2026-08-09T18:23:00.103Z</v>
       </c>
     </row>
     <row r="158">
@@ -5546,13 +5546,13 @@
         <v>PASS</v>
       </c>
       <c r="H158">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I158" t="str">
         <v/>
       </c>
       <c r="J158" t="str">
-        <v>2026-08-09T18:19:37.832Z</v>
+        <v>2026-08-09T18:23:00.119Z</v>
       </c>
     </row>
     <row r="159">
@@ -5584,7 +5584,7 @@
         <v/>
       </c>
       <c r="J159" t="str">
-        <v>2026-08-09T18:19:37.848Z</v>
+        <v>2026-08-09T18:23:00.135Z</v>
       </c>
     </row>
     <row r="160">
@@ -5610,13 +5610,13 @@
         <v>PASS</v>
       </c>
       <c r="H160">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I160" t="str">
         <v/>
       </c>
       <c r="J160" t="str">
-        <v>2026-08-09T18:19:37.863Z</v>
+        <v>2026-08-09T18:23:00.151Z</v>
       </c>
     </row>
     <row r="161">
@@ -5642,13 +5642,13 @@
         <v>PASS</v>
       </c>
       <c r="H161">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I161" t="str">
         <v/>
       </c>
       <c r="J161" t="str">
-        <v>2026-08-09T18:19:37.879Z</v>
+        <v>2026-08-09T18:23:00.166Z</v>
       </c>
     </row>
     <row r="162">
@@ -5674,13 +5674,13 @@
         <v>PASS</v>
       </c>
       <c r="H162">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I162" t="str">
         <v/>
       </c>
       <c r="J162" t="str">
-        <v>2026-08-09T18:19:37.896Z</v>
+        <v>2026-08-09T18:23:00.180Z</v>
       </c>
     </row>
     <row r="163">
@@ -5706,13 +5706,13 @@
         <v>PASS</v>
       </c>
       <c r="H163">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I163" t="str">
         <v/>
       </c>
       <c r="J163" t="str">
-        <v>2026-08-09T18:19:37.911Z</v>
+        <v>2026-08-09T18:23:00.197Z</v>
       </c>
     </row>
     <row r="164">
@@ -5744,7 +5744,7 @@
         <v/>
       </c>
       <c r="J164" t="str">
-        <v>2026-08-09T18:19:37.927Z</v>
+        <v>2026-08-09T18:23:00.213Z</v>
       </c>
     </row>
     <row r="165">
@@ -5770,13 +5770,13 @@
         <v>PASS</v>
       </c>
       <c r="H165">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I165" t="str">
         <v/>
       </c>
       <c r="J165" t="str">
-        <v>2026-08-09T18:19:37.941Z</v>
+        <v>2026-08-09T18:23:00.228Z</v>
       </c>
     </row>
     <row r="166">
@@ -5802,13 +5802,13 @@
         <v>PASS</v>
       </c>
       <c r="H166">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I166" t="str">
         <v/>
       </c>
       <c r="J166" t="str">
-        <v>2026-08-09T18:19:37.957Z</v>
+        <v>2026-08-09T18:23:00.243Z</v>
       </c>
     </row>
     <row r="167">
@@ -5840,7 +5840,7 @@
         <v/>
       </c>
       <c r="J167" t="str">
-        <v>2026-08-09T18:19:37.972Z</v>
+        <v>2026-08-09T18:23:00.258Z</v>
       </c>
     </row>
     <row r="168">
@@ -5866,13 +5866,13 @@
         <v>PASS</v>
       </c>
       <c r="H168">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I168" t="str">
         <v/>
       </c>
       <c r="J168" t="str">
-        <v>2026-08-09T18:19:37.987Z</v>
+        <v>2026-08-09T18:23:00.274Z</v>
       </c>
     </row>
     <row r="169">
@@ -5904,7 +5904,7 @@
         <v/>
       </c>
       <c r="J169" t="str">
-        <v>2026-08-09T18:19:38.002Z</v>
+        <v>2026-08-09T18:23:00.289Z</v>
       </c>
     </row>
     <row r="170">
@@ -5930,13 +5930,13 @@
         <v>PASS</v>
       </c>
       <c r="H170">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I170" t="str">
         <v/>
       </c>
       <c r="J170" t="str">
-        <v>2026-08-09T18:19:38.018Z</v>
+        <v>2026-08-09T18:23:00.304Z</v>
       </c>
     </row>
     <row r="171">
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="J171" t="str">
-        <v>2026-08-09T18:19:38.034Z</v>
+        <v>2026-08-09T18:23:00.320Z</v>
       </c>
     </row>
     <row r="172">
@@ -6000,7 +6000,7 @@
         <v/>
       </c>
       <c r="J172" t="str">
-        <v>2026-08-09T18:19:38.050Z</v>
+        <v>2026-08-09T18:23:00.336Z</v>
       </c>
     </row>
     <row r="173">
@@ -6032,7 +6032,7 @@
         <v/>
       </c>
       <c r="J173" t="str">
-        <v>2026-08-09T18:19:38.066Z</v>
+        <v>2026-08-09T18:23:00.352Z</v>
       </c>
     </row>
     <row r="174">
@@ -6058,13 +6058,13 @@
         <v>PASS</v>
       </c>
       <c r="H174">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I174" t="str">
         <v/>
       </c>
       <c r="J174" t="str">
-        <v>2026-08-09T18:19:38.081Z</v>
+        <v>2026-08-09T18:23:00.366Z</v>
       </c>
     </row>
     <row r="175">
@@ -6090,13 +6090,13 @@
         <v>PASS</v>
       </c>
       <c r="H175">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I175" t="str">
         <v/>
       </c>
       <c r="J175" t="str">
-        <v>2026-08-09T18:19:38.097Z</v>
+        <v>2026-08-09T18:23:00.383Z</v>
       </c>
     </row>
     <row r="176">
@@ -6128,7 +6128,7 @@
         <v/>
       </c>
       <c r="J176" t="str">
-        <v>2026-08-09T18:19:38.112Z</v>
+        <v>2026-08-09T18:23:00.398Z</v>
       </c>
     </row>
     <row r="177">
@@ -6154,13 +6154,13 @@
         <v>PASS</v>
       </c>
       <c r="H177">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I177" t="str">
         <v/>
       </c>
       <c r="J177" t="str">
-        <v>2026-08-09T18:19:38.128Z</v>
+        <v>2026-08-09T18:23:00.413Z</v>
       </c>
     </row>
     <row r="178">
@@ -6192,7 +6192,7 @@
         <v/>
       </c>
       <c r="J178" t="str">
-        <v>2026-08-09T18:19:38.143Z</v>
+        <v>2026-08-09T18:23:00.428Z</v>
       </c>
     </row>
     <row r="179">
@@ -6218,13 +6218,13 @@
         <v>PASS</v>
       </c>
       <c r="H179">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I179" t="str">
         <v/>
       </c>
       <c r="J179" t="str">
-        <v>2026-08-09T18:19:38.159Z</v>
+        <v>2026-08-09T18:23:00.443Z</v>
       </c>
     </row>
     <row r="180">
@@ -6250,13 +6250,13 @@
         <v>PASS</v>
       </c>
       <c r="H180">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I180" t="str">
         <v/>
       </c>
       <c r="J180" t="str">
-        <v>2026-08-09T18:19:38.177Z</v>
+        <v>2026-08-09T18:23:00.459Z</v>
       </c>
     </row>
     <row r="181">
@@ -6282,13 +6282,13 @@
         <v>PASS</v>
       </c>
       <c r="H181">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I181" t="str">
         <v/>
       </c>
       <c r="J181" t="str">
-        <v>2026-08-09T18:19:38.190Z</v>
+        <v>2026-08-09T18:23:00.475Z</v>
       </c>
     </row>
     <row r="182">
@@ -6314,13 +6314,13 @@
         <v>PASS</v>
       </c>
       <c r="H182">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I182" t="str">
         <v/>
       </c>
       <c r="J182" t="str">
-        <v>2026-08-09T18:19:38.205Z</v>
+        <v>2026-08-09T18:23:00.491Z</v>
       </c>
     </row>
     <row r="183">
@@ -6352,7 +6352,7 @@
         <v/>
       </c>
       <c r="J183" t="str">
-        <v>2026-08-09T18:19:38.221Z</v>
+        <v>2026-08-09T18:23:00.507Z</v>
       </c>
     </row>
     <row r="184">
@@ -6378,13 +6378,13 @@
         <v>PASS</v>
       </c>
       <c r="H184">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I184" t="str">
         <v/>
       </c>
       <c r="J184" t="str">
-        <v>2026-08-09T18:19:38.237Z</v>
+        <v>2026-08-09T18:23:00.537Z</v>
       </c>
     </row>
     <row r="185">
@@ -6410,13 +6410,13 @@
         <v>PASS</v>
       </c>
       <c r="H185">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I185" t="str">
         <v/>
       </c>
       <c r="J185" t="str">
-        <v>2026-08-09T18:19:38.252Z</v>
+        <v>2026-08-09T18:23:00.556Z</v>
       </c>
     </row>
     <row r="186">
@@ -6442,13 +6442,13 @@
         <v>PASS</v>
       </c>
       <c r="H186">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I186" t="str">
         <v/>
       </c>
       <c r="J186" t="str">
-        <v>2026-08-09T18:19:38.267Z</v>
+        <v>2026-08-09T18:23:00.572Z</v>
       </c>
     </row>
     <row r="187">
@@ -6480,7 +6480,7 @@
         <v/>
       </c>
       <c r="J187" t="str">
-        <v>2026-08-09T18:19:38.283Z</v>
+        <v>2026-08-09T18:23:00.588Z</v>
       </c>
     </row>
     <row r="188">
@@ -6506,13 +6506,13 @@
         <v>PASS</v>
       </c>
       <c r="H188">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I188" t="str">
         <v/>
       </c>
       <c r="J188" t="str">
-        <v>2026-08-09T18:19:38.299Z</v>
+        <v>2026-08-09T18:23:00.600Z</v>
       </c>
     </row>
     <row r="189">
@@ -6538,13 +6538,13 @@
         <v>PASS</v>
       </c>
       <c r="H189">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I189" t="str">
         <v/>
       </c>
       <c r="J189" t="str">
-        <v>2026-08-09T18:19:38.314Z</v>
+        <v>2026-08-09T18:23:00.616Z</v>
       </c>
     </row>
     <row r="190">
@@ -6576,7 +6576,7 @@
         <v/>
       </c>
       <c r="J190" t="str">
-        <v>2026-08-09T18:19:38.330Z</v>
+        <v>2026-08-09T18:23:00.632Z</v>
       </c>
     </row>
     <row r="191">
@@ -6608,7 +6608,7 @@
         <v/>
       </c>
       <c r="J191" t="str">
-        <v>2026-08-09T18:19:38.346Z</v>
+        <v>2026-08-09T18:23:00.648Z</v>
       </c>
     </row>
     <row r="192">
@@ -6634,13 +6634,13 @@
         <v>PASS</v>
       </c>
       <c r="H192">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I192" t="str">
         <v/>
       </c>
       <c r="J192" t="str">
-        <v>2026-08-09T18:19:38.363Z</v>
+        <v>2026-08-09T18:23:00.664Z</v>
       </c>
     </row>
     <row r="193">
@@ -6666,13 +6666,13 @@
         <v>PASS</v>
       </c>
       <c r="H193">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I193" t="str">
         <v/>
       </c>
       <c r="J193" t="str">
-        <v>2026-08-09T18:19:38.377Z</v>
+        <v>2026-08-09T18:23:00.680Z</v>
       </c>
     </row>
     <row r="194">
@@ -6698,13 +6698,13 @@
         <v>PASS</v>
       </c>
       <c r="H194">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I194" t="str">
         <v/>
       </c>
       <c r="J194" t="str">
-        <v>2026-08-09T18:19:38.395Z</v>
+        <v>2026-08-09T18:23:00.696Z</v>
       </c>
     </row>
     <row r="195">
@@ -6730,13 +6730,13 @@
         <v>PASS</v>
       </c>
       <c r="H195">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I195" t="str">
         <v/>
       </c>
       <c r="J195" t="str">
-        <v>2026-08-09T18:19:38.409Z</v>
+        <v>2026-08-09T18:23:00.711Z</v>
       </c>
     </row>
     <row r="196">
@@ -6762,13 +6762,13 @@
         <v>PASS</v>
       </c>
       <c r="H196">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I196" t="str">
         <v/>
       </c>
       <c r="J196" t="str">
-        <v>2026-08-09T18:19:38.423Z</v>
+        <v>2026-08-09T18:23:00.726Z</v>
       </c>
     </row>
     <row r="197">
@@ -6800,7 +6800,7 @@
         <v/>
       </c>
       <c r="J197" t="str">
-        <v>2026-08-09T18:19:38.438Z</v>
+        <v>2026-08-09T18:23:00.741Z</v>
       </c>
     </row>
     <row r="198">
@@ -6826,13 +6826,13 @@
         <v>PASS</v>
       </c>
       <c r="H198">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I198" t="str">
         <v/>
       </c>
       <c r="J198" t="str">
-        <v>2026-08-09T18:19:38.453Z</v>
+        <v>2026-08-09T18:23:00.757Z</v>
       </c>
     </row>
     <row r="199">
@@ -6858,13 +6858,13 @@
         <v>PASS</v>
       </c>
       <c r="H199">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I199" t="str">
         <v/>
       </c>
       <c r="J199" t="str">
-        <v>2026-08-09T18:19:38.469Z</v>
+        <v>2026-08-09T18:23:00.772Z</v>
       </c>
     </row>
     <row r="200">
@@ -6896,7 +6896,7 @@
         <v/>
       </c>
       <c r="J200" t="str">
-        <v>2026-08-09T18:19:38.485Z</v>
+        <v>2026-08-09T18:23:00.789Z</v>
       </c>
     </row>
     <row r="201">
@@ -6928,7 +6928,7 @@
         <v/>
       </c>
       <c r="J201" t="str">
-        <v>2026-08-09T18:19:38.500Z</v>
+        <v>2026-08-09T18:23:00.804Z</v>
       </c>
     </row>
     <row r="202">
@@ -6954,13 +6954,13 @@
         <v>PASS</v>
       </c>
       <c r="H202">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I202" t="str">
         <v/>
       </c>
       <c r="J202" t="str">
-        <v>2026-08-09T18:19:38.515Z</v>
+        <v>2026-08-09T18:23:00.820Z</v>
       </c>
     </row>
     <row r="203">
@@ -6992,7 +6992,7 @@
         <v/>
       </c>
       <c r="J203" t="str">
-        <v>2026-08-09T18:19:38.531Z</v>
+        <v>2026-08-09T18:23:00.836Z</v>
       </c>
     </row>
     <row r="204">
@@ -7018,13 +7018,13 @@
         <v>PASS</v>
       </c>
       <c r="H204">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I204" t="str">
         <v/>
       </c>
       <c r="J204" t="str">
-        <v>2026-08-09T18:19:38.547Z</v>
+        <v>2026-08-09T18:23:00.851Z</v>
       </c>
     </row>
     <row r="205">
@@ -7050,13 +7050,13 @@
         <v>PASS</v>
       </c>
       <c r="H205">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I205" t="str">
         <v/>
       </c>
       <c r="J205" t="str">
-        <v>2026-08-09T18:19:38.562Z</v>
+        <v>2026-08-09T18:23:00.867Z</v>
       </c>
     </row>
     <row r="206">
@@ -7088,7 +7088,7 @@
         <v/>
       </c>
       <c r="J206" t="str">
-        <v>2026-08-09T18:19:38.578Z</v>
+        <v>2026-08-09T18:23:00.883Z</v>
       </c>
     </row>
     <row r="207">
@@ -7114,13 +7114,13 @@
         <v>PASS</v>
       </c>
       <c r="H207">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I207" t="str">
         <v/>
       </c>
       <c r="J207" t="str">
-        <v>2026-08-09T18:19:38.595Z</v>
+        <v>2026-08-09T18:23:00.898Z</v>
       </c>
     </row>
     <row r="208">
@@ -7146,13 +7146,13 @@
         <v>PASS</v>
       </c>
       <c r="H208">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I208" t="str">
         <v/>
       </c>
       <c r="J208" t="str">
-        <v>2026-08-09T18:19:38.609Z</v>
+        <v>2026-08-09T18:23:00.913Z</v>
       </c>
     </row>
     <row r="209">
@@ -7178,13 +7178,13 @@
         <v>PASS</v>
       </c>
       <c r="H209">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I209" t="str">
         <v/>
       </c>
       <c r="J209" t="str">
-        <v>2026-08-09T18:19:38.624Z</v>
+        <v>2026-08-09T18:23:00.929Z</v>
       </c>
     </row>
     <row r="210">
@@ -7210,13 +7210,13 @@
         <v>PASS</v>
       </c>
       <c r="H210">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I210" t="str">
         <v/>
       </c>
       <c r="J210" t="str">
-        <v>2026-08-09T18:19:38.639Z</v>
+        <v>2026-08-09T18:23:00.945Z</v>
       </c>
     </row>
     <row r="211">
@@ -7242,13 +7242,13 @@
         <v>PASS</v>
       </c>
       <c r="H211">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I211" t="str">
         <v/>
       </c>
       <c r="J211" t="str">
-        <v>2026-08-09T18:19:38.654Z</v>
+        <v>2026-08-09T18:23:00.961Z</v>
       </c>
     </row>
     <row r="212">
@@ -7274,13 +7274,13 @@
         <v>PASS</v>
       </c>
       <c r="H212">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I212" t="str">
         <v/>
       </c>
       <c r="J212" t="str">
-        <v>2026-08-09T18:19:38.669Z</v>
+        <v>2026-08-09T18:23:00.978Z</v>
       </c>
     </row>
     <row r="213">
@@ -7306,13 +7306,13 @@
         <v>PASS</v>
       </c>
       <c r="H213">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I213" t="str">
         <v/>
       </c>
       <c r="J213" t="str">
-        <v>2026-08-09T18:19:38.685Z</v>
+        <v>2026-08-09T18:23:00.993Z</v>
       </c>
     </row>
     <row r="214">
@@ -7344,7 +7344,7 @@
         <v/>
       </c>
       <c r="J214" t="str">
-        <v>2026-08-09T18:19:38.701Z</v>
+        <v>2026-08-09T18:23:01.009Z</v>
       </c>
     </row>
     <row r="215">
@@ -7370,13 +7370,13 @@
         <v>PASS</v>
       </c>
       <c r="H215">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I215" t="str">
         <v/>
       </c>
       <c r="J215" t="str">
-        <v>2026-08-09T18:19:38.715Z</v>
+        <v>2026-08-09T18:23:01.025Z</v>
       </c>
     </row>
     <row r="216">
@@ -7408,7 +7408,7 @@
         <v/>
       </c>
       <c r="J216" t="str">
-        <v>2026-08-09T18:19:38.731Z</v>
+        <v>2026-08-09T18:23:01.041Z</v>
       </c>
     </row>
     <row r="217">
@@ -7434,13 +7434,13 @@
         <v>PASS</v>
       </c>
       <c r="H217">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I217" t="str">
         <v/>
       </c>
       <c r="J217" t="str">
-        <v>2026-08-09T18:19:38.746Z</v>
+        <v>2026-08-09T18:23:01.057Z</v>
       </c>
     </row>
     <row r="218">
@@ -7472,7 +7472,7 @@
         <v/>
       </c>
       <c r="J218" t="str">
-        <v>2026-08-09T18:19:38.762Z</v>
+        <v>2026-08-09T18:23:01.073Z</v>
       </c>
     </row>
     <row r="219">
@@ -7498,13 +7498,13 @@
         <v>PASS</v>
       </c>
       <c r="H219">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I219" t="str">
         <v/>
       </c>
       <c r="J219" t="str">
-        <v>2026-08-09T18:19:38.777Z</v>
+        <v>2026-08-09T18:23:01.089Z</v>
       </c>
     </row>
     <row r="220">
@@ -7530,13 +7530,13 @@
         <v>PASS</v>
       </c>
       <c r="H220">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I220" t="str">
         <v/>
       </c>
       <c r="J220" t="str">
-        <v>2026-08-09T18:19:38.794Z</v>
+        <v>2026-08-09T18:23:01.104Z</v>
       </c>
     </row>
     <row r="221">
@@ -7562,13 +7562,13 @@
         <v>PASS</v>
       </c>
       <c r="H221">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I221" t="str">
         <v/>
       </c>
       <c r="J221" t="str">
-        <v>2026-08-09T18:19:38.810Z</v>
+        <v>2026-08-09T18:23:01.119Z</v>
       </c>
     </row>
     <row r="222">
@@ -7594,13 +7594,13 @@
         <v>PASS</v>
       </c>
       <c r="H222">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I222" t="str">
         <v/>
       </c>
       <c r="J222" t="str">
-        <v>2026-08-09T18:19:38.826Z</v>
+        <v>2026-08-09T18:23:01.136Z</v>
       </c>
     </row>
     <row r="223">
@@ -7632,7 +7632,7 @@
         <v/>
       </c>
       <c r="J223" t="str">
-        <v>2026-08-09T18:19:38.841Z</v>
+        <v>2026-08-09T18:23:01.151Z</v>
       </c>
     </row>
     <row r="224">
@@ -7664,7 +7664,7 @@
         <v/>
       </c>
       <c r="J224" t="str">
-        <v>2026-08-09T18:19:38.856Z</v>
+        <v>2026-08-09T18:23:01.166Z</v>
       </c>
     </row>
     <row r="225">
@@ -7696,7 +7696,7 @@
         <v/>
       </c>
       <c r="J225" t="str">
-        <v>2026-08-09T18:19:38.872Z</v>
+        <v>2026-08-09T18:23:01.182Z</v>
       </c>
     </row>
     <row r="226">
@@ -7722,13 +7722,13 @@
         <v>PASS</v>
       </c>
       <c r="H226">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I226" t="str">
         <v/>
       </c>
       <c r="J226" t="str">
-        <v>2026-08-09T18:19:38.888Z</v>
+        <v>2026-08-09T18:23:01.197Z</v>
       </c>
     </row>
     <row r="227">
@@ -7760,7 +7760,7 @@
         <v/>
       </c>
       <c r="J227" t="str">
-        <v>2026-08-09T18:19:38.903Z</v>
+        <v>2026-08-09T18:23:01.212Z</v>
       </c>
     </row>
     <row r="228">
@@ -7792,7 +7792,7 @@
         <v/>
       </c>
       <c r="J228" t="str">
-        <v>2026-08-09T18:19:38.919Z</v>
+        <v>2026-08-09T18:23:01.228Z</v>
       </c>
     </row>
     <row r="229">
@@ -7818,13 +7818,13 @@
         <v>PASS</v>
       </c>
       <c r="H229">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I229" t="str">
         <v/>
       </c>
       <c r="J229" t="str">
-        <v>2026-08-09T18:19:38.935Z</v>
+        <v>2026-08-09T18:23:01.242Z</v>
       </c>
     </row>
     <row r="230">
@@ -7856,7 +7856,7 @@
         <v/>
       </c>
       <c r="J230" t="str">
-        <v>2026-08-09T18:19:38.951Z</v>
+        <v>2026-08-09T18:23:01.258Z</v>
       </c>
     </row>
     <row r="231">
@@ -7882,13 +7882,13 @@
         <v>PASS</v>
       </c>
       <c r="H231">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I231" t="str">
         <v/>
       </c>
       <c r="J231" t="str">
-        <v>2026-08-09T18:19:38.965Z</v>
+        <v>2026-08-09T18:23:01.273Z</v>
       </c>
     </row>
     <row r="232">
@@ -7914,13 +7914,13 @@
         <v>PASS</v>
       </c>
       <c r="H232">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I232" t="str">
         <v/>
       </c>
       <c r="J232" t="str">
-        <v>2026-08-09T18:19:38.981Z</v>
+        <v>2026-08-09T18:23:01.290Z</v>
       </c>
     </row>
     <row r="233">
@@ -7946,13 +7946,13 @@
         <v>PASS</v>
       </c>
       <c r="H233">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I233" t="str">
         <v/>
       </c>
       <c r="J233" t="str">
-        <v>2026-08-09T18:19:38.997Z</v>
+        <v>2026-08-09T18:23:01.304Z</v>
       </c>
     </row>
     <row r="234">
@@ -7978,13 +7978,13 @@
         <v>PASS</v>
       </c>
       <c r="H234">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I234" t="str">
         <v/>
       </c>
       <c r="J234" t="str">
-        <v>2026-08-09T18:19:39.012Z</v>
+        <v>2026-08-09T18:23:01.320Z</v>
       </c>
     </row>
     <row r="235">
@@ -8010,13 +8010,13 @@
         <v>PASS</v>
       </c>
       <c r="H235">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I235" t="str">
         <v/>
       </c>
       <c r="J235" t="str">
-        <v>2026-08-09T18:19:39.029Z</v>
+        <v>2026-08-09T18:23:01.336Z</v>
       </c>
     </row>
     <row r="236">
@@ -8048,7 +8048,7 @@
         <v/>
       </c>
       <c r="J236" t="str">
-        <v>2026-08-09T18:19:39.045Z</v>
+        <v>2026-08-09T18:23:01.352Z</v>
       </c>
     </row>
     <row r="237">
@@ -8080,7 +8080,7 @@
         <v/>
       </c>
       <c r="J237" t="str">
-        <v>2026-08-09T18:19:39.059Z</v>
+        <v>2026-08-09T18:23:01.366Z</v>
       </c>
     </row>
     <row r="238">
@@ -8106,13 +8106,13 @@
         <v>PASS</v>
       </c>
       <c r="H238">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I238" t="str">
         <v/>
       </c>
       <c r="J238" t="str">
-        <v>2026-08-09T18:19:39.076Z</v>
+        <v>2026-08-09T18:23:01.382Z</v>
       </c>
     </row>
     <row r="239">
@@ -8144,7 +8144,7 @@
         <v/>
       </c>
       <c r="J239" t="str">
-        <v>2026-08-09T18:19:39.091Z</v>
+        <v>2026-08-09T18:23:01.397Z</v>
       </c>
     </row>
     <row r="240">
@@ -8176,7 +8176,7 @@
         <v/>
       </c>
       <c r="J240" t="str">
-        <v>2026-08-09T18:19:39.107Z</v>
+        <v>2026-08-09T18:23:01.413Z</v>
       </c>
     </row>
     <row r="241">
@@ -8208,7 +8208,7 @@
         <v/>
       </c>
       <c r="J241" t="str">
-        <v>2026-08-09T18:19:39.122Z</v>
+        <v>2026-08-09T18:23:01.428Z</v>
       </c>
     </row>
     <row r="242">
@@ -8234,13 +8234,13 @@
         <v>PASS</v>
       </c>
       <c r="H242">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I242" t="str">
         <v/>
       </c>
       <c r="J242" t="str">
-        <v>2026-08-09T18:19:39.137Z</v>
+        <v>2026-08-09T18:23:01.444Z</v>
       </c>
     </row>
     <row r="243">
@@ -8266,13 +8266,13 @@
         <v>PASS</v>
       </c>
       <c r="H243">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I243" t="str">
         <v/>
       </c>
       <c r="J243" t="str">
-        <v>2026-08-09T18:19:39.153Z</v>
+        <v>2026-08-09T18:23:01.459Z</v>
       </c>
     </row>
     <row r="244">
@@ -8298,13 +8298,13 @@
         <v>PASS</v>
       </c>
       <c r="H244">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I244" t="str">
         <v/>
       </c>
       <c r="J244" t="str">
-        <v>2026-08-09T18:19:39.169Z</v>
+        <v>2026-08-09T18:23:01.476Z</v>
       </c>
     </row>
     <row r="245">
@@ -8330,13 +8330,13 @@
         <v>PASS</v>
       </c>
       <c r="H245">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I245" t="str">
         <v/>
       </c>
       <c r="J245" t="str">
-        <v>2026-08-09T18:19:39.184Z</v>
+        <v>2026-08-09T18:23:01.490Z</v>
       </c>
     </row>
     <row r="246">
@@ -8362,13 +8362,13 @@
         <v>PASS</v>
       </c>
       <c r="H246">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I246" t="str">
         <v/>
       </c>
       <c r="J246" t="str">
-        <v>2026-08-09T18:19:39.199Z</v>
+        <v>2026-08-09T18:23:01.507Z</v>
       </c>
     </row>
     <row r="247">
@@ -8394,13 +8394,13 @@
         <v>PASS</v>
       </c>
       <c r="H247">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I247" t="str">
         <v/>
       </c>
       <c r="J247" t="str">
-        <v>2026-08-09T18:19:39.215Z</v>
+        <v>2026-08-09T18:23:01.522Z</v>
       </c>
     </row>
     <row r="248">
@@ -8426,13 +8426,13 @@
         <v>PASS</v>
       </c>
       <c r="H248">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I248" t="str">
         <v/>
       </c>
       <c r="J248" t="str">
-        <v>2026-08-09T18:19:39.231Z</v>
+        <v>2026-08-09T18:23:01.537Z</v>
       </c>
     </row>
     <row r="249">
@@ -8458,13 +8458,13 @@
         <v>PASS</v>
       </c>
       <c r="H249">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I249" t="str">
         <v/>
       </c>
       <c r="J249" t="str">
-        <v>2026-08-09T18:19:39.247Z</v>
+        <v>2026-08-09T18:23:01.552Z</v>
       </c>
     </row>
     <row r="250">
@@ -8490,13 +8490,13 @@
         <v>PASS</v>
       </c>
       <c r="H250">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I250" t="str">
         <v/>
       </c>
       <c r="J250" t="str">
-        <v>2026-08-09T18:19:39.263Z</v>
+        <v>2026-08-09T18:23:01.567Z</v>
       </c>
     </row>
     <row r="251">
@@ -8522,13 +8522,13 @@
         <v>PASS</v>
       </c>
       <c r="H251">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I251" t="str">
         <v/>
       </c>
       <c r="J251" t="str">
-        <v>2026-08-09T18:19:39.279Z</v>
+        <v>2026-08-09T18:23:01.582Z</v>
       </c>
     </row>
     <row r="252">
@@ -8554,13 +8554,13 @@
         <v>PASS</v>
       </c>
       <c r="H252">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I252" t="str">
         <v/>
       </c>
       <c r="J252" t="str">
-        <v>2026-08-09T18:19:39.294Z</v>
+        <v>2026-08-09T18:23:01.598Z</v>
       </c>
     </row>
     <row r="253">
@@ -8586,13 +8586,13 @@
         <v>PASS</v>
       </c>
       <c r="H253">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I253" t="str">
         <v/>
       </c>
       <c r="J253" t="str">
-        <v>2026-08-09T18:19:39.309Z</v>
+        <v>2026-08-09T18:23:01.614Z</v>
       </c>
     </row>
     <row r="254">
@@ -8624,7 +8624,7 @@
         <v/>
       </c>
       <c r="J254" t="str">
-        <v>2026-08-09T18:19:39.324Z</v>
+        <v>2026-08-09T18:23:01.629Z</v>
       </c>
     </row>
     <row r="255">
@@ -8656,7 +8656,7 @@
         <v/>
       </c>
       <c r="J255" t="str">
-        <v>2026-08-09T18:19:39.339Z</v>
+        <v>2026-08-09T18:23:01.644Z</v>
       </c>
     </row>
     <row r="256">
@@ -8682,13 +8682,13 @@
         <v>PASS</v>
       </c>
       <c r="H256">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I256" t="str">
         <v/>
       </c>
       <c r="J256" t="str">
-        <v>2026-08-09T18:19:39.355Z</v>
+        <v>2026-08-09T18:23:01.661Z</v>
       </c>
     </row>
     <row r="257">
@@ -8714,13 +8714,13 @@
         <v>PASS</v>
       </c>
       <c r="H257">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I257" t="str">
         <v/>
       </c>
       <c r="J257" t="str">
-        <v>2026-08-09T18:19:39.371Z</v>
+        <v>2026-08-09T18:23:01.677Z</v>
       </c>
     </row>
     <row r="258">
@@ -8746,13 +8746,13 @@
         <v>PASS</v>
       </c>
       <c r="H258">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I258" t="str">
         <v/>
       </c>
       <c r="J258" t="str">
-        <v>2026-08-09T18:19:39.385Z</v>
+        <v>2026-08-09T18:23:01.692Z</v>
       </c>
     </row>
     <row r="259">
@@ -8778,13 +8778,13 @@
         <v>PASS</v>
       </c>
       <c r="H259">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I259" t="str">
         <v/>
       </c>
       <c r="J259" t="str">
-        <v>2026-08-09T18:19:39.400Z</v>
+        <v>2026-08-09T18:23:01.709Z</v>
       </c>
     </row>
     <row r="260">
@@ -8810,13 +8810,13 @@
         <v>PASS</v>
       </c>
       <c r="H260">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I260" t="str">
         <v/>
       </c>
       <c r="J260" t="str">
-        <v>2026-08-09T18:19:39.416Z</v>
+        <v>2026-08-09T18:23:01.723Z</v>
       </c>
     </row>
     <row r="261">
@@ -8842,13 +8842,13 @@
         <v>PASS</v>
       </c>
       <c r="H261">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I261" t="str">
         <v/>
       </c>
       <c r="J261" t="str">
-        <v>2026-08-09T18:19:39.432Z</v>
+        <v>2026-08-09T18:23:01.740Z</v>
       </c>
     </row>
     <row r="262">
@@ -8874,13 +8874,13 @@
         <v>PASS</v>
       </c>
       <c r="H262">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I262" t="str">
         <v/>
       </c>
       <c r="J262" t="str">
-        <v>2026-08-09T18:19:39.448Z</v>
+        <v>2026-08-09T18:23:01.755Z</v>
       </c>
     </row>
     <row r="263">
@@ -8906,13 +8906,13 @@
         <v>PASS</v>
       </c>
       <c r="H263">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I263" t="str">
         <v/>
       </c>
       <c r="J263" t="str">
-        <v>2026-08-09T18:19:39.462Z</v>
+        <v>2026-08-09T18:23:01.771Z</v>
       </c>
     </row>
     <row r="264">
@@ -8938,13 +8938,13 @@
         <v>PASS</v>
       </c>
       <c r="H264">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I264" t="str">
         <v/>
       </c>
       <c r="J264" t="str">
-        <v>2026-08-09T18:19:39.478Z</v>
+        <v>2026-08-09T18:23:01.785Z</v>
       </c>
     </row>
     <row r="265">
@@ -8970,13 +8970,13 @@
         <v>PASS</v>
       </c>
       <c r="H265">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I265" t="str">
         <v/>
       </c>
       <c r="J265" t="str">
-        <v>2026-08-09T18:19:39.495Z</v>
+        <v>2026-08-09T18:23:01.801Z</v>
       </c>
     </row>
     <row r="266">
@@ -9008,7 +9008,7 @@
         <v/>
       </c>
       <c r="J266" t="str">
-        <v>2026-08-09T18:19:39.510Z</v>
+        <v>2026-08-09T18:23:01.816Z</v>
       </c>
     </row>
     <row r="267">
@@ -9034,13 +9034,13 @@
         <v>PASS</v>
       </c>
       <c r="H267">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I267" t="str">
         <v/>
       </c>
       <c r="J267" t="str">
-        <v>2026-08-09T18:19:39.525Z</v>
+        <v>2026-08-09T18:23:01.832Z</v>
       </c>
     </row>
     <row r="268">
@@ -9066,13 +9066,13 @@
         <v>PASS</v>
       </c>
       <c r="H268">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I268" t="str">
         <v/>
       </c>
       <c r="J268" t="str">
-        <v>2026-08-09T18:19:39.541Z</v>
+        <v>2026-08-09T18:23:01.848Z</v>
       </c>
     </row>
     <row r="269">
@@ -9098,13 +9098,13 @@
         <v>PASS</v>
       </c>
       <c r="H269">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I269" t="str">
         <v/>
       </c>
       <c r="J269" t="str">
-        <v>2026-08-09T18:19:39.555Z</v>
+        <v>2026-08-09T18:23:01.863Z</v>
       </c>
     </row>
     <row r="270">
@@ -9136,7 +9136,7 @@
         <v/>
       </c>
       <c r="J270" t="str">
-        <v>2026-08-09T18:19:39.570Z</v>
+        <v>2026-08-09T18:23:01.878Z</v>
       </c>
     </row>
     <row r="271">
@@ -9162,13 +9162,13 @@
         <v>PASS</v>
       </c>
       <c r="H271">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I271" t="str">
         <v/>
       </c>
       <c r="J271" t="str">
-        <v>2026-08-09T18:19:39.587Z</v>
+        <v>2026-08-09T18:23:01.894Z</v>
       </c>
     </row>
     <row r="272">
@@ -9194,13 +9194,13 @@
         <v>PASS</v>
       </c>
       <c r="H272">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I272" t="str">
         <v/>
       </c>
       <c r="J272" t="str">
-        <v>2026-08-09T18:19:39.601Z</v>
+        <v>2026-08-09T18:23:01.911Z</v>
       </c>
     </row>
     <row r="273">
@@ -9226,13 +9226,13 @@
         <v>PASS</v>
       </c>
       <c r="H273">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I273" t="str">
         <v/>
       </c>
       <c r="J273" t="str">
-        <v>2026-08-09T18:19:39.618Z</v>
+        <v>2026-08-09T18:23:01.926Z</v>
       </c>
     </row>
     <row r="274">
@@ -9258,13 +9258,13 @@
         <v>PASS</v>
       </c>
       <c r="H274">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I274" t="str">
         <v/>
       </c>
       <c r="J274" t="str">
-        <v>2026-08-09T18:19:39.633Z</v>
+        <v>2026-08-09T18:23:01.942Z</v>
       </c>
     </row>
     <row r="275">
@@ -9290,13 +9290,13 @@
         <v>PASS</v>
       </c>
       <c r="H275">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I275" t="str">
         <v/>
       </c>
       <c r="J275" t="str">
-        <v>2026-08-09T18:19:39.649Z</v>
+        <v>2026-08-09T18:23:01.957Z</v>
       </c>
     </row>
     <row r="276">
@@ -9322,13 +9322,13 @@
         <v>PASS</v>
       </c>
       <c r="H276">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I276" t="str">
         <v/>
       </c>
       <c r="J276" t="str">
-        <v>2026-08-09T18:19:39.665Z</v>
+        <v>2026-08-09T18:23:01.972Z</v>
       </c>
     </row>
     <row r="277">
@@ -9360,7 +9360,7 @@
         <v/>
       </c>
       <c r="J277" t="str">
-        <v>2026-08-09T18:19:39.681Z</v>
+        <v>2026-08-09T18:23:01.988Z</v>
       </c>
     </row>
     <row r="278">
@@ -9386,13 +9386,13 @@
         <v>PASS</v>
       </c>
       <c r="H278">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I278" t="str">
         <v/>
       </c>
       <c r="J278" t="str">
-        <v>2026-08-09T18:19:39.696Z</v>
+        <v>2026-08-09T18:23:02.004Z</v>
       </c>
     </row>
     <row r="279">
@@ -9418,13 +9418,13 @@
         <v>PASS</v>
       </c>
       <c r="H279">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I279" t="str">
         <v/>
       </c>
       <c r="J279" t="str">
-        <v>2026-08-09T18:19:39.712Z</v>
+        <v>2026-08-09T18:23:02.018Z</v>
       </c>
     </row>
     <row r="280">
@@ -9450,13 +9450,13 @@
         <v>PASS</v>
       </c>
       <c r="H280">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I280" t="str">
         <v/>
       </c>
       <c r="J280" t="str">
-        <v>2026-08-09T18:19:39.727Z</v>
+        <v>2026-08-09T18:23:02.034Z</v>
       </c>
     </row>
     <row r="281">
@@ -9482,13 +9482,13 @@
         <v>PASS</v>
       </c>
       <c r="H281">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I281" t="str">
         <v/>
       </c>
       <c r="J281" t="str">
-        <v>2026-08-09T18:19:39.742Z</v>
+        <v>2026-08-09T18:23:02.050Z</v>
       </c>
     </row>
     <row r="282">
@@ -9514,13 +9514,13 @@
         <v>PASS</v>
       </c>
       <c r="H282">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I282" t="str">
         <v/>
       </c>
       <c r="J282" t="str">
-        <v>2026-08-09T18:19:39.757Z</v>
+        <v>2026-08-09T18:23:02.065Z</v>
       </c>
     </row>
     <row r="283">
@@ -9546,13 +9546,13 @@
         <v>PASS</v>
       </c>
       <c r="H283">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I283" t="str">
         <v/>
       </c>
       <c r="J283" t="str">
-        <v>2026-08-09T18:19:39.774Z</v>
+        <v>2026-08-09T18:23:02.080Z</v>
       </c>
     </row>
     <row r="284">
@@ -9578,13 +9578,13 @@
         <v>PASS</v>
       </c>
       <c r="H284">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I284" t="str">
         <v/>
       </c>
       <c r="J284" t="str">
-        <v>2026-08-09T18:19:39.788Z</v>
+        <v>2026-08-09T18:23:02.096Z</v>
       </c>
     </row>
     <row r="285">
@@ -9610,13 +9610,13 @@
         <v>PASS</v>
       </c>
       <c r="H285">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I285" t="str">
         <v/>
       </c>
       <c r="J285" t="str">
-        <v>2026-08-09T18:19:39.803Z</v>
+        <v>2026-08-09T18:23:02.112Z</v>
       </c>
     </row>
     <row r="286">
@@ -9648,7 +9648,7 @@
         <v/>
       </c>
       <c r="J286" t="str">
-        <v>2026-08-09T18:19:39.819Z</v>
+        <v>2026-08-09T18:23:02.128Z</v>
       </c>
     </row>
     <row r="287">
@@ -9674,13 +9674,13 @@
         <v>PASS</v>
       </c>
       <c r="H287">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I287" t="str">
         <v/>
       </c>
       <c r="J287" t="str">
-        <v>2026-08-09T18:19:39.835Z</v>
+        <v>2026-08-09T18:23:02.143Z</v>
       </c>
     </row>
     <row r="288">
@@ -9712,7 +9712,7 @@
         <v/>
       </c>
       <c r="J288" t="str">
-        <v>2026-08-09T18:19:39.850Z</v>
+        <v>2026-08-09T18:23:02.158Z</v>
       </c>
     </row>
     <row r="289">
@@ -9744,7 +9744,7 @@
         <v/>
       </c>
       <c r="J289" t="str">
-        <v>2026-08-09T18:19:39.866Z</v>
+        <v>2026-08-09T18:23:02.174Z</v>
       </c>
     </row>
     <row r="290">
@@ -9770,13 +9770,13 @@
         <v>PASS</v>
       </c>
       <c r="H290">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I290" t="str">
         <v/>
       </c>
       <c r="J290" t="str">
-        <v>2026-08-09T18:19:39.882Z</v>
+        <v>2026-08-09T18:23:02.189Z</v>
       </c>
     </row>
     <row r="291">
@@ -9802,13 +9802,13 @@
         <v>PASS</v>
       </c>
       <c r="H291">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I291" t="str">
         <v/>
       </c>
       <c r="J291" t="str">
-        <v>2026-08-09T18:19:39.897Z</v>
+        <v>2026-08-09T18:23:02.205Z</v>
       </c>
     </row>
     <row r="292">
@@ -9834,13 +9834,13 @@
         <v>PASS</v>
       </c>
       <c r="H292">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I292" t="str">
         <v/>
       </c>
       <c r="J292" t="str">
-        <v>2026-08-09T18:19:39.914Z</v>
+        <v>2026-08-09T18:23:02.221Z</v>
       </c>
     </row>
     <row r="293">
@@ -9866,13 +9866,13 @@
         <v>PASS</v>
       </c>
       <c r="H293">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I293" t="str">
         <v/>
       </c>
       <c r="J293" t="str">
-        <v>2026-08-09T18:19:39.930Z</v>
+        <v>2026-08-09T18:23:02.237Z</v>
       </c>
     </row>
     <row r="294">
@@ -9898,13 +9898,13 @@
         <v>PASS</v>
       </c>
       <c r="H294">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I294" t="str">
         <v/>
       </c>
       <c r="J294" t="str">
-        <v>2026-08-09T18:19:39.944Z</v>
+        <v>2026-08-09T18:23:02.253Z</v>
       </c>
     </row>
     <row r="295">
@@ -9930,13 +9930,13 @@
         <v>PASS</v>
       </c>
       <c r="H295">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I295" t="str">
         <v/>
       </c>
       <c r="J295" t="str">
-        <v>2026-08-09T18:19:39.960Z</v>
+        <v>2026-08-09T18:23:02.268Z</v>
       </c>
     </row>
     <row r="296">
@@ -9962,13 +9962,13 @@
         <v>PASS</v>
       </c>
       <c r="H296">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I296" t="str">
         <v/>
       </c>
       <c r="J296" t="str">
-        <v>2026-08-09T18:19:39.976Z</v>
+        <v>2026-08-09T18:23:02.284Z</v>
       </c>
     </row>
     <row r="297">
@@ -9994,13 +9994,13 @@
         <v>PASS</v>
       </c>
       <c r="H297">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I297" t="str">
         <v/>
       </c>
       <c r="J297" t="str">
-        <v>2026-08-09T18:19:39.991Z</v>
+        <v>2026-08-09T18:23:02.298Z</v>
       </c>
     </row>
     <row r="298">
@@ -10026,13 +10026,13 @@
         <v>PASS</v>
       </c>
       <c r="H298">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I298" t="str">
         <v/>
       </c>
       <c r="J298" t="str">
-        <v>2026-08-09T18:19:40.007Z</v>
+        <v>2026-08-09T18:23:02.314Z</v>
       </c>
     </row>
     <row r="299">
@@ -10064,7 +10064,7 @@
         <v/>
       </c>
       <c r="J299" t="str">
-        <v>2026-08-09T18:19:40.022Z</v>
+        <v>2026-08-09T18:23:02.329Z</v>
       </c>
     </row>
     <row r="300">
@@ -10090,13 +10090,13 @@
         <v>PASS</v>
       </c>
       <c r="H300">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I300" t="str">
         <v/>
       </c>
       <c r="J300" t="str">
-        <v>2026-08-09T18:19:40.037Z</v>
+        <v>2026-08-09T18:23:02.345Z</v>
       </c>
     </row>
     <row r="301">
@@ -10122,13 +10122,13 @@
         <v>PASS</v>
       </c>
       <c r="H301">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I301" t="str">
         <v/>
       </c>
       <c r="J301" t="str">
-        <v>2026-08-09T18:19:40.053Z</v>
+        <v>2026-08-09T18:23:02.360Z</v>
       </c>
     </row>
     <row r="302">
@@ -10154,13 +10154,13 @@
         <v>PASS</v>
       </c>
       <c r="H302">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I302" t="str">
         <v/>
       </c>
       <c r="J302" t="str">
-        <v>2026-08-09T18:19:40.068Z</v>
+        <v>2026-08-09T18:23:02.376Z</v>
       </c>
     </row>
     <row r="303">
@@ -10186,13 +10186,13 @@
         <v>PASS</v>
       </c>
       <c r="H303">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I303" t="str">
         <v/>
       </c>
       <c r="J303" t="str">
-        <v>2026-08-09T18:19:40.084Z</v>
+        <v>2026-08-09T18:23:02.391Z</v>
       </c>
     </row>
     <row r="304">
@@ -10218,13 +10218,13 @@
         <v>PASS</v>
       </c>
       <c r="H304">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I304" t="str">
         <v/>
       </c>
       <c r="J304" t="str">
-        <v>2026-08-09T18:19:40.099Z</v>
+        <v>2026-08-09T18:23:02.407Z</v>
       </c>
     </row>
     <row r="305">
@@ -10250,13 +10250,13 @@
         <v>PASS</v>
       </c>
       <c r="H305">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I305" t="str">
         <v/>
       </c>
       <c r="J305" t="str">
-        <v>2026-08-09T18:19:40.115Z</v>
+        <v>2026-08-09T18:23:02.424Z</v>
       </c>
     </row>
     <row r="306">
@@ -10288,7 +10288,7 @@
         <v/>
       </c>
       <c r="J306" t="str">
-        <v>2026-08-09T18:19:40.131Z</v>
+        <v>2026-08-09T18:23:02.439Z</v>
       </c>
     </row>
     <row r="307">
@@ -10314,13 +10314,13 @@
         <v>PASS</v>
       </c>
       <c r="H307">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I307" t="str">
         <v/>
       </c>
       <c r="J307" t="str">
-        <v>2026-08-09T18:19:40.147Z</v>
+        <v>2026-08-09T18:23:02.454Z</v>
       </c>
     </row>
     <row r="308">
@@ -10346,13 +10346,13 @@
         <v>PASS</v>
       </c>
       <c r="H308">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I308" t="str">
         <v/>
       </c>
       <c r="J308" t="str">
-        <v>2026-08-09T18:19:40.162Z</v>
+        <v>2026-08-09T18:23:02.470Z</v>
       </c>
     </row>
     <row r="309">
@@ -10378,13 +10378,13 @@
         <v>PASS</v>
       </c>
       <c r="H309">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I309" t="str">
         <v/>
       </c>
       <c r="J309" t="str">
-        <v>2026-08-09T18:19:40.178Z</v>
+        <v>2026-08-09T18:23:02.485Z</v>
       </c>
     </row>
     <row r="310">
@@ -10410,13 +10410,13 @@
         <v>PASS</v>
       </c>
       <c r="H310">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I310" t="str">
         <v/>
       </c>
       <c r="J310" t="str">
-        <v>2026-08-09T18:19:40.195Z</v>
+        <v>2026-08-09T18:23:02.501Z</v>
       </c>
     </row>
     <row r="311">
@@ -10442,13 +10442,13 @@
         <v>PASS</v>
       </c>
       <c r="H311">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I311" t="str">
         <v/>
       </c>
       <c r="J311" t="str">
-        <v>2026-08-09T18:19:40.211Z</v>
+        <v>2026-08-09T18:23:02.516Z</v>
       </c>
     </row>
     <row r="312">
@@ -10474,13 +10474,13 @@
         <v>PASS</v>
       </c>
       <c r="H312">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I312" t="str">
         <v/>
       </c>
       <c r="J312" t="str">
-        <v>2026-08-09T18:19:40.226Z</v>
+        <v>2026-08-09T18:23:02.531Z</v>
       </c>
     </row>
     <row r="313">
@@ -10506,13 +10506,13 @@
         <v>PASS</v>
       </c>
       <c r="H313">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I313" t="str">
         <v/>
       </c>
       <c r="J313" t="str">
-        <v>2026-08-09T18:19:40.241Z</v>
+        <v>2026-08-09T18:23:02.547Z</v>
       </c>
     </row>
     <row r="314">
@@ -10538,13 +10538,13 @@
         <v>PASS</v>
       </c>
       <c r="H314">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I314" t="str">
         <v/>
       </c>
       <c r="J314" t="str">
-        <v>2026-08-09T18:19:40.256Z</v>
+        <v>2026-08-09T18:23:02.563Z</v>
       </c>
     </row>
     <row r="315">
@@ -10570,13 +10570,13 @@
         <v>PASS</v>
       </c>
       <c r="H315">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I315" t="str">
         <v/>
       </c>
       <c r="J315" t="str">
-        <v>2026-08-09T18:19:40.273Z</v>
+        <v>2026-08-09T18:23:02.578Z</v>
       </c>
     </row>
     <row r="316">
@@ -10602,13 +10602,13 @@
         <v>PASS</v>
       </c>
       <c r="H316">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I316" t="str">
         <v/>
       </c>
       <c r="J316" t="str">
-        <v>2026-08-09T18:19:40.288Z</v>
+        <v>2026-08-09T18:23:02.594Z</v>
       </c>
     </row>
     <row r="317">
@@ -10634,13 +10634,13 @@
         <v>PASS</v>
       </c>
       <c r="H317">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I317" t="str">
         <v/>
       </c>
       <c r="J317" t="str">
-        <v>2026-08-09T18:19:40.303Z</v>
+        <v>2026-08-09T18:23:02.609Z</v>
       </c>
     </row>
     <row r="318">
@@ -10666,13 +10666,13 @@
         <v>PASS</v>
       </c>
       <c r="H318">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I318" t="str">
         <v/>
       </c>
       <c r="J318" t="str">
-        <v>2026-08-09T18:19:40.319Z</v>
+        <v>2026-08-09T18:23:02.624Z</v>
       </c>
     </row>
     <row r="319">
@@ -10698,13 +10698,13 @@
         <v>PASS</v>
       </c>
       <c r="H319">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I319" t="str">
         <v/>
       </c>
       <c r="J319" t="str">
-        <v>2026-08-09T18:19:40.334Z</v>
+        <v>2026-08-09T18:23:02.640Z</v>
       </c>
     </row>
     <row r="320">
@@ -10736,7 +10736,7 @@
         <v/>
       </c>
       <c r="J320" t="str">
-        <v>2026-08-09T18:19:40.349Z</v>
+        <v>2026-08-09T18:23:02.655Z</v>
       </c>
     </row>
     <row r="321">
@@ -10768,7 +10768,7 @@
         <v/>
       </c>
       <c r="J321" t="str">
-        <v>2026-08-09T18:19:40.365Z</v>
+        <v>2026-08-09T18:23:02.671Z</v>
       </c>
     </row>
     <row r="322">
@@ -10800,7 +10800,7 @@
         <v/>
       </c>
       <c r="J322" t="str">
-        <v>2026-08-09T18:19:40.382Z</v>
+        <v>2026-08-09T18:23:02.687Z</v>
       </c>
     </row>
     <row r="323">
@@ -10826,13 +10826,13 @@
         <v>PASS</v>
       </c>
       <c r="H323">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I323" t="str">
         <v/>
       </c>
       <c r="J323" t="str">
-        <v>2026-08-09T18:19:40.396Z</v>
+        <v>2026-08-09T18:23:02.702Z</v>
       </c>
     </row>
     <row r="324">
@@ -10864,7 +10864,7 @@
         <v/>
       </c>
       <c r="J324" t="str">
-        <v>2026-08-09T18:19:40.412Z</v>
+        <v>2026-08-09T18:23:02.718Z</v>
       </c>
     </row>
     <row r="325">
@@ -10896,7 +10896,7 @@
         <v/>
       </c>
       <c r="J325" t="str">
-        <v>2026-08-09T18:19:40.427Z</v>
+        <v>2026-08-09T18:23:02.733Z</v>
       </c>
     </row>
     <row r="326">
@@ -10922,13 +10922,13 @@
         <v>PASS</v>
       </c>
       <c r="H326">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I326" t="str">
         <v/>
       </c>
       <c r="J326" t="str">
-        <v>2026-08-09T18:19:40.444Z</v>
+        <v>2026-08-09T18:23:02.749Z</v>
       </c>
     </row>
     <row r="327">
@@ -10954,13 +10954,13 @@
         <v>PASS</v>
       </c>
       <c r="H327">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I327" t="str">
         <v/>
       </c>
       <c r="J327" t="str">
-        <v>2026-08-09T18:19:40.460Z</v>
+        <v>2026-08-09T18:23:02.764Z</v>
       </c>
     </row>
     <row r="328">
@@ -10986,13 +10986,13 @@
         <v>PASS</v>
       </c>
       <c r="H328">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I328" t="str">
         <v/>
       </c>
       <c r="J328" t="str">
-        <v>2026-08-09T18:19:40.476Z</v>
+        <v>2026-08-09T18:23:02.779Z</v>
       </c>
     </row>
     <row r="329">
@@ -11018,13 +11018,13 @@
         <v>PASS</v>
       </c>
       <c r="H329">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I329" t="str">
         <v/>
       </c>
       <c r="J329" t="str">
-        <v>2026-08-09T18:19:40.490Z</v>
+        <v>2026-08-09T18:23:02.794Z</v>
       </c>
     </row>
     <row r="330">
@@ -11050,13 +11050,13 @@
         <v>PASS</v>
       </c>
       <c r="H330">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I330" t="str">
         <v/>
       </c>
       <c r="J330" t="str">
-        <v>2026-08-09T18:19:40.505Z</v>
+        <v>2026-08-09T18:23:02.810Z</v>
       </c>
     </row>
     <row r="331">
@@ -11088,7 +11088,7 @@
         <v/>
       </c>
       <c r="J331" t="str">
-        <v>2026-08-09T18:19:40.520Z</v>
+        <v>2026-08-09T18:23:02.825Z</v>
       </c>
     </row>
     <row r="332">
@@ -11114,13 +11114,13 @@
         <v>PASS</v>
       </c>
       <c r="H332">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I332" t="str">
         <v/>
       </c>
       <c r="J332" t="str">
-        <v>2026-08-09T18:19:40.535Z</v>
+        <v>2026-08-09T18:23:02.840Z</v>
       </c>
     </row>
     <row r="333">
@@ -11152,7 +11152,7 @@
         <v/>
       </c>
       <c r="J333" t="str">
-        <v>2026-08-09T18:19:40.551Z</v>
+        <v>2026-08-09T18:23:02.856Z</v>
       </c>
     </row>
     <row r="334">
@@ -11178,13 +11178,13 @@
         <v>PASS</v>
       </c>
       <c r="H334">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I334" t="str">
         <v/>
       </c>
       <c r="J334" t="str">
-        <v>2026-08-09T18:19:40.567Z</v>
+        <v>2026-08-09T18:23:02.871Z</v>
       </c>
     </row>
     <row r="335">
@@ -11216,7 +11216,7 @@
         <v/>
       </c>
       <c r="J335" t="str">
-        <v>2026-08-09T18:19:40.583Z</v>
+        <v>2026-08-09T18:23:02.887Z</v>
       </c>
     </row>
     <row r="336">
@@ -11248,7 +11248,7 @@
         <v/>
       </c>
       <c r="J336" t="str">
-        <v>2026-08-09T18:19:40.598Z</v>
+        <v>2026-08-09T18:23:02.902Z</v>
       </c>
     </row>
     <row r="337">
@@ -11274,13 +11274,13 @@
         <v>PASS</v>
       </c>
       <c r="H337">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I337" t="str">
         <v/>
       </c>
       <c r="J337" t="str">
-        <v>2026-08-09T18:19:40.614Z</v>
+        <v>2026-08-09T18:23:02.917Z</v>
       </c>
     </row>
     <row r="338">
@@ -11312,7 +11312,7 @@
         <v/>
       </c>
       <c r="J338" t="str">
-        <v>2026-08-09T18:19:40.629Z</v>
+        <v>2026-08-09T18:23:02.932Z</v>
       </c>
     </row>
     <row r="339">
@@ -11344,7 +11344,7 @@
         <v/>
       </c>
       <c r="J339" t="str">
-        <v>2026-08-09T18:19:40.645Z</v>
+        <v>2026-08-09T18:23:02.948Z</v>
       </c>
     </row>
     <row r="340">
@@ -11370,13 +11370,13 @@
         <v>PASS</v>
       </c>
       <c r="H340">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I340" t="str">
         <v/>
       </c>
       <c r="J340" t="str">
-        <v>2026-08-09T18:19:40.660Z</v>
+        <v>2026-08-09T18:23:02.964Z</v>
       </c>
     </row>
     <row r="341">
@@ -11408,7 +11408,7 @@
         <v/>
       </c>
       <c r="J341" t="str">
-        <v>2026-08-09T18:19:40.676Z</v>
+        <v>2026-08-09T18:23:02.980Z</v>
       </c>
     </row>
     <row r="342">
@@ -11440,7 +11440,7 @@
         <v/>
       </c>
       <c r="J342" t="str">
-        <v>2026-08-09T18:19:40.691Z</v>
+        <v>2026-08-09T18:23:02.995Z</v>
       </c>
     </row>
     <row r="343">
@@ -11466,13 +11466,13 @@
         <v>PASS</v>
       </c>
       <c r="H343">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I343" t="str">
         <v/>
       </c>
       <c r="J343" t="str">
-        <v>2026-08-09T18:19:40.707Z</v>
+        <v>2026-08-09T18:23:03.010Z</v>
       </c>
     </row>
     <row r="344">
@@ -11498,13 +11498,13 @@
         <v>PASS</v>
       </c>
       <c r="H344">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I344" t="str">
         <v/>
       </c>
       <c r="J344" t="str">
-        <v>2026-08-09T18:19:40.722Z</v>
+        <v>2026-08-09T18:23:03.026Z</v>
       </c>
     </row>
     <row r="345">
@@ -11530,13 +11530,13 @@
         <v>PASS</v>
       </c>
       <c r="H345">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I345" t="str">
         <v/>
       </c>
       <c r="J345" t="str">
-        <v>2026-08-09T18:19:40.737Z</v>
+        <v>2026-08-09T18:23:03.042Z</v>
       </c>
     </row>
     <row r="346">
@@ -11562,13 +11562,13 @@
         <v>PASS</v>
       </c>
       <c r="H346">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I346" t="str">
         <v/>
       </c>
       <c r="J346" t="str">
-        <v>2026-08-09T18:19:40.753Z</v>
+        <v>2026-08-09T18:23:03.057Z</v>
       </c>
     </row>
     <row r="347">
@@ -11600,7 +11600,7 @@
         <v/>
       </c>
       <c r="J347" t="str">
-        <v>2026-08-09T18:19:40.768Z</v>
+        <v>2026-08-09T18:23:03.073Z</v>
       </c>
     </row>
     <row r="348">
@@ -11632,7 +11632,7 @@
         <v/>
       </c>
       <c r="J348" t="str">
-        <v>2026-08-09T18:19:40.784Z</v>
+        <v>2026-08-09T18:23:03.088Z</v>
       </c>
     </row>
     <row r="349">
@@ -11658,13 +11658,13 @@
         <v>PASS</v>
       </c>
       <c r="H349">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I349" t="str">
         <v/>
       </c>
       <c r="J349" t="str">
-        <v>2026-08-09T18:19:40.799Z</v>
+        <v>2026-08-09T18:23:03.104Z</v>
       </c>
     </row>
     <row r="350">
@@ -11690,13 +11690,13 @@
         <v>PASS</v>
       </c>
       <c r="H350">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I350" t="str">
         <v/>
       </c>
       <c r="J350" t="str">
-        <v>2026-08-09T18:19:40.815Z</v>
+        <v>2026-08-09T18:23:03.119Z</v>
       </c>
     </row>
     <row r="351">
@@ -11722,13 +11722,13 @@
         <v>PASS</v>
       </c>
       <c r="H351">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I351" t="str">
         <v/>
       </c>
       <c r="J351" t="str">
-        <v>2026-08-09T18:19:40.830Z</v>
+        <v>2026-08-09T18:23:03.135Z</v>
       </c>
     </row>
     <row r="352">
@@ -11754,13 +11754,13 @@
         <v>PASS</v>
       </c>
       <c r="H352">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I352" t="str">
         <v/>
       </c>
       <c r="J352" t="str">
-        <v>2026-08-09T18:19:40.846Z</v>
+        <v>2026-08-09T18:23:03.151Z</v>
       </c>
     </row>
     <row r="353">
@@ -11786,13 +11786,13 @@
         <v>PASS</v>
       </c>
       <c r="H353">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I353" t="str">
         <v/>
       </c>
       <c r="J353" t="str">
-        <v>2026-08-09T18:19:40.862Z</v>
+        <v>2026-08-09T18:23:03.166Z</v>
       </c>
     </row>
     <row r="354">
@@ -11818,13 +11818,13 @@
         <v>PASS</v>
       </c>
       <c r="H354">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I354" t="str">
         <v/>
       </c>
       <c r="J354" t="str">
-        <v>2026-08-09T18:19:40.877Z</v>
+        <v>2026-08-09T18:23:03.184Z</v>
       </c>
     </row>
     <row r="355">
@@ -11850,13 +11850,13 @@
         <v>PASS</v>
       </c>
       <c r="H355">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I355" t="str">
         <v/>
       </c>
       <c r="J355" t="str">
-        <v>2026-08-09T18:19:40.893Z</v>
+        <v>2026-08-09T18:23:03.198Z</v>
       </c>
     </row>
     <row r="356">
@@ -11882,13 +11882,13 @@
         <v>PASS</v>
       </c>
       <c r="H356">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I356" t="str">
         <v/>
       </c>
       <c r="J356" t="str">
-        <v>2026-08-09T18:19:40.908Z</v>
+        <v>2026-08-09T18:23:03.214Z</v>
       </c>
     </row>
     <row r="357">
@@ -11914,13 +11914,13 @@
         <v>PASS</v>
       </c>
       <c r="H357">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I357" t="str">
         <v/>
       </c>
       <c r="J357" t="str">
-        <v>2026-08-09T18:19:40.923Z</v>
+        <v>2026-08-09T18:23:03.228Z</v>
       </c>
     </row>
     <row r="358">
@@ -11946,13 +11946,13 @@
         <v>PASS</v>
       </c>
       <c r="H358">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I358" t="str">
         <v/>
       </c>
       <c r="J358" t="str">
-        <v>2026-08-09T18:19:40.938Z</v>
+        <v>2026-08-09T18:23:03.244Z</v>
       </c>
     </row>
     <row r="359">
@@ -11984,7 +11984,7 @@
         <v/>
       </c>
       <c r="J359" t="str">
-        <v>2026-08-09T18:19:40.954Z</v>
+        <v>2026-08-09T18:23:03.260Z</v>
       </c>
     </row>
     <row r="360">
@@ -12010,13 +12010,13 @@
         <v>PASS</v>
       </c>
       <c r="H360">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I360" t="str">
         <v/>
       </c>
       <c r="J360" t="str">
-        <v>2026-08-09T18:19:40.970Z</v>
+        <v>2026-08-09T18:23:03.275Z</v>
       </c>
     </row>
     <row r="361">
@@ -12042,13 +12042,13 @@
         <v>PASS</v>
       </c>
       <c r="H361">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I361" t="str">
         <v/>
       </c>
       <c r="J361" t="str">
-        <v>2026-08-09T18:19:40.984Z</v>
+        <v>2026-08-09T18:23:03.292Z</v>
       </c>
     </row>
     <row r="362">
@@ -12074,13 +12074,13 @@
         <v>PASS</v>
       </c>
       <c r="H362">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I362" t="str">
         <v/>
       </c>
       <c r="J362" t="str">
-        <v>2026-08-09T18:19:41.000Z</v>
+        <v>2026-08-09T18:23:03.306Z</v>
       </c>
     </row>
     <row r="363">
@@ -12106,13 +12106,13 @@
         <v>PASS</v>
       </c>
       <c r="H363">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I363" t="str">
         <v/>
       </c>
       <c r="J363" t="str">
-        <v>2026-08-09T18:19:41.015Z</v>
+        <v>2026-08-09T18:23:03.322Z</v>
       </c>
     </row>
     <row r="364">
@@ -12144,7 +12144,7 @@
         <v/>
       </c>
       <c r="J364" t="str">
-        <v>2026-08-09T18:19:41.031Z</v>
+        <v>2026-08-09T18:23:03.338Z</v>
       </c>
     </row>
     <row r="365">
@@ -12170,13 +12170,13 @@
         <v>PASS</v>
       </c>
       <c r="H365">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I365" t="str">
         <v/>
       </c>
       <c r="J365" t="str">
-        <v>2026-08-09T18:19:41.047Z</v>
+        <v>2026-08-09T18:23:03.352Z</v>
       </c>
     </row>
     <row r="366">
@@ -12208,7 +12208,7 @@
         <v/>
       </c>
       <c r="J366" t="str">
-        <v>2026-08-09T18:19:41.063Z</v>
+        <v>2026-08-09T18:23:03.368Z</v>
       </c>
     </row>
     <row r="367">
@@ -12240,7 +12240,7 @@
         <v/>
       </c>
       <c r="J367" t="str">
-        <v>2026-08-09T18:19:41.079Z</v>
+        <v>2026-08-09T18:23:03.384Z</v>
       </c>
     </row>
     <row r="368">
@@ -12272,7 +12272,7 @@
         <v/>
       </c>
       <c r="J368" t="str">
-        <v>2026-08-09T18:19:41.094Z</v>
+        <v>2026-08-09T18:23:03.399Z</v>
       </c>
     </row>
     <row r="369">
@@ -12298,13 +12298,13 @@
         <v>PASS</v>
       </c>
       <c r="H369">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I369" t="str">
         <v/>
       </c>
       <c r="J369" t="str">
-        <v>2026-08-09T18:19:41.110Z</v>
+        <v>2026-08-09T18:23:03.413Z</v>
       </c>
     </row>
     <row r="370">
@@ -12336,7 +12336,7 @@
         <v/>
       </c>
       <c r="J370" t="str">
-        <v>2026-08-09T18:19:41.125Z</v>
+        <v>2026-08-09T18:23:03.429Z</v>
       </c>
     </row>
     <row r="371">
@@ -12362,13 +12362,13 @@
         <v>PASS</v>
       </c>
       <c r="H371">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I371" t="str">
         <v/>
       </c>
       <c r="J371" t="str">
-        <v>2026-08-09T18:19:41.140Z</v>
+        <v>2026-08-09T18:23:03.445Z</v>
       </c>
     </row>
     <row r="372">
@@ -12394,13 +12394,13 @@
         <v>PASS</v>
       </c>
       <c r="H372">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I372" t="str">
         <v/>
       </c>
       <c r="J372" t="str">
-        <v>2026-08-09T18:19:41.156Z</v>
+        <v>2026-08-09T18:23:03.461Z</v>
       </c>
     </row>
     <row r="373">
@@ -12426,13 +12426,13 @@
         <v>PASS</v>
       </c>
       <c r="H373">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I373" t="str">
         <v/>
       </c>
       <c r="J373" t="str">
-        <v>2026-08-09T18:19:41.172Z</v>
+        <v>2026-08-09T18:23:03.476Z</v>
       </c>
     </row>
     <row r="374">
@@ -12464,7 +12464,7 @@
         <v/>
       </c>
       <c r="J374" t="str">
-        <v>2026-08-09T18:19:41.188Z</v>
+        <v>2026-08-09T18:23:03.492Z</v>
       </c>
     </row>
     <row r="375">
@@ -12496,7 +12496,7 @@
         <v/>
       </c>
       <c r="J375" t="str">
-        <v>2026-08-09T18:19:41.204Z</v>
+        <v>2026-08-09T18:23:03.508Z</v>
       </c>
     </row>
     <row r="376">
@@ -12528,7 +12528,7 @@
         <v/>
       </c>
       <c r="J376" t="str">
-        <v>2026-08-09T18:19:41.219Z</v>
+        <v>2026-08-09T18:23:03.524Z</v>
       </c>
     </row>
     <row r="377">
@@ -12560,7 +12560,7 @@
         <v/>
       </c>
       <c r="J377" t="str">
-        <v>2026-08-09T18:19:41.234Z</v>
+        <v>2026-08-09T18:23:03.539Z</v>
       </c>
     </row>
     <row r="378">
@@ -12592,7 +12592,7 @@
         <v/>
       </c>
       <c r="J378" t="str">
-        <v>2026-08-09T18:19:41.250Z</v>
+        <v>2026-08-09T18:23:03.555Z</v>
       </c>
     </row>
     <row r="379">
@@ -12618,13 +12618,13 @@
         <v>PASS</v>
       </c>
       <c r="H379">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I379" t="str">
         <v/>
       </c>
       <c r="J379" t="str">
-        <v>2026-08-09T18:19:41.266Z</v>
+        <v>2026-08-09T18:23:03.570Z</v>
       </c>
     </row>
     <row r="380">
@@ -12656,7 +12656,7 @@
         <v/>
       </c>
       <c r="J380" t="str">
-        <v>2026-08-09T18:19:41.282Z</v>
+        <v>2026-08-09T18:23:03.586Z</v>
       </c>
     </row>
     <row r="381">
@@ -12688,7 +12688,7 @@
         <v/>
       </c>
       <c r="J381" t="str">
-        <v>2026-08-09T18:19:41.298Z</v>
+        <v>2026-08-09T18:23:03.601Z</v>
       </c>
     </row>
     <row r="382">
@@ -12714,13 +12714,13 @@
         <v>PASS</v>
       </c>
       <c r="H382">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I382" t="str">
         <v/>
       </c>
       <c r="J382" t="str">
-        <v>2026-08-09T18:19:41.314Z</v>
+        <v>2026-08-09T18:23:03.617Z</v>
       </c>
     </row>
     <row r="383">
@@ -12752,7 +12752,7 @@
         <v/>
       </c>
       <c r="J383" t="str">
-        <v>2026-08-09T18:19:41.329Z</v>
+        <v>2026-08-09T18:23:03.633Z</v>
       </c>
     </row>
     <row r="384">
@@ -12784,7 +12784,7 @@
         <v/>
       </c>
       <c r="J384" t="str">
-        <v>2026-08-09T18:19:41.344Z</v>
+        <v>2026-08-09T18:23:03.648Z</v>
       </c>
     </row>
     <row r="385">
@@ -12810,13 +12810,13 @@
         <v>PASS</v>
       </c>
       <c r="H385">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I385" t="str">
         <v/>
       </c>
       <c r="J385" t="str">
-        <v>2026-08-09T18:19:41.359Z</v>
+        <v>2026-08-09T18:23:03.664Z</v>
       </c>
     </row>
     <row r="386">
@@ -12842,13 +12842,13 @@
         <v>PASS</v>
       </c>
       <c r="H386">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I386" t="str">
         <v/>
       </c>
       <c r="J386" t="str">
-        <v>2026-08-09T18:19:41.374Z</v>
+        <v>2026-08-09T18:23:03.678Z</v>
       </c>
     </row>
     <row r="387">
@@ -12880,7 +12880,7 @@
         <v/>
       </c>
       <c r="J387" t="str">
-        <v>2026-08-09T18:19:41.390Z</v>
+        <v>2026-08-09T18:23:03.694Z</v>
       </c>
     </row>
     <row r="388">
@@ -12906,13 +12906,13 @@
         <v>PASS</v>
       </c>
       <c r="H388">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I388" t="str">
         <v/>
       </c>
       <c r="J388" t="str">
-        <v>2026-08-09T18:19:41.406Z</v>
+        <v>2026-08-09T18:23:03.709Z</v>
       </c>
     </row>
     <row r="389">
@@ -12944,7 +12944,7 @@
         <v/>
       </c>
       <c r="J389" t="str">
-        <v>2026-08-09T18:19:41.421Z</v>
+        <v>2026-08-09T18:23:03.724Z</v>
       </c>
     </row>
     <row r="390">
@@ -12976,7 +12976,7 @@
         <v/>
       </c>
       <c r="J390" t="str">
-        <v>2026-08-09T18:19:41.437Z</v>
+        <v>2026-08-09T18:23:03.740Z</v>
       </c>
     </row>
     <row r="391">
@@ -13002,13 +13002,13 @@
         <v>PASS</v>
       </c>
       <c r="H391">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I391" t="str">
         <v/>
       </c>
       <c r="J391" t="str">
-        <v>2026-08-09T18:19:41.452Z</v>
+        <v>2026-08-09T18:23:03.756Z</v>
       </c>
     </row>
     <row r="392">
@@ -13034,13 +13034,13 @@
         <v>PASS</v>
       </c>
       <c r="H392">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I392" t="str">
         <v/>
       </c>
       <c r="J392" t="str">
-        <v>2026-08-09T18:19:41.467Z</v>
+        <v>2026-08-09T18:23:03.771Z</v>
       </c>
     </row>
     <row r="393">
@@ -13072,7 +13072,7 @@
         <v/>
       </c>
       <c r="J393" t="str">
-        <v>2026-08-09T18:19:41.483Z</v>
+        <v>2026-08-09T18:23:03.787Z</v>
       </c>
     </row>
     <row r="394">
@@ -13098,13 +13098,13 @@
         <v>PASS</v>
       </c>
       <c r="H394">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I394" t="str">
         <v/>
       </c>
       <c r="J394" t="str">
-        <v>2026-08-09T18:19:41.500Z</v>
+        <v>2026-08-09T18:23:03.803Z</v>
       </c>
     </row>
     <row r="395">
@@ -13130,13 +13130,13 @@
         <v>PASS</v>
       </c>
       <c r="H395">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I395" t="str">
         <v/>
       </c>
       <c r="J395" t="str">
-        <v>2026-08-09T18:19:41.515Z</v>
+        <v>2026-08-09T18:23:03.819Z</v>
       </c>
     </row>
     <row r="396">
@@ -13168,7 +13168,7 @@
         <v/>
       </c>
       <c r="J396" t="str">
-        <v>2026-08-09T18:19:41.531Z</v>
+        <v>2026-08-09T18:23:03.835Z</v>
       </c>
     </row>
     <row r="397">
@@ -13200,7 +13200,7 @@
         <v/>
       </c>
       <c r="J397" t="str">
-        <v>2026-08-09T18:19:41.546Z</v>
+        <v>2026-08-09T18:23:03.850Z</v>
       </c>
     </row>
     <row r="398">
@@ -13226,13 +13226,13 @@
         <v>PASS</v>
       </c>
       <c r="H398">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I398" t="str">
         <v/>
       </c>
       <c r="J398" t="str">
-        <v>2026-08-09T18:19:41.561Z</v>
+        <v>2026-08-09T18:23:03.864Z</v>
       </c>
     </row>
     <row r="399">
@@ -13264,7 +13264,7 @@
         <v/>
       </c>
       <c r="J399" t="str">
-        <v>2026-08-09T18:19:41.577Z</v>
+        <v>2026-08-09T18:23:03.880Z</v>
       </c>
     </row>
     <row r="400">
@@ -13296,7 +13296,7 @@
         <v/>
       </c>
       <c r="J400" t="str">
-        <v>2026-08-09T18:19:41.593Z</v>
+        <v>2026-08-09T18:23:03.896Z</v>
       </c>
     </row>
     <row r="401">
@@ -13322,13 +13322,13 @@
         <v>PASS</v>
       </c>
       <c r="H401">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I401" t="str">
         <v/>
       </c>
       <c r="J401" t="str">
-        <v>2026-08-09T18:19:41.608Z</v>
+        <v>2026-08-09T18:23:03.912Z</v>
       </c>
     </row>
   </sheetData>
